--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -459,7 +459,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -752,7 +752,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -806,7 +806,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -839,7 +839,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="F5" s="45" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf</t>
+          <t>https://t.me/photolab_vf/55</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="F6" s="45" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf</t>
+          <t>https://t.me/photolab_vf/60</t>
         </is>
       </c>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Dashboard" sheetId="1" r:id="R835eaa4126f843b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Master_Facts" sheetId="2" r:id="R3483dfbfc8414c63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Branches" sheetId="3" r:id="Rfb29fd8fd9b94a10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Lessons_Map" sheetId="4" r:id="Rdf953e7d2e094497"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Sources" sheetId="5" r:id="Rb175d41dea6c4dee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Lists" sheetId="6" r:id="R69ff9f62362a4fe5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="7" r:id="R289b632f91844611"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Dashboard" sheetId="1" r:id="R89bc147ec81d4166"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Master_Facts" sheetId="2" r:id="Rcae5aa9a01104fb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Branches" sheetId="3" r:id="Rfb28ea5c5c7246e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Lessons_Map" sheetId="4" r:id="R41a94ce12af846ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Sources" sheetId="5" r:id="R17f69793fedb41b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Lists" sheetId="6" r:id="R8f7418347b3b429e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="7" r:id="R6823f14f8b7e4aa2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4250,7 +4250,7 @@
     <x:xf numFmtId="9" fontId="1" fillId="0" borderId="1"/>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4355,6 +4355,16 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="7">
@@ -4850,7 +4860,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R69693deb70094111"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9bcb1fa2f44e4f69"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5063,7 +5073,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="29" t="str">
-        <x:v>PHOTO LAB — Master Timeline v0.6</x:v>
+        <x:v>PHOTO LAB — Master Timeline v0.7</x:v>
       </x:c>
       <x:c r="B1" s="28"/>
       <x:c r="C1" s="28"/>
@@ -5090,7 +5100,7 @@
       </x:c>
       <x:c r="B3" s="33" t="n">
         <x:f>COUNTA('01_Master_Facts'!$A$2:$A$500)</x:f>
-        <x:v>88</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C3" s="32" t="s">
         <x:v>4</x:v>
@@ -5104,7 +5114,7 @@
       </x:c>
       <x:c r="B4" s="33" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$N$2:$N$500,5)</x:f>
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C4" s="32" t="s">
         <x:v>6</x:v>
@@ -5114,11 +5124,11 @@
     </x:row>
     <x:row r="5" ht="15.75" customHeight="1">
       <x:c r="A5" s="32" t="str">
-        <x:v>Узлов для PL-001–PL-009</x:v>
+        <x:v>Узлов для PL-001–PL-010</x:v>
       </x:c>
       <x:c r="B5" s="33" t="n">
-        <x:f>SUM(COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-001"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-002"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-003"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-004"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-005"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-006"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-007"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-008"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-009"))</x:f>
-        <x:v>77</x:v>
+        <x:f>SUM(COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-001"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-002"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-003"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-004"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-005"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-006"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-007"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-008"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-009"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-010"))</x:f>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C5" s="32" t="str">
         <x:v>Без будущих PL и межурочных узлов</x:v>
@@ -5132,7 +5142,7 @@
       </x:c>
       <x:c r="B6" s="33" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$W$2:$W$500,"&lt;&gt;")</x:f>
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="32" t="s">
         <x:v>8</x:v>
@@ -5192,7 +5202,7 @@
       </x:c>
       <x:c r="B11" s="34" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A11)</x:f>
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="28"/>
       <x:c r="D11" s="34" t="s">
@@ -5277,7 +5287,7 @@
       </x:c>
       <x:c r="B16" s="34" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A16)</x:f>
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C16" s="28"/>
       <x:c r="D16" s="34" t="s">
@@ -5332,11 +5342,11 @@
       </x:c>
       <x:c r="C19" s="28"/>
       <x:c r="D19" s="28" t="str">
-        <x:v>будущие PL</x:v>
+        <x:v>PL-010</x:v>
       </x:c>
       <x:c r="E19" s="28" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D19)</x:f>
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15.75" customHeight="1">
@@ -5349,11 +5359,11 @@
       </x:c>
       <x:c r="C20" s="28"/>
       <x:c r="D20" s="28" t="str">
-        <x:v>межурочный узел</x:v>
+        <x:v>будущие PL</x:v>
       </x:c>
       <x:c r="E20" s="28" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D20)</x:f>
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1">
@@ -5366,11 +5376,11 @@
       </x:c>
       <x:c r="C21" s="28"/>
       <x:c r="D21" s="28" t="str">
-        <x:v>проверить</x:v>
+        <x:v>межурочный узел</x:v>
       </x:c>
       <x:c r="E21" s="28" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D21)</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15.75" customHeight="1">
@@ -5382,8 +5392,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C22" s="28"/>
-      <x:c r="D22" s="28"/>
-      <x:c r="E22" s="28"/>
+      <x:c r="D22" s="28" t="str">
+        <x:v>проверить</x:v>
+      </x:c>
+      <x:c r="E22" s="28" t="n">
+        <x:f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D22)</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="15" customHeight="1">
       <x:c r="A23" s="34"/>
@@ -5428,7 +5443,7 @@
       </x:c>
       <x:c r="B27" s="34" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A27)</x:f>
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C27" s="28"/>
       <x:c r="D27" s="28"/>
@@ -5440,7 +5455,7 @@
       </x:c>
       <x:c r="B28" s="34" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A28)</x:f>
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="28"/>
       <x:c r="D28" s="28"/>
@@ -5476,7 +5491,7 @@
       </x:c>
       <x:c r="B31" s="34" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A31)</x:f>
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C31" s="28"/>
       <x:c r="D31" s="28"/>
@@ -5500,7 +5515,7 @@
       </x:c>
       <x:c r="B33" s="34" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A33)</x:f>
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C33" s="28"/>
       <x:c r="D33" s="28"/>
@@ -5524,7 +5539,7 @@
       </x:c>
       <x:c r="B35" s="34" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A35)</x:f>
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C35" s="28"/>
       <x:c r="D35" s="28"/>
@@ -5536,7 +5551,7 @@
       </x:c>
       <x:c r="B36" s="34" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A36)</x:f>
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="28"/>
       <x:c r="D36" s="28"/>
@@ -5599,7 +5614,7 @@
     <x:mergeCell ref="A1:F1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ef0fb7dbbdf46ec"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6d48fd5b5524888"/>
 </x:worksheet>
 </file>
 
@@ -12604,16 +12619,802 @@
       </x:c>
       <x:c r="AA89" s="28"/>
     </x:row>
-    <x:row r="90" ht="12.75" customHeight="1"/>
-    <x:row r="91" ht="12.75" customHeight="1"/>
-    <x:row r="92" ht="12.75" customHeight="1"/>
-    <x:row r="93" ht="12.75" customHeight="1"/>
-    <x:row r="94" ht="12.75" customHeight="1"/>
-    <x:row r="95" ht="12.75" customHeight="1"/>
-    <x:row r="96" ht="12.75" customHeight="1"/>
-    <x:row r="97" ht="12.75" customHeight="1"/>
-    <x:row r="98" ht="12.75" customHeight="1"/>
-    <x:row r="99" ht="12.75" customHeight="1"/>
+    <x:row r="90" ht="12.75" customHeight="1">
+      <x:c r="A90" s="28" t="str">
+        <x:v>PL-HIST-0089</x:v>
+      </x:c>
+      <x:c r="B90" s="28" t="str">
+        <x:v>1913–1914</x:v>
+      </x:c>
+      <x:c r="C90" s="28" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D90" s="28" t="str">
+        <x:v>Германия</x:v>
+      </x:c>
+      <x:c r="E90" s="28" t="str">
+        <x:v>Вецлар</x:v>
+      </x:c>
+      <x:c r="F90" s="28" t="str">
+        <x:v>Оскар Барнак / Ernst Leitz</x:v>
+      </x:c>
+      <x:c r="G90" s="28" t="str">
+        <x:v>Оскар Барнак создаёт прототип Ur-Leica: компактную камеру под 35-мм киноплёнку, которая станет основой будущей Leica I.</x:v>
+      </x:c>
+      <x:c r="H90" s="28" t="str">
+        <x:v>Оптические инструменты</x:v>
+      </x:c>
+      <x:c r="I90" s="28" t="str">
+        <x:v>Ur-Leica prototype</x:v>
+      </x:c>
+      <x:c r="J90" s="28" t="str">
+        <x:v>Идея 35 мм перестаёт быть только кинематографической: появляется замысел маленькой фотокамеры для серьёзной съёмки.</x:v>
+      </x:c>
+      <x:c r="K90" s="28" t="str">
+        <x:v>35-мм киноплёнка и кадр 24×36</x:v>
+      </x:c>
+      <x:c r="L90" s="28" t="str">
+        <x:v>Leica 0-Series and Leica I</x:v>
+      </x:c>
+      <x:c r="M90" s="28" t="str">
+        <x:v>Переходная технология</x:v>
+      </x:c>
+      <x:c r="N90" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O90" s="28" t="str">
+        <x:v>PL-010</x:v>
+      </x:c>
+      <x:c r="P90" s="28" t="str">
+        <x:v>SRC-062</x:v>
+      </x:c>
+      <x:c r="Q90" s="28" t="str">
+        <x:v>Leica Camera — The History of the Leica I</x:v>
+      </x:c>
+      <x:c r="R90" s="28" t="str">
+        <x:v>https://leica-camera.com/en-int/photography/100-years/the-history-of-the-leica-I</x:v>
+      </x:c>
+      <x:c r="S90" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T90" s="28" t="str">
+        <x:v>Для урока важно показать: Leica I родилась не из желания сделать игрушку, а из идеи мобильной серьёзной камеры.</x:v>
+      </x:c>
+      <x:c r="U90" s="28" t="str">
+        <x:v>Маленький прототип на рабочем столе Барнака рядом с полоской 35-мм киноплёнки.</x:v>
+      </x:c>
+      <x:c r="V90" s="28" t="str">
+        <x:v>#PL010 #Ur-Leica #Barnack #Wetzlar #35mm</x:v>
+      </x:c>
+      <x:c r="W90" s="28"/>
+      <x:c r="X90" s="28" t="str">
+        <x:v>50.5619, 8.5044</x:v>
+      </x:c>
+      <x:c r="Y90" s="28" t="str">
+        <x:v>Leica I / прототип</x:v>
+      </x:c>
+      <x:c r="Z90" s="28" t="str">
+        <x:v>Инструмент / устройство</x:v>
+      </x:c>
+      <x:c r="AA90" s="28"/>
+    </x:row>
+    <x:row r="91" ht="12.75" customHeight="1">
+      <x:c r="A91" s="28" t="str">
+        <x:v>PL-HIST-0090</x:v>
+      </x:c>
+      <x:c r="B91" s="28" t="str">
+        <x:v>1923</x:v>
+      </x:c>
+      <x:c r="C91" s="28" t="str">
+        <x:v>год</x:v>
+      </x:c>
+      <x:c r="D91" s="28" t="str">
+        <x:v>Германия</x:v>
+      </x:c>
+      <x:c r="E91" s="28" t="str">
+        <x:v>Вецлар</x:v>
+      </x:c>
+      <x:c r="F91" s="28" t="str">
+        <x:v>Оскар Барнак / Ernst Leitz</x:v>
+      </x:c>
+      <x:c r="G91" s="28" t="str">
+        <x:v>После прототипов появляется проверочная серия Leica 0-Series: небольшая партия камер для испытаний перед коммерческим запуском.</x:v>
+      </x:c>
+      <x:c r="H91" s="28" t="str">
+        <x:v>Оптические инструменты</x:v>
+      </x:c>
+      <x:c r="I91" s="28" t="str">
+        <x:v>Leica 0-Series</x:v>
+      </x:c>
+      <x:c r="J91" s="28" t="str">
+        <x:v>Идея маленькой 35-мм камеры проходит практическую проверку: её нужно не просто изобрести, а сделать пригодной для реальных фотографов.</x:v>
+      </x:c>
+      <x:c r="K91" s="28" t="str">
+        <x:v>Ur-Leica prototype</x:v>
+      </x:c>
+      <x:c r="L91" s="28" t="str">
+        <x:v>Decision to enter serial production</x:v>
+      </x:c>
+      <x:c r="M91" s="28" t="str">
+        <x:v>Переходная технология</x:v>
+      </x:c>
+      <x:c r="N91" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O91" s="28" t="str">
+        <x:v>PL-010</x:v>
+      </x:c>
+      <x:c r="P91" s="28" t="str">
+        <x:v>SRC-062</x:v>
+      </x:c>
+      <x:c r="Q91" s="28" t="str">
+        <x:v>Leica Camera — The History of the Leica I</x:v>
+      </x:c>
+      <x:c r="R91" s="28" t="str">
+        <x:v>https://leica-camera.com/en-int/photography/100-years/the-history-of-the-leica-I</x:v>
+      </x:c>
+      <x:c r="S91" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T91" s="28" t="str">
+        <x:v>Хороший storytelling-узел: между прототипом и рынком всегда есть испытание, сомнение и проверка.</x:v>
+      </x:c>
+      <x:c r="U91" s="28" t="str">
+        <x:v>Небольшая партия камер Leica 0-Series на столе в мастерской Leitz.</x:v>
+      </x:c>
+      <x:c r="V91" s="28" t="str">
+        <x:v>#PL010 #Leica0 #preproduction #Leitz #Barnack</x:v>
+      </x:c>
+      <x:c r="W91" s="28" t="str">
+        <x:v>Проверить точное количество камер 0-Series в финальной лекции: источники обычно указывают малую проверочную серию, но формулировки различаются.</x:v>
+      </x:c>
+      <x:c r="X91" s="28" t="str">
+        <x:v>50.5619, 8.5044</x:v>
+      </x:c>
+      <x:c r="Y91" s="28" t="str">
+        <x:v>Leica I / проверочная серия</x:v>
+      </x:c>
+      <x:c r="Z91" s="28" t="str">
+        <x:v>Связь / переход</x:v>
+      </x:c>
+      <x:c r="AA91" s="28"/>
+    </x:row>
+    <x:row r="92" ht="12.75" customHeight="1">
+      <x:c r="A92" s="28" t="str">
+        <x:v>PL-HIST-0091</x:v>
+      </x:c>
+      <x:c r="B92" s="28" t="str">
+        <x:v>конец 1924</x:v>
+      </x:c>
+      <x:c r="C92" s="28" t="str">
+        <x:v>точная дата</x:v>
+      </x:c>
+      <x:c r="D92" s="28" t="str">
+        <x:v>Германия</x:v>
+      </x:c>
+      <x:c r="E92" s="28" t="str">
+        <x:v>Вецлар</x:v>
+      </x:c>
+      <x:c r="F92" s="28" t="str">
+        <x:v>Ernst Leitz II / Ernst Leitz Werke</x:v>
+      </x:c>
+      <x:c r="G92" s="28" t="str">
+        <x:v>Первая серийная версия Leica I официально входит в производство в конце 1924 года, опираясь на опыт Leica 0-Series.</x:v>
+      </x:c>
+      <x:c r="H92" s="28" t="str">
+        <x:v>Оптические инструменты</x:v>
+      </x:c>
+      <x:c r="I92" s="28" t="str">
+        <x:v>Leica I serial production begins</x:v>
+      </x:c>
+      <x:c r="J92" s="28" t="str">
+        <x:v>Leica перестаёт быть лабораторным экспериментом и становится промышленным изделием.</x:v>
+      </x:c>
+      <x:c r="K92" s="28" t="str">
+        <x:v>Leica 0-Series tests</x:v>
+      </x:c>
+      <x:c r="L92" s="28" t="str">
+        <x:v>Public presentation at Leipzig Spring Fair 1925</x:v>
+      </x:c>
+      <x:c r="M92" s="28" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N92" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O92" s="28" t="str">
+        <x:v>PL-010</x:v>
+      </x:c>
+      <x:c r="P92" s="28" t="str">
+        <x:v>SRC-062</x:v>
+      </x:c>
+      <x:c r="Q92" s="28" t="str">
+        <x:v>Leica Camera — The History of the Leica I</x:v>
+      </x:c>
+      <x:c r="R92" s="28" t="str">
+        <x:v>https://leica-camera.com/en-int/photography/100-years/the-history-of-the-leica-I</x:v>
+      </x:c>
+      <x:c r="S92" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T92" s="28" t="str">
+        <x:v>Объяснить просто: революция начинается не в момент идеи, а когда идею удалось произвести серийно.</x:v>
+      </x:c>
+      <x:c r="U92" s="28" t="str">
+        <x:v>Фабричная сборка маленьких Leica I в Вецларе, рядом детали корпуса и объектив.</x:v>
+      </x:c>
+      <x:c r="V92" s="28" t="str">
+        <x:v>#PL010 #LeicaI #serial-production #Leitz</x:v>
+      </x:c>
+      <x:c r="W92" s="28"/>
+      <x:c r="X92" s="28" t="str">
+        <x:v>50.5619, 8.5044</x:v>
+      </x:c>
+      <x:c r="Y92" s="28" t="str">
+        <x:v>Leica I / начало производства</x:v>
+      </x:c>
+      <x:c r="Z92" s="28" t="str">
+        <x:v>Распространение / коммерциализация</x:v>
+      </x:c>
+      <x:c r="AA92" s="28"/>
+    </x:row>
+    <x:row r="93" ht="12.75" customHeight="1">
+      <x:c r="A93" s="28" t="str">
+        <x:v>PL-HIST-0092</x:v>
+      </x:c>
+      <x:c r="B93" s="28" t="str">
+        <x:v>1925</x:v>
+      </x:c>
+      <x:c r="C93" s="28" t="str">
+        <x:v>год</x:v>
+      </x:c>
+      <x:c r="D93" s="28" t="str">
+        <x:v>Германия</x:v>
+      </x:c>
+      <x:c r="E93" s="28" t="str">
+        <x:v>Лейпциг</x:v>
+      </x:c>
+      <x:c r="F93" s="28" t="str">
+        <x:v>Ernst Leitz / Leica</x:v>
+      </x:c>
+      <x:c r="G93" s="28" t="str">
+        <x:v>Leica I представлена публике на Лейпцигской весенней ярмарке как первая серийная 35-мм камера Leitz.</x:v>
+      </x:c>
+      <x:c r="H93" s="28" t="str">
+        <x:v>Оптические инструменты</x:v>
+      </x:c>
+      <x:c r="I93" s="28" t="str">
+        <x:v>Leica I at Leipzig Spring Fair</x:v>
+      </x:c>
+      <x:c r="J93" s="28" t="str">
+        <x:v>35 мм получает публичный коммерческий вход в фотографию: маленькая камера становится реальным продуктом.</x:v>
+      </x:c>
+      <x:c r="K93" s="28" t="str">
+        <x:v>Serial production begins at Leitz</x:v>
+      </x:c>
+      <x:c r="L93" s="28" t="str">
+        <x:v>Compact 35 mm photography spreads</x:v>
+      </x:c>
+      <x:c r="M93" s="28" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N93" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O93" s="28" t="str">
+        <x:v>PL-010</x:v>
+      </x:c>
+      <x:c r="P93" s="28" t="str">
+        <x:v>SRC-063</x:v>
+      </x:c>
+      <x:c r="Q93" s="28" t="str">
+        <x:v>Leica Camera — 100 Years of Leica: Witness to a Century</x:v>
+      </x:c>
+      <x:c r="R93" s="28" t="str">
+        <x:v>https://leica-camera.com/en-GB/press/100-years-leica-witness-century-1925-2025-1</x:v>
+      </x:c>
+      <x:c r="S93" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T93" s="28" t="str">
+        <x:v>Это главный исторический момент урока: Leica I выходит к публике и меняет представление о серьёзной камере.</x:v>
+      </x:c>
+      <x:c r="U93" s="28" t="str">
+        <x:v>Витрина Leica I на ярмарке в Лейпциге; маленькая камера среди больших фотоаппаратов эпохи.</x:v>
+      </x:c>
+      <x:c r="V93" s="28" t="str">
+        <x:v>#PL010 #LeicaI #Leipzig #1925 #35mm-camera</x:v>
+      </x:c>
+      <x:c r="W93" s="28"/>
+      <x:c r="X93" s="28" t="str">
+        <x:v>51.3397, 12.3731</x:v>
+      </x:c>
+      <x:c r="Y93" s="28" t="str">
+        <x:v>Leica I / публичный дебют</x:v>
+      </x:c>
+      <x:c r="Z93" s="28" t="str">
+        <x:v>Ключевой исторический узел</x:v>
+      </x:c>
+      <x:c r="AA93" s="28" t="str">
+        <x:v>да</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="12.75" customHeight="1">
+      <x:c r="A94" s="28" t="str">
+        <x:v>PL-HIST-0093</x:v>
+      </x:c>
+      <x:c r="B94" s="28" t="str">
+        <x:v>1925</x:v>
+      </x:c>
+      <x:c r="C94" s="28" t="str">
+        <x:v>год</x:v>
+      </x:c>
+      <x:c r="D94" s="28" t="str">
+        <x:v>Германия</x:v>
+      </x:c>
+      <x:c r="E94" s="28" t="str">
+        <x:v>Вецлар</x:v>
+      </x:c>
+      <x:c r="F94" s="28" t="str">
+        <x:v>Oskar Barnack / Ernst Leitz</x:v>
+      </x:c>
+      <x:c r="G94" s="28" t="str">
+        <x:v>Leica 1(A), разработанная Барнаком, становится первой коммерчески доступной Leica 35-мм камерой и быстро популяризирует 35-мм фотографию.</x:v>
+      </x:c>
+      <x:c r="H94" s="28" t="str">
+        <x:v>Оптические инструменты</x:v>
+      </x:c>
+      <x:c r="I94" s="28" t="str">
+        <x:v>Leica 1(A) 35 mm camera</x:v>
+      </x:c>
+      <x:c r="J94" s="28" t="str">
+        <x:v>Компактность становится серьёзным фотографическим преимуществом: камера теперь может быть постоянно с фотографом.</x:v>
+      </x:c>
+      <x:c r="K94" s="28" t="str">
+        <x:v>Leica I public launch</x:v>
+      </x:c>
+      <x:c r="L94" s="28" t="str">
+        <x:v>New mobile visual practice</x:v>
+      </x:c>
+      <x:c r="M94" s="28" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N94" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O94" s="28" t="str">
+        <x:v>PL-010</x:v>
+      </x:c>
+      <x:c r="P94" s="28" t="str">
+        <x:v>SRC-064</x:v>
+      </x:c>
+      <x:c r="Q94" s="28" t="str">
+        <x:v>Smithsonian NMAH — Leica 35 mm 1(A) Camera</x:v>
+      </x:c>
+      <x:c r="R94" s="28" t="str">
+        <x:v>https://americanhistory.si.edu/collections/object/nmah_834692</x:v>
+      </x:c>
+      <x:c r="S94" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T94" s="28" t="str">
+        <x:v>Новичку важно понять: Leica I — это не просто новая модель, а изменение поведения фотографа.</x:v>
+      </x:c>
+      <x:c r="U94" s="28" t="str">
+        <x:v>Маленькая Leica I в руке фотографа рядом с большой складной камерой как контраст старого и нового.</x:v>
+      </x:c>
+      <x:c r="V94" s="28" t="str">
+        <x:v>#PL010 #Leica1A #compact-camera #35mm #Barnack</x:v>
+      </x:c>
+      <x:c r="W94" s="28"/>
+      <x:c r="X94" s="28" t="str">
+        <x:v>50.5619, 8.5044</x:v>
+      </x:c>
+      <x:c r="Y94" s="28" t="str">
+        <x:v>Leica I / компактная камера</x:v>
+      </x:c>
+      <x:c r="Z94" s="28" t="str">
+        <x:v>Инструмент / устройство</x:v>
+      </x:c>
+      <x:c r="AA94" s="28"/>
+    </x:row>
+    <x:row r="95" ht="12.75" customHeight="1">
+      <x:c r="A95" s="28" t="str">
+        <x:v>PL-HIST-0094</x:v>
+      </x:c>
+      <x:c r="B95" s="28" t="str">
+        <x:v>1925</x:v>
+      </x:c>
+      <x:c r="C95" s="28" t="str">
+        <x:v>год</x:v>
+      </x:c>
+      <x:c r="D95" s="28" t="str">
+        <x:v>Германия</x:v>
+      </x:c>
+      <x:c r="E95" s="28" t="str">
+        <x:v>Вецлар</x:v>
+      </x:c>
+      <x:c r="F95" s="28" t="str">
+        <x:v>Макс Берек / Leitz</x:v>
+      </x:c>
+      <x:c r="G95" s="28" t="str">
+        <x:v>Первые объективы Leica разрабатывает Макс Берек: 50 мм f/3.5 Anastigmat / Elmax, затем Elmar, чтобы маленький негатив можно было качественно увеличивать.</x:v>
+      </x:c>
+      <x:c r="H95" s="28" t="str">
+        <x:v>Оптические инструменты</x:v>
+      </x:c>
+      <x:c r="I95" s="28" t="str">
+        <x:v>Leica Anastigmat / Elmax / Elmar 50 mm f/3.5</x:v>
+      </x:c>
+      <x:c r="J95" s="28" t="str">
+        <x:v>Малый формат требует сильной оптики: качество объектива становится условием идеи «маленький негатив — большой отпечаток».</x:v>
+      </x:c>
+      <x:c r="K95" s="28" t="str">
+        <x:v>24×36 mm small negative</x:v>
+      </x:c>
+      <x:c r="L95" s="28" t="str">
+        <x:v>Leica becomes practical system for enlargement and printing</x:v>
+      </x:c>
+      <x:c r="M95" s="28" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N95" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O95" s="28" t="str">
+        <x:v>PL-010</x:v>
+      </x:c>
+      <x:c r="P95" s="28" t="str">
+        <x:v>SRC-065</x:v>
+      </x:c>
+      <x:c r="Q95" s="28" t="str">
+        <x:v>Leica Camera — Understanding Leica Lenses</x:v>
+      </x:c>
+      <x:c r="R95" s="28" t="str">
+        <x:v>https://leica-camera.com/en-int/photography/understanding-leica-lenses</x:v>
+      </x:c>
+      <x:c r="S95" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T95" s="28" t="str">
+        <x:v>Это мост к будущим урокам про объективы: формат победил не один, ему понадобилась точная оптика.</x:v>
+      </x:c>
+      <x:c r="U95" s="28" t="str">
+        <x:v>Схема: маленький негатив 24×36 → объектив Elmar → увеличенный отпечаток.</x:v>
+      </x:c>
+      <x:c r="V95" s="28" t="str">
+        <x:v>#PL010 #MaxBerek #Elmar #Leica-lens #small-negative</x:v>
+      </x:c>
+      <x:c r="W95" s="28" t="str">
+        <x:v>Уточнить в финальном тексте различие Anastigmat / Elmax / Elmar, чтобы не смешать ранние версии объектива.</x:v>
+      </x:c>
+      <x:c r="X95" s="28" t="str">
+        <x:v>50.5619, 8.5044</x:v>
+      </x:c>
+      <x:c r="Y95" s="28" t="str">
+        <x:v>Leica I / оптика и Elmar</x:v>
+      </x:c>
+      <x:c r="Z95" s="28" t="str">
+        <x:v>Технология / процесс</x:v>
+      </x:c>
+      <x:c r="AA95" s="28"/>
+    </x:row>
+    <x:row r="96" ht="12.75" customHeight="1">
+      <x:c r="A96" s="28" t="str">
+        <x:v>PL-HIST-0095</x:v>
+      </x:c>
+      <x:c r="B96" s="28" t="str">
+        <x:v>1925–1930</x:v>
+      </x:c>
+      <x:c r="C96" s="28" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D96" s="28" t="str">
+        <x:v>Германия</x:v>
+      </x:c>
+      <x:c r="E96" s="28" t="str">
+        <x:v>Вецлар</x:v>
+      </x:c>
+      <x:c r="F96" s="28" t="str">
+        <x:v>Ernst Leitz Werke / пользователи Leica</x:v>
+      </x:c>
+      <x:c r="G96" s="28" t="str">
+        <x:v>За 1925–1930 годы Leica I выпускается десятками тысяч экземпляров в разных вариантах и закрепляет 35-мм компактную камеру как рабочий фотографический инструмент.</x:v>
+      </x:c>
+      <x:c r="H96" s="28" t="str">
+        <x:v>Негатив-позитив</x:v>
+      </x:c>
+      <x:c r="I96" s="28" t="str">
+        <x:v>Leica I mass adoption</x:v>
+      </x:c>
+      <x:c r="J96" s="28" t="str">
+        <x:v>35 мм перестаёт быть нишевым экспериментом и становится устойчивой практикой съёмки.</x:v>
+      </x:c>
+      <x:c r="K96" s="28" t="str">
+        <x:v>Leica I launch</x:v>
+      </x:c>
+      <x:c r="L96" s="28" t="str">
+        <x:v>Global 35 mm compact camera standard</x:v>
+      </x:c>
+      <x:c r="M96" s="28" t="str">
+        <x:v>Распространение / коммерциализация</x:v>
+      </x:c>
+      <x:c r="N96" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O96" s="28" t="str">
+        <x:v>PL-010</x:v>
+      </x:c>
+      <x:c r="P96" s="28" t="str">
+        <x:v>SRC-062</x:v>
+      </x:c>
+      <x:c r="Q96" s="28" t="str">
+        <x:v>Leica Camera — The History of the Leica I</x:v>
+      </x:c>
+      <x:c r="R96" s="28" t="str">
+        <x:v>https://leica-camera.com/en-int/photography/100-years/the-history-of-the-leica-I</x:v>
+      </x:c>
+      <x:c r="S96" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T96" s="28" t="str">
+        <x:v>Не перегружать цифрами, но показать масштаб: камера стала не редкостью, а узнаваемым инструментом.</x:v>
+      </x:c>
+      <x:c r="U96" s="28" t="str">
+        <x:v>Ряд Leica I на производственной полке, рядом отметка 1925–1930.</x:v>
+      </x:c>
+      <x:c r="V96" s="28" t="str">
+        <x:v>#PL010 #LeicaI #mass-production #35mm-standard</x:v>
+      </x:c>
+      <x:c r="W96" s="28"/>
+      <x:c r="X96" s="28" t="str">
+        <x:v>50.5619, 8.5044</x:v>
+      </x:c>
+      <x:c r="Y96" s="28" t="str">
+        <x:v>Leica I / массовое принятие</x:v>
+      </x:c>
+      <x:c r="Z96" s="28" t="str">
+        <x:v>Распространение / коммерциализация</x:v>
+      </x:c>
+      <x:c r="AA96" s="28"/>
+    </x:row>
+    <x:row r="97" ht="12.75" customHeight="1">
+      <x:c r="A97" s="28" t="str">
+        <x:v>PL-HIST-0096</x:v>
+      </x:c>
+      <x:c r="B97" s="28" t="str">
+        <x:v>1920-е–1930-е</x:v>
+      </x:c>
+      <x:c r="C97" s="28" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D97" s="28" t="str">
+        <x:v>Европа / США</x:v>
+      </x:c>
+      <x:c r="E97" s="28" t="str">
+        <x:v>распределённый процесс</x:v>
+      </x:c>
+      <x:c r="F97" s="28" t="str">
+        <x:v>Фотографы нового поколения</x:v>
+      </x:c>
+      <x:c r="G97" s="28" t="str">
+        <x:v>Компактная, быстрая и мобильная Leica I помогает сформировать более интимный, спонтанный визуальный язык — основу репортажа и уличной фотографии.</x:v>
+      </x:c>
+      <x:c r="H97" s="28" t="str">
+        <x:v>Оптические инструменты</x:v>
+      </x:c>
+      <x:c r="I97" s="28" t="str">
+        <x:v>Mobile 35 mm visual language</x:v>
+      </x:c>
+      <x:c r="J97" s="28" t="str">
+        <x:v>Фотограф становится менее заметным и быстрее реагирует на жизнь: камера начинает следовать за событием, а не заставлять событие приходить в студию.</x:v>
+      </x:c>
+      <x:c r="K97" s="28" t="str">
+        <x:v>Leica I mass adoption</x:v>
+      </x:c>
+      <x:c r="L97" s="28" t="str">
+        <x:v>Rangefinder and reportage traditions</x:v>
+      </x:c>
+      <x:c r="M97" s="28" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N97" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O97" s="28" t="str">
+        <x:v>PL-010</x:v>
+      </x:c>
+      <x:c r="P97" s="28" t="str">
+        <x:v>SRC-062</x:v>
+      </x:c>
+      <x:c r="Q97" s="28" t="str">
+        <x:v>Leica Camera — The History of the Leica I</x:v>
+      </x:c>
+      <x:c r="R97" s="28" t="str">
+        <x:v>https://leica-camera.com/en-int/photography/100-years/the-history-of-the-leica-I</x:v>
+      </x:c>
+      <x:c r="S97" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T97" s="28" t="str">
+        <x:v>Смысл PL-010: Leica изменила не только размер камеры, но и способ видеть — ближе, быстрее, тише.</x:v>
+      </x:c>
+      <x:c r="U97" s="28" t="str">
+        <x:v>Фотограф с маленькой камерой среди городской жизни; люди не позируют, момент происходит сам.</x:v>
+      </x:c>
+      <x:c r="V97" s="28" t="str">
+        <x:v>#PL010 #reportage #street-photography #mobile-camera #visual-language</x:v>
+      </x:c>
+      <x:c r="W97" s="28"/>
+      <x:c r="X97" s="28"/>
+      <x:c r="Y97" s="28" t="str">
+        <x:v>Leica I / новая визуальная практика</x:v>
+      </x:c>
+      <x:c r="Z97" s="28" t="str">
+        <x:v>Применение / жанр</x:v>
+      </x:c>
+      <x:c r="AA97" s="28"/>
+    </x:row>
+    <x:row r="98" ht="12.75" customHeight="1">
+      <x:c r="A98" s="28" t="str">
+        <x:v>PL-HIST-0097</x:v>
+      </x:c>
+      <x:c r="B98" s="28" t="str">
+        <x:v>1930</x:v>
+      </x:c>
+      <x:c r="C98" s="28" t="str">
+        <x:v>год</x:v>
+      </x:c>
+      <x:c r="D98" s="28" t="str">
+        <x:v>Германия</x:v>
+      </x:c>
+      <x:c r="E98" s="28" t="str">
+        <x:v>Вецлар</x:v>
+      </x:c>
+      <x:c r="F98" s="28" t="str">
+        <x:v>Ernst Leitz Werke</x:v>
+      </x:c>
+      <x:c r="G98" s="28" t="str">
+        <x:v>Leica I(C) вводит сменные объективы; к концу 1930 года появляется стандартизированный крепёж, позволяющий использовать объективы с разными камерами Leica 1(C).</x:v>
+      </x:c>
+      <x:c r="H98" s="28" t="str">
+        <x:v>Оптические инструменты</x:v>
+      </x:c>
+      <x:c r="I98" s="28" t="str">
+        <x:v>Leica I(C) interchangeable lenses</x:v>
+      </x:c>
+      <x:c r="J98" s="28" t="str">
+        <x:v>Leica превращается из отдельной камеры в систему: корпус, объективы и аксессуары начинают развиваться вместе.</x:v>
+      </x:c>
+      <x:c r="K98" s="28" t="str">
+        <x:v>Leica I fixed-lens camera</x:v>
+      </x:c>
+      <x:c r="L98" s="28" t="str">
+        <x:v>Leica system and rangefinder cameras</x:v>
+      </x:c>
+      <x:c r="M98" s="28" t="str">
+        <x:v>Связь / переход</x:v>
+      </x:c>
+      <x:c r="N98" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O98" s="28" t="str">
+        <x:v>PL-010</x:v>
+      </x:c>
+      <x:c r="P98" s="28" t="str">
+        <x:v>SRC-067</x:v>
+      </x:c>
+      <x:c r="Q98" s="28" t="str">
+        <x:v>Smithsonian NMAH — Leica 1(C)</x:v>
+      </x:c>
+      <x:c r="R98" s="28" t="str">
+        <x:v>https://americanhistory.si.edu/collections/object/nmah_1145349</x:v>
+      </x:c>
+      <x:c r="S98" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T98" s="28" t="str">
+        <x:v>Это не центральный узел PL-010, а мост: после Leica I важной становится идея системы.</x:v>
+      </x:c>
+      <x:c r="U98" s="28" t="str">
+        <x:v>Корпус Leica I(C) и три объектива рядом: 50 мм, широкоугольный и телеобъектив.</x:v>
+      </x:c>
+      <x:c r="V98" s="28" t="str">
+        <x:v>#PL010 #LeicaIC #interchangeable-lenses #Leica-system</x:v>
+      </x:c>
+      <x:c r="W98" s="28" t="str">
+        <x:v>Проверить терминологию крепления: в источниках встречаются screw mount / standardized mount; не называть это байонетом в финальном русском тексте.</x:v>
+      </x:c>
+      <x:c r="X98" s="28" t="str">
+        <x:v>50.5619, 8.5044</x:v>
+      </x:c>
+      <x:c r="Y98" s="28" t="str">
+        <x:v>Leica I / сменные объективы</x:v>
+      </x:c>
+      <x:c r="Z98" s="28" t="str">
+        <x:v>Связь / переход</x:v>
+      </x:c>
+      <x:c r="AA98" s="28"/>
+    </x:row>
+    <x:row r="99" ht="12.75" customHeight="1">
+      <x:c r="A99" s="28" t="str">
+        <x:v>PL-HIST-0098</x:v>
+      </x:c>
+      <x:c r="B99" s="28" t="str">
+        <x:v>1932</x:v>
+      </x:c>
+      <x:c r="C99" s="28" t="str">
+        <x:v>год</x:v>
+      </x:c>
+      <x:c r="D99" s="28" t="str">
+        <x:v>Германия</x:v>
+      </x:c>
+      <x:c r="E99" s="28" t="str">
+        <x:v>Вецлар</x:v>
+      </x:c>
+      <x:c r="F99" s="28" t="str">
+        <x:v>Ernst Leitz Werke</x:v>
+      </x:c>
+      <x:c r="G99" s="28" t="str">
+        <x:v>Leica II становится первой Leica со встроенным дальномером, продолжая линию малой 35-мм камеры в сторону точной быстрой фокусировки.</x:v>
+      </x:c>
+      <x:c r="H99" s="28" t="str">
+        <x:v>Оптические инструменты</x:v>
+      </x:c>
+      <x:c r="I99" s="28" t="str">
+        <x:v>Leica II built-in rangefinder</x:v>
+      </x:c>
+      <x:c r="J99" s="28" t="str">
+        <x:v>Следующий шаг после компактности — скорость и точность наведения: Leica формирует основу дальномерной культуры съёмки.</x:v>
+      </x:c>
+      <x:c r="K99" s="28" t="str">
+        <x:v>Leica I and Leica system</x:v>
+      </x:c>
+      <x:c r="L99" s="28" t="str">
+        <x:v>Future rangefinder photography and Leica M lineage</x:v>
+      </x:c>
+      <x:c r="M99" s="28" t="str">
+        <x:v>Связь / переход</x:v>
+      </x:c>
+      <x:c r="N99" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O99" s="28" t="str">
+        <x:v>PL-010</x:v>
+      </x:c>
+      <x:c r="P99" s="28" t="str">
+        <x:v>SRC-068</x:v>
+      </x:c>
+      <x:c r="Q99" s="28" t="str">
+        <x:v>Leica Timeline — 1932</x:v>
+      </x:c>
+      <x:c r="R99" s="28" t="str">
+        <x:v>https://timeline.leica-camera.com/en-US/years/1932</x:v>
+      </x:c>
+      <x:c r="S99" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T99" s="28" t="str">
+        <x:v>Финальный мост урока: PL-010 завершает Модуль 1, но открывает будущие темы про камеры, дальномер и объективы.</x:v>
+      </x:c>
+      <x:c r="U99" s="28" t="str">
+        <x:v>Leica II рядом с Leica I: появляется дальномер как следующий слой управления камерой.</x:v>
+      </x:c>
+      <x:c r="V99" s="28" t="str">
+        <x:v>#PL010 #LeicaII #rangefinder #future-lessons #Leica-system</x:v>
+      </x:c>
+      <x:c r="W99" s="28"/>
+      <x:c r="X99" s="28" t="str">
+        <x:v>50.5619, 8.5044</x:v>
+      </x:c>
+      <x:c r="Y99" s="28" t="str">
+        <x:v>Leica I / мост к дальномерной системе</x:v>
+      </x:c>
+      <x:c r="Z99" s="28" t="str">
+        <x:v>Связь / переход</x:v>
+      </x:c>
+      <x:c r="AA99" s="28"/>
+    </x:row>
     <x:row r="100" ht="12.75" customHeight="1"/>
     <x:row r="101" ht="12.75" customHeight="1"/>
     <x:row r="102" ht="12.75" customHeight="1"/>
@@ -13054,7 +13855,7 @@
       <x:formula1>'06_Lists'!$E$2:$E$6</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="O2:O500">
-      <x:formula1>'06_Lists'!$C$2:$C$13</x:formula1>
+      <x:formula1>'06_Lists'!$C$2:$C$14</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="S2:S500">
       <x:formula1>'06_Lists'!$F$2:$F$6</x:formula1>
@@ -13063,7 +13864,7 @@
       <x:formula1>'06_Lists'!$D$2:$D$14</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="Y2:Y500">
-      <x:formula1>'06_Lists'!$H$2:$H$66</x:formula1>
+      <x:formula1>'06_Lists'!$H$2:$H$76</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="Z2:Z500">
       <x:formula1>'06_Lists'!$G$2:$G$11</x:formula1>
@@ -13071,7 +13872,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabafe04e4bd648ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f890d577a2349a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13126,7 +13927,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="6" t="str">
-        <x:v>camera lucida, stereoscope, portable camera obscura, compact 35mm cameras, Leica system</x:v>
+        <x:v>camera lucida, stereoscope, portable camera obscura, compact 35mm cameras, Leica I, Leica system, rangefinder lineage</x:v>
       </x:c>
       <x:c r="C3" s="6" t="str">
         <x:v>PL-001 / PL-009 / PL-010 / будущие PL</x:v>
@@ -13211,10 +14012,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>бумажный негатив, калотип, стеклянный негатив, сухая желатиновая пластина, рулонная плёнка, Brownie, 120 film, 35 мм, 24×36, 135 cartridge, копирование</x:v>
+        <x:v>бумажный негатив, калотип, стеклянный негатив, сухая желатиновая пластина, рулонная плёнка, Brownie, 120 film, 35 мм, 24×36, Leica I, 135 cartridge, копирование</x:v>
       </x:c>
       <x:c r="C8" s="6" t="str">
-        <x:v>PL-004 / PL-006 / PL-007 / PL-008 / PL-009</x:v>
+        <x:v>PL-004 / PL-006 / PL-007 / PL-008 / PL-009 / PL-010</x:v>
       </x:c>
       <x:c r="D8" s="6" t="s">
         <x:v>1224</x:v>
@@ -13328,7 +14129,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re200c697a2e94cf8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16153f6431224d74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13547,26 +14348,46 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="28" t="str">
+        <x:v>PL-010</x:v>
+      </x:c>
+      <x:c r="B11" s="28" t="str">
+        <x:v>Leica I</x:v>
+      </x:c>
+      <x:c r="C11" s="28" t="str">
+        <x:v>PL-HIST-0089…0098</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="str">
+        <x:v>Leica I сделала 35 мм не просто форматом плёнки, а языком мобильной фотографии: маленькая камера стала серьёзным инструментом репортажа, улицы и повседневного наблюдения.</x:v>
+      </x:c>
+      <x:c r="E11" s="28" t="str">
+        <x:v>основа заполнена</x:v>
+      </x:c>
+      <x:c r="F11" s="28" t="str">
+        <x:v>https://t.me/photolab_vf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="28" t="str">
         <x:v>будущие PL</x:v>
       </x:c>
-      <x:c r="B11" s="28" t="str">
-        <x:v>Расширение после PL-009</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="str">
-        <x:v>Leica I, цвет, вспышка, автофокус, цифровая фотография, смартфоны, AI</x:v>
-      </x:c>
-      <x:c r="D11" s="28" t="str">
-        <x:v>Фотография станет ещё компактнее, цветной, автоматической, цифровой и вычислительной.</x:v>
-      </x:c>
-      <x:c r="E11" s="28" t="str">
+      <x:c r="B12" s="28" t="str">
+        <x:v>Расширение после PL-010</x:v>
+      </x:c>
+      <x:c r="C12" s="28" t="str">
+        <x:v>Цвет, вспышка, автофокус, цифровая фотография, смартфоны, AI</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="str">
+        <x:v>После Leica фотография будет развиваться как система: материал, камера, объектив, экспозиция, фокус, жанры, печать и авторский проект.</x:v>
+      </x:c>
+      <x:c r="E12" s="28" t="str">
         <x:v>планируется</x:v>
       </x:c>
-      <x:c r="F11" s="28"/>
+      <x:c r="F12" s="28"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R062f7f485cc64ced"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53660eaa7e6944b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14636,10 +15457,129 @@
         <x:v>музейная карточка предмета</x:v>
       </x:c>
     </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="28" t="str">
+        <x:v>SRC-062</x:v>
+      </x:c>
+      <x:c r="B63" s="28" t="str">
+        <x:v>Leica Camera — The History of the Leica I</x:v>
+      </x:c>
+      <x:c r="C63" s="28" t="str">
+        <x:v>https://leica-camera.com/en-int/photography/100-years/the-history-of-the-leica-I</x:v>
+      </x:c>
+      <x:c r="D63" s="28" t="str">
+        <x:v>Leica I production, Leipzig 1925, compact mobile camera, around 57,000 units, visual language of reportage and street photography</x:v>
+      </x:c>
+      <x:c r="E63" s="28" t="str">
+        <x:v>официальная история Leica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="28" t="str">
+        <x:v>SRC-063</x:v>
+      </x:c>
+      <x:c r="B64" s="28" t="str">
+        <x:v>Leica Camera — 100 Years of Leica: Witness to a Century</x:v>
+      </x:c>
+      <x:c r="C64" s="28" t="str">
+        <x:v>https://leica-camera.com/en-GB/press/100-years-leica-witness-century-1925-2025-1</x:v>
+      </x:c>
+      <x:c r="D64" s="28" t="str">
+        <x:v>Leica I first series-produced Leica 35mm camera, presented at Leipzig Spring Fair 1925, compact format and new photographic applications</x:v>
+      </x:c>
+      <x:c r="E64" s="28" t="str">
+        <x:v>официальный пресс-материал Leica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="28" t="str">
+        <x:v>SRC-064</x:v>
+      </x:c>
+      <x:c r="B65" s="28" t="str">
+        <x:v>Smithsonian NMAH — Leica 35 mm 1(A) Camera</x:v>
+      </x:c>
+      <x:c r="C65" s="28" t="str">
+        <x:v>https://americanhistory.si.edu/collections/object/nmah_834692</x:v>
+      </x:c>
+      <x:c r="D65" s="28" t="str">
+        <x:v>Leica 1(A), designed by Oskar Barnack, announced 1924, sold 1925, popularized 35mm film photography</x:v>
+      </x:c>
+      <x:c r="E65" s="28" t="str">
+        <x:v>музейная карточка предмета</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="28" t="str">
+        <x:v>SRC-065</x:v>
+      </x:c>
+      <x:c r="B66" s="28" t="str">
+        <x:v>Leica Camera — Understanding Leica Lenses</x:v>
+      </x:c>
+      <x:c r="C66" s="28" t="str">
+        <x:v>https://leica-camera.com/en-int/photography/understanding-leica-lenses</x:v>
+      </x:c>
+      <x:c r="D66" s="28" t="str">
+        <x:v>Max Berek and early Leica lenses for Ur-Leica and Leica system</x:v>
+      </x:c>
+      <x:c r="E66" s="28" t="str">
+        <x:v>официальный материал Leica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="28" t="str">
+        <x:v>SRC-066</x:v>
+      </x:c>
+      <x:c r="B67" s="28" t="str">
+        <x:v>LFI — Elmar 50 mm f/3.5</x:v>
+      </x:c>
+      <x:c r="C67" s="28" t="str">
+        <x:v>https://lfi-online.de/en/stories/elmar-50-mm-f-3-5-19122.html</x:v>
+      </x:c>
+      <x:c r="D67" s="28" t="str">
+        <x:v>Anastigmat, Elmax and Elmar 50mm f/3.5; Max Berek and early Leica I lenses</x:v>
+      </x:c>
+      <x:c r="E67" s="28" t="str">
+        <x:v>профильный материал Leica Fotografie International</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="28" t="str">
+        <x:v>SRC-067</x:v>
+      </x:c>
+      <x:c r="B68" s="28" t="str">
+        <x:v>Smithsonian NMAH — Leica 1(C)</x:v>
+      </x:c>
+      <x:c r="C68" s="28" t="str">
+        <x:v>https://americanhistory.si.edu/collections/object/nmah_1145349</x:v>
+      </x:c>
+      <x:c r="D68" s="28" t="str">
+        <x:v>First Leica with interchangeable lenses in 1930; standardized lens mount by the end of 1930</x:v>
+      </x:c>
+      <x:c r="E68" s="28" t="str">
+        <x:v>музейная карточка предмета</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="28" t="str">
+        <x:v>SRC-068</x:v>
+      </x:c>
+      <x:c r="B69" s="28" t="str">
+        <x:v>Leica Timeline — 1932</x:v>
+      </x:c>
+      <x:c r="C69" s="28" t="str">
+        <x:v>https://timeline.leica-camera.com/en-US/years/1932</x:v>
+      </x:c>
+      <x:c r="D69" s="28" t="str">
+        <x:v>Leica II becomes the first Leica with a built-in rangefinder</x:v>
+      </x:c>
+      <x:c r="E69" s="28" t="str">
+        <x:v>официальная история Leica</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R720e8126b0d84c7c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb64bb8c9dd7f4843"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14691,8 +15631,8 @@
       <x:c r="B2" s="6" t="s">
         <x:v>416</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
-        <x:v>13</x:v>
+      <x:c r="C2" s="34" t="str">
+        <x:v>PL-001</x:v>
       </x:c>
       <x:c r="D2" s="6" t="s">
         <x:v>12</x:v>
@@ -14717,8 +15657,8 @@
       <x:c r="B3" s="6" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="C3" s="6" t="s">
-        <x:v>15</x:v>
+      <x:c r="C3" s="34" t="str">
+        <x:v>PL-002</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
         <x:v>14</x:v>
@@ -14743,8 +15683,8 @@
       <x:c r="B4" s="6" t="s">
         <x:v>664</x:v>
       </x:c>
-      <x:c r="C4" s="6" t="s">
-        <x:v>17</x:v>
+      <x:c r="C4" s="34" t="str">
+        <x:v>PL-003</x:v>
       </x:c>
       <x:c r="D4" s="6" t="s">
         <x:v>16</x:v>
@@ -14769,8 +15709,8 @@
       <x:c r="B5" s="6" t="s">
         <x:v>399</x:v>
       </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>19</x:v>
+      <x:c r="C5" s="34" t="str">
+        <x:v>PL-004</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
         <x:v>18</x:v>
@@ -14795,8 +15735,8 @@
       <x:c r="B6" s="6" t="s">
         <x:v>756</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>21</x:v>
+      <x:c r="C6" s="34" t="str">
+        <x:v>PL-005</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
         <x:v>20</x:v>
@@ -14819,8 +15759,8 @@
       <x:c r="B7" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="s">
-        <x:v>23</x:v>
+      <x:c r="C7" s="34" t="str">
+        <x:v>PL-006</x:v>
       </x:c>
       <x:c r="D7" s="6" t="s">
         <x:v>22</x:v>
@@ -14839,8 +15779,8 @@
       <x:c r="B8" s="6" t="s">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="s">
-        <x:v>25</x:v>
+      <x:c r="C8" s="34" t="str">
+        <x:v>PL-007</x:v>
       </x:c>
       <x:c r="D8" s="6" t="s">
         <x:v>24</x:v>
@@ -14859,8 +15799,8 @@
       <x:c r="B9" s="6" t="s">
         <x:v>555</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="s">
-        <x:v>27</x:v>
+      <x:c r="C9" s="34" t="str">
+        <x:v>PL-008</x:v>
       </x:c>
       <x:c r="D9" s="6" t="s">
         <x:v>26</x:v>
@@ -14879,7 +15819,7 @@
       <x:c r="B10" s="6" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C10" s="34" t="str">
         <x:v>PL-009</x:v>
       </x:c>
       <x:c r="D10" s="6" t="s">
@@ -14899,8 +15839,8 @@
       <x:c r="B11" s="6" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
-        <x:v>будущие PL</x:v>
+      <x:c r="C11" s="34" t="str">
+        <x:v>PL-010</x:v>
       </x:c>
       <x:c r="D11" s="6" t="s">
         <x:v>29</x:v>
@@ -14917,8 +15857,8 @@
     <x:row r="12" ht="15.75" customHeight="1">
       <x:c r="A12" s="6"/>
       <x:c r="B12" s="6"/>
-      <x:c r="C12" s="6" t="str">
-        <x:v>межурочный узел</x:v>
+      <x:c r="C12" s="34" t="str">
+        <x:v>будущие PL</x:v>
       </x:c>
       <x:c r="D12" s="6" t="s">
         <x:v>30</x:v>
@@ -14935,8 +15875,8 @@
     <x:row r="13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6"/>
       <x:c r="B13" s="6"/>
-      <x:c r="C13" s="6" t="str">
-        <x:v>проверить</x:v>
+      <x:c r="C13" s="34" t="str">
+        <x:v>межурочный узел</x:v>
       </x:c>
       <x:c r="D13" s="6" t="s">
         <x:v>31</x:v>
@@ -14951,7 +15891,9 @@
     <x:row r="14" ht="15.75" customHeight="1">
       <x:c r="A14" s="6"/>
       <x:c r="B14" s="6"/>
-      <x:c r="C14" s="6"/>
+      <x:c r="C14" s="34" t="str">
+        <x:v>проверить</x:v>
+      </x:c>
       <x:c r="D14" s="6" t="s">
         <x:v>32</x:v>
       </x:c>
@@ -15444,6 +16386,56 @@
     <x:row r="66">
       <x:c r="H66" s="28" t="str">
         <x:v>35 мм / 135 cartridge</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="H67" s="28" t="str">
+        <x:v>Leica I / прототип</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="H68" s="28" t="str">
+        <x:v>Leica I / проверочная серия</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="H69" s="28" t="str">
+        <x:v>Leica I / начало производства</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="H70" s="28" t="str">
+        <x:v>Leica I / публичный дебют</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="H71" s="28" t="str">
+        <x:v>Leica I / компактная камера</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="H72" s="28" t="str">
+        <x:v>Leica I / оптика и Elmar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="H73" s="28" t="str">
+        <x:v>Leica I / массовое принятие</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="H74" s="28" t="str">
+        <x:v>Leica I / новая визуальная практика</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="H75" s="28" t="str">
+        <x:v>Leica I / сменные объективы</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="H76" s="28" t="str">
+        <x:v>Leica I / мост к дальномерной системе</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -15461,7 +16453,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="35" t="str">
-        <x:v>PHOTO LAB — History Map Master v0.6</x:v>
+        <x:v>PHOTO LAB — History Map Master v0.7</x:v>
       </x:c>
       <x:c r="B1" s="28"/>
     </x:row>
@@ -15475,10 +16467,10 @@
     </x:row>
     <x:row r="3" ht="15.75" customHeight="1">
       <x:c r="A3" s="36" t="str">
-        <x:v>Охват v0.6</x:v>
+        <x:v>Охват v0.7</x:v>
       </x:c>
       <x:c r="B3" s="32" t="str">
-        <x:v>От оптических предпосылок камеры-обскуры до мокрого коллодия, сухих желатиновых пластин, рулонной плёнки, Kodak, Brownie, snapshot-культуры и 35-мм малого формата; основа для PL-001–PL-009.</x:v>
+        <x:v>От оптических предпосылок камеры-обскуры до мокрого коллодия, сухих желатиновых пластин, рулонной плёнки, Kodak, Brownie, snapshot-культуры, 35-мм малого формата и Leica I; основа для PL-001–PL-010.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15.75" customHeight="1">
@@ -15510,7 +16502,7 @@
         <x:v>Правило веток</x:v>
       </x:c>
       <x:c r="B7" s="32" t="str">
-        <x:v>Ветка развития = одна из 13 крупных линий из 02_Branches. Для PL-006…PL-009 сухие пластины, рулонная плёнка, Brownie, snapshot-культура и 35 мм пока идут внутри крупных веток «Негатив-позитив», «Печать / тиражирование», «Проекция / распространение» и «Оптические инструменты», а детали фиксируются в подветках.</x:v>
+        <x:v>Ветка развития = одна из 13 крупных линий из 02_Branches. Для PL-006…PL-010 сухие пластины, рулонная плёнка, Brownie, snapshot-культура, 35 мм и Leica I пока идут внутри крупных веток «Негатив-позитив», «Печать / тиражирование», «Проекция / распространение» и «Оптические инструменты», а детали фиксируются в подветках.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" customHeight="1">
@@ -15518,7 +16510,7 @@
         <x:v>Правило подветок</x:v>
       </x:c>
       <x:c r="B8" s="32" t="str">
-        <x:v>Подветка (детали) = уточнение внутри крупной ветки: химия, камера, распространение, фотокнига, медицинское применение, сухие пластины, рулонная плёнка, Brownie, snapshot-культура, 35 мм и т.п.</x:v>
+        <x:v>Подветка (детали) = уточнение внутри крупной ветки: химия, камера, распространение, фотокнига, медицинское применение, сухие пластины, рулонная плёнка, Brownie, snapshot-культура, 35 мм, Leica I и т.п.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="12.75" customHeight="1">
@@ -15587,26 +16579,34 @@
     </x:row>
     <x:row r="17" ht="28">
       <x:c r="A17" s="28" t="str">
-        <x:v>Правило флагманских узлов</x:v>
+        <x:v>Что изменено в v0.7</x:v>
       </x:c>
       <x:c r="B17" s="28" t="str">
-        <x:v>Колонка «Флагман урока (да/нет)» = ровно один узел на урок, который представляет тему в компактном/обзорном режиме карты (Journey Mode). Значение проставляется вручную автором, не вычисляется автоматически.</x:v>
+        <x:v>Заполнен PL-010: добавлены PL-HIST-0089…0098 по Leica I, Ur-Leica, Leica 0-Series, серийному запуску 1924/1925, публичному дебюту в Лейпциге, оптике Max Berek / Elmar, массовому распространению, новой мобильной визуальной практике, Leica I(C) и мосту к Leica II. Добавлены источники SRC-062…SRC-068 и флагманский узел PL-HIST-0092.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="14">
       <x:c r="A18" s="28" t="str">
-        <x:v>Ссылка на урок в Telegram</x:v>
+        <x:v>Правило флагманских узлов</x:v>
       </x:c>
       <x:c r="B18" s="28" t="str">
-        <x:v>Колонка F в 03_Lessons_Map сейчас указывает на канал целиком (https://t.me/photolab_vf), т.к. точные номера постов для каждого PL-00X не зафиксированы. Когда номера постов будут известны, заменить на прямые ссылки вида https://t.me/photolab_vf/123 — сайт должен брать значение из этой колонки, не хранить ссылки в коде.</x:v>
+        <x:v>Колонка «Флагман урока (да/нет)» = ровно один узел на урок, который представляет тему в компактном/обзорном режиме карты (Journey Mode). Значение проставляется вручную автором, не вычисляется автоматически.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="28" t="str">
+        <x:v>Ссылка на урок в Telegram</x:v>
+      </x:c>
+      <x:c r="B19" s="28" t="str">
+        <x:v>Колонка F в 03_Lessons_Map сейчас указывает на канал целиком, если точные номера постов для конкретного PL-00X не зафиксированы. Когда номера постов будут известны, заменить на прямые ссылки вида https://t.me/photolab_vf/123 — сайт должен брать значение из этой колонки, не хранить ссылки в коде.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="28" t="str">
         <x:v>Следующий шаг</x:v>
       </x:c>
-      <x:c r="B19" s="28" t="str">
-        <x:v>PL-010 логично строить вокруг Leica I как камеры, которая сделала 35-мм формат полноценным языком мобильной фотографии.</x:v>
+      <x:c r="B20" s="28" t="str">
+        <x:v>PL-011 начинает Модуль 2: плёнка как светочувствительный материал — нужно перейти от исторической камеры Leica к пониманию самой фотоплёнки.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Dashboard" sheetId="1" r:id="Rb2e52cf26c554f00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Master_Facts" sheetId="2" r:id="R2e4a22a7fae04fcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Branches" sheetId="3" r:id="Rbf043961ad56466d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Lessons_Map" sheetId="4" r:id="R7a3c3b16f1c9478f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Sources" sheetId="5" r:id="Rc255602c47ba42d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Lists" sheetId="6" r:id="Ref54882c02fb4044"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="7" r:id="R9c741b947b55448a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Dashboard" sheetId="1" r:id="R098f4fefea5f4cc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Master_Facts" sheetId="2" r:id="R5f3a5bd46c744089"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Branches" sheetId="3" r:id="R9a64e19e61714f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Lessons_Map" sheetId="4" r:id="Rd57601f432f84380"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Sources" sheetId="5" r:id="Ree9092e357514b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Lists" sheetId="6" r:id="R3f6baed17f894a74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="7" r:id="R867ad533b46846b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -768,7 +768,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rea34b6358a1a4141"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1da690355b344fe3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -985,7 +985,7 @@
   <x:sheetData>
     <x:row r="1" s="46" customFormat="1" ht="40" customHeight="1">
       <x:c r="A1" s="31" t="str">
-        <x:v>PHOTO LAB — Master Timeline v0.12</x:v>
+        <x:v>PHOTO LAB — Master Timeline v0.13</x:v>
       </x:c>
       <x:c r="B1" s="20" t="n"/>
       <x:c r="C1" s="20" t="n"/>
@@ -1020,7 +1020,7 @@
       </x:c>
       <x:c r="B3" s="55" t="n">
         <x:f>COUNTA('01_Master_Facts'!$A$2:$A$500)</x:f>
-        <x:v>153</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C3" s="54" t="inlineStr">
         <x:is>
@@ -1038,7 +1038,7 @@
       </x:c>
       <x:c r="B4" s="55" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$N$2:$N$500,5)</x:f>
-        <x:v>67</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C4" s="54" t="inlineStr">
         <x:is>
@@ -1050,11 +1050,11 @@
     </x:row>
     <x:row r="5" s="46" customFormat="1" ht="21" customHeight="1">
       <x:c r="A5" s="54" t="str">
-        <x:v>Узлов для PL-001–PL-015</x:v>
+        <x:v>Узлов для PL-001–PL-016</x:v>
       </x:c>
       <x:c r="B5" s="55" t="n">
-        <x:f>SUM(COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-001"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-002"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-003"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-004"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-005"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-006"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-007"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-008"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-009"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-010"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-011"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-012"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-013"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-014"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-015"))</x:f>
-        <x:v>142</x:v>
+        <x:f>SUM(COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-001"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-002"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-003"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-004"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-005"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-006"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-007"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-008"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-009"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-010"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-011"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-012"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-013"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-014"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-015"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-016"))</x:f>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C5" s="54" t="str">
         <x:v>Без будущих PL и межурочных узлов</x:v>
@@ -1070,7 +1070,7 @@
       </x:c>
       <x:c r="B6" s="55" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$W$2:$W$500,"&lt;&gt;")</x:f>
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C6" s="54" t="inlineStr">
         <x:is>
@@ -1167,7 +1167,7 @@
       </x:c>
       <x:c r="B12" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A12)</x:f>
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C12" s="49" t="n"/>
       <x:c r="D12" s="50" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </x:c>
       <x:c r="B16" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A16)</x:f>
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C16" s="49" t="n"/>
       <x:c r="D16" s="50" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </x:c>
       <x:c r="B18" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A18)</x:f>
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="49" t="n"/>
       <x:c r="D18" s="49" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </x:c>
       <x:c r="B21" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A21)</x:f>
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="49" t="n"/>
       <x:c r="D21" s="49" t="inlineStr">
@@ -1419,11 +1419,11 @@
       <x:c r="B25" s="47" t="n"/>
       <x:c r="C25" s="49" t="n"/>
       <x:c r="D25" s="49" t="str">
-        <x:v>будущие PL</x:v>
+        <x:v>PL-016</x:v>
       </x:c>
       <x:c r="E25" s="49" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D25)</x:f>
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="26" s="46" customFormat="1" ht="21" customHeight="1">
@@ -1431,11 +1431,11 @@
       <x:c r="B26" s="50" t="n"/>
       <x:c r="C26" s="49" t="n"/>
       <x:c r="D26" s="49" t="str">
-        <x:v>межурочный узел</x:v>
+        <x:v>будущие PL</x:v>
       </x:c>
       <x:c r="E26" s="49" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D26)</x:f>
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="27" s="46" customFormat="1" ht="21" customHeight="1">
@@ -1443,19 +1443,24 @@
       <x:c r="B27" s="50"/>
       <x:c r="C27" s="49" t="n"/>
       <x:c r="D27" s="49" t="str">
-        <x:v>проверить</x:v>
+        <x:v>межурочный узел</x:v>
       </x:c>
       <x:c r="E27" s="49" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D27)</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="28" s="46" customFormat="1" ht="21" customHeight="1">
       <x:c r="A28" s="50"/>
       <x:c r="B28" s="50"/>
       <x:c r="C28" s="49" t="n"/>
-      <x:c r="D28" s="49" t="n"/>
-      <x:c r="E28" s="49" t="n"/>
+      <x:c r="D28" s="49" t="str">
+        <x:v>проверить</x:v>
+      </x:c>
+      <x:c r="E28" s="49" t="n">
+        <x:f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D28)</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" s="46" customFormat="1" ht="21" customHeight="1">
       <x:c r="A29" s="50" t="str">
@@ -1486,7 +1491,7 @@
       </x:c>
       <x:c r="B31" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A31)</x:f>
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C31" s="49" t="n"/>
       <x:c r="D31" s="49" t="n"/>
@@ -1534,7 +1539,7 @@
       </x:c>
       <x:c r="B35" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A35)</x:f>
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C35" s="49" t="n"/>
       <x:c r="D35" s="49" t="n"/>
@@ -1546,7 +1551,7 @@
       </x:c>
       <x:c r="B36" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A36)</x:f>
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C36" s="49" t="n"/>
       <x:c r="D36" s="49" t="n"/>
@@ -1558,7 +1563,7 @@
       </x:c>
       <x:c r="B37" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A37)</x:f>
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C37" s="49" t="n"/>
       <x:c r="D37" s="49" t="n"/>
@@ -1582,7 +1587,7 @@
       </x:c>
       <x:c r="B39" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A39)</x:f>
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C39" s="49" t="n"/>
       <x:c r="D39" s="49" t="n"/>
@@ -1594,7 +1599,7 @@
       </x:c>
       <x:c r="B40" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A40)</x:f>
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C40" s="49" t="n"/>
       <x:c r="D40" s="49" t="n"/>
@@ -1629,7 +1634,7 @@
     <x:mergeCell ref="A1:F1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb984e65a15db4931"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a64b63413434ff9"/>
 </x:worksheet>
 </file>
 
@@ -20401,17 +20406,863 @@
       </x:c>
       <x:c r="AA154"/>
     </x:row>
-    <x:row r="155" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="156" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="157" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="158" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="159" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="160" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="161" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="162" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="163" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="164" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="165" s="46" customFormat="1" ht="17" customHeight="1"/>
+    <x:row r="155" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A155" t="str">
+        <x:v>PL-HIST-0154</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>1942</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>год</x:v>
+      </x:c>
+      <x:c r="D155" t="str">
+        <x:v>США</x:v>
+      </x:c>
+      <x:c r="E155" t="str">
+        <x:v>Рочестер, Нью-Йорк</x:v>
+      </x:c>
+      <x:c r="F155" t="str">
+        <x:v>Eastman Kodak Company</x:v>
+      </x:c>
+      <x:c r="G155" t="str">
+        <x:v>Kodak объявляет KODACOLOR Film для отпечатков — первый настоящий цветной негативный фильм для фотографии.</x:v>
+      </x:c>
+      <x:c r="H155" t="str">
+        <x:v>Цвет</x:v>
+      </x:c>
+      <x:c r="I155" t="str">
+        <x:v>KODACOLOR / color negative film</x:v>
+      </x:c>
+      <x:c r="J155" t="str">
+        <x:v>Цветная фотография получает привычную для массового пользователя логику: снять негатив, а затем получить цветные позитивные отпечатки на бумаге.</x:v>
+      </x:c>
+      <x:c r="K155" t="str">
+        <x:v>Чёрно-белая негативная плёнка и ранние цветные позитивные процессы</x:v>
+      </x:c>
+      <x:c r="L155" t="str">
+        <x:v>Цветная негативная плёнка как стандарт семейной, любительской и лабораторной фотографии</x:v>
+      </x:c>
+      <x:c r="M155" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N155" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O155" t="str">
+        <x:v>PL-016</x:v>
+      </x:c>
+      <x:c r="P155" t="str">
+        <x:v>SRC-120</x:v>
+      </x:c>
+      <x:c r="Q155" t="str">
+        <x:v>Kodak — Photography History</x:v>
+      </x:c>
+      <x:c r="R155" t="str">
+        <x:v>https://www.kodak.com/en/company/page/photography-history/</x:v>
+      </x:c>
+      <x:c r="S155" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T155" t="str">
+        <x:v>Флагманская мысль урока: цветной негатив — это не «цветная картинка сразу», а цветная матрица для будущего отпечатка.</x:v>
+      </x:c>
+      <x:c r="U155" t="str">
+        <x:v>Кассета Kodacolor и рядом оранжевый негатив, из которого появляется цветной семейный отпечаток.</x:v>
+      </x:c>
+      <x:c r="V155" t="str">
+        <x:v>#PL016 #Kodacolor #color-negative #Kodak #prints</x:v>
+      </x:c>
+      <x:c r="W155"/>
+      <x:c r="X155" t="str">
+        <x:v>43.1566, -77.6088</x:v>
+      </x:c>
+      <x:c r="Y155" t="str">
+        <x:v>Цветная негативная плёнка / Kodacolor</x:v>
+      </x:c>
+      <x:c r="Z155" t="str">
+        <x:v>Ключевой исторический узел</x:v>
+      </x:c>
+      <x:c r="AA155" t="str">
+        <x:v>да</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A156" t="str">
+        <x:v>PL-HIST-0155</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>1942</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>год</x:v>
+      </x:c>
+      <x:c r="D156" t="str">
+        <x:v>США</x:v>
+      </x:c>
+      <x:c r="E156" t="str">
+        <x:v>распределённый процесс</x:v>
+      </x:c>
+      <x:c r="F156" t="str">
+        <x:v>Eastman Kodak Company / фотолаборатории</x:v>
+      </x:c>
+      <x:c r="G156" t="str">
+        <x:v>Kodacolor закрепляет отрицательно-положительную цветную систему: цветной негатив предназначен не для прямого просмотра, а для печати позитивов.</x:v>
+      </x:c>
+      <x:c r="H156" t="str">
+        <x:v>Негатив-позитив</x:v>
+      </x:c>
+      <x:c r="I156" t="str">
+        <x:v>Color negative / positive print process</x:v>
+      </x:c>
+      <x:c r="J156" t="str">
+        <x:v>Пользователь начинает мыслить цветную фотографию как маршрут: экспонировать плёнку → проявить цветной негатив → напечатать цветной позитив.</x:v>
+      </x:c>
+      <x:c r="K156" t="str">
+        <x:v>Классическая чёрно-белая система «негатив → позитив»</x:v>
+      </x:c>
+      <x:c r="L156" t="str">
+        <x:v>Цветная лабораторная печать, Ektacolor и массовые семейные отпечатки</x:v>
+      </x:c>
+      <x:c r="M156" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N156" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O156" t="str">
+        <x:v>PL-016</x:v>
+      </x:c>
+      <x:c r="P156" t="str">
+        <x:v>SRC-121</x:v>
+      </x:c>
+      <x:c r="Q156" t="str">
+        <x:v>Library of Congress — Dye coupler negatives</x:v>
+      </x:c>
+      <x:c r="R156" t="str">
+        <x:v>https://www.loc.gov/pictures/item/tgm003415/</x:v>
+      </x:c>
+      <x:c r="S156" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T156" t="str">
+        <x:v>Связать PL-016 с PL-013: принцип «негатив-позитив» остаётся тем же, но теперь каждый канал цвета записывается отдельной красочной информацией.</x:v>
+      </x:c>
+      <x:c r="U156" t="str">
+        <x:v>Схема из трёх шагов: цветная сцена → оранжевый негатив → нормальный цветной отпечаток.</x:v>
+      </x:c>
+      <x:c r="V156" t="str">
+        <x:v>#PL016 #negative-positive #Kodacolor #color-print</x:v>
+      </x:c>
+      <x:c r="W156" t="str">
+        <x:v>Проверить, как детально показывать Ektacolor — лучше оставить для печати или лаборатории.</x:v>
+      </x:c>
+      <x:c r="X156"/>
+      <x:c r="Y156" t="str">
+        <x:v>Цветная негативная плёнка / негатив-позитив</x:v>
+      </x:c>
+      <x:c r="Z156" t="str">
+        <x:v>Связь / переход</x:v>
+      </x:c>
+      <x:c r="AA156"/>
+    </x:row>
+    <x:row r="157" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A157" t="str">
+        <x:v>PL-HIST-0156</x:v>
+      </x:c>
+      <x:c r="B157" t="str">
+        <x:v>1940-е – XX век</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D157" t="str">
+        <x:v>глобально</x:v>
+      </x:c>
+      <x:c r="E157" t="str">
+        <x:v>распределённый процесс</x:v>
+      </x:c>
+      <x:c r="F157" t="str">
+        <x:v>Производители цветной плёнки</x:v>
+      </x:c>
+      <x:c r="G157" t="str">
+        <x:v>Современные цветные процессы формируют изображение через отдельные слои красителей: голубой, пурпурный и жёлтый складываются в полноцветную картину.</x:v>
+      </x:c>
+      <x:c r="H157" t="str">
+        <x:v>Цвет</x:v>
+      </x:c>
+      <x:c r="I157" t="str">
+        <x:v>Cyan / magenta / yellow dye layers</x:v>
+      </x:c>
+      <x:c r="J157" t="str">
+        <x:v>Цветная плёнка оказывается не «одним цветным слоем», а системой нескольких записей цвета, которые затем нужно правильно совместить в печати или сканировании.</x:v>
+      </x:c>
+      <x:c r="K157" t="str">
+        <x:v>Серебряно-желатиновая эмульсия и чёрно-белый негатив</x:v>
+      </x:c>
+      <x:c r="L157" t="str">
+        <x:v>Многослойная цветная негативная плёнка и цветное проявление</x:v>
+      </x:c>
+      <x:c r="M157" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N157" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O157" t="str">
+        <x:v>PL-016</x:v>
+      </x:c>
+      <x:c r="P157" t="str">
+        <x:v>SRC-122</x:v>
+      </x:c>
+      <x:c r="Q157" t="str">
+        <x:v>National Archives — Identifying Motion Picture Film Formats</x:v>
+      </x:c>
+      <x:c r="R157" t="str">
+        <x:v>https://www.archives.gov/preservation/formats/motion-picture-film-identify-formats.html</x:v>
+      </x:c>
+      <x:c r="S157" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T157" t="str">
+        <x:v>Новичку важно увидеть: цвет на плёнке строится из нескольких слоёв, а не появляется как один готовый «цветной пиксель».</x:v>
+      </x:c>
+      <x:c r="U157" t="str">
+        <x:v>Разрез цветной плёнки с тремя условными слоями: yellow, magenta, cyan.</x:v>
+      </x:c>
+      <x:c r="V157" t="str">
+        <x:v>#PL016 #CMY #dye-layers #color-film</x:v>
+      </x:c>
+      <x:c r="W157"/>
+      <x:c r="X157"/>
+      <x:c r="Y157" t="str">
+        <x:v>Цветная негативная плёнка / слои красителей</x:v>
+      </x:c>
+      <x:c r="Z157" t="str">
+        <x:v>Технология / процесс</x:v>
+      </x:c>
+      <x:c r="AA157"/>
+    </x:row>
+    <x:row r="158" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A158" t="str">
+        <x:v>PL-HIST-0157</x:v>
+      </x:c>
+      <x:c r="B158" t="str">
+        <x:v>1940-е – XX век</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D158" t="str">
+        <x:v>глобально</x:v>
+      </x:c>
+      <x:c r="E158" t="str">
+        <x:v>распределённый процесс</x:v>
+      </x:c>
+      <x:c r="F158" t="str">
+        <x:v>Kodak и другие производители цветных материалов</x:v>
+      </x:c>
+      <x:c r="G158" t="str">
+        <x:v>В цветной негативной плёнке светочувствительные слои содержат цветообразующие компоненты — couplers; во время проявления они формируют красители.</x:v>
+      </x:c>
+      <x:c r="H158" t="str">
+        <x:v>Фотохимия</x:v>
+      </x:c>
+      <x:c r="I158" t="str">
+        <x:v>Color couplers / chromogenic development</x:v>
+      </x:c>
+      <x:c r="J158" t="str">
+        <x:v>Проявление цветной плёнки становится не просто проявлением серебра: химия создаёт красочное изображение из скрытой цветовой записи.</x:v>
+      </x:c>
+      <x:c r="K158" t="str">
+        <x:v>Скрытое изображение и серебряное проявление в PL-012 / PL-015</x:v>
+      </x:c>
+      <x:c r="L158" t="str">
+        <x:v>C-41 как стандартизированный цветной негативный процесс</x:v>
+      </x:c>
+      <x:c r="M158" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N158" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O158" t="str">
+        <x:v>PL-016</x:v>
+      </x:c>
+      <x:c r="P158" t="str">
+        <x:v>SRC-123</x:v>
+      </x:c>
+      <x:c r="Q158" t="str">
+        <x:v>Kodak — Essential Reference Guide for Filmmakers</x:v>
+      </x:c>
+      <x:c r="R158" t="str">
+        <x:v>https://www.kodak.com/content/products-brochures/Film/kodak-essential-reference-guide-for-filmmakers.pdf</x:v>
+      </x:c>
+      <x:c r="S158" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T158" t="str">
+        <x:v>Объяснять просто: свет оставляет след, проявитель запускает реакцию, а couplers помогают родиться цветным красителям.</x:v>
+      </x:c>
+      <x:c r="U158" t="str">
+        <x:v>Микро-схема: кристалл серебра + проявитель + coupler → цветной краситель.</x:v>
+      </x:c>
+      <x:c r="V158" t="str">
+        <x:v>#PL016 #color-couplers #chromogenic #developer</x:v>
+      </x:c>
+      <x:c r="W158"/>
+      <x:c r="X158"/>
+      <x:c r="Y158" t="str">
+        <x:v>Цветная негативная плёнка / color couplers</x:v>
+      </x:c>
+      <x:c r="Z158" t="str">
+        <x:v>Технология / процесс</x:v>
+      </x:c>
+      <x:c r="AA158"/>
+    </x:row>
+    <x:row r="159" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A159" t="str">
+        <x:v>PL-HIST-0158</x:v>
+      </x:c>
+      <x:c r="B159" t="str">
+        <x:v>XX век</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D159" t="str">
+        <x:v>глобально</x:v>
+      </x:c>
+      <x:c r="E159" t="str">
+        <x:v>распределённый процесс</x:v>
+      </x:c>
+      <x:c r="F159" t="str">
+        <x:v>Производители цветных негативных плёнок</x:v>
+      </x:c>
+      <x:c r="G159" t="str">
+        <x:v>Цветной негатив получает характерную оранжевую маску: напрямую он выглядит странно, но эта маска помогает корректнее воспроизводить цвет при печати.</x:v>
+      </x:c>
+      <x:c r="H159" t="str">
+        <x:v>Цвет</x:v>
+      </x:c>
+      <x:c r="I159" t="str">
+        <x:v>Orange mask in color negative film</x:v>
+      </x:c>
+      <x:c r="J159" t="str">
+        <x:v>Появляется важный парадокс: хороший цветной негатив не обязан выглядеть красиво глазами — он создан для последующей интерпретации лабораторией или сканером.</x:v>
+      </x:c>
+      <x:c r="K159" t="str">
+        <x:v>Цветные слои и красители в негативной плёнке</x:v>
+      </x:c>
+      <x:c r="L159" t="str">
+        <x:v>Печать и цифровая инверсия цветного негатива</x:v>
+      </x:c>
+      <x:c r="M159" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N159" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O159" t="str">
+        <x:v>PL-016</x:v>
+      </x:c>
+      <x:c r="P159" t="str">
+        <x:v>SRC-124</x:v>
+      </x:c>
+      <x:c r="Q159" t="str">
+        <x:v>Kodak — Processing KODAK Motion Picture Films, Module 7</x:v>
+      </x:c>
+      <x:c r="R159" t="str">
+        <x:v>https://www.kodak.com/content/products-brochures/Film/Processing-KODAK-Motion-Picture-Films-Module-7.pdf</x:v>
+      </x:c>
+      <x:c r="S159" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T159" t="str">
+        <x:v>Это один из самых полезных моментов урока: оранжевый цвет плёнки — не ошибка и не брак, а часть системы цветокоррекции.</x:v>
+      </x:c>
+      <x:c r="U159" t="str">
+        <x:v>Оранжевая полоска негатива на световом столе; рядом правильно отпечатанный цветной кадр.</x:v>
+      </x:c>
+      <x:c r="V159" t="str">
+        <x:v>#PL016 #orange-mask #color-negative #printing #scan</x:v>
+      </x:c>
+      <x:c r="W159"/>
+      <x:c r="X159"/>
+      <x:c r="Y159" t="str">
+        <x:v>Цветная негативная плёнка / оранжевая маска</x:v>
+      </x:c>
+      <x:c r="Z159" t="str">
+        <x:v>Технология / процесс</x:v>
+      </x:c>
+      <x:c r="AA159"/>
+    </x:row>
+    <x:row r="160" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A160" t="str">
+        <x:v>PL-HIST-0159</x:v>
+      </x:c>
+      <x:c r="B160" t="str">
+        <x:v>1940-е – XX век</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D160" t="str">
+        <x:v>США / глобально</x:v>
+      </x:c>
+      <x:c r="E160" t="str">
+        <x:v>фотолаборатории</x:v>
+      </x:c>
+      <x:c r="F160" t="str">
+        <x:v>Фотоиндустрия и фотолаборатории</x:v>
+      </x:c>
+      <x:c r="G160" t="str">
+        <x:v>Цветная негативная плёнка работает в паре с цветной хромогенной печатью: негатив проецируют на фотобумагу, где формируется позитивный цветной отпечаток.</x:v>
+      </x:c>
+      <x:c r="H160" t="str">
+        <x:v>Печать / тиражирование</x:v>
+      </x:c>
+      <x:c r="I160" t="str">
+        <x:v>Chromogenic color print from color negative</x:v>
+      </x:c>
+      <x:c r="J160" t="str">
+        <x:v>Цветной негатив становится основой массового фотосервиса: человек приносит плёнку и получает готовые цветные фотографии.</x:v>
+      </x:c>
+      <x:c r="K160" t="str">
+        <x:v>Kodacolor как первый массовый цветной негатив для отпечатков</x:v>
+      </x:c>
+      <x:c r="L160" t="str">
+        <x:v>RA-4, минилабы, семейные альбомы и современные лабораторные отпечатки</x:v>
+      </x:c>
+      <x:c r="M160" t="str">
+        <x:v>Главная линия / временная доминирующая линия</x:v>
+      </x:c>
+      <x:c r="N160" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O160" t="str">
+        <x:v>PL-016</x:v>
+      </x:c>
+      <x:c r="P160" t="str">
+        <x:v>SRC-125</x:v>
+      </x:c>
+      <x:c r="Q160" t="str">
+        <x:v>National Archives — Photographic Prints in the Still Picture Branch</x:v>
+      </x:c>
+      <x:c r="R160" t="str">
+        <x:v>https://www.archives.gov/research/still-pictures/still-picture-photographic-prints</x:v>
+      </x:c>
+      <x:c r="S160" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T160" t="str">
+        <x:v>Связать с опытом зрителя: многие семейные фото XX века — это не «файл», а результат цепочки цветной негатив + цветная бумага.</x:v>
+      </x:c>
+      <x:c r="U160" t="str">
+        <x:v>Увеличитель или минилаб: цветной негатив проецируется на бумагу, рядом появляются отпечатки 10×15.</x:v>
+      </x:c>
+      <x:c r="V160" t="str">
+        <x:v>#PL016 #chromogenic-print #color-lab #family-prints</x:v>
+      </x:c>
+      <x:c r="W160"/>
+      <x:c r="X160"/>
+      <x:c r="Y160" t="str">
+        <x:v>Цветная негативная плёнка / печать позитивов</x:v>
+      </x:c>
+      <x:c r="Z160" t="str">
+        <x:v>Тиражирование / публикация</x:v>
+      </x:c>
+      <x:c r="AA160"/>
+    </x:row>
+    <x:row r="161" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A161" t="str">
+        <x:v>PL-HIST-0160</x:v>
+      </x:c>
+      <x:c r="B161" t="str">
+        <x:v>1970-е – XXI век</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D161" t="str">
+        <x:v>глобально</x:v>
+      </x:c>
+      <x:c r="E161" t="str">
+        <x:v>фотолаборатории</x:v>
+      </x:c>
+      <x:c r="F161" t="str">
+        <x:v>Kodak / фотолаборатории</x:v>
+      </x:c>
+      <x:c r="G161" t="str">
+        <x:v>Процесс C-41 становится стандартной лабораторной логикой для большинства цветных негативных фотоплёнок.</x:v>
+      </x:c>
+      <x:c r="H161" t="str">
+        <x:v>Фотохимия</x:v>
+      </x:c>
+      <x:c r="I161" t="str">
+        <x:v>C-41 color negative process</x:v>
+      </x:c>
+      <x:c r="J161" t="str">
+        <x:v>Цветная негативная плёнка получает промышленную повторяемость: разные плёнки можно обрабатывать по единому температурному и химическому маршруту.</x:v>
+      </x:c>
+      <x:c r="K161" t="str">
+        <x:v>Ранние цветные негативные процессы</x:v>
+      </x:c>
+      <x:c r="L161" t="str">
+        <x:v>Современная проявка цветной негативной плёнки в лаборатории или домашнем наборе C-41</x:v>
+      </x:c>
+      <x:c r="M161" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N161" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O161" t="str">
+        <x:v>PL-016</x:v>
+      </x:c>
+      <x:c r="P161" t="str">
+        <x:v>SRC-126</x:v>
+      </x:c>
+      <x:c r="Q161" t="str">
+        <x:v>Kodak — C-41 Color Negative Control Strips</x:v>
+      </x:c>
+      <x:c r="R161" t="str">
+        <x:v>https://www.kodak.com/en/motion/page/c-41-control-strips/</x:v>
+      </x:c>
+      <x:c r="S161" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T161" t="str">
+        <x:v>Главная практическая формула: если на коробке написано C-41, это цветная негативная плёнка под стандартный цветной процесс.</x:v>
+      </x:c>
+      <x:c r="U161" t="str">
+        <x:v>Коробка с надписью Process C-41, контрольная полоска и термостатированная ванна.</x:v>
+      </x:c>
+      <x:c r="V161" t="str">
+        <x:v>#PL016 #C41 #color-negative-processing #lab</x:v>
+      </x:c>
+      <x:c r="W161" t="str">
+        <x:v>Точную дату внедрения C-41 можно уточнить отдельно; в карте пока важнее современная стандартная роль процесса.</x:v>
+      </x:c>
+      <x:c r="X161"/>
+      <x:c r="Y161" t="str">
+        <x:v>Цветная негативная плёнка / C-41</x:v>
+      </x:c>
+      <x:c r="Z161" t="str">
+        <x:v>Технология / процесс</x:v>
+      </x:c>
+      <x:c r="AA161"/>
+    </x:row>
+    <x:row r="162" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A162" t="str">
+        <x:v>PL-HIST-0161</x:v>
+      </x:c>
+      <x:c r="B162" t="str">
+        <x:v>XX–XXI век</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D162" t="str">
+        <x:v>глобально</x:v>
+      </x:c>
+      <x:c r="E162" t="str">
+        <x:v>фотолаборатории и производители химии</x:v>
+      </x:c>
+      <x:c r="F162" t="str">
+        <x:v>Kodak / Kodak Alaris / фотолаборатории</x:v>
+      </x:c>
+      <x:c r="G162" t="str">
+        <x:v>KODAK FLEXICOLOR Chemicals и аналогичные системы закрепляют C-41 как универсальный лабораторный процесс для совместимых цветных негативных плёнок разных производителей.</x:v>
+      </x:c>
+      <x:c r="H162" t="str">
+        <x:v>Фотохимия</x:v>
+      </x:c>
+      <x:c r="I162" t="str">
+        <x:v>KODAK FLEXICOLOR / C-41 compatible workflow</x:v>
+      </x:c>
+      <x:c r="J162" t="str">
+        <x:v>Цветная плёнка становится сервисной системой: не обязательно знать всю химию, чтобы понимать, что результат зависит от стабильного стандарта обработки.</x:v>
+      </x:c>
+      <x:c r="K162" t="str">
+        <x:v>Процесс C-41 как лабораторный стандарт</x:v>
+      </x:c>
+      <x:c r="L162" t="str">
+        <x:v>Минилабы, профессиональные лаборатории и домашние C-41 наборы</x:v>
+      </x:c>
+      <x:c r="M162" t="str">
+        <x:v>Распространение / коммерциализация</x:v>
+      </x:c>
+      <x:c r="N162" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O162" t="str">
+        <x:v>PL-016</x:v>
+      </x:c>
+      <x:c r="P162" t="str">
+        <x:v>SRC-127</x:v>
+      </x:c>
+      <x:c r="Q162" t="str">
+        <x:v>Kodak Alaris — Chemicals: Color Negative Film Processing Cycles (C-41)</x:v>
+      </x:c>
+      <x:c r="R162" t="str">
+        <x:v>https://www.kodakprofessional.com/en-gb/taxonomy/term/245</x:v>
+      </x:c>
+      <x:c r="S162" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T162" t="str">
+        <x:v>Пояснить отличие от ч/б: C-41 гораздо чувствительнее к температуре и стандарту процесса, поэтому цвет чаще отдавали в лабораторию.</x:v>
+      </x:c>
+      <x:c r="U162" t="str">
+        <x:v>Цветная лаборатория: термостат, C-41 химия, кассеты разных брендов и одинаковый маршрут обработки.</x:v>
+      </x:c>
+      <x:c r="V162" t="str">
+        <x:v>#PL016 #Flexicolor #C41 #photolab #processing</x:v>
+      </x:c>
+      <x:c r="W162"/>
+      <x:c r="X162"/>
+      <x:c r="Y162" t="str">
+        <x:v>Цветная негативная плёнка / лабораторный стандарт</x:v>
+      </x:c>
+      <x:c r="Z162" t="str">
+        <x:v>Распространение / коммерциализация</x:v>
+      </x:c>
+      <x:c r="AA162"/>
+    </x:row>
+    <x:row r="163" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A163" t="str">
+        <x:v>PL-HIST-0162</x:v>
+      </x:c>
+      <x:c r="B163" t="str">
+        <x:v>XX–XXI век</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D163" t="str">
+        <x:v>глобально</x:v>
+      </x:c>
+      <x:c r="E163" t="str">
+        <x:v>распределённый процесс</x:v>
+      </x:c>
+      <x:c r="F163" t="str">
+        <x:v>Фотографы и производители плёнки</x:v>
+      </x:c>
+      <x:c r="G163" t="str">
+        <x:v>Цветная негативная плёнка ценится за практичность: она рассчитана на печать и сканирование, даёт гибкость цвета и обычно терпимее к небольшим ошибкам экспозиции, чем слайд.</x:v>
+      </x:c>
+      <x:c r="H163" t="str">
+        <x:v>Цвет</x:v>
+      </x:c>
+      <x:c r="I163" t="str">
+        <x:v>Color negative exposure latitude / print flexibility</x:v>
+      </x:c>
+      <x:c r="J163" t="str">
+        <x:v>Фотограф получает более прощающий материал для повседневной съёмки: особенно важно для семьи, улицы, путешествий и портрета.</x:v>
+      </x:c>
+      <x:c r="K163" t="str">
+        <x:v>C-41 как устойчивый стандарт обработки</x:v>
+      </x:c>
+      <x:c r="L163" t="str">
+        <x:v>Слайдовая плёнка как более требовательный материал в PL-017</x:v>
+      </x:c>
+      <x:c r="M163" t="str">
+        <x:v>Главная линия / практическое управление</x:v>
+      </x:c>
+      <x:c r="N163" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O163" t="str">
+        <x:v>PL-016</x:v>
+      </x:c>
+      <x:c r="P163" t="str">
+        <x:v>SRC-128</x:v>
+      </x:c>
+      <x:c r="Q163" t="str">
+        <x:v>Kodak Professional — Color Films</x:v>
+      </x:c>
+      <x:c r="R163" t="str">
+        <x:v>https://kodakprofessional.com/photographers/film/color</x:v>
+      </x:c>
+      <x:c r="S163" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T163" t="str">
+        <x:v>Важно не противопоставлять грубо: цветной негатив гибче, а слайд точнее показывает итог сразу и требует аккуратной экспозиции.</x:v>
+      </x:c>
+      <x:c r="U163" t="str">
+        <x:v>Сравнение двух полосок: цветной негатив с запасом по экспозиции и слайд с узким допуском.</x:v>
+      </x:c>
+      <x:c r="V163" t="str">
+        <x:v>#PL016 #exposure-latitude #color-negative #print-film</x:v>
+      </x:c>
+      <x:c r="W163" t="str">
+        <x:v>Формулировать аккуратно: конкретная широта зависит от плёнки, экспозиции, проявки и сканирования.</x:v>
+      </x:c>
+      <x:c r="X163"/>
+      <x:c r="Y163" t="str">
+        <x:v>Цветная негативная плёнка / экспозиционная гибкость</x:v>
+      </x:c>
+      <x:c r="Z163" t="str">
+        <x:v>Применение / жанр</x:v>
+      </x:c>
+      <x:c r="AA163"/>
+    </x:row>
+    <x:row r="164" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A164" t="str">
+        <x:v>PL-HIST-0163</x:v>
+      </x:c>
+      <x:c r="B164" t="str">
+        <x:v>1990-е – XXI век</x:v>
+      </x:c>
+      <x:c r="C164" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D164" t="str">
+        <x:v>глобально</x:v>
+      </x:c>
+      <x:c r="E164" t="str">
+        <x:v>профессиональная и любительская фотография</x:v>
+      </x:c>
+      <x:c r="F164" t="str">
+        <x:v>Kodak Professional / фотографы</x:v>
+      </x:c>
+      <x:c r="G164" t="str">
+        <x:v>Современные профессиональные цветные негативные плёнки вроде PORTRA показывают, что цветной негатив остаётся не только любительским, но и профессиональным материалом.</x:v>
+      </x:c>
+      <x:c r="H164" t="str">
+        <x:v>Цвет</x:v>
+      </x:c>
+      <x:c r="I164" t="str">
+        <x:v>KODAK PROFESSIONAL PORTRA / modern color negative film</x:v>
+      </x:c>
+      <x:c r="J164" t="str">
+        <x:v>Цветной негатив закрепляет собственный визуальный язык: мягкие тона кожи, управляемый контраст, сканируемость и большой запас для печати.</x:v>
+      </x:c>
+      <x:c r="K164" t="str">
+        <x:v>Массовая C-41 система и цветная лаборатория</x:v>
+      </x:c>
+      <x:c r="L164" t="str">
+        <x:v>Современный гибридный процесс: плёнка → проявка → скан → печать</x:v>
+      </x:c>
+      <x:c r="M164" t="str">
+        <x:v>Главная линия / визуальный язык</x:v>
+      </x:c>
+      <x:c r="N164" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O164" t="str">
+        <x:v>PL-016</x:v>
+      </x:c>
+      <x:c r="P164" t="str">
+        <x:v>SRC-129</x:v>
+      </x:c>
+      <x:c r="Q164" t="str">
+        <x:v>Kodak Professional — PORTRA 400 Film</x:v>
+      </x:c>
+      <x:c r="R164" t="str">
+        <x:v>https://kodakprofessional.com/photographers/film/color/kodak-professional-portra-400-film/516</x:v>
+      </x:c>
+      <x:c r="S164" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T164" t="str">
+        <x:v>PORTRA можно использовать как современный пример: цветной негатив сегодня жив не как ностальгия, а как осознанный выбор тона и пластики.</x:v>
+      </x:c>
+      <x:c r="U164" t="str">
+        <x:v>Кассеты Portra, контактные отпечатки и портрет с мягким естественным цветом.</x:v>
+      </x:c>
+      <x:c r="V164" t="str">
+        <x:v>#PL016 #Portra #color-negative #portrait #hybrid-workflow</x:v>
+      </x:c>
+      <x:c r="W164"/>
+      <x:c r="X164"/>
+      <x:c r="Y164" t="str">
+        <x:v>Цветная негативная плёнка / современный профессиональный материал</x:v>
+      </x:c>
+      <x:c r="Z164" t="str">
+        <x:v>Применение / жанр</x:v>
+      </x:c>
+      <x:c r="AA164"/>
+    </x:row>
+    <x:row r="165" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A165" t="str">
+        <x:v>PL-HIST-0164</x:v>
+      </x:c>
+      <x:c r="B165" t="str">
+        <x:v>XX–XXI век</x:v>
+      </x:c>
+      <x:c r="C165" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D165" t="str">
+        <x:v>глобально</x:v>
+      </x:c>
+      <x:c r="E165" t="str">
+        <x:v>архивы и лаборатории</x:v>
+      </x:c>
+      <x:c r="F165" t="str">
+        <x:v>Архивисты, музеи и фотолаборатории</x:v>
+      </x:c>
+      <x:c r="G165" t="str">
+        <x:v>Цветные негативы требуют внимательного хранения: цветные красители и плёночная основа стареют, поэтому для важных материалов рекомендуют холодное хранение и архивные оболочки.</x:v>
+      </x:c>
+      <x:c r="H165" t="str">
+        <x:v>Цвет</x:v>
+      </x:c>
+      <x:c r="I165" t="str">
+        <x:v>Color film preservation / dye image stability</x:v>
+      </x:c>
+      <x:c r="J165" t="str">
+        <x:v>Цветная плёнка даёт массовую память XX века, но эта память хрупкая: негатив нужно не только проявить, но и сохранить.</x:v>
+      </x:c>
+      <x:c r="K165" t="str">
+        <x:v>Цветной негатив как семейный и профессиональный архив</x:v>
+      </x:c>
+      <x:c r="L165" t="str">
+        <x:v>Будущие уроки о сканировании, печати и хранении плёнки</x:v>
+      </x:c>
+      <x:c r="M165" t="str">
+        <x:v>Применение / жанр</x:v>
+      </x:c>
+      <x:c r="N165" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O165" t="str">
+        <x:v>PL-016</x:v>
+      </x:c>
+      <x:c r="P165" t="str">
+        <x:v>SRC-130</x:v>
+      </x:c>
+      <x:c r="Q165" t="str">
+        <x:v>National Archives — Film-Based Negatives and Positives</x:v>
+      </x:c>
+      <x:c r="R165" t="str">
+        <x:v>https://www.archives.gov/preservation/holdings-maintenance/film-based</x:v>
+      </x:c>
+      <x:c r="S165" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T165" t="str">
+        <x:v>Финальный мост: цветной негатив — это архив. Если его потерять, потеряется не один отпечаток, а источник для множества будущих интерпретаций.</x:v>
+      </x:c>
+      <x:c r="U165" t="str">
+        <x:v>Архивная коробка с цветными негативами в прозрачных рукавах; рядом сканер и отпечаток.</x:v>
+      </x:c>
+      <x:c r="V165" t="str">
+        <x:v>#PL016 #color-negative #archive #preservation #film-storage</x:v>
+      </x:c>
+      <x:c r="W165"/>
+      <x:c r="X165"/>
+      <x:c r="Y165" t="str">
+        <x:v>Цветная негативная плёнка / хранение и архив</x:v>
+      </x:c>
+      <x:c r="Z165" t="str">
+        <x:v>Применение / жанр</x:v>
+      </x:c>
+      <x:c r="AA165"/>
+    </x:row>
     <x:row r="166" s="46" customFormat="1" ht="17" customHeight="1"/>
     <x:row r="167" s="46" customFormat="1" ht="17" customHeight="1"/>
     <x:row r="168" s="46" customFormat="1" ht="17" customHeight="1"/>
@@ -20803,7 +21654,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra758634259c04f97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7808e7c7a4c44a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20907,20 +21758,16 @@
         </x:is>
       </x:c>
       <x:c r="B4" s="50" t="str">
-        <x:v>серебряные соли, потемнение от света, фиксация, желатиновые эмульсии, скрытое изображение, проявление, чувствительность, спектральная чувствительность и зерно</x:v>
+        <x:v>серебряные соли, желатиновые эмульсии, скрытое изображение, проявление, чувствительность, спектральная чувствительность, зерно, цветные слои, color couplers, C-41</x:v>
       </x:c>
       <x:c r="C4" s="50" t="str">
-        <x:v>PL-002 / PL-006 / PL-011 / PL-012 / PL-015</x:v>
-      </x:c>
-      <x:c r="D4" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">жёлтый</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Химическая половина рождения фотографии.</x:t>
-        </x:is>
+        <x:v>PL-002 / PL-006 / PL-011 / PL-012 / PL-015 / PL-016</x:v>
+      </x:c>
+      <x:c r="D4" s="50" t="str">
+        <x:v>жёлтый</x:v>
+      </x:c>
+      <x:c r="E4" s="50" t="str">
+        <x:v>Химическая половина рождения фотографии: от серебряного изображения к цветным красителям.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="46" customFormat="1" ht="21" customHeight="1">
@@ -21011,20 +21858,16 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="50" t="str">
-        <x:v>бумажный негатив, калотип, стеклянный негатив, сухая пластина, плёночный негатив, чёрно-белый негатив, позитивный отпечаток</x:v>
+        <x:v>бумажный негатив, калотип, стеклянный негатив, сухая пластина, плёночный негатив, чёрно-белый негатив, цветной негатив, позитивный отпечаток</x:v>
       </x:c>
       <x:c r="C8" s="50" t="str">
-        <x:v>PL-004 / PL-006 / PL-013 / PL-014 / PL-015</x:v>
-      </x:c>
-      <x:c r="D8" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">зелёный тёмный</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Главная идея, которая победила исторически.</x:t>
-        </x:is>
+        <x:v>PL-004 / PL-006 / PL-013 / PL-014 / PL-015 / PL-016</x:v>
+      </x:c>
+      <x:c r="D8" s="50" t="str">
+        <x:v>зелёный тёмный</x:v>
+      </x:c>
+      <x:c r="E8" s="50" t="str">
+        <x:v>Главная идея, которая победила исторически: негатив становится матрицей для будущего позитива.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="46" customFormat="1" ht="21" customHeight="1">
@@ -21057,20 +21900,16 @@
         </x:is>
       </x:c>
       <x:c r="B10" s="50" t="str">
-        <x:v>salt print, albumen print, gelatin silver print, POP/DOP, chromogenic print, фотокнига, лабораторная и сервисная печать</x:v>
+        <x:v>salt print, albumen print, gelatin silver print, POP/DOP, chromogenic print, фотокнига, лабораторная и сервисная печать, цветная печать с негатива</x:v>
       </x:c>
       <x:c r="C10" s="50" t="str">
-        <x:v>PL-004 / PL-013 / PL-014 / PL-015</x:v>
-      </x:c>
-      <x:c r="D10" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">оранжевый</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ветка распространения изображений.</x:t>
-        </x:is>
+        <x:v>PL-004 / PL-013 / PL-014 / PL-015 / PL-016</x:v>
+      </x:c>
+      <x:c r="D10" s="50" t="str">
+        <x:v>оранжевый</x:v>
+      </x:c>
+      <x:c r="E10" s="50" t="str">
+        <x:v>Ветка распространения изображений: от единичного отпечатка к массовому фотосервису.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="46" customFormat="1" ht="21" customHeight="1">
@@ -21133,25 +21972,17 @@
           <x:t xml:space="preserve">Цвет</x:t>
         </x:is>
       </x:c>
-      <x:c r="B13" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ранний цвет, Autochrome, Kodachrome, chromogenic print</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">будущие PL / PL-014</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">радужный</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">В v0.1 только ранний ориентир.</x:t>
-        </x:is>
+      <x:c r="B13" s="50" t="str">
+        <x:v>ранний цвет, Autochrome, Kodachrome, Kodacolor, цветная негативная плёнка, chromogenic print, C-41</x:v>
+      </x:c>
+      <x:c r="C13" s="50" t="str">
+        <x:v>PL-014 / PL-016 / будущие PL</x:v>
+      </x:c>
+      <x:c r="D13" s="50" t="str">
+        <x:v>радужный</x:v>
+      </x:c>
+      <x:c r="E13" s="50" t="str">
+        <x:v>Цветная фотография как отдельная технологическая и визуальная линия.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="46" customFormat="1" ht="21" customHeight="1">
@@ -21184,7 +22015,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Readbadd2eb414e9d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb01cec759f6342d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21703,26 +22534,46 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
+        <x:v>PL-016</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Цветная негативная плёнка</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>PL-HIST-0154…0164</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Цветной негатив — это не готовая картинка, а цветная матрица: несколько слоёв, красители, оранжевая маска и процесс C-41 превращают сцену в материал для печати или сканирования.</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>основа заполнена</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>https://t.me/photolab_vf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
         <x:v>будущие PL</x:v>
       </x:c>
-      <x:c r="B17" t="str">
-        <x:v>Расширение после PL-015</x:v>
-      </x:c>
-      <x:c r="C17" t="str">
-        <x:v>Цветная негативная плёнка, слайд, ISO, зерно, широта</x:v>
-      </x:c>
-      <x:c r="D17" t="str">
-        <x:v>После чёрно-белой плёнки курс переходит к цветной негативной системе, слайду и практическим параметрам материала.</x:v>
-      </x:c>
-      <x:c r="E17" t="str">
+      <x:c r="B18" t="str">
+        <x:v>Расширение после PL-016</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Слайдовая плёнка, ISO, зерно, широта</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>После цветной негативной системы курс переходит к слайдовой плёнке и практическим параметрам материала: ISO, зерно и экспозиционная широта.</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
         <x:v>планируется</x:v>
       </x:c>
-      <x:c r="F17"/>
+      <x:c r="F18"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdefa223759e4a6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1b479904f144245"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24868,10 +25719,197 @@
         <x:v>архивный консервационный источник</x:v>
       </x:c>
     </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>SRC-120</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>Kodak — Photography History</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>https://www.kodak.com/en/company/page/photography-history/</x:v>
+      </x:c>
+      <x:c r="D121" t="str">
+        <x:v>1942 KODACOLOR Film announced as the world's first true color negative film for still photography</x:v>
+      </x:c>
+      <x:c r="E121" t="str">
+        <x:v>официальная история Kodak</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>SRC-121</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>Library of Congress — Dye coupler negatives</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>https://www.loc.gov/pictures/item/tgm003415/</x:v>
+      </x:c>
+      <x:c r="D122" t="str">
+        <x:v>Kodacolor launched in 1942 as first commercial color negative process in the United States; Ektacolor 1947; dye coupler negatives</x:v>
+      </x:c>
+      <x:c r="E122" t="str">
+        <x:v>библиотечный справочник терминов</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>SRC-122</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>National Archives — Identifying Motion Picture Film Formats</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>https://www.archives.gov/preservation/formats/motion-picture-film-identify-formats.html</x:v>
+      </x:c>
+      <x:c r="D123" t="str">
+        <x:v>modern color processes embed dyes/pigments in layers producing cyan, magenta and yellow; color negatives often have orange cast</x:v>
+      </x:c>
+      <x:c r="E123" t="str">
+        <x:v>архивный консервационный источник</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>SRC-123</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>Kodak — Essential Reference Guide for Filmmakers</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>https://www.kodak.com/content/products-brochures/Film/kodak-essential-reference-guide-for-filmmakers.pdf</x:v>
+      </x:c>
+      <x:c r="D124" t="str">
+        <x:v>color emulsion layers, color couplers and subtractive dye formation in color film</x:v>
+      </x:c>
+      <x:c r="E124" t="str">
+        <x:v>официальный технический справочник Kodak</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>SRC-124</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>Kodak — Processing KODAK Motion Picture Films, Module 7</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>https://www.kodak.com/content/products-brochures/Film/Processing-KODAK-Motion-Picture-Films-Module-7.pdf</x:v>
+      </x:c>
+      <x:c r="D125" t="str">
+        <x:v>residual colored couplers and dye absorptions form masking behavior in color negative film systems</x:v>
+      </x:c>
+      <x:c r="E125" t="str">
+        <x:v>официальный технический документ Kodak</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>SRC-125</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>National Archives — Photographic Prints in the Still Picture Branch</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>https://www.archives.gov/research/still-pictures/still-picture-photographic-prints</x:v>
+      </x:c>
+      <x:c r="D126" t="str">
+        <x:v>chromogenic prints are subtractive color processes based on dye couplers forming cyan, magenta or yellow dyes</x:v>
+      </x:c>
+      <x:c r="E126" t="str">
+        <x:v>архивный образовательный источник</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str">
+        <x:v>SRC-126</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>Kodak — C-41 Color Negative Control Strips</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>https://www.kodak.com/en/motion/page/c-41-control-strips/</x:v>
+      </x:c>
+      <x:c r="D127" t="str">
+        <x:v>KODAK Control Strips, Process C-41 monitor processing of color negative films in KODAK FLEXICOLOR Chemicals</x:v>
+      </x:c>
+      <x:c r="E127" t="str">
+        <x:v>официальный источник Kodak по C-41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str">
+        <x:v>SRC-127</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>Kodak Alaris — Chemicals: Color Negative Film Processing Cycles (C-41)</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>https://www.kodakprofessional.com/en-gb/taxonomy/term/245</x:v>
+      </x:c>
+      <x:c r="D128" t="str">
+        <x:v>KODAK FLEXICOLOR Chemicals are designed for processing all KODAK Color Negative Films and other compatible films</x:v>
+      </x:c>
+      <x:c r="E128" t="str">
+        <x:v>официальный источник Kodak Alaris</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str">
+        <x:v>SRC-128</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>Kodak Professional — Color Films</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>https://kodakprofessional.com/photographers/film/color</x:v>
+      </x:c>
+      <x:c r="D129" t="str">
+        <x:v>current Kodak Professional color negative films and their practical photographic roles</x:v>
+      </x:c>
+      <x:c r="E129" t="str">
+        <x:v>официальная страница Kodak Professional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str">
+        <x:v>SRC-129</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>Kodak Professional — PORTRA 400 Film</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>https://kodakprofessional.com/photographers/film/color/kodak-professional-portra-400-film/516</x:v>
+      </x:c>
+      <x:c r="D130" t="str">
+        <x:v>KODAK PROFESSIONAL PORTRA 400 as high-speed color negative film with fine grain and portrait-oriented color performance</x:v>
+      </x:c>
+      <x:c r="E130" t="str">
+        <x:v>официальная страница продукта Kodak Professional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="str">
+        <x:v>SRC-130</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>National Archives — Film-Based Negatives and Positives</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>https://www.archives.gov/preservation/holdings-maintenance/film-based</x:v>
+      </x:c>
+      <x:c r="D131" t="str">
+        <x:v>storage and preservation guidance for film-based negatives and positives including color film and cold storage recommendations</x:v>
+      </x:c>
+      <x:c r="E131" t="str">
+        <x:v>архивный консервационный источник</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38d7abda4fb14a3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4b10c04987d4abd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25380,7 +26418,7 @@
       <x:c r="A17" s="4" t="n"/>
       <x:c r="B17" s="4" t="n"/>
       <x:c r="C17" s="50" t="str">
-        <x:v>будущие PL</x:v>
+        <x:v>PL-016</x:v>
       </x:c>
       <x:c r="D17" s="4" t="n"/>
       <x:c r="E17" s="4" t="n"/>
@@ -25396,7 +26434,7 @@
       <x:c r="A18" s="4" t="n"/>
       <x:c r="B18" s="4" t="n"/>
       <x:c r="C18" s="50" t="str">
-        <x:v>межурочный узел</x:v>
+        <x:v>будущие PL</x:v>
       </x:c>
       <x:c r="D18" s="4" t="n"/>
       <x:c r="E18" s="4" t="n"/>
@@ -25412,7 +26450,7 @@
       <x:c r="A19" s="4" t="n"/>
       <x:c r="B19" s="4" t="n"/>
       <x:c r="C19" s="4" t="str">
-        <x:v>проверить</x:v>
+        <x:v>межурочный узел</x:v>
       </x:c>
       <x:c r="D19" s="4" t="n"/>
       <x:c r="E19" s="4" t="n"/>
@@ -25427,7 +26465,9 @@
     <x:row r="20" s="46" customFormat="1" ht="20" customHeight="1">
       <x:c r="A20" s="4" t="n"/>
       <x:c r="B20" s="4" t="n"/>
-      <x:c r="C20" s="4" t="n"/>
+      <x:c r="C20" s="4" t="str">
+        <x:v>проверить</x:v>
+      </x:c>
       <x:c r="D20" s="4" t="n"/>
       <x:c r="E20" s="4" t="n"/>
       <x:c r="F20" s="4" t="n"/>
@@ -26366,6 +27406,61 @@
     <x:row r="130">
       <x:c r="H130" t="str">
         <x:v>Чёрно-белая плёнка / chromogenic B&amp;W</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="H131" t="str">
+        <x:v>Цветная негативная плёнка / Kodacolor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="H132" t="str">
+        <x:v>Цветная негативная плёнка / негатив-позитив</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="H133" t="str">
+        <x:v>Цветная негативная плёнка / слои красителей</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="H134" t="str">
+        <x:v>Цветная негативная плёнка / color couplers</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="H135" t="str">
+        <x:v>Цветная негативная плёнка / оранжевая маска</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="H136" t="str">
+        <x:v>Цветная негативная плёнка / печать позитивов</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="H137" t="str">
+        <x:v>Цветная негативная плёнка / C-41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="H138" t="str">
+        <x:v>Цветная негативная плёнка / лабораторный стандарт</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="H139" t="str">
+        <x:v>Цветная негативная плёнка / экспозиционная гибкость</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="H140" t="str">
+        <x:v>Цветная негативная плёнка / современный профессиональный материал</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="H141" t="str">
+        <x:v>Цветная негативная плёнка / хранение и архив</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -26383,7 +27478,7 @@
   <x:sheetData>
     <x:row r="1" s="46" customFormat="1" ht="40" customHeight="1">
       <x:c r="A1" s="32" t="str">
-        <x:v>PHOTO LAB — History Map Master v0.12</x:v>
+        <x:v>PHOTO LAB — History Map Master v0.13</x:v>
       </x:c>
       <x:c r="B1" s="20" t="n"/>
     </x:row>
@@ -26400,13 +27495,11 @@
       </x:c>
     </x:row>
     <x:row r="3" s="46" customFormat="1" ht="21" customHeight="1">
-      <x:c r="A3" s="56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Охват v0.11</x:t>
-        </x:is>
+      <x:c r="A3" s="56" t="str">
+        <x:v>Охват v0.13</x:v>
       </x:c>
       <x:c r="B3" s="54" t="str">
-        <x:v>От оптических предпосылок камеры-обскуры до Leica I и Модуля 2: плёнка как материал, эмульсия, негатив, позитив и чёрно-белая плёнка; основа для PL-001–PL-015.</x:v>
+        <x:v>От оптических предпосылок камеры-обскуры до Leica I и Модуля 2: плёнка как материал, эмульсия, негатив, позитив, чёрно-белая и цветная негативная плёнка; основа для PL-001–PL-016.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="46" customFormat="1" ht="21" customHeight="1">
@@ -26452,7 +27545,7 @@
         </x:is>
       </x:c>
       <x:c r="B7" s="54" t="str">
-        <x:v>Ветка развития = одна из 13 крупных линий из 02_Branches. Для PL-015 чёрно-белая плёнка связана с «Фотохимия», «Негатив-позитив», «Фиксаж / терминология» и практической обработкой материала.</x:v>
+        <x:v>Ветка развития = одна из 13 крупных линий из 02_Branches. Для PL-016 цветная негативная плёнка связана с «Цвет», «Фотохимия», «Негатив-позитив» и «Печать / тиражирование».</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="46" customFormat="1" ht="21" customHeight="1">
@@ -26462,7 +27555,7 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="54" t="str">
-        <x:v>Подветка (детали) = уточнение внутри крупной ветки: химия, камера, распространение, фотокнига, медицинское применение, сухие пластины, рулонная плёнка, Brownie, 35 мм, Leica I, структура плёнки, эмульсия, негатив/позитив, позитив, чёрно-белая плёнка и т.п.</x:v>
+        <x:v>Подветка (детали) = уточнение внутри крупной ветки: химия, камера, распространение, фотокнига, медицинское применение, сухие пластины, рулонная плёнка, Brownie, 35 мм, Leica I, структура плёнки, эмульсия, негатив/позитив, позитив, чёрно-белая плёнка, цветная негативная плёнка и т.п.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="46" customFormat="1" ht="17" customHeight="1">
@@ -26639,10 +27732,18 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
+        <x:v>Что изменено в v0.13</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>Заполнен PL-016: добавлены PL-HIST-0154…0164 по цветной негативной плёнке — Kodacolor 1942, цветная система негатив→позитив, слои CMY, color couplers, оранжевая маска, chromogenic print, C-41, Flexicolor, экспозиционная гибкость, современная Portra и архивное хранение цветных негативов. Добавлены источники SRC-120…SRC-130 и флагманский узел PL-HIST-0154.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
         <x:v>Следующий шаг</x:v>
       </x:c>
-      <x:c r="B24" t="str">
-        <x:v>PL-016: цветная негативная плёнка — перейти от серебряного ч/б изображения к цветным слоям, маске, C-41 и логике цветного негатива.</x:v>
+      <x:c r="B25" t="str">
+        <x:v>PL-017: слайдовая плёнка — объяснить цветную позитивную прозрачность, reversal-процесс, точность экспозиции и отличие от цветного негатива.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Dashboard" sheetId="1" r:id="R098f4fefea5f4cc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Master_Facts" sheetId="2" r:id="R5f3a5bd46c744089"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Branches" sheetId="3" r:id="R9a64e19e61714f20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Lessons_Map" sheetId="4" r:id="Rd57601f432f84380"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Sources" sheetId="5" r:id="Ree9092e357514b39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Lists" sheetId="6" r:id="R3f6baed17f894a74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="7" r:id="R867ad533b46846b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Dashboard" sheetId="1" r:id="R4feec28623bd4783"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Master_Facts" sheetId="2" r:id="R6d17a2f109a345b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Branches" sheetId="3" r:id="R437fc1b3b1104f1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Lessons_Map" sheetId="4" r:id="Ra5b5bc7d1d3447d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Sources" sheetId="5" r:id="Ra13b0e51596a4895"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Lists" sheetId="6" r:id="R5dacadedde4c4179"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="7" r:id="R6dedb731bc8841ae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -112,7 +112,7 @@
     <x:xf numFmtId="9" fontId="9" fillId="0" borderId="2"/>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="59">
+  <x:cellXfs count="72">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="6" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -278,6 +278,43 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -768,7 +805,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1da690355b344fe3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re6b44dfac77641ea"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -985,7 +1022,7 @@
   <x:sheetData>
     <x:row r="1" s="46" customFormat="1" ht="40" customHeight="1">
       <x:c r="A1" s="31" t="str">
-        <x:v>PHOTO LAB — Master Timeline v0.13</x:v>
+        <x:v>PHOTO LAB — Master Timeline v0.14</x:v>
       </x:c>
       <x:c r="B1" s="20" t="n"/>
       <x:c r="C1" s="20" t="n"/>
@@ -1020,7 +1057,7 @@
       </x:c>
       <x:c r="B3" s="55" t="n">
         <x:f>COUNTA('01_Master_Facts'!$A$2:$A$500)</x:f>
-        <x:v>164</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C3" s="54" t="inlineStr">
         <x:is>
@@ -1038,7 +1075,7 @@
       </x:c>
       <x:c r="B4" s="55" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$N$2:$N$500,5)</x:f>
-        <x:v>73</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C4" s="54" t="inlineStr">
         <x:is>
@@ -1050,11 +1087,11 @@
     </x:row>
     <x:row r="5" s="46" customFormat="1" ht="21" customHeight="1">
       <x:c r="A5" s="54" t="str">
-        <x:v>Узлов для PL-001–PL-016</x:v>
+        <x:v>Узлов для PL-001–PL-017</x:v>
       </x:c>
       <x:c r="B5" s="55" t="n">
-        <x:f>SUM(COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-001"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-002"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-003"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-004"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-005"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-006"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-007"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-008"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-009"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-010"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-011"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-012"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-013"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-014"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-015"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-016"))</x:f>
-        <x:v>153</x:v>
+        <x:f>SUM(COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-001"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-002"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-003"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-004"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-005"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-006"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-007"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-008"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-009"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-010"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-011"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-012"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-013"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-014"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-015"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-016"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-017"))</x:f>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C5" s="54" t="str">
         <x:v>Без будущих PL и межурочных узлов</x:v>
@@ -1070,7 +1107,7 @@
       </x:c>
       <x:c r="B6" s="55" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$W$2:$W$500,"&lt;&gt;")</x:f>
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="54" t="inlineStr">
         <x:is>
@@ -1167,7 +1204,7 @@
       </x:c>
       <x:c r="B12" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A12)</x:f>
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C12" s="49" t="n"/>
       <x:c r="D12" s="50" t="inlineStr">
@@ -1356,7 +1393,7 @@
       </x:c>
       <x:c r="B21" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A21)</x:f>
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C21" s="49" t="n"/>
       <x:c r="D21" s="49" t="inlineStr">
@@ -1377,7 +1414,7 @@
       </x:c>
       <x:c r="B22" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A22)</x:f>
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="49" t="n"/>
       <x:c r="D22" s="49" t="inlineStr">
@@ -1431,11 +1468,11 @@
       <x:c r="B26" s="50" t="n"/>
       <x:c r="C26" s="49" t="n"/>
       <x:c r="D26" s="49" t="str">
-        <x:v>будущие PL</x:v>
+        <x:v>PL-017</x:v>
       </x:c>
       <x:c r="E26" s="49" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D26)</x:f>
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="27" s="46" customFormat="1" ht="21" customHeight="1">
@@ -1443,11 +1480,11 @@
       <x:c r="B27" s="50"/>
       <x:c r="C27" s="49" t="n"/>
       <x:c r="D27" s="49" t="str">
-        <x:v>межурочный узел</x:v>
+        <x:v>будущие PL</x:v>
       </x:c>
       <x:c r="E27" s="49" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D27)</x:f>
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="28" s="46" customFormat="1" ht="21" customHeight="1">
@@ -1455,11 +1492,11 @@
       <x:c r="B28" s="50"/>
       <x:c r="C28" s="49" t="n"/>
       <x:c r="D28" s="49" t="str">
-        <x:v>проверить</x:v>
+        <x:v>межурочный узел</x:v>
       </x:c>
       <x:c r="E28" s="49" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D28)</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="29" s="46" customFormat="1" ht="21" customHeight="1">
@@ -1470,8 +1507,13 @@
         <x:v>Количество узлов</x:v>
       </x:c>
       <x:c r="C29" s="49" t="n"/>
-      <x:c r="D29" s="49" t="n"/>
-      <x:c r="E29" s="49" t="n"/>
+      <x:c r="D29" s="49" t="str">
+        <x:v>проверить</x:v>
+      </x:c>
+      <x:c r="E29" s="49" t="n">
+        <x:f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D29)</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" s="46" customFormat="1" ht="21" customHeight="1">
       <x:c r="A30" s="50" t="str">
@@ -1491,7 +1533,7 @@
       </x:c>
       <x:c r="B31" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A31)</x:f>
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C31" s="49" t="n"/>
       <x:c r="D31" s="49" t="n"/>
@@ -1539,7 +1581,7 @@
       </x:c>
       <x:c r="B35" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A35)</x:f>
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C35" s="49" t="n"/>
       <x:c r="D35" s="49" t="n"/>
@@ -1563,7 +1605,7 @@
       </x:c>
       <x:c r="B37" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A37)</x:f>
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C37" s="49" t="n"/>
       <x:c r="D37" s="49" t="n"/>
@@ -1587,7 +1629,7 @@
       </x:c>
       <x:c r="B39" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A39)</x:f>
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C39" s="49" t="n"/>
       <x:c r="D39" s="49" t="n"/>
@@ -1599,7 +1641,7 @@
       </x:c>
       <x:c r="B40" s="50" t="n">
         <x:f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A40)</x:f>
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C40" s="49" t="n"/>
       <x:c r="D40" s="49" t="n"/>
@@ -1634,7 +1676,7 @@
     <x:mergeCell ref="A1:F1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a64b63413434ff9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ed72ac1543f4793"/>
 </x:worksheet>
 </file>
 
@@ -21263,17 +21305,873 @@
       </x:c>
       <x:c r="AA165"/>
     </x:row>
-    <x:row r="166" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="167" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="168" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="169" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="170" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="171" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="172" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="173" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="174" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="175" s="46" customFormat="1" ht="17" customHeight="1"/>
-    <x:row r="176" s="46" customFormat="1" ht="17" customHeight="1"/>
+    <x:row r="166" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A166" s="62" t="str">
+        <x:v>PL-HIST-0165</x:v>
+      </x:c>
+      <x:c r="B166" s="62" t="str">
+        <x:v>1907</x:v>
+      </x:c>
+      <x:c r="C166" s="62" t="str">
+        <x:v>год</x:v>
+      </x:c>
+      <x:c r="D166" s="62" t="str">
+        <x:v>Франция</x:v>
+      </x:c>
+      <x:c r="E166" s="62" t="str">
+        <x:v>Лион / Париж</x:v>
+      </x:c>
+      <x:c r="F166" s="62" t="str">
+        <x:v>Огюст и Луи Люмьер</x:v>
+      </x:c>
+      <x:c r="G166" s="62" t="str">
+        <x:v>Autochrome Lumière становится первым практически и коммерчески успешным способом цветной фотографии: изображение получается как прозрачный позитив, который нужно смотреть на просвет.</x:v>
+      </x:c>
+      <x:c r="H166" s="62" t="str">
+        <x:v>Цвет</x:v>
+      </x:c>
+      <x:c r="I166" s="62" t="str">
+        <x:v>Autochrome Lumière / color transparency plate</x:v>
+      </x:c>
+      <x:c r="J166" s="62" t="str">
+        <x:v>Цвет перестаёт быть ручной раскраской и становится фотографическим результатом, но пока остаётся уникальной прозрачностью, а не тиражируемым негативом.</x:v>
+      </x:c>
+      <x:c r="K166" s="62" t="str">
+        <x:v>Позитив и прямые позитивные процессы в PL-014</x:v>
+      </x:c>
+      <x:c r="L166" s="62" t="str">
+        <x:v>Рулонная цветная реверсивная плёнка и Kodachrome</x:v>
+      </x:c>
+      <x:c r="M166" s="62" t="str">
+        <x:v>Исторически важная ограниченная ветка</x:v>
+      </x:c>
+      <x:c r="N166" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O166" s="62" t="str">
+        <x:v>PL-017</x:v>
+      </x:c>
+      <x:c r="P166" s="62" t="str">
+        <x:v>SRC-131</x:v>
+      </x:c>
+      <x:c r="Q166" s="62" t="str">
+        <x:v>National Science and Media Museum — A short history of colour photography</x:v>
+      </x:c>
+      <x:c r="R166" s="62" t="str">
+        <x:v>https://www.scienceandmediamuseum.org.uk/objects-and-stories/history-colour-photography</x:v>
+      </x:c>
+      <x:c r="S166" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T166" s="62" t="str">
+        <x:v>Начать урок можно с парадокса: первый успешный массовый цвет был не негативом, а прозрачным позитивом для просмотра на свет.</x:v>
+      </x:c>
+      <x:c r="U166" s="62" t="str">
+        <x:v>Автохромная стеклянная пластина на световом столе; зёрна крахмала как цветной экран.</x:v>
+      </x:c>
+      <x:c r="V166" s="62" t="str">
+        <x:v>#PL017 #Autochrome #colour #transparency #Lumiere</x:v>
+      </x:c>
+      <x:c r="W166" s="62"/>
+      <x:c r="X166" s="62" t="str">
+        <x:v>45.7640, 4.8357</x:v>
+      </x:c>
+      <x:c r="Y166" s="62" t="str">
+        <x:v>Слайдовая плёнка / ранний цветной позитив</x:v>
+      </x:c>
+      <x:c r="Z166" s="62" t="str">
+        <x:v>Ключевой исторический узел</x:v>
+      </x:c>
+      <x:c r="AA166" s="62"/>
+    </x:row>
+    <x:row r="167" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A167" s="62" t="str">
+        <x:v>PL-HIST-0166</x:v>
+      </x:c>
+      <x:c r="B167" s="62" t="str">
+        <x:v>1923</x:v>
+      </x:c>
+      <x:c r="C167" s="62" t="str">
+        <x:v>год</x:v>
+      </x:c>
+      <x:c r="D167" s="62" t="str">
+        <x:v>США</x:v>
+      </x:c>
+      <x:c r="E167" s="62" t="str">
+        <x:v>Рочестер, Нью-Йорк</x:v>
+      </x:c>
+      <x:c r="F167" s="62" t="str">
+        <x:v>Eastman Kodak Company</x:v>
+      </x:c>
+      <x:c r="G167" s="62" t="str">
+        <x:v>Kodak вводит 16-мм reversal film на безопасной ацетатной основе вместе с камерой Cine-Kodak и проектором Kodascope.</x:v>
+      </x:c>
+      <x:c r="H167" s="62" t="str">
+        <x:v>Проекция / распространение</x:v>
+      </x:c>
+      <x:c r="I167" s="62" t="str">
+        <x:v>16mm reversal film / projected positive</x:v>
+      </x:c>
+      <x:c r="J167" s="62" t="str">
+        <x:v>Реверсивный материал закрепляет простую логику показа: снятая плёнка после обработки становится позитивом, который можно проецировать.</x:v>
+      </x:c>
+      <x:c r="K167" s="62" t="str">
+        <x:v>Autochrome как ранняя цветная прозрачность</x:v>
+      </x:c>
+      <x:c r="L167" s="62" t="str">
+        <x:v>Kodachrome как цветная реверсивная плёнка</x:v>
+      </x:c>
+      <x:c r="M167" s="62" t="str">
+        <x:v>Связь / переход</x:v>
+      </x:c>
+      <x:c r="N167" s="62" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O167" s="62" t="str">
+        <x:v>PL-017</x:v>
+      </x:c>
+      <x:c r="P167" s="62" t="str">
+        <x:v>SRC-133</x:v>
+      </x:c>
+      <x:c r="Q167" s="62" t="str">
+        <x:v>Kodak — 100 Years of 16mm Film</x:v>
+      </x:c>
+      <x:c r="R167" s="62" t="str">
+        <x:v>https://www.kodak.com/en/motion/page/100-years-of-16mm-film/</x:v>
+      </x:c>
+      <x:c r="S167" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T167" s="62" t="str">
+        <x:v>Это важный мост: слайдовая логика связана не только с фотоальбомом, но и с проектором, показом, лекцией, семейным просмотром.</x:v>
+      </x:c>
+      <x:c r="U167" s="62" t="str">
+        <x:v>Домашний проектор Kodascope, катушка 16 мм и световой конус на экран.</x:v>
+      </x:c>
+      <x:c r="V167" s="62" t="str">
+        <x:v>#PL017 #reversal #16mm #projection #Kodak</x:v>
+      </x:c>
+      <x:c r="W167" s="62"/>
+      <x:c r="X167" s="62" t="str">
+        <x:v>43.1566, -77.6088</x:v>
+      </x:c>
+      <x:c r="Y167" s="62" t="str">
+        <x:v>Слайдовая плёнка / reversal и проекция</x:v>
+      </x:c>
+      <x:c r="Z167" s="62" t="str">
+        <x:v>Связь / переход</x:v>
+      </x:c>
+      <x:c r="AA167" s="62"/>
+    </x:row>
+    <x:row r="168" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A168" s="62" t="str">
+        <x:v>PL-HIST-0167</x:v>
+      </x:c>
+      <x:c r="B168" s="62" t="str">
+        <x:v>1935</x:v>
+      </x:c>
+      <x:c r="C168" s="62" t="str">
+        <x:v>год</x:v>
+      </x:c>
+      <x:c r="D168" s="62" t="str">
+        <x:v>США</x:v>
+      </x:c>
+      <x:c r="E168" s="62" t="str">
+        <x:v>Рочестер, Нью-Йорк</x:v>
+      </x:c>
+      <x:c r="F168" s="62" t="str">
+        <x:v>Leopold Mannes, Leopold Godowsky Jr. / Eastman Kodak Company</x:v>
+      </x:c>
+      <x:c r="G168" s="62" t="str">
+        <x:v>Kodak представляет Kodachrome — первый коммерчески успешный любительский цветной фильм, первоначально для 16-мм кино.</x:v>
+      </x:c>
+      <x:c r="H168" s="62" t="str">
+        <x:v>Цвет</x:v>
+      </x:c>
+      <x:c r="I168" s="62" t="str">
+        <x:v>KODACHROME / color reversal film</x:v>
+      </x:c>
+      <x:c r="J168" s="62" t="str">
+        <x:v>Качественная цветная прозрачность становится промышленным продуктом: слайдовая эстетика начинает входить в массовую и профессиональную культуру.</x:v>
+      </x:c>
+      <x:c r="K168" s="62" t="str">
+        <x:v>Autochrome и ранние цветные прозрачности</x:v>
+      </x:c>
+      <x:c r="L168" s="62" t="str">
+        <x:v>Kodachrome 35 мм для фотокамер и слайдов</x:v>
+      </x:c>
+      <x:c r="M168" s="62" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N168" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O168" s="62" t="str">
+        <x:v>PL-017</x:v>
+      </x:c>
+      <x:c r="P168" s="62" t="str">
+        <x:v>SRC-134</x:v>
+      </x:c>
+      <x:c r="Q168" s="62" t="str">
+        <x:v>Kodak — History of Film</x:v>
+      </x:c>
+      <x:c r="R168" s="62" t="str">
+        <x:v>https://www.kodak.com/en/motion/page/chronology-of-film/</x:v>
+      </x:c>
+      <x:c r="S168" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T168" s="62" t="str">
+        <x:v>Флагман урока: Kodachrome сделал цветной слайд узнаваемым визуальным языком XX века.</x:v>
+      </x:c>
+      <x:c r="U168" s="62" t="str">
+        <x:v>Коробка Kodachrome, цветная прозрачность в рамке и яркий луч проектора.</x:v>
+      </x:c>
+      <x:c r="V168" s="62" t="str">
+        <x:v>#PL017 #Kodachrome #slide-film #color-reversal #Kodak</x:v>
+      </x:c>
+      <x:c r="W168" s="62"/>
+      <x:c r="X168" s="62" t="str">
+        <x:v>43.1566, -77.6088</x:v>
+      </x:c>
+      <x:c r="Y168" s="62" t="str">
+        <x:v>Слайдовая плёнка / Kodachrome</x:v>
+      </x:c>
+      <x:c r="Z168" s="62" t="str">
+        <x:v>Ключевой исторический узел</x:v>
+      </x:c>
+      <x:c r="AA168" s="62" t="str">
+        <x:v>да</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A169" s="62" t="str">
+        <x:v>PL-HIST-0168</x:v>
+      </x:c>
+      <x:c r="B169" s="62" t="str">
+        <x:v>1936</x:v>
+      </x:c>
+      <x:c r="C169" s="62" t="str">
+        <x:v>год</x:v>
+      </x:c>
+      <x:c r="D169" s="62" t="str">
+        <x:v>США / глобально</x:v>
+      </x:c>
+      <x:c r="E169" s="62" t="str">
+        <x:v>Рочестер, Нью-Йорк / фотомагазины</x:v>
+      </x:c>
+      <x:c r="F169" s="62" t="str">
+        <x:v>Eastman Kodak Company</x:v>
+      </x:c>
+      <x:c r="G169" s="62" t="str">
+        <x:v>После 16-мм Kodachrome появляются 35-мм слайды и 8-мм домашнее кино, что переносит цветную реверсивную логику в фотографическую и бытовую практику.</x:v>
+      </x:c>
+      <x:c r="H169" s="62" t="str">
+        <x:v>Цвет</x:v>
+      </x:c>
+      <x:c r="I169" s="62" t="str">
+        <x:v>35mm Kodachrome slides / 8mm home movies</x:v>
+      </x:c>
+      <x:c r="J169" s="62" t="str">
+        <x:v>Цветной позитив становится не только киноформатом, но и форматом маленькой фотографии: кадр можно монтировать в рамку, смотреть через лупу или проецировать.</x:v>
+      </x:c>
+      <x:c r="K169" s="62" t="str">
+        <x:v>Kodachrome 1935</x:v>
+      </x:c>
+      <x:c r="L169" s="62" t="str">
+        <x:v>Профессиональная и любительская культура цветных слайдов</x:v>
+      </x:c>
+      <x:c r="M169" s="62" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N169" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O169" s="62" t="str">
+        <x:v>PL-017</x:v>
+      </x:c>
+      <x:c r="P169" s="62" t="str">
+        <x:v>SRC-134</x:v>
+      </x:c>
+      <x:c r="Q169" s="62" t="str">
+        <x:v>Kodak — History of Film</x:v>
+      </x:c>
+      <x:c r="R169" s="62" t="str">
+        <x:v>https://www.kodak.com/en/motion/page/chronology-of-film/</x:v>
+      </x:c>
+      <x:c r="S169" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T169" s="62" t="str">
+        <x:v>Связать с PL-009: 35 мм становится не только чёрно-белым и негативным форматом, но и цветным слайдом.</x:v>
+      </x:c>
+      <x:c r="U169" s="62" t="str">
+        <x:v>35-мм слайд в картонной рамке рядом с кассетой плёнки и лупой.</x:v>
+      </x:c>
+      <x:c r="V169" s="62" t="str">
+        <x:v>#PL017 #35mm #slides #Kodachrome #transparency</x:v>
+      </x:c>
+      <x:c r="W169" s="62"/>
+      <x:c r="X169" s="62" t="str">
+        <x:v>43.1566, -77.6088</x:v>
+      </x:c>
+      <x:c r="Y169" s="62" t="str">
+        <x:v>Слайдовая плёнка / 35 мм слайды</x:v>
+      </x:c>
+      <x:c r="Z169" s="62" t="str">
+        <x:v>Распространение / коммерциализация</x:v>
+      </x:c>
+      <x:c r="AA169" s="62"/>
+    </x:row>
+    <x:row r="170" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A170" s="62" t="str">
+        <x:v>PL-HIST-0169</x:v>
+      </x:c>
+      <x:c r="B170" s="62" t="str">
+        <x:v>1930-е – XX век</x:v>
+      </x:c>
+      <x:c r="C170" s="62" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D170" s="62" t="str">
+        <x:v>глобально</x:v>
+      </x:c>
+      <x:c r="E170" s="62" t="str">
+        <x:v>распределённый процесс</x:v>
+      </x:c>
+      <x:c r="F170" s="62" t="str">
+        <x:v>Фотографы, редакции, лекторы, семьи</x:v>
+      </x:c>
+      <x:c r="G170" s="62" t="str">
+        <x:v>Цветной слайд закрепляется как позитивная прозрачность: итоговое изображение находится прямо на плёнке и читается при проходящем свете.</x:v>
+      </x:c>
+      <x:c r="H170" s="62" t="str">
+        <x:v>Проекция / распространение</x:v>
+      </x:c>
+      <x:c r="I170" s="62" t="str">
+        <x:v>Mounted slide / transparency viewing</x:v>
+      </x:c>
+      <x:c r="J170" s="62" t="str">
+        <x:v>В отличие от цветного негатива, слайд уже выглядит как готовая картинка: его можно положить на световой стол, рассмотреть в лупу или показать проектором.</x:v>
+      </x:c>
+      <x:c r="K170" s="62" t="str">
+        <x:v>35-мм Kodachrome и культура проекции</x:v>
+      </x:c>
+      <x:c r="L170" s="62" t="str">
+        <x:v>Реверсивный химический процесс</x:v>
+      </x:c>
+      <x:c r="M170" s="62" t="str">
+        <x:v>Главная линия / практическое управление</x:v>
+      </x:c>
+      <x:c r="N170" s="62" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O170" s="62" t="str">
+        <x:v>PL-017</x:v>
+      </x:c>
+      <x:c r="P170" s="62" t="str">
+        <x:v>SRC-139</x:v>
+      </x:c>
+      <x:c r="Q170" s="62" t="str">
+        <x:v>National Archives — Photographs</x:v>
+      </x:c>
+      <x:c r="R170" s="62" t="str">
+        <x:v>https://www.archives.gov/preservation/holdings-maintenance/photographs</x:v>
+      </x:c>
+      <x:c r="S170" s="62" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="T170" s="62" t="str">
+        <x:v>Это центральное отличие для новичка: негатив нужно инвертировать/печатать, а слайд сам является позитивом.</x:v>
+      </x:c>
+      <x:c r="U170" s="62" t="str">
+        <x:v>Световой стол с mounted slides, лупой и проектором на заднем плане.</x:v>
+      </x:c>
+      <x:c r="V170" s="62" t="str">
+        <x:v>#PL017 #slide #transparency #projection #positive</x:v>
+      </x:c>
+      <x:c r="W170" s="62" t="str">
+        <x:v>Найти отдельный музейный источник по культуре слайд-проекций и редакционной работе со слайдами.</x:v>
+      </x:c>
+      <x:c r="X170" s="62"/>
+      <x:c r="Y170" s="62" t="str">
+        <x:v>Слайдовая плёнка / просмотр на просвет</x:v>
+      </x:c>
+      <x:c r="Z170" s="62" t="str">
+        <x:v>Применение / жанр</x:v>
+      </x:c>
+      <x:c r="AA170" s="62"/>
+    </x:row>
+    <x:row r="171" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A171" s="62" t="str">
+        <x:v>PL-HIST-0170</x:v>
+      </x:c>
+      <x:c r="B171" s="62" t="str">
+        <x:v>XX век</x:v>
+      </x:c>
+      <x:c r="C171" s="62" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D171" s="62" t="str">
+        <x:v>глобально</x:v>
+      </x:c>
+      <x:c r="E171" s="62" t="str">
+        <x:v>распределённый процесс</x:v>
+      </x:c>
+      <x:c r="F171" s="62" t="str">
+        <x:v>Производители реверсивных материалов и лаборатории</x:v>
+      </x:c>
+      <x:c r="G171" s="62" t="str">
+        <x:v>Реверсивный материал при съёмке в камере после обработки даёт позитив, а не негатив: это и есть базовый принцип slide / transparency film.</x:v>
+      </x:c>
+      <x:c r="H171" s="62" t="str">
+        <x:v>Фотохимия</x:v>
+      </x:c>
+      <x:c r="I171" s="62" t="str">
+        <x:v>Reversal stock / direct positive development</x:v>
+      </x:c>
+      <x:c r="J171" s="62" t="str">
+        <x:v>Маршрут изображения меняется: вместо «негатив → позитив» появляется «экспозиция → реверсивная обработка → готовый позитив на плёнке».</x:v>
+      </x:c>
+      <x:c r="K171" s="62" t="str">
+        <x:v>Негативно-позитивная система PL-013 / PL-016</x:v>
+      </x:c>
+      <x:c r="L171" s="62" t="str">
+        <x:v>Ektachrome и стандартизированный E-6 процесс</x:v>
+      </x:c>
+      <x:c r="M171" s="62" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N171" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O171" s="62" t="str">
+        <x:v>PL-017</x:v>
+      </x:c>
+      <x:c r="P171" s="62" t="str">
+        <x:v>SRC-137</x:v>
+      </x:c>
+      <x:c r="Q171" s="62" t="str">
+        <x:v>National Archives — Archival Formats: Glossary of Terms</x:v>
+      </x:c>
+      <x:c r="R171" s="62" t="str">
+        <x:v>https://www.archives.gov/preservation/formats/glossary.html</x:v>
+      </x:c>
+      <x:c r="S171" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T171" s="62" t="str">
+        <x:v>Объяснять через схему: цветной негатив — матрица для будущего изображения, слайд — само изображение.</x:v>
+      </x:c>
+      <x:c r="U171" s="62" t="str">
+        <x:v>Две дорожки процесса: слева негатив превращается в отпечаток, справа слайд сразу становится позитивом.</x:v>
+      </x:c>
+      <x:c r="V171" s="62" t="str">
+        <x:v>#PL017 #reversal #positive #transparency #process</x:v>
+      </x:c>
+      <x:c r="W171" s="62"/>
+      <x:c r="X171" s="62"/>
+      <x:c r="Y171" s="62" t="str">
+        <x:v>Слайдовая плёнка / reversal-процесс</x:v>
+      </x:c>
+      <x:c r="Z171" s="62" t="str">
+        <x:v>Технология / процесс</x:v>
+      </x:c>
+      <x:c r="AA171" s="62"/>
+    </x:row>
+    <x:row r="172" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A172" s="62" t="str">
+        <x:v>PL-HIST-0171</x:v>
+      </x:c>
+      <x:c r="B172" s="62" t="str">
+        <x:v>1946</x:v>
+      </x:c>
+      <x:c r="C172" s="62" t="str">
+        <x:v>год</x:v>
+      </x:c>
+      <x:c r="D172" s="62" t="str">
+        <x:v>США</x:v>
+      </x:c>
+      <x:c r="E172" s="62" t="str">
+        <x:v>Рочестер, Нью-Йорк</x:v>
+      </x:c>
+      <x:c r="F172" s="62" t="str">
+        <x:v>Eastman Kodak Company</x:v>
+      </x:c>
+      <x:c r="G172" s="62" t="str">
+        <x:v>Kodak выпускает KODAK EKTACHROME Transparency Sheet Film — цветную прозрачную плёнку, которую фотографы могли обрабатывать сами с помощью химических наборов.</x:v>
+      </x:c>
+      <x:c r="H172" s="62" t="str">
+        <x:v>Цвет</x:v>
+      </x:c>
+      <x:c r="I172" s="62" t="str">
+        <x:v>KODAK EKTACHROME Transparency Sheet Film</x:v>
+      </x:c>
+      <x:c r="J172" s="62" t="str">
+        <x:v>Цветной слайд становится более доступным для контролируемой обработки: Ektachrome отделяется от сложной сервисной модели Kodachrome.</x:v>
+      </x:c>
+      <x:c r="K172" s="62" t="str">
+        <x:v>Kodachrome как промышленный цветной слайд</x:v>
+      </x:c>
+      <x:c r="L172" s="62" t="str">
+        <x:v>Стандартизация Ektachrome и E-6</x:v>
+      </x:c>
+      <x:c r="M172" s="62" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N172" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O172" s="62" t="str">
+        <x:v>PL-017</x:v>
+      </x:c>
+      <x:c r="P172" s="62" t="str">
+        <x:v>SRC-135</x:v>
+      </x:c>
+      <x:c r="Q172" s="62" t="str">
+        <x:v>Kodak — Milestones</x:v>
+      </x:c>
+      <x:c r="R172" s="62" t="str">
+        <x:v>https://www.kodak.com/en/company/page/milestones/</x:v>
+      </x:c>
+      <x:c r="S172" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T172" s="62" t="str">
+        <x:v>Важно: Ektachrome — это шаг к большей самостоятельности фотографа и лаборатории.</x:v>
+      </x:c>
+      <x:c r="U172" s="62" t="str">
+        <x:v>Листовая Ektachrome, химический набор и проявочный бачок на лабораторном столе.</x:v>
+      </x:c>
+      <x:c r="V172" s="62" t="str">
+        <x:v>#PL017 #Ektachrome #transparency #Kodak #processing</x:v>
+      </x:c>
+      <x:c r="W172" s="62"/>
+      <x:c r="X172" s="62" t="str">
+        <x:v>43.1566, -77.6088</x:v>
+      </x:c>
+      <x:c r="Y172" s="62" t="str">
+        <x:v>Слайдовая плёнка / Ektachrome</x:v>
+      </x:c>
+      <x:c r="Z172" s="62" t="str">
+        <x:v>Распространение / коммерциализация</x:v>
+      </x:c>
+      <x:c r="AA172" s="62"/>
+    </x:row>
+    <x:row r="173" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A173" s="62" t="str">
+        <x:v>PL-HIST-0172</x:v>
+      </x:c>
+      <x:c r="B173" s="62" t="str">
+        <x:v>1970-е – XXI век</x:v>
+      </x:c>
+      <x:c r="C173" s="62" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D173" s="62" t="str">
+        <x:v>глобально</x:v>
+      </x:c>
+      <x:c r="E173" s="62" t="str">
+        <x:v>фотолаборатории</x:v>
+      </x:c>
+      <x:c r="F173" s="62" t="str">
+        <x:v>Kodak / фотолаборатории</x:v>
+      </x:c>
+      <x:c r="G173" s="62" t="str">
+        <x:v>Process E-6 закрепляется как стандартная логика обработки современных цветных реверсивных плёнок семейства Ektachrome и совместимых материалов.</x:v>
+      </x:c>
+      <x:c r="H173" s="62" t="str">
+        <x:v>Фотохимия</x:v>
+      </x:c>
+      <x:c r="I173" s="62" t="str">
+        <x:v>E-6 color reversal process</x:v>
+      </x:c>
+      <x:c r="J173" s="62" t="str">
+        <x:v>Слайдовая плёнка получает понятную лабораторную метку: если материал рассчитан на E-6, значит это цветной reversal / slide-процесс.</x:v>
+      </x:c>
+      <x:c r="K173" s="62" t="str">
+        <x:v>Ektachrome как более доступная реверсивная система</x:v>
+      </x:c>
+      <x:c r="L173" s="62" t="str">
+        <x:v>Современные слайдовые материалы и гибридное сканирование</x:v>
+      </x:c>
+      <x:c r="M173" s="62" t="str">
+        <x:v>Главная линия</x:v>
+      </x:c>
+      <x:c r="N173" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O173" s="62" t="str">
+        <x:v>PL-017</x:v>
+      </x:c>
+      <x:c r="P173" s="62" t="str">
+        <x:v>SRC-138</x:v>
+      </x:c>
+      <x:c r="Q173" s="62" t="str">
+        <x:v>Kodak — EKTACHROME Color Reversal Control Strips Process E-6</x:v>
+      </x:c>
+      <x:c r="R173" s="62" t="str">
+        <x:v>https://www.kodak.com/en/motion/page/ektachrome-color-reversal-control-strips/</x:v>
+      </x:c>
+      <x:c r="S173" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T173" s="62" t="str">
+        <x:v>Практическая формула для ученика: C-41 — цветной негатив; E-6 — цветной слайд / reversal.</x:v>
+      </x:c>
+      <x:c r="U173" s="62" t="str">
+        <x:v>Две коробки химии: C-41 и E-6; рядом две полоски плёнки — оранжевый негатив и прозрачный слайд.</x:v>
+      </x:c>
+      <x:c r="V173" s="62" t="str">
+        <x:v>#PL017 #E6 #color-reversal #processing #Ektachrome</x:v>
+      </x:c>
+      <x:c r="W173" s="62" t="str">
+        <x:v>Точную историческую дату введения E-6 при необходимости уточнить отдельно; для урока важнее современная маркировка процесса.</x:v>
+      </x:c>
+      <x:c r="X173" s="62"/>
+      <x:c r="Y173" s="62" t="str">
+        <x:v>Слайдовая плёнка / E-6</x:v>
+      </x:c>
+      <x:c r="Z173" s="62" t="str">
+        <x:v>Технология / процесс</x:v>
+      </x:c>
+      <x:c r="AA173" s="62"/>
+    </x:row>
+    <x:row r="174" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A174" s="62" t="str">
+        <x:v>PL-HIST-0173</x:v>
+      </x:c>
+      <x:c r="B174" s="62" t="str">
+        <x:v>XX–XXI век</x:v>
+      </x:c>
+      <x:c r="C174" s="62" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D174" s="62" t="str">
+        <x:v>глобально</x:v>
+      </x:c>
+      <x:c r="E174" s="62" t="str">
+        <x:v>практика фотографов</x:v>
+      </x:c>
+      <x:c r="F174" s="62" t="str">
+        <x:v>Фотографы, лаборатории, производители плёнки</x:v>
+      </x:c>
+      <x:c r="G174" s="62" t="str">
+        <x:v>Слайдовая плёнка требует более точной экспозиции, потому что итоговый позитив находится прямо на плёнке и даёт меньше места для исправления, чем негатив.</x:v>
+      </x:c>
+      <x:c r="H174" s="62" t="str">
+        <x:v>Цвет</x:v>
+      </x:c>
+      <x:c r="I174" s="62" t="str">
+        <x:v>Slide film exposure precision / narrow exposure range</x:v>
+      </x:c>
+      <x:c r="J174" s="62" t="str">
+        <x:v>Фотограф учится измерять свет внимательнее: ошибка экспозиции видна сразу на самом слайде, а не компенсируется при печати с негатива.</x:v>
+      </x:c>
+      <x:c r="K174" s="62" t="str">
+        <x:v>Цветной негатив с большой практической гибкостью PL-016</x:v>
+      </x:c>
+      <x:c r="L174" s="62" t="str">
+        <x:v>Экспозиционная широта PL-020</x:v>
+      </x:c>
+      <x:c r="M174" s="62" t="str">
+        <x:v>Главная линия / практическое управление</x:v>
+      </x:c>
+      <x:c r="N174" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O174" s="62" t="str">
+        <x:v>PL-017</x:v>
+      </x:c>
+      <x:c r="P174" s="62" t="str">
+        <x:v>SRC-141</x:v>
+      </x:c>
+      <x:c r="Q174" s="62" t="str">
+        <x:v>Kodak Moments — Ektachrome 120 FAQs</x:v>
+      </x:c>
+      <x:c r="R174" s="62" t="str">
+        <x:v>https://business.kodakmoments.com/sites/default/files/files/products/Ektachrome_120_FAQs_English.pdf</x:v>
+      </x:c>
+      <x:c r="S174" s="62" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="T174" s="62" t="str">
+        <x:v>Это мост к PL-020: слайдовая плёнка идеально объясняет, что такое экспозиционная широта и почему у разных материалов она разная.</x:v>
+      </x:c>
+      <x:c r="U174" s="62" t="str">
+        <x:v>Одна сцена снята на негатив и слайд: у слайда выбитые света и плотные тени показывают меньший запас.</x:v>
+      </x:c>
+      <x:c r="V174" s="62" t="str">
+        <x:v>#PL017 #exposure #latitude #slide-film #Ektachrome</x:v>
+      </x:c>
+      <x:c r="W174" s="62" t="str">
+        <x:v>Формулировать без абсолютов: точная широта зависит от конкретной плёнки и обработки.</x:v>
+      </x:c>
+      <x:c r="X174" s="62"/>
+      <x:c r="Y174" s="62" t="str">
+        <x:v>Слайдовая плёнка / точность экспозиции</x:v>
+      </x:c>
+      <x:c r="Z174" s="62" t="str">
+        <x:v>Применение / жанр</x:v>
+      </x:c>
+      <x:c r="AA174" s="62"/>
+    </x:row>
+    <x:row r="175" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A175" s="62" t="str">
+        <x:v>PL-HIST-0174</x:v>
+      </x:c>
+      <x:c r="B175" s="62" t="str">
+        <x:v>XXI век</x:v>
+      </x:c>
+      <x:c r="C175" s="62" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D175" s="62" t="str">
+        <x:v>США / глобально</x:v>
+      </x:c>
+      <x:c r="E175" s="62" t="str">
+        <x:v>Рочестер / современные рынки плёнки</x:v>
+      </x:c>
+      <x:c r="F175" s="62" t="str">
+        <x:v>Kodak / Kodak licensees / современные фотографы</x:v>
+      </x:c>
+      <x:c r="G175" s="62" t="str">
+        <x:v>KODAK EKTACHROME E100 остаётся современным примером слайдовой плёнки: daylight-balanced color reversal film ISO 100, рассчитанная на процесс E-6.</x:v>
+      </x:c>
+      <x:c r="H175" s="62" t="str">
+        <x:v>Цвет</x:v>
+      </x:c>
+      <x:c r="I175" s="62" t="str">
+        <x:v>KODAK EKTACHROME E100 / modern slide film</x:v>
+      </x:c>
+      <x:c r="J175" s="62" t="str">
+        <x:v>Слайдовая плёнка не только исторический материал: она остаётся живым выбором для тех, кому нужен готовый позитив, чистый цвет и характерная визуальная дисциплина.</x:v>
+      </x:c>
+      <x:c r="K175" s="62" t="str">
+        <x:v>E-6 как современный стандарт обработки</x:v>
+      </x:c>
+      <x:c r="L175" s="62" t="str">
+        <x:v>Гибридный путь: слайд → световой стол / скан → печать</x:v>
+      </x:c>
+      <x:c r="M175" s="62" t="str">
+        <x:v>Главная линия / визуальный язык</x:v>
+      </x:c>
+      <x:c r="N175" s="62" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O175" s="62" t="str">
+        <x:v>PL-017</x:v>
+      </x:c>
+      <x:c r="P175" s="62" t="str">
+        <x:v>SRC-140</x:v>
+      </x:c>
+      <x:c r="Q175" s="62" t="str">
+        <x:v>Kodak — EKTACHROME E100 Film</x:v>
+      </x:c>
+      <x:c r="R175" s="62" t="str">
+        <x:v>https://www.kodak.com/en/still-film/product/professional/ektachrome-e100-film/</x:v>
+      </x:c>
+      <x:c r="S175" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T175" s="62" t="str">
+        <x:v>Можно показать современную связь: Ektachrome сегодня — это не массовый семейный материал, а осознанный визуальный выбор.</x:v>
+      </x:c>
+      <x:c r="U175" s="62" t="str">
+        <x:v>Современная коробка Ektachrome E100, mounted slide и сканер/световой стол.</x:v>
+      </x:c>
+      <x:c r="V175" s="62" t="str">
+        <x:v>#PL017 #EktachromeE100 #E6 #slide-film #modern-film</x:v>
+      </x:c>
+      <x:c r="W175" s="62"/>
+      <x:c r="X175" s="62" t="str">
+        <x:v>43.1566, -77.6088</x:v>
+      </x:c>
+      <x:c r="Y175" s="62" t="str">
+        <x:v>Слайдовая плёнка / современный материал</x:v>
+      </x:c>
+      <x:c r="Z175" s="62" t="str">
+        <x:v>Применение / жанр</x:v>
+      </x:c>
+      <x:c r="AA175" s="62"/>
+    </x:row>
+    <x:row r="176" s="46" customFormat="1" ht="17" customHeight="1">
+      <x:c r="A176" s="62" t="str">
+        <x:v>PL-HIST-0175</x:v>
+      </x:c>
+      <x:c r="B176" s="62" t="str">
+        <x:v>XX–XXI век</x:v>
+      </x:c>
+      <x:c r="C176" s="62" t="str">
+        <x:v>диапазон</x:v>
+      </x:c>
+      <x:c r="D176" s="62" t="str">
+        <x:v>глобально</x:v>
+      </x:c>
+      <x:c r="E176" s="62" t="str">
+        <x:v>архивы, музеи, частные коллекции</x:v>
+      </x:c>
+      <x:c r="F176" s="62" t="str">
+        <x:v>Архивисты, музеи, фотографы</x:v>
+      </x:c>
+      <x:c r="G176" s="62" t="str">
+        <x:v>Слайды и прозрачности требуют аккуратного хранения: материалы должны быть архивного качества, а оригиналы лучше защищать от света, тепла и неподходящих оболочек.</x:v>
+      </x:c>
+      <x:c r="H176" s="62" t="str">
+        <x:v>Проекция / распространение</x:v>
+      </x:c>
+      <x:c r="I176" s="62" t="str">
+        <x:v>Transparency preservation / slide archive</x:v>
+      </x:c>
+      <x:c r="J176" s="62" t="str">
+        <x:v>Слайд — это не промежуточная рабочая матрица, а сам оригинальный позитив. Потеря или выцветание слайда означает потерю финального изображения.</x:v>
+      </x:c>
+      <x:c r="K176" s="62" t="str">
+        <x:v>Современная слайдовая плёнка и световой стол</x:v>
+      </x:c>
+      <x:c r="L176" s="62" t="str">
+        <x:v>Будущие уроки о сканировании, хранении и отпечатке</x:v>
+      </x:c>
+      <x:c r="M176" s="62" t="str">
+        <x:v>Применение / жанр</x:v>
+      </x:c>
+      <x:c r="N176" s="62" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O176" s="62" t="str">
+        <x:v>PL-017</x:v>
+      </x:c>
+      <x:c r="P176" s="62" t="str">
+        <x:v>SRC-142</x:v>
+      </x:c>
+      <x:c r="Q176" s="62" t="str">
+        <x:v>National Archives — What is the Best Way to Store Negatives and Transparencies?</x:v>
+      </x:c>
+      <x:c r="R176" s="62" t="str">
+        <x:v>https://www.archives.gov/preservation/storage/negatives-transparencies.html</x:v>
+      </x:c>
+      <x:c r="S176" s="62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T176" s="62" t="str">
+        <x:v>Финальный вывод: слайдовая плёнка красива, но требует дисциплины не только при съёмке, но и при хранении.</x:v>
+      </x:c>
+      <x:c r="U176" s="62" t="str">
+        <x:v>Архивная коробка с рамками слайдов, перчатки, световой стол и холодное хранилище.</x:v>
+      </x:c>
+      <x:c r="V176" s="62" t="str">
+        <x:v>#PL017 #slides #transparencies #archive #preservation</x:v>
+      </x:c>
+      <x:c r="W176" s="62"/>
+      <x:c r="X176" s="62"/>
+      <x:c r="Y176" s="62" t="str">
+        <x:v>Слайдовая плёнка / хранение и архив</x:v>
+      </x:c>
+      <x:c r="Z176" s="62" t="str">
+        <x:v>Применение / жанр</x:v>
+      </x:c>
+      <x:c r="AA176" s="62"/>
+    </x:row>
     <x:row r="177" s="46" customFormat="1" ht="17" customHeight="1"/>
     <x:row r="178" s="46" customFormat="1" ht="17" customHeight="1"/>
     <x:row r="179" s="46" customFormat="1" ht="17" customHeight="1"/>
@@ -21654,7 +22552,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7808e7c7a4c44a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6947169601ab4dc3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21758,10 +22656,10 @@
         </x:is>
       </x:c>
       <x:c r="B4" s="50" t="str">
-        <x:v>серебряные соли, желатиновые эмульсии, скрытое изображение, проявление, чувствительность, спектральная чувствительность, зерно, цветные слои, color couplers, C-41</x:v>
+        <x:v>серебряные соли, желатиновые эмульсии, скрытое изображение, проявление, чувствительность, спектральная чувствительность, зерно, цветные слои, color couplers, C-41, E-6, reversal-процесс</x:v>
       </x:c>
       <x:c r="C4" s="50" t="str">
-        <x:v>PL-002 / PL-006 / PL-011 / PL-012 / PL-015 / PL-016</x:v>
+        <x:v>PL-002 / PL-006 / PL-011 / PL-012 / PL-015 / PL-016 / PL-017</x:v>
       </x:c>
       <x:c r="D4" s="50" t="str">
         <x:v>жёлтый</x:v>
@@ -21945,15 +22843,11 @@
           <x:t xml:space="preserve">Уникальный позитив</x:t>
         </x:is>
       </x:c>
-      <x:c r="B12" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bayard, ambrotype, tintype, direct positive, instant print</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PL-003 / PL-005 / PL-014</x:t>
-        </x:is>
+      <x:c r="B12" s="50" t="str">
+        <x:v>ранний цвет, Autochrome, Kodachrome, Kodacolor, Ektachrome, цветная негативная и слайдовая плёнка, chromogenic print, C-41, E-6</x:v>
+      </x:c>
+      <x:c r="C12" s="50" t="str">
+        <x:v>PL-014 / PL-016 / PL-017 / будущие PL</x:v>
       </x:c>
       <x:c r="D12" s="50" t="inlineStr">
         <x:is>
@@ -21973,10 +22867,10 @@
         </x:is>
       </x:c>
       <x:c r="B13" s="50" t="str">
-        <x:v>ранний цвет, Autochrome, Kodachrome, Kodacolor, цветная негативная плёнка, chromogenic print, C-41</x:v>
+        <x:v>lantern slides, слайды, прозрачности, projected positive, публичный и семейный показ</x:v>
       </x:c>
       <x:c r="C13" s="50" t="str">
-        <x:v>PL-014 / PL-016 / будущие PL</x:v>
+        <x:v>PL-017 / будущие PL</x:v>
       </x:c>
       <x:c r="D13" s="50" t="str">
         <x:v>радужный</x:v>
@@ -22015,7 +22909,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb01cec759f6342d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9823732918734044"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22553,27 +23447,47 @@
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="str">
+      <x:c r="A18" s="62" t="str">
+        <x:v>PL-017</x:v>
+      </x:c>
+      <x:c r="B18" s="62" t="str">
+        <x:v>Слайдовая плёнка</x:v>
+      </x:c>
+      <x:c r="C18" s="62" t="str">
+        <x:v>PL-HIST-0165…0175</x:v>
+      </x:c>
+      <x:c r="D18" s="62" t="str">
+        <x:v>Слайдовая плёнка — это позитивная прозрачность: реверсивный процесс даёт готовое изображение прямо на плёнке, поэтому цвет, проекция и экспозиция требуют большей точности.</x:v>
+      </x:c>
+      <x:c r="E18" s="62" t="str">
+        <x:v>основа заполнена</x:v>
+      </x:c>
+      <x:c r="F18" s="62" t="str">
+        <x:v>https://t.me/photolab_vf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="62" t="str">
         <x:v>будущие PL</x:v>
       </x:c>
-      <x:c r="B18" t="str">
-        <x:v>Расширение после PL-016</x:v>
-      </x:c>
-      <x:c r="C18" t="str">
-        <x:v>Слайдовая плёнка, ISO, зерно, широта</x:v>
-      </x:c>
-      <x:c r="D18" t="str">
-        <x:v>После цветной негативной системы курс переходит к слайдовой плёнке и практическим параметрам материала: ISO, зерно и экспозиционная широта.</x:v>
-      </x:c>
-      <x:c r="E18" t="str">
+      <x:c r="B19" s="62" t="str">
+        <x:v>Расширение после PL-017</x:v>
+      </x:c>
+      <x:c r="C19" s="62" t="str">
+        <x:v>ISO плёнки, зерно, экспозиционная широта</x:v>
+      </x:c>
+      <x:c r="D19" s="62" t="str">
+        <x:v>После слайдовой плёнки курс переходит к практическим параметрам материала: ISO, зерно и экспозиционная широта.</x:v>
+      </x:c>
+      <x:c r="E19" s="62" t="str">
         <x:v>планируется</x:v>
       </x:c>
-      <x:c r="F18"/>
+      <x:c r="F19" s="62"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1b479904f144245"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff5932617418405f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25906,10 +26820,214 @@
         <x:v>архивный консервационный источник</x:v>
       </x:c>
     </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="62" t="str">
+        <x:v>SRC-131</x:v>
+      </x:c>
+      <x:c r="B132" s="62" t="str">
+        <x:v>National Science and Media Museum — A short history of colour photography</x:v>
+      </x:c>
+      <x:c r="C132" s="62" t="str">
+        <x:v>https://www.scienceandmediamuseum.org.uk/objects-and-stories/history-colour-photography</x:v>
+      </x:c>
+      <x:c r="D132" s="62" t="str">
+        <x:v>Lumière Autochrome: first practical/commercially successful colour photography process; commercial production from 1907; Kodachrome as first commercially successful integral tripack system</x:v>
+      </x:c>
+      <x:c r="E132" s="62" t="str">
+        <x:v>музейный образовательный источник</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="62" t="str">
+        <x:v>SRC-132</x:v>
+      </x:c>
+      <x:c r="B133" s="62" t="str">
+        <x:v>The Metropolitan Museum of Art — Original Autochromes Produced Using the First Color Photographic Process</x:v>
+      </x:c>
+      <x:c r="C133" s="62" t="str">
+        <x:v>https://www.metmuseum.org/de/press-releases/original-color-photographs-by-stieglitz-and-steichen-january-25-30-2011-exhibitions</x:v>
+      </x:c>
+      <x:c r="D133" s="62" t="str">
+        <x:v>Autochromes introduced in France in 1907 by Auguste and Louis Lumière; one-of-a-kind color transparencies viewed when backlit</x:v>
+      </x:c>
+      <x:c r="E133" s="62" t="str">
+        <x:v>музейный источник по автохромам</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="62" t="str">
+        <x:v>SRC-133</x:v>
+      </x:c>
+      <x:c r="B134" s="62" t="str">
+        <x:v>Kodak — 100 Years of 16mm Film</x:v>
+      </x:c>
+      <x:c r="C134" s="62" t="str">
+        <x:v>https://www.kodak.com/en/motion/page/100-years-of-16mm-film/</x:v>
+      </x:c>
+      <x:c r="D134" s="62" t="str">
+        <x:v>1923: Kodak made amateur motion pictures practical with 16mm reversal film, Cine-Kodak camera and Kodascope projector; 1935 Kodachrome introduced in 16mm</x:v>
+      </x:c>
+      <x:c r="E134" s="62" t="str">
+        <x:v>официальный исторический источник Kodak</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="62" t="str">
+        <x:v>SRC-134</x:v>
+      </x:c>
+      <x:c r="B135" s="62" t="str">
+        <x:v>Kodak — History of Film</x:v>
+      </x:c>
+      <x:c r="C135" s="62" t="str">
+        <x:v>https://www.kodak.com/en/motion/page/chronology-of-film/</x:v>
+      </x:c>
+      <x:c r="D135" s="62" t="str">
+        <x:v>Kodachrome introduced in 1935 as first commercially successful amateur color film, initially 16mm; 35mm slides and 8mm home movies followed in 1936</x:v>
+      </x:c>
+      <x:c r="E135" s="62" t="str">
+        <x:v>официальная хронология Kodak</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="62" t="str">
+        <x:v>SRC-135</x:v>
+      </x:c>
+      <x:c r="B136" s="62" t="str">
+        <x:v>Kodak — Milestones</x:v>
+      </x:c>
+      <x:c r="C136" s="62" t="str">
+        <x:v>https://www.kodak.com/en/company/page/milestones/</x:v>
+      </x:c>
+      <x:c r="D136" s="62" t="str">
+        <x:v>1935 Kodachrome introduced; 1946 Kodak marketed EKTACHROME Transparency Sheet Film, first Kodak color film photographers could process themselves using chemical kits</x:v>
+      </x:c>
+      <x:c r="E136" s="62" t="str">
+        <x:v>официальные вехи Kodak</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="62" t="str">
+        <x:v>SRC-136</x:v>
+      </x:c>
+      <x:c r="B137" s="62" t="str">
+        <x:v>V&amp;A — Colour photography</x:v>
+      </x:c>
+      <x:c r="C137" s="62" t="str">
+        <x:v>https://www.vam.ac.uk/articles/colour-photography</x:v>
+      </x:c>
+      <x:c r="D137" s="62" t="str">
+        <x:v>Autochrome became widely accessible in 1907; Kodachrome introduced in 35mm format in 1936 and replaced Autochrome as a leading colour process</x:v>
+      </x:c>
+      <x:c r="E137" s="62" t="str">
+        <x:v>музейный обзор истории цветной фотографии</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="62" t="str">
+        <x:v>SRC-137</x:v>
+      </x:c>
+      <x:c r="B138" s="62" t="str">
+        <x:v>National Archives — Archival Formats: Glossary of Terms</x:v>
+      </x:c>
+      <x:c r="C138" s="62" t="str">
+        <x:v>https://www.archives.gov/preservation/formats/glossary.html</x:v>
+      </x:c>
+      <x:c r="D138" s="62" t="str">
+        <x:v>When used in a camera, reversal stock develops into a positive; glossary also distinguishes color negatives with orange masking</x:v>
+      </x:c>
+      <x:c r="E138" s="62" t="str">
+        <x:v>архивный терминологический источник</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="62" t="str">
+        <x:v>SRC-138</x:v>
+      </x:c>
+      <x:c r="B139" s="62" t="str">
+        <x:v>Kodak — EKTACHROME Color Reversal Control Strips Process E-6</x:v>
+      </x:c>
+      <x:c r="C139" s="62" t="str">
+        <x:v>https://www.kodak.com/en/motion/page/ektachrome-color-reversal-control-strips/</x:v>
+      </x:c>
+      <x:c r="D139" s="62" t="str">
+        <x:v>KODAK EKTACHROME control strips monitor processing of color reversal films through Process E-6</x:v>
+      </x:c>
+      <x:c r="E139" s="62" t="str">
+        <x:v>официальный источник Kodak по E-6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="62" t="str">
+        <x:v>SRC-139</x:v>
+      </x:c>
+      <x:c r="B140" s="62" t="str">
+        <x:v>National Archives — Photographs</x:v>
+      </x:c>
+      <x:c r="C140" s="62" t="str">
+        <x:v>https://www.archives.gov/preservation/holdings-maintenance/photographs</x:v>
+      </x:c>
+      <x:c r="D140" s="62" t="str">
+        <x:v>NARA holdings include film-based negatives, transparencies and slides; preservation page links them to photographic processes and handling</x:v>
+      </x:c>
+      <x:c r="E140" s="62" t="str">
+        <x:v>архивный консервационный источник</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="62" t="str">
+        <x:v>SRC-140</x:v>
+      </x:c>
+      <x:c r="B141" s="62" t="str">
+        <x:v>Kodak — EKTACHROME E100 Film</x:v>
+      </x:c>
+      <x:c r="C141" s="62" t="str">
+        <x:v>https://www.kodak.com/en/still-film/product/professional/ektachrome-e100-film/</x:v>
+      </x:c>
+      <x:c r="D141" s="62" t="str">
+        <x:v>KODAK EKTACHROME E100 is daylight-balanced color reversal film, ISO 100/21°, designed for E-6 processing</x:v>
+      </x:c>
+      <x:c r="E141" s="62" t="str">
+        <x:v>официальная страница продукта Kodak</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="62" t="str">
+        <x:v>SRC-141</x:v>
+      </x:c>
+      <x:c r="B142" s="62" t="str">
+        <x:v>Kodak Moments — Ektachrome 120 FAQs</x:v>
+      </x:c>
+      <x:c r="C142" s="62" t="str">
+        <x:v>https://business.kodakmoments.com/sites/default/files/files/products/Ektachrome_120_FAQs_English.pdf</x:v>
+      </x:c>
+      <x:c r="D142" s="62" t="str">
+        <x:v>Color reversal film has a much narrower exposure range than negative-working films; transparency itself serves as a color reference for scanning</x:v>
+      </x:c>
+      <x:c r="E142" s="62" t="str">
+        <x:v>официальный/лицензионный справочник Kodak Moments</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="62" t="str">
+        <x:v>SRC-142</x:v>
+      </x:c>
+      <x:c r="B143" s="62" t="str">
+        <x:v>National Archives — What is the Best Way to Store Negatives and Transparencies?</x:v>
+      </x:c>
+      <x:c r="C143" s="62" t="str">
+        <x:v>https://www.archives.gov/preservation/storage/negatives-transparencies.html</x:v>
+      </x:c>
+      <x:c r="D143" s="62" t="str">
+        <x:v>Guidance on storage materials for negatives and transparencies, including PAT-approved papers/plastics and enclosures</x:v>
+      </x:c>
+      <x:c r="E143" s="62" t="str">
+        <x:v>архивный источник по хранению</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4b10c04987d4abd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfebf0e29465644bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26434,7 +27552,7 @@
       <x:c r="A18" s="4" t="n"/>
       <x:c r="B18" s="4" t="n"/>
       <x:c r="C18" s="50" t="str">
-        <x:v>будущие PL</x:v>
+        <x:v>PL-017</x:v>
       </x:c>
       <x:c r="D18" s="4" t="n"/>
       <x:c r="E18" s="4" t="n"/>
@@ -26450,7 +27568,7 @@
       <x:c r="A19" s="4" t="n"/>
       <x:c r="B19" s="4" t="n"/>
       <x:c r="C19" s="4" t="str">
-        <x:v>межурочный узел</x:v>
+        <x:v>будущие PL</x:v>
       </x:c>
       <x:c r="D19" s="4" t="n"/>
       <x:c r="E19" s="4" t="n"/>
@@ -26466,7 +27584,7 @@
       <x:c r="A20" s="4" t="n"/>
       <x:c r="B20" s="4" t="n"/>
       <x:c r="C20" s="4" t="str">
-        <x:v>проверить</x:v>
+        <x:v>межурочный узел</x:v>
       </x:c>
       <x:c r="D20" s="4" t="n"/>
       <x:c r="E20" s="4" t="n"/>
@@ -26481,7 +27599,9 @@
     <x:row r="21" s="46" customFormat="1" ht="20" customHeight="1">
       <x:c r="A21" s="4" t="n"/>
       <x:c r="B21" s="4" t="n"/>
-      <x:c r="C21" s="4" t="n"/>
+      <x:c r="C21" s="4" t="str">
+        <x:v>проверить</x:v>
+      </x:c>
       <x:c r="D21" s="4" t="n"/>
       <x:c r="E21" s="4" t="n"/>
       <x:c r="F21" s="4" t="n"/>
@@ -27460,7 +28580,37 @@
     </x:row>
     <x:row r="141">
       <x:c r="H141" t="str">
-        <x:v>Цветная негативная плёнка / хранение и архив</x:v>
+        <x:v>Слайдовая плёнка / ранний цветной позитив</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="H142" t="str">
+        <x:v>Слайдовая плёнка / reversal и проекция</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="H143" t="str">
+        <x:v>Слайдовая плёнка / Kodachrome</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="H144" t="str">
+        <x:v>Слайдовая плёнка / Ektachrome</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="H145" t="str">
+        <x:v>Слайдовая плёнка / E-6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="H146" t="str">
+        <x:v>Слайдовая плёнка / точность экспозиции</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="H147" t="str">
+        <x:v>Слайдовая плёнка / хранение и архив</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -27478,7 +28628,7 @@
   <x:sheetData>
     <x:row r="1" s="46" customFormat="1" ht="40" customHeight="1">
       <x:c r="A1" s="32" t="str">
-        <x:v>PHOTO LAB — History Map Master v0.13</x:v>
+        <x:v>PHOTO LAB — History Map Master v0.14</x:v>
       </x:c>
       <x:c r="B1" s="20" t="n"/>
     </x:row>
@@ -27499,7 +28649,7 @@
         <x:v>Охват v0.13</x:v>
       </x:c>
       <x:c r="B3" s="54" t="str">
-        <x:v>От оптических предпосылок камеры-обскуры до Leica I и Модуля 2: плёнка как материал, эмульсия, негатив, позитив, чёрно-белая и цветная негативная плёнка; основа для PL-001–PL-016.</x:v>
+        <x:v>От оптических предпосылок камеры-обскуры до Leica I и Модуля 2: плёнка как материал, эмульсия, негатив, позитив, чёрно-белая, цветная негативная и слайдовая плёнка; основа для PL-001–PL-017.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="46" customFormat="1" ht="21" customHeight="1">
@@ -27545,7 +28695,7 @@
         </x:is>
       </x:c>
       <x:c r="B7" s="54" t="str">
-        <x:v>Ветка развития = одна из 13 крупных линий из 02_Branches. Для PL-016 цветная негативная плёнка связана с «Цвет», «Фотохимия», «Негатив-позитив» и «Печать / тиражирование».</x:v>
+        <x:v>Ветка развития = одна из 13 крупных линий из 02_Branches. Для PL-017 слайдовая плёнка связана с «Цвет», «Фотохимия», «Проекция / распространение» и «Уникальный позитив».</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="46" customFormat="1" ht="21" customHeight="1">
@@ -27555,7 +28705,7 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="54" t="str">
-        <x:v>Подветка (детали) = уточнение внутри крупной ветки: химия, камера, распространение, фотокнига, медицинское применение, сухие пластины, рулонная плёнка, Brownie, 35 мм, Leica I, структура плёнки, эмульсия, негатив/позитив, позитив, чёрно-белая плёнка, цветная негативная плёнка и т.п.</x:v>
+        <x:v>Подветка (детали) = уточнение внутри крупной ветки: химия, камера, распространение, фотокнига, медицинское применение, сухие пластины, рулонная плёнка, Brownie, 35 мм, Leica I, структура плёнки, эмульсия, негатив/позитив, позитив, чёрно-белая плёнка, цветная негативная плёнка, слайдовая плёнка и т.п.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="46" customFormat="1" ht="17" customHeight="1">
@@ -27740,11 +28890,23 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
+        <x:v>Что изменено в v0.14</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>Заполнен PL-017: добавлены PL-HIST-0165…0175 по слайдовой плёнке — Autochrome как ранняя цветная прозрачность, 16-мм reversal, Kodachrome 1935, 35-мм слайды, принцип direct positive, Ektachrome 1946, E-6, точность экспозиции, современный Ektachrome E100 и архивное хранение прозрачностей. Добавлены источники SRC-131…SRC-142 и флагманский узел PL-HIST-0167.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
         <x:v>Следующий шаг</x:v>
       </x:c>
-      <x:c r="B25" t="str">
-        <x:v>PL-017: слайдовая плёнка — объяснить цветную позитивную прозрачность, reversal-процесс, точность экспозиции и отличие от цветного негатива.</x:v>
-      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>PL-018: ISO плёнки — объяснить светочувствительность материала, коробочный ISO, экспонометрию, push/pull и практический выбор плёнки под свет.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -435,7 +435,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -684,7 +684,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -738,7 +738,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -771,7 +771,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -1039,7 +1039,7 @@
     <row r="1" ht="40" customHeight="1" s="59">
       <c r="A1" s="31" t="inlineStr">
         <is>
-          <t>PHOTO LAB — Master Timeline v0.14</t>
+          <t>PHOTO LAB — Master Timeline v0.15</t>
         </is>
       </c>
       <c r="B1" s="20" t="n"/>
@@ -1106,11 +1106,11 @@
     <row r="5" ht="21" customHeight="1" s="59">
       <c r="A5" s="67" t="inlineStr">
         <is>
-          <t>Узлов для PL-001–PL-017</t>
+          <t>Узлов для PL-001–PL-020</t>
         </is>
       </c>
       <c r="B5" s="68">
-        <f>SUM(COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-001"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-002"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-003"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-004"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-005"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-006"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-007"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-008"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-009"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-010"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-011"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-012"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-013"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-014"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-015"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-016"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-017"))</f>
+        <f>SUM(COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-001"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-002"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-003"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-004"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-005"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-006"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-007"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-008"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-009"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-010"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-011"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-012"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-013"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-014"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-015"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-016"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-017"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-018"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-019"),COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-020"))</f>
         <v/>
       </c>
       <c r="C5" s="67" t="inlineStr">
@@ -1511,7 +1511,7 @@
       <c r="C27" s="62" t="n"/>
       <c r="D27" s="62" t="inlineStr">
         <is>
-          <t>будущие PL</t>
+          <t>PL-018</t>
         </is>
       </c>
       <c r="E27" s="62">
@@ -1525,7 +1525,7 @@
       <c r="C28" s="62" t="n"/>
       <c r="D28" s="62" t="inlineStr">
         <is>
-          <t>межурочный узел</t>
+          <t>PL-019</t>
         </is>
       </c>
       <c r="E28" s="62">
@@ -1534,20 +1534,12 @@
       </c>
     </row>
     <row r="29" ht="21" customHeight="1" s="59">
-      <c r="A29" s="63" t="inlineStr">
-        <is>
-          <t>Тип узла</t>
-        </is>
-      </c>
-      <c r="B29" s="63" t="inlineStr">
-        <is>
-          <t>Количество узлов</t>
-        </is>
-      </c>
+      <c r="A29" s="63" t="n"/>
+      <c r="B29" s="63" t="n"/>
       <c r="C29" s="62" t="n"/>
       <c r="D29" s="62" t="inlineStr">
         <is>
-          <t>проверить</t>
+          <t>PL-020</t>
         </is>
       </c>
       <c r="E29" s="62">
@@ -1556,57 +1548,43 @@
       </c>
     </row>
     <row r="30" ht="21" customHeight="1" s="59">
-      <c r="A30" s="63" t="inlineStr">
-        <is>
-          <t>Фундаментальная предпосылка</t>
-        </is>
-      </c>
-      <c r="B30" s="63">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A30)</f>
+      <c r="A30" s="63" t="n"/>
+      <c r="B30" s="63" t="n"/>
+      <c r="C30" s="62" t="n"/>
+      <c r="D30" s="62" t="inlineStr">
+        <is>
+          <t>будущие PL</t>
+        </is>
+      </c>
+      <c r="E30" s="62">
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D30)</f>
         <v/>
       </c>
-      <c r="C30" s="62" t="n"/>
-      <c r="D30" s="62" t="n"/>
-      <c r="E30" s="62" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1" s="59">
-      <c r="A31" s="63" t="inlineStr">
-        <is>
-          <t>Технология / процесс</t>
-        </is>
-      </c>
-      <c r="B31" s="63">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A31)</f>
+      <c r="A31" s="63" t="n"/>
+      <c r="B31" s="63" t="n"/>
+      <c r="C31" s="62" t="n"/>
+      <c r="D31" s="62" t="inlineStr">
+        <is>
+          <t>межурочный узел</t>
+        </is>
+      </c>
+      <c r="E31" s="62">
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D31)</f>
         <v/>
       </c>
-      <c r="C31" s="62" t="n"/>
-      <c r="D31" s="62" t="n"/>
-      <c r="E31" s="62" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1" s="59">
-      <c r="A32" s="63" t="inlineStr">
-        <is>
-          <t>Инструмент / устройство</t>
-        </is>
-      </c>
-      <c r="B32" s="63">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A32)</f>
-        <v/>
-      </c>
+      <c r="A32" s="63" t="n"/>
+      <c r="B32" s="63" t="n"/>
       <c r="C32" s="62" t="n"/>
       <c r="D32" s="62" t="n"/>
       <c r="E32" s="62" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1" s="59">
-      <c r="A33" s="63" t="inlineStr">
-        <is>
-          <t>Публикация / объявление</t>
-        </is>
-      </c>
-      <c r="B33" s="63">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A33)</f>
-        <v/>
-      </c>
+      <c r="A33" s="63" t="n"/>
+      <c r="B33" s="63" t="n"/>
       <c r="C33" s="62" t="n"/>
       <c r="D33" s="62" t="n"/>
       <c r="E33" s="62" t="n"/>
@@ -1614,12 +1592,13 @@
     <row r="34" ht="21" customHeight="1" s="59">
       <c r="A34" s="63" t="inlineStr">
         <is>
-          <t>Терминология / язык</t>
-        </is>
-      </c>
-      <c r="B34" s="63">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A34)</f>
-        <v/>
+          <t>Тип узла</t>
+        </is>
+      </c>
+      <c r="B34" s="63" t="inlineStr">
+        <is>
+          <t>Количество узлов</t>
+        </is>
       </c>
       <c r="C34" s="62" t="n"/>
       <c r="D34" s="62" t="n"/>
@@ -1628,7 +1607,7 @@
     <row r="35" ht="21" customHeight="1" s="59">
       <c r="A35" s="63" t="inlineStr">
         <is>
-          <t>Связь / переход</t>
+          <t>Фундаментальная предпосылка</t>
         </is>
       </c>
       <c r="B35" s="63">
@@ -1642,7 +1621,7 @@
     <row r="36" ht="21" customHeight="1" s="59">
       <c r="A36" s="63" t="inlineStr">
         <is>
-          <t>Тиражирование / публикация</t>
+          <t>Технология / процесс</t>
         </is>
       </c>
       <c r="B36" s="63">
@@ -1656,7 +1635,7 @@
     <row r="37" ht="20" customHeight="1" s="59">
       <c r="A37" s="63" t="inlineStr">
         <is>
-          <t>Распространение / коммерциализация</t>
+          <t>Инструмент / устройство</t>
         </is>
       </c>
       <c r="B37" s="63">
@@ -1670,7 +1649,7 @@
     <row r="38" ht="20" customHeight="1" s="59">
       <c r="A38" s="63" t="inlineStr">
         <is>
-          <t>Научное применение / пример</t>
+          <t>Публикация / объявление</t>
         </is>
       </c>
       <c r="B38" s="63">
@@ -1684,7 +1663,7 @@
     <row r="39" ht="20" customHeight="1" s="59">
       <c r="A39" s="63" t="inlineStr">
         <is>
-          <t>Применение / жанр</t>
+          <t>Терминология / язык</t>
         </is>
       </c>
       <c r="B39" s="63">
@@ -1698,7 +1677,7 @@
     <row r="40" ht="20" customHeight="1" s="59">
       <c r="A40" s="63" t="inlineStr">
         <is>
-          <t>Ключевой исторический узел</t>
+          <t>Связь / переход</t>
         </is>
       </c>
       <c r="B40" s="63">
@@ -1710,24 +1689,59 @@
       <c r="E40" s="62" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1" s="59">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="4" t="n"/>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Тиражирование / публикация</t>
+        </is>
+      </c>
+      <c r="B41" s="4">
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A41)</f>
+        <v/>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1" s="59">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="4" t="n"/>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Распространение / коммерциализация</t>
+        </is>
+      </c>
+      <c r="B42" s="4">
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A42)</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1" s="59">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="4" t="n"/>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Научное применение / пример</t>
+        </is>
+      </c>
+      <c r="B43" s="4">
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A43)</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1" s="59">
-      <c r="A44" s="4" t="n"/>
-      <c r="B44" s="4" t="n"/>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+      <c r="B44" s="4">
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A44)</f>
+        <v/>
+      </c>
     </row>
     <row r="45" ht="20" customHeight="1" s="59">
-      <c r="A45" s="4" t="n"/>
-      <c r="B45" s="4" t="n"/>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="B45" s="4">
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A45)</f>
+        <v/>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1" s="59">
       <c r="A46" s="4" t="n"/>
@@ -1748,7 +1762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA176"/>
+  <dimension ref="A1:AA209"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="14" customWidth="1" style="59" min="1" max="1"/>
@@ -23703,39 +23717,4090 @@
       </c>
       <c r="AA176" s="62" t="n"/>
     </row>
-    <row r="177" ht="17" customHeight="1" s="59"/>
-    <row r="178" ht="17" customHeight="1" s="59"/>
-    <row r="179" ht="17" customHeight="1" s="59"/>
-    <row r="180" ht="17" customHeight="1" s="59"/>
-    <row r="181" ht="17" customHeight="1" s="59"/>
-    <row r="182" ht="17" customHeight="1" s="59"/>
-    <row r="183" ht="17" customHeight="1" s="59"/>
-    <row r="184" ht="17" customHeight="1" s="59"/>
-    <row r="185" ht="17" customHeight="1" s="59"/>
-    <row r="186" ht="17" customHeight="1" s="59"/>
-    <row r="187" ht="17" customHeight="1" s="59"/>
-    <row r="188" ht="17" customHeight="1" s="59"/>
-    <row r="189" ht="17" customHeight="1" s="59"/>
-    <row r="190" ht="17" customHeight="1" s="59"/>
-    <row r="191" ht="17" customHeight="1" s="59"/>
-    <row r="192" ht="17" customHeight="1" s="59"/>
-    <row r="193" ht="17" customHeight="1" s="59"/>
-    <row r="194" ht="17" customHeight="1" s="59"/>
-    <row r="195" ht="17" customHeight="1" s="59"/>
-    <row r="196" ht="17" customHeight="1" s="59"/>
-    <row r="197" ht="17" customHeight="1" s="59"/>
-    <row r="198" ht="17" customHeight="1" s="59"/>
-    <row r="199" ht="17" customHeight="1" s="59"/>
-    <row r="200" ht="17" customHeight="1" s="59"/>
-    <row r="201" ht="17" customHeight="1" s="59"/>
-    <row r="202" ht="17" customHeight="1" s="59"/>
-    <row r="203" ht="17" customHeight="1" s="59"/>
-    <row r="204" ht="17" customHeight="1" s="59"/>
-    <row r="205" ht="17" customHeight="1" s="59"/>
-    <row r="206" ht="17" customHeight="1" s="59"/>
-    <row r="207" ht="17" customHeight="1" s="59"/>
-    <row r="208" ht="17" customHeight="1" s="59"/>
-    <row r="209" ht="17" customHeight="1" s="59"/>
+    <row r="177" ht="17" customHeight="1" s="59">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>PL-HIST-0176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>распределённая практика</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Фотографы, производители плёнки, лаборатории</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>ISO плёнки закрепляется как практический язык светочувствительности: число на коробке говорит, сколько света примерно нужно материалу.</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Film speed / ISO</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Новичок получает простой ориентир: низкий ISO требует больше света, высокий ISO помогает в темноте, но меняет характер изображения.</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Светочувствительный материал PL-011 и эмульсия PL-012</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>ISO как основа экспозиции и выбора плёнки под свет</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое управление</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>5</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>PL-018</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>SRC-146</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>ILFORD — Choosing your first ILFORD film</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/choosing-your-first-ilford-film/</t>
+        </is>
+      </c>
+      <c r="S177" t="n">
+        <v>5</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Флагман урока: ISO — это не «яркость фотографии», а чувствительность материала к свету.</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Коробки плёнки ISO 50, 100, 400 и 3200 на столе; рядом экспонометр и луч света.</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>#PL018 #ISO #film-speed #exposure #film</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>ISO плёнки / светочувствительность</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="17" customHeight="1" s="59">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>PL-HIST-0177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1980-е</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>международно</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Женева / международные стандарты</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>International Organization for Standardization / ASA / DIN</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Старые системы ASA и DIN постепенно переходят в международную систему ISO, но линейная ASA-логика продолжает жить внутри ISO-числа.</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>ASA / DIN → ISO film speed</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Фотографы из разных стран получают единый язык: ISO 100/21° означает одну и ту же практическую идею чувствительности.</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Разрозненные национальные шкалы светочувствительности</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Современная маркировка ISO на коробке плёнки и в камере</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>5</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>PL-018</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>SRC-143</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>ISO — ISO 6:1993 Camera film speed</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>https://www.iso.org/iso-6-camera-film-speed.html</t>
+        </is>
+      </c>
+      <c r="S178" t="n">
+        <v>5</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Важно не перегружать историей стандартов: ученику достаточно понять, что ISO — это общий язык света.</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Шкалы ASA, DIN и ISO, сходящиеся в одну золотую линию на фоне коробки плёнки.</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>#PL018 #ASA #DIN #ISO #standard</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>При необходимости уточнить точные годы перехода ASA/DIN в ISO в национальных стандартах.</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>46.2044, 6.1432</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>ISO плёнки / ASA-DIN-ISO</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>Терминология / язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="17" customHeight="1" s="59">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>PL-HIST-0178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>год</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>международно</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Женева</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>International Organization for Standardization</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>ISO 6 фиксирует метод определения ISO-светочувствительности для чёрно-белых негативных фотоплёнок и систем обработки.</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>ISO 6 / black-and-white negative film speed</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Чёрно-белая плёнка получает стандартизированную точку отсчёта: чувствительность связана не только с эмульсией, но и с процессом проявки.</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Чёрно-белая плёнка PL-015</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>ISO 5800 для цветного негатива</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Главная линия</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>4</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>PL-018</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>SRC-143</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>ISO — ISO 6:1993 Camera film speed</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>https://www.iso.org/iso-6-camera-film-speed.html</t>
+        </is>
+      </c>
+      <c r="S179" t="n">
+        <v>5</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Сделать акцент: для ч/б плёнки ISO связан с рекомендованной обработкой, поэтому проявка может менять практический EI.</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Чёрно-белый негатив, проявочный бачок и карточка ISO 400/27°.</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>#PL018 #ISO6 #black-and-white #negative #film-speed</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>46.2044, 6.1432</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>ISO плёнки / чёрно-белый негатив</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="17" customHeight="1" s="59">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>PL-HIST-0179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1987 / 2001</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>точная дата</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>международно</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Женева</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>International Organization for Standardization</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>ISO 5800 описывает определение ISO-светочувствительности цветных негативных плёнок для статической фотографии.</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>ISO 5800 / colour negative film speed</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Цветной негатив получает измеримый стандарт: коробочный ISO перестаёт быть рекламным числом и становится частью воспроизводимой системы.</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Цветная негативная плёнка PL-016</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Практический выбор ISO под свет и сюжет</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Главная линия</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>4</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>PL-018</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>SRC-144</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>ISO — ISO 5800:1987 Colour negative films</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>https://www.iso.org/standard/11948.html</t>
+        </is>
+      </c>
+      <c r="S180" t="n">
+        <v>5</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Здесь удобно связать PL-016 и PL-018: цветной негатив — материал; ISO — его чувствительность.</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Цветной негатив с оранжевой маской, рядом маркировка ISO 400/27°.</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>#PL018 #ISO5800 #color-negative #film-speed</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>46.2044, 6.1432</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>ISO плёнки / цветной негатив</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="17" customHeight="1" s="59">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>PL-HIST-0180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>год</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>международно</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Женева</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>International Organization for Standardization</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>ISO 2240 задаёт метод определения светочувствительности цветных обращаемых плёнок — материалов, которые смотрят на просвет или проецируют как слайды.</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>ISO 2240 / colour reversal film speed</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Слайдовая плёнка получает отдельную логику стандартизации, потому что результат — сразу позитивная прозрачность, а не печатный негатив.</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Слайдовая плёнка PL-017</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта слайда PL-020</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Главная линия</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>4</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>PL-018</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>SRC-145</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>ISO — ISO 2240:2003 Colour reversal camera films</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>https://www.iso.org/standard/34533.html</t>
+        </is>
+      </c>
+      <c r="S181" t="n">
+        <v>5</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Мост к PL-020: у слайда ISO и экспозиция особенно критичны из-за узкого диапазона ошибки.</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Слайд в рамке на световом столе и подпись ISO 100/21° без лишней инфографики.</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>#PL018 #ISO2240 #slide-film #reversal #ISO</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>46.2044, 6.1432</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>ISO плёнки / слайдовая плёнка</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="17" customHeight="1" s="59">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>PL-HIST-0181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>США / глобально</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Рочестер / кинолаборатории</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Eastman Kodak Company / операторы / фотографы</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Exposure Index показывает практическую рабочую настройку чувствительности: EI не всегда нужно понимать как абсолютно неизменную скорость материала.</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Exposure Index / EI</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Появляется важное различие: box speed — рекомендация производителя, EI — выбранная фотографом рабочая настройка под задачу и обработку.</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>ISO как стандартная маркировка</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Push/pull и тестирование конкретной плёнки</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое управление</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>5</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>PL-018</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>SRC-148</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Kodak — Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/motion/page/frequently-asked-questions/</t>
+        </is>
+      </c>
+      <c r="S182" t="n">
+        <v>5</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Объяснить просто: ISO написан на коробке, EI — как ты реально решил снимать этот материал.</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Коробка ISO 400, экспонометр выставлен на EI 800; рядом заметка «push +1».</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>#PL018 #EI #exposure-index #box-speed #push</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Формулировать аккуратно: EI не отменяет стандартизированный ISO, а описывает практическую настройку.</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>ISO плёнки / box speed и EI</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>Терминология / язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="17" customHeight="1" s="59">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>PL-HIST-0182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>XX век</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Рочестер, Нью-Йорк</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Eastman Kodak Company</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Kodak формулирует экспозицию как баланс четырёх вещей: времени выдержки, отверстия объектива, яркости сцены и скорости / EI плёнки.</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Film speed in exposure calculation</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>ISO становится частью экспозиционного треугольника: он не работает отдельно, а связан с выдержкой, диафрагмой и реальным светом сцены.</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>EI как практическая настройка</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Модуль экспозиции PL-041–PL-050</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>5</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>PL-018</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>SRC-147</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Kodak — Essential Reference Guide for Filmmakers</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/content/products-brochures/Film/kodak-essential-reference-guide-for-filmmakers.pdf</t>
+        </is>
+      </c>
+      <c r="S183" t="n">
+        <v>5</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Это лучший мост в будущий модуль экспозиции: ISO — не магия, а один из параметров расчёта света.</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Схема: сцена → объектив → плёнка; вокруг четыре подписи: свет, диафрагма, выдержка, ISO/EI.</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>#PL018 #exposure #aperture #shutter #film-speed</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>ISO плёнки / связь с экспозицией</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="17" customHeight="1" s="59">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>PL-HIST-0183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>фотомагазины и камеры</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Производители плёнки / фотографы</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Box speed становится бытовым интерфейсом плёнки: фотограф видит ISO 50, 100, 400 или 3200 и сразу понимает, в каком свете материалу комфортнее.</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Box speed / nominal sensitivity</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Выбор плёнки становится практическим: солнечный день, помещение, вечер, движение — всё это связано с ISO ещё до настройки камеры.</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Стандарты ISO</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Выбор низкой, средней и высокой чувствительности</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Распространение / коммерциализация</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>4</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>PL-018</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>SRC-152</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Kodak — Still Film Products</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/still-film/products/</t>
+        </is>
+      </c>
+      <c r="S184" t="n">
+        <v>5</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Можно показать как «этикетку света»: ISO на коробке — первое решение фотографа до съёмки.</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Полка фотомагазина с коробками плёнки разной чувствительности; крупно видны числа ISO.</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>#PL018 #box-speed #film-choice #ISO #photostore</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>ISO плёнки / коробочный ISO</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>Распространение / коммерциализация</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="17" customHeight="1" s="59">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>PL-HIST-0184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Великобритания / глобально</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Мобберли, Чешир / практика съёмки</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>ILFORD PHOTO / фотографы</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>ILFORD HP5 PLUS закрепляет практический образ ISO 400: универсальная высокочувствительная чёрно-белая плёнка для репортажа, улицы, путешествий и слабого света.</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>ISO 400 high-speed black-and-white film</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>ISO 400 становится стартовой универсальной точкой: достаточно чувствительно для жизни, но ещё контролируемо по зерну и контрасту.</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Box speed как выбор плёнки</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Push до EI 3200 и практическая гибкость</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальный язык</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>4</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>PL-018</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>SRC-149</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>ILFORD — HP5 PLUS 35mm</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/hp5-plus-35mm?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="S185" t="n">
+        <v>5</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Связать с твоим личным маршрутом входа в плёнку: ISO 400 — понятный первый выбор для переменного света.</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Кассета HP5 PLUS рядом с камерой; окно, пасмурный свет, заметка «ISO 400».</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>#PL018 #HP5 #ISO400 #black-and-white #available-light</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>53.3160, -2.3180</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>ISO плёнки / универсальный ISO 400</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="17" customHeight="1" s="59">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>PL-HIST-0185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Великобритания / глобально</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Мобберли, Чешир / ночная съёмка</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>ILFORD PHOTO / фотографы</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>DELTA 3200 показывает верхнюю сторону ISO: высокая чувствительность даёт возможность снимать в слабом свете, но делает характер изображения более активным.</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>EI 3200 high-speed film</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Фотограф получает инструмент для ночи, концертов и движения; ISO становится не только техникой, но и эстетическим выбором.</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>ISO 400 как универсальный старт</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Зерно PL-019</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальный язык</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>4</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>PL-018</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>SRC-150</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>ILFORD — DELTA 3200 PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/delta-3200-professional-bulk-length-film?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="S186" t="n">
+        <v>5</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Важно: высокий ISO — это не «хуже», а другой компромисс света, зерна и настроения.</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Ночная улица, плёнка DELTA 3200, свет фонаря и заметная фактура кадра.</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>#PL018 #Delta3200 #high-speed-film #low-light #grain</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>53.3160, -2.3180</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>ISO плёнки / высокая чувствительность</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="17" customHeight="1" s="59">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>PL-HIST-0186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>США / глобально</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>лаборатории и съёмочные площадки</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Kodak / фотографы / лаборатории</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Push/pull закрепляет идею, что практическая чувствительность связана не только со съёмкой, но и с последующей обработкой.</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Push / Pull processing</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Если света не хватило или нужен другой характер, фотограф может намеренно экспонировать не по коробочному ISO и компенсировать это проявкой.</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>EI как рабочая настройка</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта и проявка PL-020</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое управление</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>5</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>PL-018</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>SRC-151</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>Kodak — Push / Pull Film Processing</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/motion/page/push-pull-processing/</t>
+        </is>
+      </c>
+      <c r="S187" t="n">
+        <v>5</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Финальный мост: ISO — это точка старта, но плёнка живёт в связке «экспонирование + проявление».</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Плёнка ISO 400, экспонометр EI 800, проявочный бак и карточка «push +1».</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>#PL018 #push-pull #EI #processing #film-lab</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Не обещать, что push реально повышает физическую чувствительность; объяснять как компенсацию обработки.</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>ISO плёнки / push-pull</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="17" customHeight="1" s="59">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>PL-HIST-0187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>XIX–XXI век</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>оптический эффект в эмульсии</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Химики фотографии, исследователи денситометрии, производители плёнки</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>«Зерно» на снимке — не сам кристалл эмульсии, а оптический эффект: отдельные микрокристаллы серебра слишком малы, чтобы их различить глазом, а видимую фактуру создают более крупные, случайно расположенные скопления проявленного серебра (или облака красителя), которые перекрываются между собой.</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Grain clumping / RMS granularity</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Зерно перестаёт путаться с самим кристаллом эмульсии: то, что видит глаз, сканер или увеличитель, — статистическая неравномерность плотности от скоплений серебра, а не форма одной частицы. Поэтому зернистость можно измерить числом (RMS granularity), а не только оценить на глаз.</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Эмульсия PL-012</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Видимое зерно как язык чёрно-белой плёнки</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Главная линия</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>5</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>PL-019</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>SRC-166</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Wikipedia — Film grain</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Film_grain</t>
+        </is>
+      </c>
+      <c r="S188" t="n">
+        <v>4</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Флагман урока: важно развести три вещи — микроскопический кристалл в эмульсии, проявленное металлическое серебро и видимое зерно на отпечатке/скане, которое является оптическим эффектом скоплений, а не самим кристаллом.</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Три масштаба одного кадра: невидимый кристалл под микроскопом, скопления проявленного серебра и видимое зерно на увеличенном отпечатке.</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>#PL019 #grain #RMS-granularity #optical-effect #silver-clumping</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>Зерно / оптический эффект vs кристалл</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="17" customHeight="1" s="59">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>PL-HIST-0188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>съёмочная практика</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Фотографы / производители плёнки</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Связь ISO и зерна становится главным компромиссом материала: медленные плёнки обычно дают более тонкую фактуру, быстрые — больше свободы в слабом свете.</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Speed-grain tradeoff</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Фотограф начинает выбирать не только чувствительность, но и характер изображения: гладкость, фактура, резкость, атмосфера.</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>ISO плёнки PL-018</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Медленная и высокочувствительная плёнка как разные визуальные решения</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальный язык</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>5</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>PL-019</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>SRC-154</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>ILFORD — PAN F PLUS 35mm</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/pan-f-plus-35mm?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="S189" t="n">
+        <v>5</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Формулировать без абсолютов: зерно зависит не только от ISO, но ISO — один из самых понятных факторов для новичка.</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Два увеличенных фрагмента одного сюжета: ISO 50 гладко, ISO 3200 фактурно.</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>#PL019 #ISO #grain #film-speed #texture</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Не превращать в жёсткое правило: современные эмульсии могут быть быстрыми и сравнительно мелкозернистыми.</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>Зерно / компромисс ISO и фактуры</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="17" customHeight="1" s="59">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>PL-HIST-0189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Великобритания / глобально</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Мобберли, Чешир</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>ILFORD PHOTO</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>ILFORD PAN F PLUS показывает край медленной плёнки: ISO 50, высокая резкость и очень тонкое зерно для сцен, где света достаточно.</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Slow-speed fine grain black-and-white film</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Медленная плёнка становится выбором для детализации, спокойного света, штатива, студии, пейзажа и fine art-подхода.</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Зерно как оптический эффект скоплений серебра</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>FP4 PLUS как более универсальный средний вариант</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальный язык</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>4</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>PL-019</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>SRC-154</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>ILFORD — PAN F PLUS 35mm</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/pan-f-plus-35mm?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="S190" t="n">
+        <v>5</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Практический вывод: низкий ISO любит свет и дисциплину, зато может дать более гладкую фактуру.</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Плёнка PAN F PLUS, штатив, студийный предмет или пейзаж в ярком дневном свете.</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>#PL019 #PANF #ISO50 #fine-grain #detail</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>53.3160, -2.3180</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>Зерно / медленная плёнка</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="17" customHeight="1" s="59">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>PL-HIST-0190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Великобритания / глобально</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Мобберли, Чешир</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>ILFORD PHOTO</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>FP4 PLUS показывает среднюю чувствительность: ISO 125, очень мелкое зерно, резкость и широкая применимость без экстремального света.</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Medium-speed fine grain film</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Появляется понятный компромисс: не настолько медленно, как ISO 50, но всё ещё очень чисто и детально.</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Медленная плёнка ISO 50</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>ISO 400 как универсальная высокая чувствительность</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое управление</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>4</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>PL-019</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>SRC-155</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>ILFORD — FP4 PLUS Sheet Film</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/fp4-plus-sheet-film?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="S191" t="n">
+        <v>5</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Для новичка FP4 можно объяснить как «точная спокойная плёнка»: требует света, но не такая строгая, как ISO 50.</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Кассета FP4 PLUS, светлый натюрморт и увеличитель/лупа на краю кадра.</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>#PL019 #FP4 #ISO125 #fine-grain #sharpness</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>53.3160, -2.3180</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>Зерно / средняя чувствительность</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="17" customHeight="1" s="59">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>PL-HIST-0191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Великобритания / глобально</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Мобберли, Чешир</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>ILFORD PHOTO</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>HP5 PLUS показывает практический баланс ISO 400: достаточно света для репортажа и помещения, заметный плёночный характер и широкая экспозиционная гибкость.</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>ISO 400 classic grain / all-purpose film</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Зерно становится частью живого изображения, а не только техническим ограничением; ISO 400 часто выбирают именно за универсальный характер.</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Средняя чувствительность ISO 125</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Высокая чувствительность и выразительное зерно</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальный язык</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>5</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>PL-019</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>SRC-149</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>ILFORD — HP5 PLUS 35mm</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/hp5-plus-35mm?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="S192" t="n">
+        <v>5</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Связать с реальными условиями съёмки: ISO 400 не идеален математически, но удобен в жизни.</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Уличный кадр на HP5: мягкий контраст, фактура, движение и свет из окна.</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>#PL019 #HP5 #ISO400 #grain #documentary</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>53.3160, -2.3180</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>Зерно / классический ISO 400</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="17" customHeight="1" s="59">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>PL-HIST-0192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Великобритания / глобально</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Мобберли, Чешир</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>ILFORD PHOTO</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>DELTA Professional показывает, что форма кристаллов и технология эмульсии меняют вид зерна: более новая структура может дать чище тон и выше резкость.</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Core-Shell crystal technology / DELTA films</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Зерно перестаёт быть только вопросом ISO: технология кристаллов, эмульсия и разработка производителя формируют характер материала.</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Классические PLUS-плёнки</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Kodak T-GRAIN как параллельная технологическая линия</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Главная линия</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>5</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>PL-019</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>SRC-157</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>ILFORD — Film FAQs</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/faqs/ilford-film-faqs/?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="S193" t="n">
+        <v>5</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Сравнить PLUS и DELTA без оценки «лучше/хуже»: это разные эстетики и технологии.</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Две полоски негатива: традиционная кубическая фактура и более чистая modern-emulsion фактура.</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>#PL019 #Delta #CoreShell #emulsion #grain-structure</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>53.3160, -2.3180</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>Зерно / структура кристаллов</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="17" customHeight="1" s="59">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>PL-HIST-0193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>XX век</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Рочестер, Нью-Йорк</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Eastman Kodak Company</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Kodak T-GRAIN описывает таблетчатые кристаллы вместо традиционных серебряных кристаллов: такая форма помогает совмещать скорость и более мелкое зерно.</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>KODAK T-GRAIN Emulsion</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Технология зерна становится инженерным инструментом: производитель меняет форму кристалла, чтобы изменить резкость, светопоглощение и вид изображения.</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>ILFORD Core-Shell / новые эмульсии</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>T-MAX как практический пример T-GRAIN</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Главная линия</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>5</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>PL-019</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>SRC-158</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Kodak — Glossary of Motion Picture Terms</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/motion/page/glossary-of-motion-picture-terms/</t>
+        </is>
+      </c>
+      <c r="S194" t="n">
+        <v>5</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Показать на схеме: кубик и плоская таблетка — не как химия для специалистов, а как понятная форма.</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Инфографика двух кристаллов: conventional grain и flat T-GRAIN, с мягким светом и увеличенным негативом.</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>#PL019 #Tgrain #Kodak #emulsion #fine-grain</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>Зерно / T-GRAIN</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="17" customHeight="1" s="59">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>PL-HIST-0194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>США / глобально</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Рочестер / фотолаборатории</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Kodak Professional / фотографы</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>T-MAX 100 показывает, как мелкозернистый материал используется для максимальной детализации, больших увеличений и чистой тональной работы.</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>KODAK T-MAX 100 / fine grain film</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Мелкое зерно становится выбором для печати, сканирования и fine art-изображений, где важна гладкая фактура и детализация.</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>T-GRAIN как инженерная технология</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Ультравысокая чувствительность как другой компромисс</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальный язык</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>4</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>PL-019</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>SRC-159</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Kodak Professional — T-MAX 100 Film</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>https://www.kodakprofessional.com/photographers/film/black-white/kodak-professional-t-max-100-film/525</t>
+        </is>
+      </c>
+      <c r="S195" t="n">
+        <v>5</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Это хороший мост к твоим fine art объектам: зерно влияет на масштаб печати и ощущение поверхности.</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Большой отпечаток с лупой, рядом негатив T-MAX 100 и шкала увеличения.</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>#PL019 #TMAX100 #fine-grain #print #fine-art</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>Зерно / мелкозернистая плёнка</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="17" customHeight="1" s="59">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>PL-HIST-0195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>США / глобально</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Рочестер / ночная и концертная съёмка</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Kodak Professional / фотографы</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>T-MAX P3200 показывает, что высокая чувствительность может быть отдельным художественным инструментом: зерно, контраст и движение становятся частью языка.</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>KODAK T-MAX P3200 / ultra-high speed film</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Высокая чувствительность даёт съёмку там, где медленная плёнка невозможна; фотограф платит за это активной фактурой и более сложной экспозицией.</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Мелкозернистая T-MAX 100</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Проявка и push-практика</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальный язык</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>4</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>PL-019</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>SRC-160</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>Kodak Professional — T-MAX P3200 Technical Data</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>https://www.kodakprofessional.com/sites/default/files/wysiwyg/pro/resources/f4001_tmax_3200_0.pdf</t>
+        </is>
+      </c>
+      <c r="S196" t="n">
+        <v>5</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Не говорить «зерно — плохо»: для репортажа, сцены и ночи оно часто усиливает ощущение жизни.</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Ночной портрет, зернистая фактура, кассета T-MAX P3200 и свет вывески.</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>#PL019 #TMAXP3200 #high-speed #grain #low-light</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>Зерно / высокая чувствительность</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="17" customHeight="1" s="59">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>PL-HIST-0196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>США / глобально</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Рочестер / цветная фотоплёнка</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Kodak / фотографы</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>На цветной плёнке зернистость ощущается иначе: цветное изображение строится через слои и красители, а низкочувствительные плёнки вроде EKTAR 100 ориентированы на гладкость и насыщенный цвет.</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Цвет</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Color negative fine grain / dye image</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Зерно становится важным не только в ч/б, но и в цвете: оно влияет на сканы, печать, кожу, небо и большие увеличения.</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Чёрно-белое зерно как серебряная фактура</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта цветного негатива PL-020</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальный язык</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>4</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>PL-019</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>SRC-161</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Kodak — EKTAR 100 Film</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/still-film/product/professional/ektar-100-film/</t>
+        </is>
+      </c>
+      <c r="S197" t="n">
+        <v>5</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Связать с печатью: гладкое цветное зерно важно для больших интерьерных отпечатков.</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Крупный отпечаток цветного пейзажа, коробка EKTAR 100, лупа на участке неба.</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>#PL019 #Ektar100 #color-negative #fine-grain #print</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>Зерно / цветная плёнка</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="17" customHeight="1" s="59">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>PL-HIST-0197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Великобритания / глобально</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>лаборатории и сканирование</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>ILFORD PHOTO / лаборатории / фотографы</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Проявитель и сканирование меняют вид зерна: одни проявители уменьшают зернистость, а резкое цифровое шарпление может сделать зерно заметнее.</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Developer choice and scanning grain</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Фотограф понимает, что зерно формируется не только в камере: проявка, сканер, резкость и печать тоже влияют на итоговую фактуру.</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Выбор плёнки по зерну</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта и обработка PL-020</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое управление</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>5</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>PL-019</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>SRC-156</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>ILFORD — Introduction to ILFORD Film Developers</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/beginners-guide-film-developers/?___from_store=ilford_uk</t>
+        </is>
+      </c>
+      <c r="S198" t="n">
+        <v>5</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Финальная мысль: зерно — это цепочка «плёнка + экспозиция + проявка + скан/печать».</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Один негатив и три варианта скана/печати: мягко, резко, зернисто; рядом проявочные бутылки.</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>#PL019 #developer #scanning #grain #print</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Добавить при необходимости отдельный источник по цифровому шуму, чтобы точно развести noise и grain.</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>53.3160, -2.3180</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>Зерно / проявка и сканирование</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="17" customHeight="1" s="59">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>PL-HIST-0198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>XX век</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Рочестер, Нью-Йорк</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Eastman Kodak Company / сенситометрия</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Экспозиционную широту можно объяснить через характеристическую кривую: плёнка записывает свет не бесконечно, а в пределах полезного диапазона.</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Exposure latitude / characteristic curve</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Фотограф начинает видеть экспозицию как диапазон допуска: часть ошибок материал выдерживает, часть уже теряет тени или света.</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>ISO плёнки PL-018 и зерно PL-019</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Тень, средние тона и света на кривой плёнки</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Главная линия</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>5</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>PL-020</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>SRC-162</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Kodak — Basic Photographic Sensitometry Workbook</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/content/products-brochures/Film/Basic-Photographic-Sensitometry-Workbook.pdf</t>
+        </is>
+      </c>
+      <c r="S199" t="n">
+        <v>5</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Флагман урока: широта — это не «сколько можно ошибаться», а сколько света плёнка способна перевести в полезный тон.</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Простая H-D кривая: toe, straight line, shoulder; рядом один негатив с тенями и светами.</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>#PL020 #exposure-latitude #sensitometry #characteristic-curve #film</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Объяснить без математической перегрузки: кривая нужна как образ, не как полноценная сенситометрическая лекция.</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / характеристическая кривая</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="17" customHeight="1" s="59">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>PL-HIST-0199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>XX век</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Рочестер, Нью-Йорк</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Eastman Kodak Company</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Характеристическая кривая делится на три зоны: toe, straight-line и shoulder — тени, рабочие средние тона и область перегруза светов.</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Toe / straight line / shoulder</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Появляется простой язык для ошибок экспозиции: недодержка проваливается в toe, нормальная экспозиция живёт на прямом участке, передержка упирается в shoulder.</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Широта как общий диапазон</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Потеря теней и светов</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Главная линия</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>5</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>PL-020</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>SRC-162</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>Kodak — Basic Photographic Sensitometry Workbook</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/content/products-brochures/Film/Basic-Photographic-Sensitometry-Workbook.pdf</t>
+        </is>
+      </c>
+      <c r="S200" t="n">
+        <v>5</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Хорошо показать на одной карточке: слева темный кадр, центр нормальный, справа передержка.</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Три фрагмента негатива на одной кривой: тени, середина, света.</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>#PL020 #toe #shoulder #curve #exposure</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / toe-straight-shoulder</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>Терминология / язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="17" customHeight="1" s="59">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>PL-HIST-0200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>XX век</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Рочестер, Нью-Йорк</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Eastman Kodak Company</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Toe кривой объясняет, почему тени боятся недодержки: если света слишком мало, детали в тенях уже нечем проявить или вытянуть без грубой потери качества.</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Underexposure latitude / shadow detail</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Новичок понимает практическое правило плёнки: недостаток света опасен для теней, особенно если сюжет важен в тёмных областях.</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Характеристическая кривая</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Нормальная экспозиция по серой карте</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое управление</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>5</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>PL-020</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>SRC-158</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>Kodak — Glossary of Motion Picture Terms</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/motion/page/glossary-of-motion-picture-terms/</t>
+        </is>
+      </c>
+      <c r="S201" t="n">
+        <v>5</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Формула для урока: недодержка убивает информацию в тенях, а не просто делает кадр «темнее».</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Один негатив с прозрачными тенями и рядом увеличенный участок без деталей.</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>#PL020 #underexposure #shadows #toe #latitude</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / недодержка и тени</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="17" customHeight="1" s="59">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>PL-HIST-0201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>XX век</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Рочестер, Нью-Йорк</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Eastman Kodak Company</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Shoulder и D-Max показывают предел плотности: после некоторого уровня дополнительный свет уже не даёт пропорционального роста деталей.</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Overexposure / shoulder / D-Max</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Фотограф понимает, что передержка меняет света и контраст: иногда плёнка терпит её мягко, а иногда важные светлые детали сжимаются.</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Toe и тени</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Сравнение негатива и слайда</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое управление</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>5</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>PL-020</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>SRC-158</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Kodak — Glossary of Motion Picture Terms</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/motion/page/glossary-of-motion-picture-terms/</t>
+        </is>
+      </c>
+      <c r="S202" t="n">
+        <v>5</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Сделать аккуратно: у негатива передержка часто терпимее, но она всё равно меняет тональность и печать/скан.</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Светлая сцена: белое платье или облака; рядом плотный негатив и участок кривой shoulder.</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>#PL020 #overexposure #highlights #shoulder #Dmax</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / передержка и света</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="17" customHeight="1" s="59">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>PL-HIST-0202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>США / глобально</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Рочестер / современные фотографы</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Kodak Professional / фотографы</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Слайдовая плёнка показывает узкую экспозиционную широту: цветной позитив на самой плёнке почти не прощает ошибки, особенно в светах.</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Цвет</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Color reversal narrow exposure range</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Становится понятно, почему со слайдом экспонометрия строже: ошибка видна сразу на оригинальной прозрачности.</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Слайдовая плёнка PL-017</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Цветной негатив как более гибкий материал</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое управление</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>5</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>PL-020</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>SRC-163</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>Kodak Professional — EKTACHROME E100 FAQs 2024</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>https://www.kodakprofessional.com/sites/default/files/wysiwyg/E100%20FAQs%20PDF%202024.pdf</t>
+        </is>
+      </c>
+      <c r="S203" t="n">
+        <v>5</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Идеальная связка: слайд учит дисциплине экспозиции, негатив учит гибкости.</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Проектор и два слайда: один точный, второй с выбитыми светами.</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>#PL020 #slide-film #Ektachrome #latitude #exposure</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / слайдовая плёнка</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="17" customHeight="1" s="59">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>PL-HIST-0203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>США / глобально</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Рочестер / фотолаборатории</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Kodak / фотографы</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Цветной негатив закрепляется как материал с большой практической гибкостью: он лучше переносит вариации экспозиции и рассчитан на последующую печать или сканирование.</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Цвет</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Color negative exposure latitude</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Цветной негатив становится удобным для повседневной фотографии: он допускает несовершенный свет, быстрые решения и лабораторную интерпретацию.</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Слайдовая узкая широта</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Практика экспонирования «по теням» и сканирования</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое управление</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>5</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>PL-020</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>SRC-164</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Kodak — EKTACOLOR PRO 400 Film</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/still-film/product/professional/ektacolor/ektacolor-pro-400-film/</t>
+        </is>
+      </c>
+      <c r="S204" t="n">
+        <v>5</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Подчеркнуть отличие: негатив не «лучше» слайда, просто у него другая задача и другой допуск.</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Цветной негатив, контактный лист и сканер; рядом шкала -2/-1/0/+1/+2.</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>#PL020 #color-negative #latitude #C41 #scanning</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / цветной негатив</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="17" customHeight="1" s="59">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>PL-HIST-0204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Великобритания / глобально</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Мобберли, Чешир</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>ILFORD PHOTO / фотографы</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>HP5 PLUS показывает, что чёрно-белая негативная плёнка может иметь широкую экспозиционную широту и оставаться полезной для новичков, репортажа и сложного света.</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Негатив-позитив</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>B&amp;W negative exposure latitude</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Чёрно-белый негатив становится тренировочным материалом: он позволяет ошибаться, анализировать и учиться видеть свет без цвета.</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Чёрно-белая плёнка PL-015</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>FP4 PLUS и push/pull-практика</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое управление</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>5</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>PL-020</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>SRC-149</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>ILFORD — HP5 PLUS 35mm</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/hp5-plus-35mm?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="S205" t="n">
+        <v>5</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Связать с новичками: HP5/ISO 400 хорош как учебная плёнка именно из-за терпимости и универсальности.</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Одна сцена в окне: три негатива HP5 с разной экспозицией и один итоговый отпечаток.</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>#PL020 #HP5 #black-and-white #latitude #learning</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>53.3160, -2.3180</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / чёрно-белый негатив</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="17" customHeight="1" s="59">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>PL-HIST-0205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Великобритания / глобально</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Мобберли, Чешир</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>ILFORD PHOTO / фотографы</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>FP4 PLUS показывает более спокойную сторону широты: средняя чувствительность ISO 125, очень мелкое зерно и возможность работать выше или ниже номинала при соответствующей обработке.</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Негатив-позитив</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Exposure latitude around ISO 125</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Широта становится не только спасением ошибки, но и способом управлять контрастом, зерном и тональной пластикой.</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>HP5 как универсальная плёнка</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Push/pull как осознанная обработка</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое управление</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>4</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>PL-020</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>SRC-155</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>ILFORD — FP4 PLUS Sheet Film</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/fp4-plus-sheet-film?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="S206" t="n">
+        <v>5</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Показать, что даже низко/среднечувствительная плёнка не обязательно «хрупкая», но требует понимания света.</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>FP4 PLUS, серый клин и таблица экспозиции с аккуратными отметками -1/0/+1.</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>#PL020 #FP4 #ISO125 #latitude #tone</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>53.3160, -2.3180</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / средняя чувствительность</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="17" customHeight="1" s="59">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>PL-HIST-0206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>США / глобально</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>лаборатории</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Kodak / лаборатории / фотографы</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Push/pull processing показывает, что широта связана с обработкой: нестандартную экспозицию можно частично компенсировать изменением процесса.</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Push/Pull as exposure compensation</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Плёнка становится управляемой системой: результат зависит не только от того, сколько света попало, но и от того, как негатив проявили.</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>ISO и EI PL-018</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Проявка, сканирование и печать PL-081–PL-090</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое управление</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>5</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>PL-020</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>SRC-151</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Kodak — Push / Pull Film Processing</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/motion/page/push-pull-processing/</t>
+        </is>
+      </c>
+      <c r="S207" t="n">
+        <v>5</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Сказать честно: push/pull не возвращает чудесно потерянную информацию, но помогает получить рабочий результат и нужный контраст.</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Проявочный бак, карточки push +1 / pull -1 и три полоски негатива разной плотности.</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>#PL020 #push-pull #processing #latitude #EI</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Не обещать полное спасение сильно ошибочной экспозиции; диапазон зависит от плёнки, сцены и лаборатории.</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / push-pull</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="17" customHeight="1" s="59">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>PL-HIST-0207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>США / глобально</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>съёмочная площадка / фотостудия</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Kodak / операторы / фотографы</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Серая карта и нормальная экспозиция помогают получить full-range negative: негатив, в котором есть опорная точка для последующей печати, сканирования или грейдинга.</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Gray card / normal exposure / full-range negative</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Широта не отменяет дисциплину: правильная опорная экспозиция даёт больше свободы после съёмки, чем случайное угадывание.</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Push/pull и обработка</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Модуль экспонометра PL-049</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>4</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>PL-020</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>SRC-165</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Kodak — Gray Card for the Cinematographer</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/motion/page/for-the-cinematographer/</t>
+        </is>
+      </c>
+      <c r="S208" t="n">
+        <v>5</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Мост в будущую экспозицию: экспонометр и серая карта нужны не ради правил, а ради управляемого негатива.</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Фотограф держит серую карту перед сценой; рядом экспонометр и негативная полоса.</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>#PL020 #gray-card #metering #full-range-negative #exposure</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>43.1566, -77.6088</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / серая карта</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="17" customHeight="1" s="59">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>PL-HIST-0208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>XX–XXI век</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>практика съёмки и печати</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Фотографы, лаборатории, сканировщики</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Практический вывод PL-020: экспозиционная широта — это запас материала, но не повод снимать бездумно; она влияет на тени, света, зерно, контраст и итоговую печать.</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Practical exposure latitude workflow</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Фотограф начинает мыслить финальным изображением: что сохранить в тенях, что допустить в светах, как негатив потом будет сканироваться или печататься.</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Сенситометрия и типы плёнок</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Переход к плёночным камерам PL-021 и будущей экспозиции</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>5</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>PL-020</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>SRC-162</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>Kodak — Basic Photographic Sensitometry Workbook</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/content/products-brochures/Film/Basic-Photographic-Sensitometry-Workbook.pdf</t>
+        </is>
+      </c>
+      <c r="S209" t="n">
+        <v>5</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Финал Модуля 2: мы поняли материал. Дальше логично перейти к камере, которая этот материал экспонирует.</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Одна сцена и три решения: сохранить тени, сохранить света, средняя экспозиция; рядом готовый отпечаток.</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>#PL020 #exposure-latitude #tone #print #film-workflow</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / практический выбор</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
     <row r="210" ht="17" customHeight="1" s="59"/>
     <row r="211" ht="17" customHeight="1" s="59"/>
     <row r="212" ht="17" customHeight="1" s="59"/>
@@ -24193,12 +28258,12 @@
       </c>
       <c r="B4" s="63" t="inlineStr">
         <is>
-          <t>серебряные соли, желатиновые эмульсии, скрытое изображение, проявление, чувствительность, спектральная чувствительность, зерно, цветные слои, color couplers, C-41, E-6, reversal-процесс</t>
+          <t>серебряные соли, желатиновые эмульсии, скрытое изображение, проявление, чувствительность, ISO / film speed, EI, push/pull, спектральная чувствительность, зерно, цветные слои, color couplers, C-41, E-6, reversal-процесс, экспозиционная широта, сенситометрия / характеристическая кривая</t>
         </is>
       </c>
       <c r="C4" s="63" t="inlineStr">
         <is>
-          <t>PL-002 / PL-006 / PL-011 / PL-012 / PL-015 / PL-016 / PL-017</t>
+          <t>PL-002 / PL-006 / PL-011 / PL-012 / PL-015 / PL-016 / PL-017 / PL-018 / PL-019 / PL-020</t>
         </is>
       </c>
       <c r="D4" s="63" t="inlineStr">
@@ -24208,7 +28273,7 @@
       </c>
       <c r="E4" s="63" t="inlineStr">
         <is>
-          <t>Химическая половина рождения фотографии: от серебряного изображения к цветным красителям.</t>
+          <t>Химическая половина рождения фотографии: от серебряного изображения к чувствительности, зерну, цвету и экспозиционному диапазону материала.</t>
         </is>
       </c>
     </row>
@@ -24301,12 +28366,12 @@
       </c>
       <c r="B8" s="63" t="inlineStr">
         <is>
-          <t>бумажный негатив, калотип, стеклянный негатив, сухая пластина, плёночный негатив, чёрно-белый негатив, цветной негатив, позитивный отпечаток</t>
+          <t>бумажный негатив, калотип, стеклянный негатив, сухая пластина, плёночный негатив, чёрно-белый негатив, цветной негатив, позитивный отпечаток, экспозиционная широта негативных материалов</t>
         </is>
       </c>
       <c r="C8" s="63" t="inlineStr">
         <is>
-          <t>PL-004 / PL-006 / PL-013 / PL-014 / PL-015 / PL-016</t>
+          <t>PL-004 / PL-006 / PL-013 / PL-014 / PL-015 / PL-016 / PL-020</t>
         </is>
       </c>
       <c r="D8" s="63" t="inlineStr">
@@ -24316,34 +28381,34 @@
       </c>
       <c r="E8" s="63" t="inlineStr">
         <is>
-          <t>Главная идея, которая победила исторически: негатив становится матрицей для будущего позитива.</t>
+          <t>Главная идея, которая победила исторически: негатив становится матрицей для будущего позитива и допускает интерпретацию при печати/сканировании.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1" s="59">
       <c r="A9" s="63" t="inlineStr">
         <is>
-          <t>Фиксаж / терминология</t>
+          <t>Печать / тиражирование</t>
         </is>
       </c>
       <c r="B9" s="63" t="inlineStr">
         <is>
-          <t>Herschel, hypo, terms photography/negative/positive, фиксация серебряно-желатиновых материалов и ч/б плёнки</t>
+          <t>salt print, albumen print, gelatin silver print, POP/DOP, chromogenic print, фотокнига, лабораторная и сервисная печать, цветная печать с негатива, влияние зерна и экспозиции на скан/отпечаток</t>
         </is>
       </c>
       <c r="C9" s="63" t="inlineStr">
         <is>
-          <t>PL-004 / PL-012 / PL-013 / PL-015</t>
+          <t>PL-004 / PL-013 / PL-014 / PL-015 / PL-016 / PL-019 / PL-020</t>
         </is>
       </c>
       <c r="D9" s="63" t="inlineStr">
         <is>
-          <t>фиолетовый</t>
+          <t>оранжевый</t>
         </is>
       </c>
       <c r="E9" s="63" t="inlineStr">
         <is>
-          <t>Фотография нуждается в языке и стабильности.</t>
+          <t>Ветка распространения изображений: от единичного отпечатка к массовому фотосервису и авторскому управлению финальной фактурой.</t>
         </is>
       </c>
     </row>
@@ -24377,54 +28442,54 @@
     <row r="11" ht="21" customHeight="1" s="59">
       <c r="A11" s="63" t="inlineStr">
         <is>
-          <t>Мокрый коллодий</t>
+          <t>Уникальный позитив</t>
         </is>
       </c>
       <c r="B11" s="63" t="inlineStr">
         <is>
-          <t>стеклянный негатив, коллодий, нитрат серебра</t>
+          <t>ранний цвет, Autochrome, Kodachrome, Kodacolor, Ektachrome, цветная негативная и слайдовая плёнка, chromogenic print, C-41, E-6, узкая широта слайдового позитива</t>
         </is>
       </c>
       <c r="C11" s="63" t="inlineStr">
         <is>
-          <t>PL-005</t>
+          <t>PL-014 / PL-016 / PL-017 / PL-020 / будущие PL</t>
         </is>
       </c>
       <c r="D11" s="63" t="inlineStr">
         <is>
-          <t>красный</t>
+          <t>серый</t>
         </is>
       </c>
       <c r="E11" s="63" t="inlineStr">
         <is>
-          <t>Мост между резкостью и тиражом.</t>
+          <t>Важные, но технологически ограниченные ветки; слайдовая прозрачность особенно хорошо показывает цену ошибки экспозиции.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1" s="59">
       <c r="A12" s="63" t="inlineStr">
         <is>
-          <t>Уникальный позитив</t>
+          <t>Цвет</t>
         </is>
       </c>
       <c r="B12" s="63" t="inlineStr">
         <is>
-          <t>ранний цвет, Autochrome, Kodachrome, Kodacolor, Ektachrome, цветная негативная и слайдовая плёнка, chromogenic print, C-41, E-6</t>
+          <t>цветные негативы, слайды, прозрачности, projected positive, Kodachrome, Ektachrome, EKTAR, EKTACOLOR, цветное зерно/красители, широта цветного негатива и слайда</t>
         </is>
       </c>
       <c r="C12" s="63" t="inlineStr">
         <is>
-          <t>PL-014 / PL-016 / PL-017 / будущие PL</t>
+          <t>PL-016 / PL-017 / PL-019 / PL-020 / будущие PL</t>
         </is>
       </c>
       <c r="D12" s="63" t="inlineStr">
         <is>
-          <t>серый</t>
+          <t>радужный</t>
         </is>
       </c>
       <c r="E12" s="63" t="inlineStr">
         <is>
-          <t>Важные, но технологически ограниченные ветки.</t>
+          <t>Цветная фотография как отдельная технологическая и визуальная линия: материал, проявка, просмотр, печать и экспозиционный допуск.</t>
         </is>
       </c>
     </row>
@@ -24496,7 +28561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="9.6640625" customWidth="1" style="59" min="1" max="1"/>
@@ -24887,7 +28952,7 @@
       </c>
       <c r="F12" s="62" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf_pro/4/145</t>
+          <t>https://t.me/photolab_vf</t>
         </is>
       </c>
     </row>
@@ -24919,7 +28984,7 @@
       </c>
       <c r="F13" s="62" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf_pro/4/151</t>
+          <t>https://t.me/photolab_vf</t>
         </is>
       </c>
     </row>
@@ -24951,7 +29016,7 @@
       </c>
       <c r="F14" s="62" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf_pro/4/162</t>
+          <t>https://t.me/photolab_vf</t>
         </is>
       </c>
     </row>
@@ -24983,7 +29048,7 @@
       </c>
       <c r="F15" s="62" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf_pro/4/168</t>
+          <t>https://t.me/photolab_vf</t>
         </is>
       </c>
     </row>
@@ -25015,7 +29080,7 @@
       </c>
       <c r="F16" s="62" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf_pro/4/173</t>
+          <t>https://t.me/photolab_vf</t>
         </is>
       </c>
     </row>
@@ -25047,7 +29112,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf_pro/4/181</t>
+          <t>https://t.me/photolab_vf</t>
         </is>
       </c>
     </row>
@@ -25086,30 +29151,125 @@
     <row r="19">
       <c r="A19" s="62" t="inlineStr">
         <is>
+          <t>PL-018</t>
+        </is>
+      </c>
+      <c r="B19" s="62" t="inlineStr">
+        <is>
+          <t>ISO плёнки</t>
+        </is>
+      </c>
+      <c r="C19" s="62" t="inlineStr">
+        <is>
+          <t>PL-HIST-0176…0186</t>
+        </is>
+      </c>
+      <c r="D19" s="62" t="inlineStr">
+        <is>
+          <t>ISO — это язык светочувствительности плёнки: число на коробке помогает выбрать материал под свет, связать его с выдержкой/диафрагмой и понять разницу между box speed, EI и push/pull.</t>
+        </is>
+      </c>
+      <c r="E19" s="62" t="inlineStr">
+        <is>
+          <t>основа заполнена</t>
+        </is>
+      </c>
+      <c r="F19" s="62" t="inlineStr">
+        <is>
+          <t>https://t.me/photolab_vf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PL-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Зерно</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PL-HIST-0187…0197</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Зерно — это не цифровой шум и не просто дефект, а материальная фактура плёнки: кристаллы, эмульсия, ISO, проявитель, сканирование и печать формируют характер изображения.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>основа заполнена</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://t.me/photolab_vf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PL-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PL-HIST-0198…0208</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта — это запас материала: плёнка может выдержать часть ошибок экспозиции, но тени, света, контраст, зерно и печать всё равно меняются.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>основа заполнена</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://t.me/photolab_vf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>будущие PL</t>
         </is>
       </c>
-      <c r="B19" s="62" t="inlineStr">
-        <is>
-          <t>Расширение после PL-017</t>
-        </is>
-      </c>
-      <c r="C19" s="62" t="inlineStr">
-        <is>
-          <t>ISO плёнки, зерно, экспозиционная широта</t>
-        </is>
-      </c>
-      <c r="D19" s="62" t="inlineStr">
-        <is>
-          <t>После слайдовой плёнки курс переходит к практическим параметрам материала: ISO, зерно и экспозиционная широта.</t>
-        </is>
-      </c>
-      <c r="E19" s="62" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Расширение после PL-020</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Плёночные камеры, механика, автоматика, дальномерные и зеркальные системы</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>После материала плёнки курс переходит к устройству камер: как камера держит плёнку, открывает путь свету и помогает управлять кадром.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
-      <c r="F19" s="62" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25125,7 +29285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E143"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="14" customWidth="1" style="59" min="1" max="1"/>
@@ -28993,6 +33153,654 @@
       <c r="E143" s="62" t="inlineStr">
         <is>
           <t>архивный источник по хранению</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>SRC-143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ISO — ISO 6:1993 Camera film speed</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://www.iso.org/iso-6-camera-film-speed.html</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Official ISO article explaining camera film speed, ASA heritage and ISO film-speed standards</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>официальный источник ISO по светочувствительности плёнки</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SRC-144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ISO — ISO 5800:1987 Colour negative films</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://www.iso.org/standard/11948.html</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Photography — Colour negative films for still photography — Determination of ISO speed</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>официальный стандарт ISO для цветных негативных плёнок</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>SRC-145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ISO — ISO 2240:2003 Colour reversal camera films</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://www.iso.org/standard/34533.html</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Method for determining ISO speed of colour reversal camera films intended for viewing as transparencies or projection as slides</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>официальный стандарт ISO для обращаемых / слайдовых плёнок</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>SRC-146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ILFORD — Choosing your first ILFORD film</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/choosing-your-first-ilford-film/</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Film speed / ISO is the measure of film sensitivity to light; film families and speed choices explained for beginners</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>официальный учебный источник ILFORD</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>SRC-147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Kodak — Essential Reference Guide for Filmmakers</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/content/products-brochures/Film/kodak-essential-reference-guide-for-filmmakers.pdf</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Proper exposure depends on exposure time, lens opening, scene luminance and film speed / Exposure Index; includes characteristic curve basics</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>официальное справочное руководство Kodak</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>SRC-148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Kodak — Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/motion/page/frequently-asked-questions/</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Exposure Index values should not be treated as absolute fixed speed values and may be adjusted after tests</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>официальный источник Kodak по EI и практическому тестированию</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>SRC-149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>ILFORD — HP5 PLUS 35mm</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/hp5-plus-35mm?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>HP5 PLUS is ISO 400 high-speed black and white film with wide exposure latitude</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>официальная страница продукта ILFORD</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>SRC-150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>ILFORD — DELTA 3200 PROFESSIONAL</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/delta-3200-professional-bulk-length-film?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>DELTA 3200 Professional: exceptionally high-speed black and white film with nominal sensitivity EI 3200/36°</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>официальная страница продукта ILFORD</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>SRC-151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Kodak — Push / Pull Film Processing</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/motion/page/push-pull-processing/</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Push/pull processing can compensate for non-standard exposure / speed conditions used for film</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>официальный источник Kodak по push/pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>SRC-152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Kodak — Still Film Products</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/still-film/products/</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Kodak still-film catalogue noting films with ISO speeds, broad exposure latitude and multi-speed push capabilities</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>официальный каталог плёнки Kodak</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>SRC-153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ILFORD — Silver halide prints</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/silver-halide</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Silver halide crystals in gelatin form part of an emulsion used to coat photographic paper or film</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>официальный источник ILFORD по серебряно-желатиновому принципу</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>SRC-154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>ILFORD — PAN F PLUS 35mm</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/pan-f-plus-35mm?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>PAN F PLUS is a slow speed black and white film offering exceptionally fine grain, sharpness and detail</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>официальная страница продукта ILFORD</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>SRC-155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>ILFORD — FP4 PLUS Sheet Film</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/fp4-plus-sheet-film?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>FP4 PLUS is medium-speed all-purpose black and white film with very fine grain, outstanding sharpness and superb exposure latitude</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>официальная страница продукта ILFORD</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>SRC-156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ILFORD — Introduction to ILFORD Film Developers</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/beginners-guide-film-developers/?___from_store=ilford_uk</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Some developers exploit film speed; others act on grain structure by reducing grain</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>официальный учебный источник ILFORD по проявителям</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>SRC-157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ILFORD — Film FAQs</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/faqs/ilford-film-faqs/?___from_store=ilford_uk&amp;___store=ilford_brochure</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Scanner auto-sharpening can enhance visible grain; DELTA films use newer Core-Shell crystal structure for finer grain and sharpness</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>официальный FAQ ILFORD</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>SRC-158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Kodak — Glossary of Motion Picture Terms</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/motion/page/glossary-of-motion-picture-terms/</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Defines T-GRAIN Emulsion, toe/shoulder/D-Max and other sensitometric terms related to film response</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>официальный словарь Kodak</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>SRC-159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Kodak Professional — T-MAX 100 Film</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://www.kodakprofessional.com/photographers/film/black-white/kodak-professional-t-max-100-film/525</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>KODAK PROFESSIONAL T-MAX 100 is described as extremely fine-grained 100-speed black-and-white film</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>официальная страница Kodak Professional</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>SRC-160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Kodak Professional — T-MAX P3200 Technical Data</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://www.kodakprofessional.com/sites/default/files/wysiwyg/pro/resources/f4001_tmax_3200_0.pdf</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>T-MAX P3200 combines high to ultra-high film speeds with finer grain than other fast black-and-white films; uses KODAK T-GRAIN emulsion</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>официальный технический PDF Kodak Professional</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SRC-161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Kodak — EKTAR 100 Film</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/still-film/product/professional/ektar-100-film/</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>EKTAR 100 is low-speed ISO 100/21° colour negative film with very smooth/fine grain positioning</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>официальная страница продукта Kodak</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>SRC-162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Kodak — Basic Photographic Sensitometry Workbook</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/content/products-brochures/Film/Basic-Photographic-Sensitometry-Workbook.pdf</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>The characteristic curve tells key film characteristics and includes toe, straight-line portion and shoulder</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>официальный учебный PDF Kodak по сенситометрии</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>SRC-163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Kodak Professional — EKTACHROME E100 FAQs 2024</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://www.kodakprofessional.com/sites/default/files/wysiwyg/E100%20FAQs%20PDF%202024.pdf</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Color reversal films have much narrower exposure range than negative-working films, about +/- half a stop</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>официальный FAQ Kodak Professional по слайдовой плёнке</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SRC-164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Kodak — EKTACOLOR PRO 400 Film</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/still-film/product/professional/ektacolor/ektacolor-pro-400-film/</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>EKTACOLOR PRO family offers outstanding exposure latitude and accommodates variations in exposure</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>официальная страница продукта Kodak</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>SRC-165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Kodak — Gray Card for the Cinematographer</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://www.kodak.com/en/motion/page/for-the-cinematographer/</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Kodak recommends normal exposure with gray card to provide a full-range negative for transfer grading and film timing</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>официальный источник Kodak по нормальной экспозиции и серой карте</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SRC-166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Wikipedia — Film grain</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Film_grain</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>PL-HIST-0187 (флагман PL-019): зерно как оптический эффект скоплений серебра, а не отдельный кристалл</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Общий образовательный источник (не производитель); проверено по содержанию статьи вручную</t>
         </is>
       </c>
     </row>
@@ -29010,7 +33818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="13.6640625" customWidth="1" style="59" min="1" max="1"/>
@@ -29552,7 +34360,7 @@
       <c r="B19" s="4" t="n"/>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>будущие PL</t>
+          <t>PL-018</t>
         </is>
       </c>
       <c r="D19" s="4" t="n"/>
@@ -29570,7 +34378,7 @@
       <c r="B20" s="4" t="n"/>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>межурочный узел</t>
+          <t>PL-019</t>
         </is>
       </c>
       <c r="D20" s="4" t="n"/>
@@ -29588,7 +34396,7 @@
       <c r="B21" s="4" t="n"/>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>проверить</t>
+          <t>PL-020</t>
         </is>
       </c>
       <c r="D21" s="4" t="n"/>
@@ -29604,7 +34412,11 @@
     <row r="22" ht="20" customHeight="1" s="59">
       <c r="A22" s="4" t="n"/>
       <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>будущие PL</t>
+        </is>
+      </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
@@ -29618,7 +34430,11 @@
     <row r="23" ht="20" customHeight="1" s="59">
       <c r="A23" s="4" t="n"/>
       <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>межурочный узел</t>
+        </is>
+      </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
@@ -29632,7 +34448,11 @@
     <row r="24" ht="20" customHeight="1" s="59">
       <c r="A24" s="4" t="n"/>
       <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
@@ -30655,6 +35475,237 @@
       <c r="H147" t="inlineStr">
         <is>
           <t>Слайдовая плёнка / хранение и архив</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>ISO плёнки / светочувствительность</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>ISO плёнки / ASA-DIN-ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>ISO плёнки / чёрно-белый негатив</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>ISO плёнки / цветной негатив</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>ISO плёнки / слайдовая плёнка</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>ISO плёнки / box speed и EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>ISO плёнки / связь с экспозицией</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>ISO плёнки / коробочный ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>ISO плёнки / универсальный ISO 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>ISO плёнки / высокая чувствительность</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>ISO плёнки / push-pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Зерно / материальная основа</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Зерно / компромисс ISO и фактуры</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Зерно / медленная плёнка</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Зерно / средняя чувствительность</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Зерно / классический ISO 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Зерно / структура кристаллов</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Зерно / T-GRAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Зерно / мелкозернистая плёнка</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Зерно / высокая чувствительность</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Зерно / цветная плёнка</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Зерно / проявка и сканирование</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / характеристическая кривая</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / toe-straight-shoulder</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / недодержка и тени</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / передержка и света</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / слайдовая плёнка</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / цветной негатив</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / чёрно-белый негатив</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / средняя чувствительность</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / push-pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / серая карта</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Экспозиционная широта / практический выбор</t>
         </is>
       </c>
     </row>
@@ -30679,7 +35730,7 @@
     <row r="1" ht="40" customHeight="1" s="59">
       <c r="A1" s="32" t="inlineStr">
         <is>
-          <t>PHOTO LAB — History Map Master v0.14</t>
+          <t>PHOTO LAB — History Map Master v0.15</t>
         </is>
       </c>
       <c r="B1" s="20" t="n"/>
@@ -30699,12 +35750,12 @@
     <row r="3" ht="21" customHeight="1" s="59">
       <c r="A3" s="69" t="inlineStr">
         <is>
-          <t>Охват v0.13</t>
+          <t>Охват v0.15</t>
         </is>
       </c>
       <c r="B3" s="67" t="inlineStr">
         <is>
-          <t>От оптических предпосылок камеры-обскуры до Leica I и Модуля 2: плёнка как материал, эмульсия, негатив, позитив, чёрно-белая, цветная негативная и слайдовая плёнка; основа для PL-001–PL-017.</t>
+          <t>От оптических предпосылок камеры-обскуры до Leica I и полного Модуля 2: плёнка как материал, эмульсия, негатив, позитив, чёрно-белая, цветная негативная и слайдовая плёнка, ISO, зерно и экспозиционная широта; основа для PL-001–PL-020.</t>
         </is>
       </c>
     </row>
@@ -30752,7 +35803,7 @@
       </c>
       <c r="B7" s="67" t="inlineStr">
         <is>
-          <t>Ветка развития = одна из 13 крупных линий из 02_Branches. Для PL-017 слайдовая плёнка связана с «Цвет», «Фотохимия», «Проекция / распространение» и «Уникальный позитив».</t>
+          <t>Ветка развития = одна из 13 крупных линий из 02_Branches. Для PL-018–PL-020 ISO, зерно и экспозиционная широта в основном относятся к «Фотохимия», но могут связываться с «Негатив-позитив», «Цвет» и «Печать / тиражирование».</t>
         </is>
       </c>
     </row>
@@ -30764,7 +35815,7 @@
       </c>
       <c r="B8" s="67" t="inlineStr">
         <is>
-          <t>Подветка (детали) = уточнение внутри крупной ветки: химия, камера, распространение, фотокнига, медицинское применение, сухие пластины, рулонная плёнка, Brownie, 35 мм, Leica I, структура плёнки, эмульсия, негатив/позитив, позитив, чёрно-белая плёнка, цветная негативная плёнка, слайдовая плёнка и т.п.</t>
+          <t>Подветка (детали) = уточнение внутри крупной ветки: химия, камера, распространение, фотокнига, медицинское применение, сухие пластины, рулонная плёнка, Brownie, 35 мм, Leica I, структура плёнки, эмульсия, негатив/позитив, позитив, чёрно-белая плёнка, цветная негативная плёнка, слайдовая плёнка, ISO, зерно, экспозиционная широта и т.п.</t>
         </is>
       </c>
     </row>
@@ -30949,42 +36000,53 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="62" t="inlineStr">
         <is>
           <t>Что изменено в v0.13</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="62" t="inlineStr">
         <is>
           <t>Заполнен PL-016: добавлены PL-HIST-0154…0164 по цветной негативной плёнке — Kodacolor 1942, цветная система негатив→позитив, слои CMY, color couplers, оранжевая маска, chromogenic print, C-41, Flexicolor, экспозиционная гибкость, современная Portra и архивное хранение цветных негативов. Добавлены источники SRC-120…SRC-130 и флагманский узел PL-HIST-0154.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="62" t="inlineStr">
         <is>
           <t>Что изменено в v0.14</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="62" t="inlineStr">
         <is>
           <t>Заполнен PL-017: добавлены PL-HIST-0165…0175 по слайдовой плёнке — Autochrome как ранняя цветная прозрачность, 16-мм reversal, Kodachrome 1935, 35-мм слайды, принцип direct positive, Ektachrome 1946, E-6, точность экспозиции, современный Ektachrome E100 и архивное хранение прозрачностей. Добавлены источники SRC-131…SRC-142 и флагманский узел PL-HIST-0167.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="62" t="inlineStr">
+        <is>
+          <t>Что изменено в v0.15</t>
+        </is>
+      </c>
+      <c r="B26" s="62" t="inlineStr">
+        <is>
+          <t>Заполнены PL-018, PL-019 и PL-020: добавлены PL-HIST-0176…0208 по ISO плёнки, box speed/EI, push/pull, зерну, серебряным кристаллам, T-GRAIN/Core-Shell, влиянию проявки/сканирования, характеристической кривой, toe/shoulder, широте негатива и слайда. Добавлены источники SRC-143…SRC-165 и флагманские узлы PL-HIST-0176, PL-HIST-0187, PL-HIST-0198.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="62" t="inlineStr">
         <is>
           <t>Следующий шаг</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>PL-018: ISO плёнки — объяснить светочувствительность материала, коробочный ISO, экспонометрию, push/pull и практический выбор плёнки под свет.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
+      <c r="B27" s="62" t="inlineStr">
+        <is>
+          <t>PL-021: Из чего состоит плёночная камера — перейти от материала плёнки к устройству камеры, кассете, затвору, объективу, видоискателю, перемотке и прижимному столику.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -28952,7 +28952,7 @@
       </c>
       <c r="F12" s="62" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf</t>
+          <t>https://t.me/photolab_vf_pro/4/145</t>
         </is>
       </c>
     </row>
@@ -28984,7 +28984,7 @@
       </c>
       <c r="F13" s="62" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf</t>
+          <t>https://t.me/photolab_vf_pro/4/151</t>
         </is>
       </c>
     </row>
@@ -29016,7 +29016,7 @@
       </c>
       <c r="F14" s="62" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf</t>
+          <t>https://t.me/photolab_vf_pro/4/162</t>
         </is>
       </c>
     </row>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="F15" s="62" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf</t>
+          <t>https://t.me/photolab_vf_pro/4/168</t>
         </is>
       </c>
     </row>
@@ -29080,7 +29080,7 @@
       </c>
       <c r="F16" s="62" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf</t>
+          <t>https://t.me/photolab_vf_pro/4/173</t>
         </is>
       </c>
     </row>
@@ -29112,7 +29112,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf</t>
+          <t>https://t.me/photolab_vf_pro/4/181</t>
         </is>
       </c>
     </row>
@@ -29144,7 +29144,7 @@
       </c>
       <c r="F18" s="62" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf</t>
+          <t>https://t.me/photolab_vf_pro</t>
         </is>
       </c>
     </row>
@@ -29176,7 +29176,7 @@
       </c>
       <c r="F19" s="62" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf</t>
+          <t>https://t.me/photolab_vf_pro</t>
         </is>
       </c>
     </row>
@@ -29208,7 +29208,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf</t>
+          <t>https://t.me/photolab_vf_pro</t>
         </is>
       </c>
     </row>
@@ -29240,7 +29240,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://t.me/photolab_vf</t>
+          <t>https://t.me/photolab_vf_pro</t>
         </is>
       </c>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -1064,7 +1064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="37.1640625" customWidth="1" style="72" min="1" max="1"/>
@@ -1076,7 +1076,7 @@
     <row r="1" ht="40" customHeight="1" s="72">
       <c r="A1" s="31" t="inlineStr">
         <is>
-          <t>PHOTO LAB — Master Timeline v0.17</t>
+          <t>PHOTO LAB — Master Timeline v0.18</t>
         </is>
       </c>
       <c r="B1" s="20" t="n"/>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="B3" s="81">
-        <f>COUNTA('01_Master_Facts'!$A$2:$A$500)</f>
+        <f>COUNTA('01_Master_Facts'!$A$2:$A$600)</f>
         <v/>
       </c>
       <c r="C3" s="80" t="inlineStr">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="B4" s="81">
-        <f>COUNTIF('01_Master_Facts'!$N$2:$N$500,5)</f>
+        <f>COUNTIF('01_Master_Facts'!$N$2:$N$600,5)</f>
         <v/>
       </c>
       <c r="C4" s="80" t="inlineStr">
@@ -1143,11 +1143,11 @@
     <row r="5" ht="21" customHeight="1" s="72">
       <c r="A5" s="80" t="inlineStr">
         <is>
-          <t>Узлов для PL-001–PL-028</t>
+          <t>Узлов для PL-001–PL-033</t>
         </is>
       </c>
       <c r="B5" s="81">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-001")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-002")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-003")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-004")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-005")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-006")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-007")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-008")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-009")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-010")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-011")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-012")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-013")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-014")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-015")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-016")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-017")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-018")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-019")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-020")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-021")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-022")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-023")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-024")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-025")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-026")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-027")+COUNTIF('01_Master_Facts'!$O$2:$O$500,"PL-028")</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-001")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-002")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-003")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-004")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-005")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-006")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-007")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-008")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-009")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-010")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-011")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-012")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-013")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-014")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-015")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-016")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-017")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-018")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-019")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-020")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-021")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-022")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-023")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-024")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-025")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-026")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-027")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-028")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-029")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-030")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-031")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-032")+COUNTIF('01_Master_Facts'!$O$2:$O$600,"PL-033")</f>
         <v/>
       </c>
       <c r="C5" s="80" t="inlineStr">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="B6" s="81">
-        <f>COUNTIF('01_Master_Facts'!$W$2:$W$500,"&lt;&gt;")</f>
+        <f>COUNTIF('01_Master_Facts'!$W$2:$W$600,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="80" t="inlineStr">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B10" s="76">
-        <f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A10)</f>
+        <f>COUNTIF('01_Master_Facts'!$H$2:$H$600,A10)</f>
         <v/>
       </c>
       <c r="C10" s="75" t="n"/>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="E10" s="76">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D10)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D10)</f>
         <v/>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B11" s="76">
-        <f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A11)</f>
+        <f>COUNTIF('01_Master_Facts'!$H$2:$H$600,A11)</f>
         <v/>
       </c>
       <c r="C11" s="75" t="n"/>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="E11" s="76">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D11)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D11)</f>
         <v/>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="B12" s="76">
-        <f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A12)</f>
+        <f>COUNTIF('01_Master_Facts'!$H$2:$H$600,A12)</f>
         <v/>
       </c>
       <c r="C12" s="75" t="n"/>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="E12" s="76">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D12)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D12)</f>
         <v/>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="B13" s="76">
-        <f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A13)</f>
+        <f>COUNTIF('01_Master_Facts'!$H$2:$H$600,A13)</f>
         <v/>
       </c>
       <c r="C13" s="75" t="n"/>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="E13" s="76">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D13)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D13)</f>
         <v/>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B14" s="76">
-        <f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A14)</f>
+        <f>COUNTIF('01_Master_Facts'!$H$2:$H$600,A14)</f>
         <v/>
       </c>
       <c r="C14" s="75" t="n"/>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="E14" s="76">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D14)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D14)</f>
         <v/>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B15" s="76">
-        <f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A15)</f>
+        <f>COUNTIF('01_Master_Facts'!$H$2:$H$600,A15)</f>
         <v/>
       </c>
       <c r="C15" s="75" t="n"/>
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="E15" s="76">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D15)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D15)</f>
         <v/>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="B16" s="76">
-        <f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A16)</f>
+        <f>COUNTIF('01_Master_Facts'!$H$2:$H$600,A16)</f>
         <v/>
       </c>
       <c r="C16" s="75" t="n"/>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="E16" s="76">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D16)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D16)</f>
         <v/>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="B17" s="76">
-        <f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A17)</f>
+        <f>COUNTIF('01_Master_Facts'!$H$2:$H$600,A17)</f>
         <v/>
       </c>
       <c r="C17" s="75" t="n"/>
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="E17" s="76">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D17)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D17)</f>
         <v/>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="B18" s="76">
-        <f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A18)</f>
+        <f>COUNTIF('01_Master_Facts'!$H$2:$H$600,A18)</f>
         <v/>
       </c>
       <c r="C18" s="75" t="n"/>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="E18" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D18)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D18)</f>
         <v/>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B19" s="76">
-        <f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A19)</f>
+        <f>COUNTIF('01_Master_Facts'!$H$2:$H$600,A19)</f>
         <v/>
       </c>
       <c r="C19" s="75" t="n"/>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="E19" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D19)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D19)</f>
         <v/>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="B20" s="76">
-        <f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A20)</f>
+        <f>COUNTIF('01_Master_Facts'!$H$2:$H$600,A20)</f>
         <v/>
       </c>
       <c r="C20" s="75" t="n"/>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="E20" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D20)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D20)</f>
         <v/>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="B21" s="76">
-        <f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A21)</f>
+        <f>COUNTIF('01_Master_Facts'!$H$2:$H$600,A21)</f>
         <v/>
       </c>
       <c r="C21" s="75" t="n"/>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="E21" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D21)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D21)</f>
         <v/>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="B22" s="76">
-        <f>COUNTIF('01_Master_Facts'!$H$2:$H$500,A22)</f>
+        <f>COUNTIF('01_Master_Facts'!$H$2:$H$600,A22)</f>
         <v/>
       </c>
       <c r="C22" s="75" t="n"/>
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="E22" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D22)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D22)</f>
         <v/>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="E23" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D23)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D23)</f>
         <v/>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="E24" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D24)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D24)</f>
         <v/>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="E25" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D25)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D25)</f>
         <v/>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="E26" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D26)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D26)</f>
         <v/>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="E27" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D27)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D27)</f>
         <v/>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="E28" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D28)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D28)</f>
         <v/>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="E29" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D29)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D29)</f>
         <v/>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="E30" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D30)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D30)</f>
         <v/>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="E31" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D31)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D31)</f>
         <v/>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="E32" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D32)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D32)</f>
         <v/>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="E33" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D33)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D33)</f>
         <v/>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="E34" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D34)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D34)</f>
         <v/>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="E35" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D35)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D35)</f>
         <v/>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="E36" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D36)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D36)</f>
         <v/>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E37" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D37)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D37)</f>
         <v/>
       </c>
     </row>
@@ -1702,11 +1702,11 @@
       <c r="C38" s="75" t="n"/>
       <c r="D38" s="75" t="inlineStr">
         <is>
-          <t>будущие PL</t>
+          <t>PL-029</t>
         </is>
       </c>
       <c r="E38" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D38)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D38)</f>
         <v/>
       </c>
     </row>
@@ -1716,11 +1716,11 @@
       <c r="C39" s="75" t="n"/>
       <c r="D39" s="75" t="inlineStr">
         <is>
-          <t>межурочный узел</t>
+          <t>PL-030</t>
         </is>
       </c>
       <c r="E39" s="75">
-        <f>COUNTIF('01_Master_Facts'!$O$2:$O$500,D39)</f>
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D39)</f>
         <v/>
       </c>
     </row>
@@ -1728,143 +1728,201 @@
       <c r="A40" s="76" t="n"/>
       <c r="B40" s="76" t="n"/>
       <c r="C40" s="75" t="n"/>
-      <c r="D40" s="75" t="n"/>
-      <c r="E40" s="75" t="n"/>
+      <c r="D40" s="75" t="inlineStr">
+        <is>
+          <t>PL-031</t>
+        </is>
+      </c>
+      <c r="E40" s="75">
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D40)</f>
+        <v/>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1" s="72">
       <c r="A41" s="4" t="n"/>
       <c r="B41" s="4" t="n"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
+      <c r="E41">
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D41)</f>
+        <v/>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1" s="72">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Тип узла</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Количество узлов</t>
-        </is>
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="4" t="n"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
+      <c r="E42">
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D42)</f>
+        <v/>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1" s="72">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Фундаментальная предпосылка</t>
-        </is>
-      </c>
-      <c r="B43" s="4">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A43)</f>
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="n"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>будущие PL</t>
+        </is>
+      </c>
+      <c r="E43">
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D43)</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" s="72">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Технология / процесс</t>
-        </is>
-      </c>
-      <c r="B44" s="4">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A44)</f>
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>межурочный узел</t>
+        </is>
+      </c>
+      <c r="E44">
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$600,D44)</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1" s="72">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Инструмент / устройство</t>
-        </is>
-      </c>
-      <c r="B45" s="4">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A45)</f>
-        <v/>
-      </c>
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
     </row>
     <row r="46" ht="20" customHeight="1" s="72">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>Публикация / объявление</t>
-        </is>
-      </c>
-      <c r="B46" s="4">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A46)</f>
-        <v/>
-      </c>
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Терминология / язык</t>
-        </is>
-      </c>
-      <c r="B47">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A47)</f>
-        <v/>
+          <t>Тип узла</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Связь / переход</t>
+          <t>Фундаментальная предпосылка</t>
         </is>
       </c>
       <c r="B48">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A48)</f>
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$600,A48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Тиражирование / публикация</t>
+          <t>Технология / процесс</t>
         </is>
       </c>
       <c r="B49">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A49)</f>
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$600,A49)</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Распространение / коммерциализация</t>
+          <t>Инструмент / устройство</t>
         </is>
       </c>
       <c r="B50">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A50)</f>
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$600,A50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Научное применение / пример</t>
+          <t>Публикация / объявление</t>
         </is>
       </c>
       <c r="B51">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A51)</f>
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$600,A51)</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Применение / жанр</t>
+          <t>Терминология / язык</t>
         </is>
       </c>
       <c r="B52">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A52)</f>
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$600,A52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="B53">
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$600,A53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Тиражирование / публикация</t>
+        </is>
+      </c>
+      <c r="B54">
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$600,A54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Распространение / коммерциализация</t>
+        </is>
+      </c>
+      <c r="B55">
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$600,A55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Научное применение / пример</t>
+        </is>
+      </c>
+      <c r="B56">
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$600,A56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+      <c r="B57">
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$600,A57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Ключевой исторический узел</t>
         </is>
       </c>
-      <c r="B53">
-        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$500,A53)</f>
+      <c r="B58">
+        <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$600,A58)</f>
         <v/>
       </c>
     </row>
@@ -1883,7 +1941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA297"/>
+  <dimension ref="A1:AA352"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="14" customWidth="1" style="72" min="1" max="1"/>
@@ -38747,61 +38805,6521 @@
       </c>
       <c r="AA297" s="75" t="n"/>
     </row>
-    <row r="298" ht="17" customHeight="1" s="72"/>
-    <row r="299" ht="17" customHeight="1" s="72"/>
-    <row r="300" ht="17" customHeight="1" s="72"/>
-    <row r="301" ht="17" customHeight="1" s="72"/>
-    <row r="302" ht="17" customHeight="1" s="72"/>
-    <row r="303" ht="17" customHeight="1" s="72"/>
-    <row r="304" ht="17" customHeight="1" s="72"/>
-    <row r="305" ht="17" customHeight="1" s="72"/>
-    <row r="306" ht="17" customHeight="1" s="72"/>
-    <row r="307" ht="17" customHeight="1" s="72"/>
-    <row r="308" ht="17" customHeight="1" s="72"/>
-    <row r="309" ht="17" customHeight="1" s="72"/>
-    <row r="310" ht="17" customHeight="1" s="72"/>
-    <row r="311" ht="17" customHeight="1" s="72"/>
-    <row r="312" ht="17" customHeight="1" s="72"/>
-    <row r="313" ht="17" customHeight="1" s="72"/>
-    <row r="314" ht="17" customHeight="1" s="72"/>
-    <row r="315" ht="17" customHeight="1" s="72"/>
-    <row r="316" ht="17" customHeight="1" s="72"/>
-    <row r="317" ht="17" customHeight="1" s="72"/>
-    <row r="318" ht="17" customHeight="1" s="72"/>
-    <row r="319" ht="17" customHeight="1" s="72"/>
-    <row r="320" ht="17" customHeight="1" s="72"/>
-    <row r="321" ht="17" customHeight="1" s="72"/>
-    <row r="322" ht="17" customHeight="1" s="72"/>
-    <row r="323" ht="17" customHeight="1" s="72"/>
-    <row r="324" ht="17" customHeight="1" s="72"/>
-    <row r="325" ht="17" customHeight="1" s="72"/>
-    <row r="326" ht="17" customHeight="1" s="72"/>
-    <row r="327" ht="17" customHeight="1" s="72"/>
-    <row r="328" ht="17" customHeight="1" s="72"/>
-    <row r="329" ht="17" customHeight="1" s="72"/>
-    <row r="330" ht="17" customHeight="1" s="72"/>
-    <row r="331" ht="17" customHeight="1" s="72"/>
-    <row r="332" ht="17" customHeight="1" s="72"/>
-    <row r="333" ht="17" customHeight="1" s="72"/>
-    <row r="334" ht="17" customHeight="1" s="72"/>
-    <row r="335" ht="17" customHeight="1" s="72"/>
-    <row r="336" ht="17" customHeight="1" s="72"/>
-    <row r="337" ht="17" customHeight="1" s="72"/>
-    <row r="338" ht="17" customHeight="1" s="72"/>
-    <row r="339" ht="17" customHeight="1" s="72"/>
-    <row r="340" ht="17" customHeight="1" s="72"/>
-    <row r="341" ht="17" customHeight="1" s="72"/>
-    <row r="342" ht="17" customHeight="1" s="72"/>
-    <row r="343" ht="17" customHeight="1" s="72"/>
-    <row r="344" ht="17" customHeight="1" s="72"/>
-    <row r="345" ht="17" customHeight="1" s="72"/>
-    <row r="346" ht="17" customHeight="1" s="72"/>
-    <row r="347" ht="17" customHeight="1" s="72"/>
-    <row r="348" ht="17" customHeight="1" s="72"/>
-    <row r="349" ht="17" customHeight="1" s="72"/>
-    <row r="350" ht="17" customHeight="1" s="72"/>
-    <row r="351" ht="17" customHeight="1" s="72"/>
-    <row r="352" ht="17" customHeight="1" s="72"/>
+    <row r="298" ht="17" customHeight="1" s="72">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>PL-HIST-0297</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>вторичный рынок / фотомагазины</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>новичок / фотограф</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Выбор первой плёночной камеры начинается не с легендарной модели, а с понятной задачи: какой формат, какой тип камеры, сколько контроля и насколько легко ей пользоваться.</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>First film camera choice</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>Камера становится учебным инструментом: она должна помогать понять кадр, экспозицию и плёнку, а не мешать сложностью или ремонтом.</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Большой формат / медленный рабочий процесс</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Формат плёнки и доступность сервиса</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N298" t="n">
+        <v>5</v>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>PL-029</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>SRC-241</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Tips for Buying Your First Film Camera</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/tips-for-buying-your-first-film-camera</t>
+        </is>
+      </c>
+      <c r="S298" t="n">
+        <v>5</v>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>Флагман PL-029: выбрать не «самую красивую», а рабочую и понятную камеру под первый опыт.</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>На столе три камеры: 35mm SLR, compact и rangefinder; рядом карточка с вопросами «что снимаю? где проявляю? сколько готов контролировать?»</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>#PL029 #first-film-camera #camera-choice</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / критерии</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="17" customHeight="1" s="72">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>PL-HIST-0298</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>магазины плёнки / лаборатории</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>ILFORD / лаборатории / фотографы</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Первый фильтр выбора — формат плёнки: 35 мм проще найти, дешевле пробовать и легче проявлять; 120 даёт больший кадр, но дороже и медленнее; листовая плёнка требует опыта.</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Фотохимия</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Film format availability</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Новичок выбирает не только камеру, но и весь рабочий цикл: купить плёнку, отснять, проявить, отсканировать и повторить.</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>PL-029 / общий выбор камеры</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Тип камеры</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>Главная линия / пользовательское удобство</t>
+        </is>
+      </c>
+      <c r="N299" t="n">
+        <v>5</v>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>PL-029</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>SRC-218</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>ILFORD Photo — Choosing your first ILFORD film</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/choosing-your-first-ilford-film/</t>
+        </is>
+      </c>
+      <c r="S299" t="n">
+        <v>5</v>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>Сделать практическое правило: для старта чаще всего 35 мм, если цель — учиться чаще и дешевле.</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>Инфографика: 35mm canister → 120 roll → 4×5 sheet; рядом стоимость/доступность/сложность.</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>#PL029 #film-format #35mm #120film #sheetfilm</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / формат плёнки</t>
+        </is>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="17" customHeight="1" s="72">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>PL-HIST-0299</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>вторичный рынок</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>покупатель / мастер</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Перед покупкой нужно проверять состояние: затвор, выдержки, протяжку и обратную перемотку, светоуплотнители, батарейный отсек, экспонометр, объектив и следы плесени.</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Used camera condition checklist</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>Камера перестаёт быть просто предметом желания: она становится механизмом, который должен стабильно работать на каждом кадре.</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Формат плёнки</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Ремонтопригодность</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>Главная линия / проверка перед покупкой</t>
+        </is>
+      </c>
+      <c r="N300" t="n">
+        <v>5</v>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>PL-029</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>SRC-243</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Buying Guide for the Film Photography Student</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/buying-guide/buying-guide-for-the-film-photography-student</t>
+        </is>
+      </c>
+      <c r="S300" t="n">
+        <v>5</v>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>Хороший узел для чек-листа перед Avito/eBay/магазином.</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>Крупный план: открытая задняя крышка камеры, фонарик, тестовая батарейка, список проверок.</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>#PL029 #used-camera #checklist #repair</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / проверка состояния</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="17" customHeight="1" s="72">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>PL-HIST-0300</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>обучение / фотошкола</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>новичок / преподаватель</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Ручная 35-мм SLR часто удобна для обучения: через неё видно, как связаны фокус, диафрагма, выдержка, объектив и кадр.</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Manual 35mm SLR for learning</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>Новичок получает максимум учебного контроля в относительно доступном формате.</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Проверка состояния</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Механическая независимость</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>Главная линия / учебная камера</t>
+        </is>
+      </c>
+      <c r="N301" t="n">
+        <v>5</v>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>PL-029</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>SRC-168</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>Nikon — FM2 Instruction Manual</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>https://cdn-10.nikon-cdn.com/pdf/manuals/archive/FM2.pdf</t>
+        </is>
+      </c>
+      <c r="S301" t="n">
+        <v>5</v>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>Можно использовать Nikon FM2 как пример, но не как единственный правильный выбор.</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>35-мм SLR сверху, вокруг подписи: shutter, aperture, focus, film advance.</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>#PL029 #35mmSLR #manual-camera #learning</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / 35mm SLR</t>
+        </is>
+      </c>
+      <c r="Z301" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="17" customHeight="1" s="72">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>PL-HIST-0301</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>город / улица</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>фотографы / дальномерные системы</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Дальномерная камера хороша для тихой и быстрой съёмки, но требует привыкнуть к отдельному видоискателю, совмещению пятна фокусировки и параллаксу.</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Rangefinder as first camera</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Выбор камеры зависит от стиля: дальномер даёт наблюдение и компактность, но не показывает кадр через объектив.</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>35mm SLR</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Compact camera</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Главная линия / осознанный выбор</t>
+        </is>
+      </c>
+      <c r="N302" t="n">
+        <v>4</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>PL-029</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>SRC-196</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>B&amp;H Explora — Rangefinder Camera Guide</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/buying-guide/primer-rangefinder-cameras</t>
+        </is>
+      </c>
+      <c r="S302" t="n">
+        <v>5</v>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>Уточнить: дальномер может быть прекрасным стартом, но не для всех новичков.</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>Сцена на улице: фотограф смотрит в рамочный видоискатель, рядом маленькая схема параллакса.</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>#PL029 #rangefinder #Leica #parallax</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / дальномер</t>
+        </is>
+      </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="17" customHeight="1" s="72">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>PL-HIST-0302</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>семья / путешествие / улица</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>новичок / пользователи compact</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Компактная point-and-shoot камера снимает быстро и просто: автофокус, автоэкспозиция и встроенная вспышка убирают часть решений, но уменьшают контроль автора.</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Point-and-shoot as first camera</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>Камера становится входом без страха перед настройками, но ученик должен понимать её ограничения.</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Дальномерный выбор</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Автоматизация / электроника</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Главная линия / простота входа</t>
+        </is>
+      </c>
+      <c r="N303" t="n">
+        <v>4</v>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>PL-029</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>SRC-181</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>Canon Camera Museum — Sure Shot / AF35M</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>https://global.canon/en/c-museum/product/film102.html</t>
+        </is>
+      </c>
+      <c r="S303" t="n">
+        <v>5</v>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>Хорошая ветка для тех, кто хочет начать с личного дневника, семьи и путешествий.</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>Компактная камера лежит на билете/карте; на фоне маленькая встроенная вспышка.</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>#PL029 #compactcamera #pointandshoot #autofocus</t>
+        </is>
+      </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / компакт</t>
+        </is>
+      </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="17" customHeight="1" s="72">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>PL-HIST-0303</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>студия / пейзаж / fine art</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>среднеформатные и крупноформатные фотографы</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Средний и большой формат могут дать больше площади кадра и детализации, но для первой камеры часто усложняют старт: меньше кадров, выше цена ошибки, медленнее процесс.</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Medium and large format as advanced choice</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>Формат — это компромисс между качеством, скоростью, стоимостью и количеством практики.</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Compact camera</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Цена владения</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N304" t="n">
+        <v>4</v>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>PL-029</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>SRC-237</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>ILFORD Photo — Shooting large format film</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/shooting-large-format-film/</t>
+        </is>
+      </c>
+      <c r="S304" t="n">
+        <v>5</v>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>Связать с уроками PL-027/028: не запрещать, а объяснить цену выбора.</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>Три стопки: 36 кадров 35 мм, 12 кадров 120, один лист 4×5; подпись «скорость / цена / контроль».</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>#PL029 #mediumformat #largeformat #learning-curve</t>
+        </is>
+      </c>
+      <c r="Y304" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / формат и цена ошибки</t>
+        </is>
+      </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="17" customHeight="1" s="72">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>PL-HIST-0304</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>вторичный рынок объективов</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>фотограф / продавец</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>При выборе системы важен объектив: байонет, доступность 50 мм или 35 мм, цена оптики и возможность ремонта часто важнее редкости корпуса.</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Lens and mount ecosystem</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Новичок выбирает не корпус отдельно, а систему: камера + объектив + расходники + сервис.</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Формат и цена ошибки</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Батарейки и экспонометр</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>Главная линия / системный выбор</t>
+        </is>
+      </c>
+      <c r="N305" t="n">
+        <v>5</v>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>PL-029</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>SRC-241</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Tips for Buying Your First Film Camera</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/tips-for-buying-your-first-film-camera</t>
+        </is>
+      </c>
+      <c r="S305" t="n">
+        <v>5</v>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>Подвести к Модулю 4: объектив будет следующим большим разделом курса.</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>Камера без объектива и три объектива рядом; золотая линия показывает совместимость байонета.</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>#PL029 #lensmount #50mm #system-choice</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / система и объектив</t>
+        </is>
+      </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="17" customHeight="1" s="72">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>PL-HIST-0305</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>вторичный рынок</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>покупатель / мастер</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Батарейки и экспонометр нужно проверять отдельно: одни камеры полностью механические, другие без питания теряют замер, автоматику или вообще работоспособность.</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Battery / light meter dependency</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>Выбор камеры становится вопросом надёжности: чем больше электроники, тем важнее состояние питания и контактов.</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Система и объектив</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Цена владения</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Главная линия / эксплуатационная проверка</t>
+        </is>
+      </c>
+      <c r="N306" t="n">
+        <v>5</v>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>PL-029</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>SRC-169</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>Leica — M-A (Typ 127)</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>https://leica-camera.com/en-US/photography/cameras/m/m-a-typ-127-black</t>
+        </is>
+      </c>
+      <c r="S306" t="n">
+        <v>5</v>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>Leica M-A — пример полностью механической камеры; AE/AF compact — пример зависимости от электроники.</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>Две камеры: механическая без батарейки и compact с открытым батарейным отсеком.</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>#PL029 #battery #lightmeter #mechanicalcamera</t>
+        </is>
+      </c>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / батарейки и экспонометр</t>
+        </is>
+      </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="17" customHeight="1" s="72">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>PL-HIST-0306</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>покупка / лаборатория</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>новичок</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Реальная цена первой плёночной камеры — это не только корпус: объектив, батарейки, ремень, плёнка, проявка, сканирование, возможный ремонт и первые испорченные кадры.</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Печать / тиражирование</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Total cost of film camera ownership</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Плёночная фотография становится циклом расходов и повторений; чем проще цикл, тем быстрее растёт навык.</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Батарейки и экспонометр</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Матрица выбора</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Главная линия / практическая экономика</t>
+        </is>
+      </c>
+      <c r="N307" t="n">
+        <v>5</v>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>PL-029</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>SRC-243</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Buying Guide for the Film Photography Student</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/buying-guide/buying-guide-for-the-film-photography-student</t>
+        </is>
+      </c>
+      <c r="S307" t="n">
+        <v>5</v>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>Сделать честный блок: лучше рабочая простая камера + плёнка, чем дорогая легенда без практики.</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>Чек-лист бюджета: body / lens / film / dev / scan / repair.</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>#PL029 #budget #film-cost #devscan</t>
+        </is>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / цена владения</t>
+        </is>
+      </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>Распространение / коммерциализация</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="17" customHeight="1" s="72">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>PL-HIST-0307</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>PHOTO LAB / обучение</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>PHOTO LAB by VF</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Итоговый выбор можно свести к матрице: хочу учиться настройкам — 35-мм SLR; хочу лёгкий дневник — compact; хочу тихую улицу — rangefinder; хочу качество и медленный ритм — средний формат.</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>First camera decision matrix</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>Камера выбирается под поведение фотографа, а не под статус модели.</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Цена владения</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>PL-030 — роль автора</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N308" t="n">
+        <v>5</v>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>PL-029</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>SRC-242</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Best Film and Camera Combos: A Guide for Beginners</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/videos/photography/best-film-and-camera-combos-a-guide-for-beginners</t>
+        </is>
+      </c>
+      <c r="S308" t="n">
+        <v>5</v>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>Финал PL-029 и мост к PL-030: камера помогает, но не делает фотографа.</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>Четыре карточки выбора с иконками: учёба / дневник / улица / медленный fine art.</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>#PL029 #decision-matrix #first-camera #photolab</t>
+        </is>
+      </c>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / матрица решения</t>
+        </is>
+      </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="17" customHeight="1" s="72">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>PL-HIST-0308</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>фотографическая практика</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Камера не делает фотографию за автора: она фиксирует свет, но не выбирает тему, момент, дистанцию, свет, рамку и смысл кадра.</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Camera as tool, not author</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Фокус обучения смещается с покупки техники на зрение, решение и ответственность фотографа.</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>PL-029 — выбор камеры</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Куда смотреть и когда нажать</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N309" t="n">
+        <v>5</v>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>PL-030</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>SRC-250</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Introduction to Learning Photography</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/introduction-to-learning-photography</t>
+        </is>
+      </c>
+      <c r="S309" t="n">
+        <v>5</v>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>Флагман PL-030: идеальный финал модуля камер — камера важна, но автор важнее.</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>Камера лежит на столе, а рядом пустая рамка кадра; за рамкой видна сцена, которую ещё надо заметить.</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>#PL030 #camera-is-tool #photographer #visual-thinking</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>Автор и камера / инструмент</t>
+        </is>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="17" customHeight="1" s="72">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>PL-HIST-0309</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>любой сюжет</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Перед кадром фотограф принимает три главных решения: где стоять, что включить в рамку и в какой момент нажать спуск.</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Position / frame / moment</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>Фотография появляется не из настроек, а из последовательности авторских решений.</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Камера как инструмент</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Свет как выбор</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальное решение</t>
+        </is>
+      </c>
+      <c r="N310" t="n">
+        <v>5</v>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>PL-030</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>SRC-250</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Introduction to Learning Photography</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/introduction-to-learning-photography</t>
+        </is>
+      </c>
+      <c r="S310" t="n">
+        <v>5</v>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>Хорошее практическое правило: место, рамка, момент.</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>Схема из трёх золотых точек: позиция → рамка → момент.</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>#PL030 #frame #moment #position</t>
+        </is>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>Автор и камера / место-рамка-момент</t>
+        </is>
+      </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="17" customHeight="1" s="72">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>PL-HIST-0310</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>улица / интерьер / портрет</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Один и тот же фотоаппарат даст разный результат при разном свете: мягком, жёстком, боковом, контровом или плоском.</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Seeing light before settings</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>Фотограф учится сначала видеть свет, а уже потом крутить настройки.</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Место-рамка-момент</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Композиция</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальное мышление</t>
+        </is>
+      </c>
+      <c r="N311" t="n">
+        <v>5</v>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>PL-030</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>SRC-250</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Introduction to Learning Photography</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/introduction-to-learning-photography</t>
+        </is>
+      </c>
+      <c r="S311" t="n">
+        <v>5</v>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>Связать с будущим модулем «Свет и композиция».</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>Одна камера, четыре маленьких сцены света: боковой, контровой, мягкий, жёсткий.</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>#PL030 #light #seeing #visual-thinking</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>Автор и камера / видеть свет</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="17" customHeight="1" s="72">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>PL-HIST-0311</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>кадр / сцена</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Композиция — это не сетка в видоискателе, а решение, что оставить внутри кадра, что убрать и как элементы будут работать друг с другом.</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Framing and composition</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>Камера записывает всё внутри рамки, но рамку строит фотограф.</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Видеть свет</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Момент</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Главная линия / композиционное решение</t>
+        </is>
+      </c>
+      <c r="N312" t="n">
+        <v>5</v>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>PL-030</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>SRC-245</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>The Metropolitan Museum of Art — Henri Cartier-Bresson, Seville</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>https://www.metmuseum.org/art/collection/search/283312</t>
+        </is>
+      </c>
+      <c r="S312" t="n">
+        <v>5</v>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>Использовать пример Картье-Брессона как мост: форма и событие сходятся в одном кадре.</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>Через видоискатель видны линии улицы и фигура; часть хаоса остаётся за рамкой.</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>#PL030 #composition #framing #CartierBresson</t>
+        </is>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>Автор и камера / композиция</t>
+        </is>
+      </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="17" customHeight="1" s="72">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>PL-HIST-0312</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Франция / США</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Париж / Нью-Йорк</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Henri Cartier-Bresson / ICP / MoMA</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Идея «решающего момента» показывает, что фотография зависит от мгновения: форма, жест и смысл должны встретиться до нажатия спуска.</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Decisive moment</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>Даже самая дорогая камера не знает, когда сцена стала выразительной; это должен почувствовать фотограф.</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Композиция</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Дистанция</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>Главная линия / момент</t>
+        </is>
+      </c>
+      <c r="N313" t="n">
+        <v>5</v>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>PL-030</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>SRC-249</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>International Center of Photography — Henri Cartier-Bresson</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>https://www.icp.org/browse/archive/constituents/henri-cartier-bresson</t>
+        </is>
+      </c>
+      <c r="S313" t="n">
+        <v>5</v>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>Не романтизировать фразу, а объяснить как практику внимания к событию и форме.</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>Фигура пересекает светлое пятно; палец у кнопки спуска, но кадр ещё ждёт долю секунды.</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>#PL030 #decisivemoment #CartierBresson #moment</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>Автор и камера / решающий момент</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>Терминология / язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="17" customHeight="1" s="72">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>PL-HIST-0313</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>улица / портрет / предмет</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Дистанция меняет фотографию: шаг ближе делает кадр интимнее и активнее, шаг дальше даёт контекст и воздух.</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Distance and viewpoint</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>Фотограф управляет отношением к объекту ногами и позицией, а не только объективом.</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Момент</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>Главная линия / точка съёмки</t>
+        </is>
+      </c>
+      <c r="N314" t="n">
+        <v>5</v>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>PL-030</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>SRC-252</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Understanding Camera Lenses</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-lenses.htm</t>
+        </is>
+      </c>
+      <c r="S314" t="n">
+        <v>5</v>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>Важный мост к PL-033: перспектива определяется положением камеры.</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>Две рамки одной сцены: близко — жест и лицо; далеко — человек в среде.</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>#PL030 #distance #viewpoint #perspective</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>Автор и камера / дистанция</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="17" customHeight="1" s="72">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>PL-HIST-0314</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>объективы / кадр</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Объектив помогает выбрать угол зрения и масштаб, но он не заменяет взгляда: 28 мм, 50 мм и 85 мм дают разные языки только в руках думающего автора.</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Lens as visual language</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>Техника превращается в выразительный выбор, когда фотограф понимает, зачем ему это фокусное расстояние.</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Дистанция</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Отбор кадра</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N315" t="n">
+        <v>5</v>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>PL-030</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>SRC-252</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Understanding Camera Lenses</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-lenses.htm</t>
+        </is>
+      </c>
+      <c r="S315" t="n">
+        <v>5</v>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>Прямой мост к Модулю 4 об объективах.</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>Три кадра одной сцены с подписью 28 / 50 / 85 мм; разная эмоция пространства.</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>#PL030 #lens-language #focallength #visual-choice</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>Автор и камера / объектив как язык</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="17" customHeight="1" s="72">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>PL-HIST-0315</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>портрет / документальная съёмка</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>фотограф / герой кадра</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>В портрете и документальной съёмке камера не решает отношение к человеку: уважение, дистанция, доверие и момент взаимодействия остаются за автором.</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Human relationship in photography</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>Фотография становится не только техническим, но и этическим действием.</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Объектив как язык</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Редактирование и отбор</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Главная линия / авторская ответственность</t>
+        </is>
+      </c>
+      <c r="N316" t="n">
+        <v>4</v>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>PL-030</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>SRC-247</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>SFMOMA — Henri Cartier-Bresson: The Modern Century</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>https://www.sfmoma.org/exhibition/henri-cartier-bresson/</t>
+        </is>
+      </c>
+      <c r="S316" t="n">
+        <v>5</v>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>Сильно, но без морализаторства: человек в кадре не «объект», а участник ситуации.</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>Фотограф опускает камеру и разговаривает с человеком перед портретом.</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>#PL030 #portrait #documentary #ethics</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>Автор и камера / отношение к человеку</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="17" customHeight="1" s="72">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>PL-HIST-0316</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>редакция / лаборатория / печать</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>фотограф / редактор</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Авторство продолжается после нажатия на спуск: выбор дубля, кадрирование, последовательность, печать и подпись могут изменить смысл работы.</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Печать / тиражирование</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Editing / sequencing / printing</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>Кадр — это не только момент съёмки, но и последующая работа с изображением.</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Отношение к человеку</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Техника как усилитель</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Главная линия / авторская работа</t>
+        </is>
+      </c>
+      <c r="N317" t="n">
+        <v>5</v>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>PL-030</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>SRC-248</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>The Metropolitan Museum of Art — Faking It</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>https://www.metmuseum.org/exhibitions/listings/2012/faking-it</t>
+        </is>
+      </c>
+      <c r="S317" t="n">
+        <v>5</v>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>Связать с будущими модулями про отбор, отпечаток и коллекционность.</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>Контактный лист с обведённым кадром; рядом тестовый отпечаток и карандашные пометки.</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>#PL030 #editing #contactsheet #print</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>Автор и камера / отбор и печать</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>Тиражирование / публикация</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="17" customHeight="1" s="72">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>PL-HIST-0317</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>фотографическая техника</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Хорошая камера расширяет возможности: быстрее фокусируется, точнее меряет свет, удобнее держится. Но она усиливает решение фотографа, а не создаёт его вместо него.</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Camera capability vs photographic decision</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>Техника важна, но она не должна становиться оправданием отсутствия идеи, света и кадра.</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Отбор и печать</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Переход к объективам</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>5</v>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>PL-030</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>SRC-250</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Introduction to Learning Photography</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/introduction-to-learning-photography</t>
+        </is>
+      </c>
+      <c r="S318" t="n">
+        <v>5</v>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>Это честная формула курса: не обесценивать технику, но вернуть ответственность автору.</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>Две колонки: «камера может» и «фотограф решает».</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>#PL030 #camera-capability #photographer-decision</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>Автор и камера / техника усиливает решение</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="17" customHeight="1" s="72">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>PL-HIST-0318</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>PHOTO LAB / курс</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>PHOTO LAB by VF</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Финальный вывод модуля камер: камера определяет способ работы, но фотография рождается из света, выбора, момента и взгляда. Следующий шаг — понять объектив.</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Bridge to lens module</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Модуль 3 завершается переходом от корпуса камеры к оптике: теперь важно понять, как объектив строит изображение.</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Техника усиливает решение</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>PL-031 — что такое объектив</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N319" t="n">
+        <v>5</v>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>PL-030</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>SRC-252</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Understanding Camera Lenses</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-lenses.htm</t>
+        </is>
+      </c>
+      <c r="S319" t="n">
+        <v>5</v>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>Мост к PL-031: камера — коробка и механизм, объектив — способ собрать свет.</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>Камера без объектива; отдельно объектив, через который проходит золотой луч.</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>#PL030 #module3 #lens #bridge</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>Автор и камера / мост к объективам</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="17" customHeight="1" s="72">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>PL-HIST-0319</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>камера / объектив</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>фотографы / производители объективов</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Объектив — это оптическая система, которая собирает свет от сцены и фокусирует его на плоскости плёнки или сенсора, чтобы получилось резкое изображение.</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Lens as light-focusing system</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>После камеры-обскуры фотография получает больше света, контроль фокуса и возможность менять характер изображения.</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>PL-030 — камера как инструмент</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Объектив вместо отверстия</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N320" t="n">
+        <v>5</v>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>PL-031</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>SRC-251</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>Canon Science Lab — Photographs</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>https://global.canon/en/technology/s_labo/light/003/01.html</t>
+        </is>
+      </c>
+      <c r="S320" t="n">
+        <v>5</v>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>Флагман PL-031: объектив — не «стекло спереди», а система управления светом.</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>Луч света проходит через объектив и собирается на плёнке внутри камеры.</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>#PL031 #lens #optics #focus</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>Объектив / базовое определение</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="17" customHeight="1" s="72">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>PL-HIST-0320</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>XIX век — сегодня</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>камера-обскура / камера</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>оптики / фотографы</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Отверстие камеры-обскуры может дать изображение, но линза собирает больше света и позволяет управлять резкостью через фокусировку.</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Lens vs pinhole</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Фотограф переходит от простой проекции к управляемой оптике.</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Объектив как система</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Фокальная плоскость</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N321" t="n">
+        <v>5</v>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>PL-031</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>SRC-251</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>Canon Science Lab — Photographs</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>https://global.canon/en/technology/s_labo/light/003/01.html</t>
+        </is>
+      </c>
+      <c r="S321" t="n">
+        <v>5</v>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>Связать начало курса с модулем объективов: от дырочки к стеклу.</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>Слева pinhole с тусклой проекцией, справа объектив с ярким резким изображением.</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>#PL031 #pinhole #cameraobscura #lens</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>Объектив / линза против отверстия</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="17" customHeight="1" s="72">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>PL-HIST-0321</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>внутри камеры</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>фотограф / ученик</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Фокальная плоскость — место, где должен сформироваться резкий рисунок: в плёночной камере там находится плёнка, в цифровой — сенсор.</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Image plane / focal plane</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Резкость становится понятной геометрией: свет должен собраться именно на поверхности материала, который записывает изображение.</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Линза против отверстия</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Фокусировка</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Главная линия / оптический принцип</t>
+        </is>
+      </c>
+      <c r="N322" t="n">
+        <v>5</v>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>PL-031</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>SRC-255</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — How Your Digital Camera Works</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/how-your-digital-camera-works</t>
+        </is>
+      </c>
+      <c r="S322" t="n">
+        <v>5</v>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>Объяснить через разрез камеры.</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>Схема: lens → converging rays → film plane; золотая линия на плоскости плёнки.</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>#PL031 #imageplane #filmplane #sensor</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>Объектив / фокальная плоскость</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="17" customHeight="1" s="72">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>PL-HIST-0322</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>объектив / камера</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Фокусировка меняет положение линзы или группы линз так, чтобы лучи от выбранной дистанции сошлись на плёнке.</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Focusing movement</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>Объектив перестаёт быть пассивным стеклом: он настраивается под расстояние до объекта.</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Фокальная плоскость</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Диафрагма</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Главная линия / фокусировка</t>
+        </is>
+      </c>
+      <c r="N323" t="n">
+        <v>5</v>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>PL-031</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>SRC-257</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — How Focus Works</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/how-focus-works</t>
+        </is>
+      </c>
+      <c r="S323" t="n">
+        <v>5</v>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>Ключ к будущим урокам про фокус и ГРИП.</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>Макро-разрез объектива: двигающаяся фокусировочная группа и шкала расстояний.</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>#PL031 #focusing #focusring #opticalgroup</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>Объектив / фокусировка</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="17" customHeight="1" s="72">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>PL-HIST-0323</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>внутри объектива</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>производители / фотографы</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Диафрагма регулирует свет не в абсолютных миллиметрах, а через число f — отношение фокусного расстояния объектива к диаметру входного отверстия (f/N = фокусное расстояние ÷ диаметр диафрагмы). Поэтому одно и то же f/2.8 на разных объективах — это разные физические отверстия, но одинаковая доля света относительно кадра.</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>F-number ratio (focal length / aperture diameter)</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>Число диафрагмы перестаёт быть просто «шкалой на кольце»: это стандартизированное отношение, которое позволяет сравнивать светосилу и экспозицию между совершенно разными объективами и фокусными расстояниями.</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Фокусировка</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Главная линия / световой контроль</t>
+        </is>
+      </c>
+      <c r="N324" t="n">
+        <v>5</v>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>PL-031</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>SRC-241</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>Wikipedia — F-number</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/F-number</t>
+        </is>
+      </c>
+      <c r="S324" t="n">
+        <v>4</v>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>Ключевая деталь: f/2.8 на 50 мм объективе — отверстие ~18 мм, а на 200 мм объективе при том же f/2.8 — уже ~71 мм. Число f — это пропорция, а не размер дырки.</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>Схема: фокусное расстояние (стрелка) делится на диаметр отверстия диафрагмы — получается число f, подписанное f/2.8.</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>#PL031 #aperture #f-number #ratio #optics</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>Объектив / формула числа диафрагмы</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="17" customHeight="1" s="72">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>PL-HIST-0324</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>объективы 24/50/85 мм</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние определяет угол зрения и масштаб изображения: короткое показывает шире, длинное — уже и крупнее при той же позиции камеры.</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Focal length basics</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Объектив становится выбором пространства: он меняет, сколько мира войдёт в кадр.</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Диафрагма</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Prime и zoom</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Главная линия / угол зрения</t>
+        </is>
+      </c>
+      <c r="N325" t="n">
+        <v>5</v>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>PL-031</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>SRC-253</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding Focal Length</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-focal-length</t>
+        </is>
+      </c>
+      <c r="S325" t="n">
+        <v>5</v>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>Мост к PL-033.</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>Три конуса угла зрения от камеры: 24 мм широкий, 50 мм средний, 135 мм узкий.</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>#PL031 #focallength #angleofview #magnification</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>Объектив / фокусное расстояние</t>
+        </is>
+      </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="17" customHeight="1" s="72">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>PL-HIST-0325</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>системы объективов</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Фикс-объектив имеет одно фокусное расстояние; zoom позволяет менять фокусное расстояние в диапазоне, но обычно добавляет сложность, вес и компромиссы.</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Prime vs zoom lens</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>Выбор объектива становится выбором поведения: фикс заставляет двигаться, zoom даёт гибкость кадрирования.</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Светосила</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Главная линия / тип объектива</t>
+        </is>
+      </c>
+      <c r="N326" t="n">
+        <v>5</v>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>PL-031</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>SRC-252</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Understanding Camera Lenses</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-lenses.htm</t>
+        </is>
+      </c>
+      <c r="S326" t="n">
+        <v>5</v>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>Практически важно для новичка: 50 мм фикс как учебный тренажёр, но не догма.</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>Слева 50mm prime, справа 24–70 zoom; между ними стрелки «двигаться / менять масштаб».</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>#PL031 #prime #zoom #lenschoice</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>Объектив / фикс и зум</t>
+        </is>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="17" customHeight="1" s="72">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>PL-HIST-0326</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>объективы f/1.4–f/5.6</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Светосила показывает максимальное открытие диафрагмы: чем меньше число f, тем больше света может пройти через объектив и тем сильнее можно отделить объект размытием.</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Maximum aperture / lens speed</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>Объектив влияет на работу при слабом свете и на выразительность глубины резкости.</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Фикс и зум</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Аберрации</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>Главная линия / светосила</t>
+        </is>
+      </c>
+      <c r="N327" t="n">
+        <v>5</v>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>PL-031</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>SRC-252</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Understanding Camera Lenses</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-lenses.htm</t>
+        </is>
+      </c>
+      <c r="S327" t="n">
+        <v>5</v>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>Связать с будущим PL-038 «Светосила».</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>Два объектива: f/1.4 и f/4; позади — разная степень размытия.</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>#PL031 #maximumaperture #lensspeed #bokeh</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>Объектив / светосила</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="17" customHeight="1" s="72">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>PL-HIST-0327</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>оптическое проектирование</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>оптики / производители</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Объективы состоят из нескольких элементов, потому что одиночная линза даёт искажения: сферические и хроматические аберрации, падение резкости и другие ошибки.</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Optical aberrations and correction</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>Оптика становится инженерной задачей: нужно не просто собрать свет, а собрать его правильно.</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Светосила</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Покрытия</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Главная линия / оптическая коррекция</t>
+        </is>
+      </c>
+      <c r="N328" t="n">
+        <v>5</v>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>PL-031</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>SRC-252</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Understanding Camera Lenses</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-lenses.htm</t>
+        </is>
+      </c>
+      <c r="S328" t="n">
+        <v>5</v>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>Показать, почему объектив — это не одна линза.</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>Световые лучи разных цветов сходятся не в одной точке; рядом исправленная схема через группу линз.</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>#PL031 #aberration #lens-elements #optics</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>Объектив / аберрации</t>
+        </is>
+      </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="17" customHeight="1" s="72">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>PL-HIST-0328</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>оптическое производство</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Canon / ZEISS / производители</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Покрытия на линзах уменьшают отражения, блики и потерю контраста, особенно когда объектив состоит из многих стеклянных поверхностей.</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Lens coatings / flare control</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>Качество объектива зависит не только от схемы, но и от материала, просветления и контроля паразитного света.</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Аберрации</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Характер объектива</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>Главная линия / просветление</t>
+        </is>
+      </c>
+      <c r="N329" t="n">
+        <v>5</v>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>PL-031</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>SRC-258</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>Canon Science Lab — Lens Coatings</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>https://global.canon/en/technology/s_labo/light/003/03.html</t>
+        </is>
+      </c>
+      <c r="S329" t="n">
+        <v>5</v>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>Простой смысл: просветление помогает свету пройти через объектив без лишних отражений.</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>Макро линзы с зелёно-фиолетовым отблеском покрытия; сбоку схема отражений.</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>#PL031 #coating #flare #contrast</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>Объектив / просветление</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="17" customHeight="1" s="72">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>PL-HIST-0329</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>фотографическая практика</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Итог PL-031: объектив не просто делает картинку резкой. Он задаёт угол зрения, светосилу, рисунок, контраст, характер размытия и способ смотреть на сцену.</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Lens character as visual choice</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>Модуль объективов начинается с понимания: оптика — это язык фотографии, а не только техническая деталь.</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Характер объектива</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>PL-032 — из чего состоит объектив</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N330" t="n">
+        <v>5</v>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>PL-031</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>SRC-252</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Understanding Camera Lenses</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-lenses.htm</t>
+        </is>
+      </c>
+      <c r="S330" t="n">
+        <v>5</v>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>Финал и переход: следующий урок — анатомия объектива.</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>Один сюжет снят разными объективами; в центре подпись «объектив = способ видеть».</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>#PL031 #lens-character #visual-language #module4</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>Объектив / характер изображения</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="17" customHeight="1" s="72">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>PL-HIST-0330</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>объектив / система камеры</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>производители объективов</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Объектив состоит из оптических элементов, групп, корпуса, байонета, механизма фокусировки, диафрагмы, шкал или электронных контактов и защитных элементов.</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Lens anatomy</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>Объектив становится понятной системой: каждая деталь управляет светом, точностью, совместимостью или удобством работы.</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>PL-031 — что такое объектив</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Элементы и группы</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N331" t="n">
+        <v>5</v>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>SRC-259</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>Nikon — NIKKOR Lens Glossary</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>https://imaging.nikon.com/imaging/lineup/lens/glossary/</t>
+        </is>
+      </c>
+      <c r="S331" t="n">
+        <v>5</v>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>Флагман PL-032: разобрать объектив как механизм, а не как загадочную трубу.</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>Разрез объектива с подписанными зонами без перегруза: элементы, диафрагма, фокус, байонет.</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>#PL032 #lens-anatomy #lens-elements #aperture</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>Объектив / анатомия</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="17" customHeight="1" s="72">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>PL-HIST-0331</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>внутри объектива</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Canon / оптики</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Оптические элементы — это отдельные линзы; группы — элементы, работающие вместе. Их форма, стекло и положение корректируют резкость, цвет и искажения.</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Lens elements and groups</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>Фотограф начинает понимать, почему в характеристиках пишут «6 элементов в 5 группах» или «11 элементов».</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Анатомия объектива</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Корпус объектива</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Главная линия / оптическая схема</t>
+        </is>
+      </c>
+      <c r="N332" t="n">
+        <v>5</v>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>SRC-260</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>Canon Camera Museum — EF50mm f/1.8</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>https://global.canon/en/c-museum/product/ef259.html</t>
+        </is>
+      </c>
+      <c r="S332" t="n">
+        <v>5</v>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>Использовать Canon EF 50mm f/1.8 как простой пример элементов/групп.</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>Схематический разрез 50 мм объектива: шесть стеклянных элементов в группах.</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>#PL032 #elements #groups #lensconstruction</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>Объектив / элементы и группы</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="17" customHeight="1" s="72">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>PL-HIST-0332</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>корпус объектива</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>производители</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Корпус объектива удерживает элементы строго на своих местах: даже маленькое смещение может испортить резкость, центрировку и работу фокуса.</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Lens barrel / alignment</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>Механическая точность становится частью качества изображения.</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Элементы и группы</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Фокусировочный механизм</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Главная линия / механическая точность</t>
+        </is>
+      </c>
+      <c r="N333" t="n">
+        <v>4</v>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>SRC-262</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>Nikon — What's inside a Nikon Z mount camera lens?</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>https://www.nikon.nl/nl_NL/learn-and-explore/magazine/gear/whats-inside-a-z-mount-camera-lens</t>
+        </is>
+      </c>
+      <c r="S333" t="n">
+        <v>5</v>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>Объяснить: объектив — точный прибор, не просто набор стекла.</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>Металлический корпус в разрезе, элементы закреплены в кольцах.</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>#PL032 #lensbarrel #alignment #mechanics</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>Объектив / корпус и центрировка</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="17" customHeight="1" s="72">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>PL-HIST-0333</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>механизм фокусировки</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>фотограф / производители</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Фокусировочное кольцо или мотор двигает линзоблок, меняя расстояние фокусировки и точку, где лучи сходятся на плёнке.</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Focus ring / focusing group</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Резкость становится управляемым движением внутри объектива.</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Корпус и центрировка</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Диафрагма</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Главная линия / фокусировочный механизм</t>
+        </is>
+      </c>
+      <c r="N334" t="n">
+        <v>5</v>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>SRC-257</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — How Focus Works</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/how-focus-works</t>
+        </is>
+      </c>
+      <c r="S334" t="n">
+        <v>5</v>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>Отличный визуальный слайд: поворот кольца → движение группы.</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>Макро: рука поворачивает focus ring, внутри золото подсвечивает двигающуюся группу.</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>#PL032 #focusring #focusinggroup #manualfocus</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>Объектив / фокусировочный механизм</t>
+        </is>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="17" customHeight="1" s="72">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>PL-HIST-0334</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>внутри объектива</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Nikon / Canon / ZEISS</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Диафрагма состоит из подвижных лепестков, которые образуют отверстие разного размера и регулируют поток света.</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Aperture diaphragm blades</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>Внутри объектива появляется управляемая «радужка», похожая по смыслу на зрачок глаза.</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Фокусировочный механизм</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Кольцо диафрагмы / электронное управление</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>Главная линия / диафрагма</t>
+        </is>
+      </c>
+      <c r="N335" t="n">
+        <v>5</v>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>SRC-259</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>Nikon — NIKKOR Lens Glossary</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>https://imaging.nikon.com/imaging/lineup/lens/glossary/</t>
+        </is>
+      </c>
+      <c r="S335" t="n">
+        <v>5</v>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>Подготовка к PL-039 про диафрагму внутри объектива.</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>Крупный план лепестков диафрагмы на f/2.8, f/8, f/16.</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>#PL032 #diaphragm #apertureblades #fstop</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>Объектив / лепестки диафрагмы</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="17" customHeight="1" s="72">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>PL-HIST-0335</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>XX век — сегодня</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>мануальные и электронные объективы</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>производители камер</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>На старых объективах диафрагму часто меняют кольцом, а в современных системах камера может управлять ей через рычаги или электронные контакты.</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Aperture control ring / electronic diaphragm</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>Связь между камерой и объективом становится частью экспозиции и автоматизации.</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Лепестки диафрагмы</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Байонет</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>Главная линия / управление объективом</t>
+        </is>
+      </c>
+      <c r="N336" t="n">
+        <v>5</v>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>SRC-259</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>Nikon — NIKKOR Lens Glossary</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>https://imaging.nikon.com/imaging/lineup/lens/glossary/</t>
+        </is>
+      </c>
+      <c r="S336" t="n">
+        <v>5</v>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>Связать с PL-022/023: механика и автоматика продолжаются внутри объектива.</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>Старое кольцо диафрагмы рядом с современным байонетом с электронными контактами.</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>#PL032 #aperturering #electronicdiaphragm #lenscontrol</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>Объектив / управление диафрагмой</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="17" customHeight="1" s="72">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>PL-HIST-0336</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>XX век — сегодня</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>байонет камеры</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Nikon / Canon / Leica / производители</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Байонет соединяет объектив с камерой: он задаёт совместимость, рабочий отрезок, механические или электронные связи и передачу управления.</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Lens mount / bayonet</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>Выбор системы объективов становится частью выбора камеры и будущего набора оптики.</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Управление диафрагмой</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Шкалы объектива</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Главная линия / системная совместимость</t>
+        </is>
+      </c>
+      <c r="N337" t="n">
+        <v>5</v>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>SRC-171</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>Nikon — 50th Anniversary of Nikon F-Mount</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>https://www.nikon.com/company/news/2009/0303_f-mount50th_01/</t>
+        </is>
+      </c>
+      <c r="S337" t="n">
+        <v>5</v>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>Использовать уже имеющуюся историю Nikon F-mount как пример устойчивой системы.</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>Байонет крупным планом: металлические лепестки, красная точка, контакты.</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>#PL032 #lensmount #bayonet #compatibility</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>Объектив / байонет</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="17" customHeight="1" s="72">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>PL-HIST-0337</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>XX век — сегодня</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>мануальные объективы</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>фотографы</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Шкала расстояний и шкала глубины резкости помогают заранее оценить фокус и зону резкости, особенно на механических и дальномерных камерах.</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Distance scale / depth-of-field scale</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>Объектив становится не только оптикой, но и визуальным калькулятором фокуса.</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Байонет</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Покрытия и материалы</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Главная линия / ручной контроль</t>
+        </is>
+      </c>
+      <c r="N338" t="n">
+        <v>4</v>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>SRC-168</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>Nikon — FM2 Instruction Manual</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>https://cdn-10.nikon-cdn.com/pdf/manuals/archive/FM2.pdf</t>
+        </is>
+      </c>
+      <c r="S338" t="n">
+        <v>5</v>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>Полезно для будущих уроков про зонную фокусировку.</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>Крупный план шкалы 1m–∞ и меток f/8–f/16 на старом объективе.</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>#PL032 #distancescale #dofscale #zonefocus</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>Объектив / шкалы фокуса</t>
+        </is>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="17" customHeight="1" s="72">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>PL-HIST-0338</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>оптическое производство</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Canon / ZEISS</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Стекло, специальные элементы и просветление влияют на контраст, цветопередачу, блики, резкость и устойчивость к сложному свету.</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Glass / coatings / optical materials</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>Материалы объектива становятся частью его характера и цены.</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Шкалы фокуса</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Автофокус и стабилизация</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Главная линия / оптические материалы</t>
+        </is>
+      </c>
+      <c r="N339" t="n">
+        <v>5</v>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>SRC-261</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>ZEISS — Classic Lenses</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>https://www.zeiss.com/photonics-and-optics/en/photography/products/lenses-for-slr-cameras/classic-lenses.html</t>
+        </is>
+      </c>
+      <c r="S339" t="n">
+        <v>5</v>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>Пояснить, почему две линзы с похожими цифрами могут рисовать по-разному.</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>Срез стеклянных элементов с тонким цветным отблеском покрытий.</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>#PL032 #glass #coating #contrast #flare</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>Объектив / стекло и покрытия</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="17" customHeight="1" s="72">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>PL-HIST-0339</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>конец XX века — сегодня</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>диапазон</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>автофокусные объективы</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Nikon / Canon / производители</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>В современных объективах могут быть моторы автофокуса, стабилизация, электронные контакты и внутренние датчики; в старых — механические кольца, рычаги и кулачки.</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>AF motor / VR / electronic lens systems</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>Объектив превращается из чистой оптики в мехатронную систему.</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Стекло и покрытия</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Бленда и фильтр</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Главная линия / современная механика</t>
+        </is>
+      </c>
+      <c r="N340" t="n">
+        <v>4</v>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>SRC-262</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>Nikon — What's inside a Nikon Z mount camera lens?</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>https://www.nikon.nl/nl_NL/learn-and-explore/magazine/gear/whats-inside-a-z-mount-camera-lens</t>
+        </is>
+      </c>
+      <c r="S340" t="n">
+        <v>5</v>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>Объяснить разницу между полностью механическим и современным электронным объективом.</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>Разрез современного объектива: мотор, шлейф, стабилизирующая группа.</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>#PL032 #autofocus #VR #electroniclens</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>Объектив / моторы и стабилизация</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="17" customHeight="1" s="72">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>PL-HIST-0340</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>передняя часть объектива</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>фотографы</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Резьба под фильтр и бленда защищают объектив и управляют нежелательным светом: фильтры меняют или защищают, бленда снижает боковые блики.</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Filter thread / lens hood</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>Внешние детали тоже влияют на практическое качество кадра и удобство работы.</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Моторы и стабилизация</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>PL-033 — маркировка фокусного расстояния</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Главная линия / практические элементы</t>
+        </is>
+      </c>
+      <c r="N341" t="n">
+        <v>4</v>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>SRC-258</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>Canon Science Lab — Lens Coatings</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>https://global.canon/en/technology/s_labo/light/003/03.html</t>
+        </is>
+      </c>
+      <c r="S341" t="n">
+        <v>5</v>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>Финальный практический элемент PL-032: внешние детали помогают контролировать паразитный свет и защищать оптику.</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>Объектив с установленной блендой и фильтром; боковой луч отсекается.</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>#PL032 #filterthread #lenshood #flarecontrol</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>Объектив / фильтр и бленда</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="17" customHeight="1" s="72">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>PL-HIST-0341</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>маркировка объективов</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Canon / Nikon / производители</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние обычно видно прямо в названии объектива: например, 50mm, 35mm или 24–70mm. Это первая цифра, по которой фотограф понимает угол зрения.</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Reading focal length on lens name</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>Новичок учится читать объектив не как набор букв, а как карту возможностей: байонет, фокусное расстояние, светосила и технологии.</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>PL-032 — устройство объектива</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>PL-033 — определение фокусного расстояния</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N342" t="n">
+        <v>5</v>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>SRC-266</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>Canon UK Store — How to Read a Canon Lens Name</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>https://www.canon.co.uk/store/buying-guides/how-to-read-canon-lens/</t>
+        </is>
+      </c>
+      <c r="S342" t="n">
+        <v>5</v>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>Мост от анатомии объектива к фокусному расстоянию: сначала научиться читать надписи на объективе.</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>Крупный план переднего кольца объектива с маркировкой 50mm f/1.8; стрелка выделяет фокусное расстояние.</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>#PL033 #lensname #focallength #50mm</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / маркировка объектива</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="17" customHeight="1" s="72">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>PL-HIST-0342</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>объективы / кадр</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Nikon / Canon / фотографы</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние — это оптическая величина в миллиметрах, которая определяет угол зрения и масштаб изображения; это не просто физическая длина объектива.</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Focal length definition</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>Фотограф получает главный язык выбора объектива: сколько пространства войдёт в кадр и насколько крупно будет выглядеть объект.</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>PL-032 — устройство объектива</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Широкий угол</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N343" t="n">
+        <v>5</v>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>SRC-253</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding Focal Length</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-focal-length</t>
+        </is>
+      </c>
+      <c r="S343" t="n">
+        <v>5</v>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>Флагман PL-033: фокусное расстояние = угол зрения и масштаб, а не «длина трубы».</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>Три объектива 24/50/135 мм и три разных конуса угла зрения.</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>#PL033 #focallength #angleofview #magnification</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / определение</t>
+        </is>
+      </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="17" customHeight="1" s="72">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>PL-HIST-0343</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>широкоугольная съёмка</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Короткое фокусное расстояние даёт широкий угол зрения: в кадр входит больше пространства, а близкие предметы становятся визуально активнее.</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Wide-angle focal lengths</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>Широкий угол усиливает ощущение пространства и близости, но требует аккуратной работы с краями и перспективой.</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Определение</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Нормальный объектив</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>Главная линия / широкий угол</t>
+        </is>
+      </c>
+      <c r="N344" t="n">
+        <v>5</v>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>SRC-263</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Using Wide Angle Lenses</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/wide-angle-lenses.htm</t>
+        </is>
+      </c>
+      <c r="S344" t="n">
+        <v>5</v>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>Подготовка к PL-034.</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>Схема 24 мм: широкий конус, передний план крупный, фон далеко.</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>#PL033 #wideangle #24mm #space</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / широкий угол</t>
+        </is>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="17" customHeight="1" s="72">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>PL-HIST-0344</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>35 мм формат</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>фотографы</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Около 50 мм на 35-мм кадре часто воспринимается как «нормальный» угол: он не слишком широкий и не слишком узкий, поэтому удобен для обучения взгляду.</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Normal lens around 50mm</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>Нормальный объектив становится учебной точкой отсчёта между широким и длинным фокусным расстоянием.</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Широкий угол</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Телефото</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>Главная линия / нормальный объектив</t>
+        </is>
+      </c>
+      <c r="N345" t="n">
+        <v>5</v>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>SRC-265</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>Nikon UK — What is focal length?</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>https://www.nikon.co.uk/en_GB/learn-and-explore/magazine/tips-and-tricks/what-is-focal-length-in-photography-a-guide-for-beginners</t>
+        </is>
+      </c>
+      <c r="S345" t="n">
+        <v>5</v>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>Важно не говорить, что 50 мм «повторяет глаз» буквально; лучше — удобная нейтральная точка отсчёта.</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>Кадр 50 мм: человек в среде без сильного искажения и без сильного сжатия.</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>#PL033 #50mm #normal-lens #35mm</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / нормальный объектив</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>Терминология / язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="17" customHeight="1" s="72">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>PL-HIST-0345</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>портрет / спорт / детали</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Длинное фокусное расстояние даёт узкий угол зрения и увеличивает далёкие объекты в кадре: фотограф может выделить деталь, лицо или дальний фрагмент сцены.</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Telephoto focal lengths</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>Телефото превращает выбор объектива в способ изоляции объекта и уплотнения визуального поля.</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Нормальный объектив</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Перспектива и дистанция</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>Главная линия / телефото</t>
+        </is>
+      </c>
+      <c r="N346" t="n">
+        <v>5</v>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>SRC-264</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Using Telephoto Lenses</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/telephoto-lenses.htm</t>
+        </is>
+      </c>
+      <c r="S346" t="n">
+        <v>5</v>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>Подготовка к PL-037.</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>Схема 135 мм: узкий конус, объект крупный, фон кажется ближе.</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>#PL033 #telephoto #135mm #isolation</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / телефото</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="17" customHeight="1" s="72">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>PL-HIST-0346</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>любая съёмка</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>фотограф / преподаватель</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Перспектива зависит от позиции камеры, а не от фокусного расстояния само по себе. Но выбранный объектив часто заставляет фотографа подойти ближе или отойти дальше.</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Focal length vs perspective</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>Урок снимает частую ошибку: «объектив сжимает перспективу» — на практике это связано с дистанцией съёмки и кадрированием.</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Телефото</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Одинаковый масштаб разными объективами</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>Главная линия / исправление заблуждения</t>
+        </is>
+      </c>
+      <c r="N347" t="n">
+        <v>5</v>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>SRC-252</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Understanding Camera Lenses</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-lenses.htm</t>
+        </is>
+      </c>
+      <c r="S347" t="n">
+        <v>5</v>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>Очень важная образовательная точка для новичков.</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>Две камеры на разных расстояниях от портрета; линии перспективы показывают изменение дистанции.</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>#PL033 #perspective #distance #lensmyth</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / перспектива и дистанция</t>
+        </is>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>Терминология / язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="17" customHeight="1" s="72">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>PL-HIST-0347</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>портрет / улица</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Если сохранить объект одного размера в кадре, но менять фокусное расстояние, фотограф будет менять дистанцию — поэтому фон, лицо и пространство начнут выглядеть иначе.</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Same framing with different focal lengths</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние становится практическим выбором дистанции и отношений между объектом и фоном.</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Перспектива и дистанция</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Формат кадра</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальный эксперимент</t>
+        </is>
+      </c>
+      <c r="N348" t="n">
+        <v>5</v>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>SRC-264</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Using Telephoto Lenses</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/telephoto-lenses.htm</t>
+        </is>
+      </c>
+      <c r="S348" t="n">
+        <v>5</v>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>Практика: снять портрет на 28/50/85 с одинаковым размером лица.</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>Триптих портрета: 28 мм близко, 50 мм средне, 85 мм дальше.</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>#PL033 #portrait #sameframing #backgroundcompression</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / одинаковый масштаб</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="17" customHeight="1" s="72">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>PL-HIST-0348</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>35 мм / APS-C / средний формат</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>фотографы</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Один и тот же объектив даёт разный угол зрения на разных форматах кадра: меньший кадр обрезает изображение, больший показывает шире.</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Format / crop factor and angle of view</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние нужно понимать вместе с размером кадра: 50 мм на разных форматах не даёт одинакового поля зрения.</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Одинаковый масштаб</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Фикс и зум</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>Главная линия / формат кадра</t>
+        </is>
+      </c>
+      <c r="N349" t="n">
+        <v>5</v>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>SRC-253</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding Focal Length</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-focal-length</t>
+        </is>
+      </c>
+      <c r="S349" t="n">
+        <v>5</v>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>Связать плёнку 35 мм, средний формат и цифровые сенсоры.</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>Один круг изображения, внутри рамки: 35 мм, APS-C, 6×6; разный crop.</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>#PL033 #cropfactor #format #angleofview</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / формат кадра</t>
+        </is>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="17" customHeight="1" s="72">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>PL-HIST-0349</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>набор объективов</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Фикс учит заранее думать углом зрения, а zoom даёт быстро менять кадр без смены объектива. Оба варианта полезны, если фотограф понимает задачу.</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Prime and zoom focal-length workflow</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние становится не только числом, но и способом двигаться, выбирать расстояние и строить серию.</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Формат кадра</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Минимальная дистанция фокусировки</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>Главная линия / рабочий процесс</t>
+        </is>
+      </c>
+      <c r="N350" t="n">
+        <v>5</v>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>SRC-252</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Understanding Camera Lenses</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-lenses.htm</t>
+        </is>
+      </c>
+      <c r="S350" t="n">
+        <v>5</v>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>Сформулировать без догмы: фикс не «лучше», zoom не «хуже» — это разные рабочие ритмы.</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>Фотограф с фикс-объективом шагает; рядом фотограф меняет кольцо зума.</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>#PL033 #prime #zoom #workflow</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / фикс и зум</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="17" customHeight="1" s="72">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>PL-HIST-0350</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>макро / предметка</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние не равно масштабу макро: для крупного плана важны минимальная дистанция фокусировки, увеличение и конструкция объектива.</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Minimum focus distance / magnification</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>Новичок учится читать характеристики объектива шире, чем только «сколько миллиметров».</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Фикс и зум</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Выбор фокусного под жанр</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>Главная линия / практическая характеристика</t>
+        </is>
+      </c>
+      <c r="N351" t="n">
+        <v>4</v>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>SRC-257</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — How Focus Works</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/how-focus-works</t>
+        </is>
+      </c>
+      <c r="S351" t="n">
+        <v>5</v>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>Важно перед будущими уроками о предметке и макро.</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>Объектив фокусируется на маленьком предмете; подписи MFD и magnification.</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>#PL033 #minimumfocusdistance #magnification #macro</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / минимальная дистанция</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="17" customHeight="1" s="72">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>PL-HIST-0351</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>PHOTO LAB / модуль объективов</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>PHOTO LAB by VF</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Итог PL-033: фокусное расстояние — это выбор угла зрения, дистанции работы и ощущения пространства. Дальше можно отдельно разобрать широкий, нормальный, портретный и телеобъектив.</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Focal length as visual language</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние превращается из технической цифры в авторский инструмент.</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Минимальная дистанция фокусировки</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>PL-034 — широкоугольный объектив</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N352" t="n">
+        <v>5</v>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>SRC-265</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>Nikon UK — What is focal length?</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>https://www.nikon.co.uk/en_GB/learn-and-explore/magazine/tips-and-tricks/what-is-focal-length-in-photography-a-guide-for-beginners</t>
+        </is>
+      </c>
+      <c r="S352" t="n">
+        <v>5</v>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>Финальный мост к PL-034–PL-037.</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>Лента из четырёх кадров: wide / normal / portrait / telephoto.</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>#PL033 #visual-language #wide #normal #telephoto</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / мост к типам объективов</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
     <row r="353" ht="17" customHeight="1" s="72"/>
     <row r="354" ht="17" customHeight="1" s="72"/>
     <row r="355" ht="17" customHeight="1" s="72"/>
@@ -39089,12 +45607,12 @@
       </c>
       <c r="B3" s="76" t="inlineStr">
         <is>
-          <t>camera lucida, stereoscope, portable camera obscura, compact 35mm cameras, Leica I, Leica system, rangefinder lineage, SLR, TLR, compact point-and-shoot, средний формат, большой формат, view camera, устройство плёночной камеры, корпус, байонет, затвор, видоискатель, протяжка, механические и автоматические камеры</t>
+          <t>camera lucida, stereoscope, portable camera obscura, compact 35mm cameras, Leica I, Leica system, rangefinder lineage, SLR, TLR, compact point-and-shoot, средний формат, большой формат, view camera, устройство плёночной камеры, выбор первой камеры, авторская роль камеры, объектив, элементы объектива, байонет, диафрагма, фокусное расстояние, угол зрения</t>
         </is>
       </c>
       <c r="C3" s="76" t="inlineStr">
         <is>
-          <t>PL-001 / PL-009 / PL-010 / PL-021 / PL-022 / PL-023 / PL-024 / PL-025 / PL-026 / PL-027 / PL-028 / будущие PL</t>
+          <t>PL-001 / PL-009 / PL-010 / PL-021 / PL-022 / PL-023 / PL-024 / PL-025 / PL-026 / PL-027 / PL-028 / PL-029 / PL-030 / PL-031 / PL-032 / PL-033 / будущие PL</t>
         </is>
       </c>
       <c r="D3" s="76" t="inlineStr">
@@ -39104,7 +45622,7 @@
       </c>
       <c r="E3" s="76" t="inlineStr">
         <is>
-          <t>Помогает объяснить, как оптические и механические устройства постепенно стали современной плёночной камерой: от дальномера и SLR до компактных, среднеформатных и крупноформатных систем.</t>
+          <t>Помогает объяснить, как оптические и механические устройства постепенно стали современной фотографической системой: камера выбирается под задачу, объектив собирает свет, а фокусное расстояние формирует угол зрения и язык кадра.</t>
         </is>
       </c>
     </row>
@@ -39419,7 +45937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="9.6640625" customWidth="1" style="72" min="1" max="1"/>
@@ -40361,30 +46879,189 @@
     <row r="30">
       <c r="A30" s="75" t="inlineStr">
         <is>
+          <t>PL-029</t>
+        </is>
+      </c>
+      <c r="B30" s="75" t="inlineStr">
+        <is>
+          <t>Как выбрать первую плёночную камеру</t>
+        </is>
+      </c>
+      <c r="C30" s="75" t="inlineStr">
+        <is>
+          <t>PL-HIST-0297…0307</t>
+        </is>
+      </c>
+      <c r="D30" s="75" t="inlineStr">
+        <is>
+          <t>Первая камера выбирается не по легендарности модели, а по задаче: формат плёнки, состояние, объектив, батарейки, ремонтопригодность, доступность проявки и реальная цена владения.</t>
+        </is>
+      </c>
+      <c r="E30" s="75" t="inlineStr">
+        <is>
+          <t>основа заполнена</t>
+        </is>
+      </c>
+      <c r="F30" s="75" t="inlineStr">
+        <is>
+          <t>https://t.me/photolab_vf_pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PL-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Почему камера не делает фотографию за автора</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PL-HIST-0308…0318</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Камера фиксирует свет, но автор выбирает тему, момент, дистанцию, свет, рамку, отношение к человеку, отбор и финальную форму изображения.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>основа заполнена</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://t.me/photolab_vf_pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PL-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Что такое объектив</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PL-HIST-0319…0329</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Объектив — это оптическая система, которая собирает свет и фокусирует его на плёнке или сенсоре; он задаёт угол зрения, резкость, светосилу и характер изображения.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>основа заполнена</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://t.me/photolab_vf_pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Из чего состоит объектив</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PL-HIST-0330…0340</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Объектив состоит из элементов и групп, корпуса, байонета, фокусировочного механизма, диафрагмы, покрытий, шкал и внешних защитных деталей.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>основа заполнена</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://t.me/photolab_vf_pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PL-HIST-0341…0351</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние определяет угол зрения и масштаб изображения; вместе с дистанцией съёмки и размером кадра оно формирует ощущение пространства.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>основа заполнена</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://t.me/photolab_vf_pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>будущие PL</t>
         </is>
       </c>
-      <c r="B30" s="75" t="inlineStr">
-        <is>
-          <t>Расширение после PL-028</t>
-        </is>
-      </c>
-      <c r="C30" s="75" t="inlineStr">
-        <is>
-          <t>PL-029 — как выбрать первую плёночную камеру; PL-030 — почему камера не делает фотографию за автора</t>
-        </is>
-      </c>
-      <c r="D30" s="75" t="inlineStr">
-        <is>
-          <t>После типов камер курс завершит модуль 3 выбором первой камеры и выводом о роли автора.</t>
-        </is>
-      </c>
-      <c r="E30" s="75" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Расширение после PL-033</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PL-034 — широкоугольный объектив; PL-035 — нормальный объектив 50 мм; PL-036 — портретный объектив; PL-037 — телеобъектив</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>После понимания камеры и базовой анатомии объектива курс переходит к типам фокусных расстояний и выразительности оптики.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
-      <c r="F30" s="75" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -40400,7 +47077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E242"/>
+  <dimension ref="A1:E269"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="14" customWidth="1" style="72" min="1" max="1"/>
@@ -46939,6 +53616,735 @@
         </is>
       </c>
       <c r="E242" t="inlineStr">
+        <is>
+          <t>Общий образовательный источник (не производитель); проверено по содержанию статьи вручную</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>SRC-241</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Tips for Buying Your First Film Camera</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/tips-for-buying-your-first-film-camera</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Practical criteria for choosing a first film camera: SLR, compact, rangefinder; same film stock can be used across cameras</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник B&amp;H</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>SRC-242</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Best Film and Camera Combos: A Guide for Beginners</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/videos/photography/best-film-and-camera-combos-a-guide-for-beginners</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Beginner-oriented combinations of film cameras and film stocks, including 35mm SLR and medium-format rangefinder</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник B&amp;H</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SRC-243</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Buying Guide for the Film Photography Student</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/buying-guide/buying-guide-for-the-film-photography-student</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Film-student buying context: popularity, availability and cost of 35mm; manual 35mm SLR advice</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник B&amp;H</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SRC-244</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>ILFORD Photo — Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>https://www.ilfordphoto.com/beginners-guide/</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Beginner guide including first film camera, film formats, ISO and darkroom/processing basics</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал ILFORD</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>SRC-245</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>The Metropolitan Museum of Art — Henri Cartier-Bresson, Seville</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>https://www.metmuseum.org/art/collection/search/283312</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Cartier-Bresson, Leica, composition and decisive-moment philosophy; photographer's recognition of event and form</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>музейный источник The Met</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SRC-246</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>MoMA — Henri Cartier-Bresson, Seville, Spain, 1933</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>https://www.moma.org/collection/works/49890</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>MoMA object text on Cartier-Bresson and the decisive moment</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>музейный источник MoMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>SRC-247</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>SFMOMA — Henri Cartier-Bresson: The Modern Century</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>https://www.sfmoma.org/exhibition/henri-cartier-bresson/</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Cartier-Bresson as innovative artist and trailblazing photojournalist; creative potential of modern photography</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>музейный источник SFMOMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SRC-248</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>The Metropolitan Museum of Art — Faking It</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>https://www.metmuseum.org/exhibitions/listings/2012/faking-it</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Photographic manipulation, staging, combination printing and the photographer's ability to shape reality</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>музейный источник The Met</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>SRC-249</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>International Center of Photography — Henri Cartier-Bresson</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>https://www.icp.org/browse/archive/constituents/henri-cartier-bresson</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Cartier-Bresson and the decisive moment as ordering of world and meaning by a gifted photographer</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>музейный / архивный источник ICP</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>SRC-250</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Introduction to Learning Photography</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/introduction-to-learning-photography</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Learning photography: value of understanding camera technology, controls and how camera/lens record light</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник B&amp;H</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>SRC-251</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Canon Science Lab — Photographs</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>https://global.canon/en/technology/s_labo/light/003/01.html</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Present-day cameras work on the camera obscura principle with lens, aperture ring, shutter and film/CCD</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Canon</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>SRC-252</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Understanding Camera Lenses</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-lenses.htm</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Overview of focal length, perspective, prime/zoom, aperture and image quality</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>SRC-253</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding Focal Length</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-focal-length</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Focal length determines angle of view and magnification; explanation for photographers</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Nikon</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>SRC-254</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Canon — Interchangeable Lenses</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>https://global.canon/en/technology/canon-tech/tech/iclenses/</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Focal length definition and Canon optical technologies for interchangeable lenses</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Canon</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>SRC-255</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — How Your Digital Camera Works</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/how-your-digital-camera-works</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Lens elements focus light on image plane; diaphragm blades change aperture; shutter opens to expose image plane</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник B&amp;H</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>SRC-256</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Nikon USA — DSLR Lenses Overview</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/c/lenses/dslr-lenses/overview</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Nikon lens basics: focal length, angle of view, magnification and DSLR lens context</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Nikon</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>SRC-257</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — How Focus Works</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/how-focus-works</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Elements/groups and focusing group movement; focus ring changes where light converges</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник B&amp;H</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>SRC-258</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Canon Science Lab — Lens Coatings</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>https://global.canon/en/technology/s_labo/light/003/03.html</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Lens coatings and how multiple elements reduce light transmission/reflections</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Canon</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>SRC-259</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Nikon — NIKKOR Lens Glossary</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>https://imaging.nikon.com/imaging/lineup/lens/glossary/</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Lens terms including focus ring, diaphragm blade unit, aperture control and lens mechanisms</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>официальный справочник Nikon</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>SRC-260</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Canon Camera Museum — EF50mm f/1.8</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>https://global.canon/en/c-museum/product/ef259.html</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Example lens specifications: 6 elements in 5 groups and diaphragm blades</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>официальный Canon Camera Museum</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>SRC-261</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>ZEISS — Classic Lenses</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>https://www.zeiss.com/photonics-and-optics/en/photography/products/lenses-for-slr-cameras/classic-lenses.html</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Optical elements, T* anti-reflective coating and diaphragm blades as part of lens character</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>официальный источник ZEISS</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>SRC-262</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Nikon — What's inside a Nikon Z mount camera lens?</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>https://www.nikon.nl/nl_NL/learn-and-explore/magazine/gear/whats-inside-a-z-mount-camera-lens</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Inside modern lens: autofocus motors, aperture iris, VR system, optical elements and focusing on focal plane</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Nikon</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>SRC-263</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Using Wide Angle Lenses</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/wide-angle-lenses.htm</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Short focal lengths, wide angle of view and visual effects of wide-angle lenses</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>SRC-264</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Using Telephoto Lenses</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/telephoto-lenses.htm</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Telephoto focal lengths, narrow angle of view and the role of subject distance in perspective</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>SRC-265</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Nikon UK — What is focal length?</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>https://www.nikon.co.uk/en_GB/learn-and-explore/magazine/tips-and-tricks/what-is-focal-length-in-photography-a-guide-for-beginners</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Focal length explanation for beginners, field of view categories and storytelling use</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Nikon</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>SRC-266</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Canon UK Store — How to Read a Canon Lens Name</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>https://www.canon.co.uk/store/buying-guides/how-to-read-canon-lens/</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Lens name elements: mount, focal length, aperture and specific technologies</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Canon</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>SRC-241</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Wikipedia — F-number</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/F-number</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>PL-HIST-0323 (PL-031): число f как отношение фокусного расстояния к диаметру диафрагмы</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
         <is>
           <t>Общий образовательный источник (не производитель); проверено по содержанию статьи вручную</t>
         </is>
@@ -46958,7 +54364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H268"/>
+  <dimension ref="A1:H324"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="13.6640625" customWidth="1" style="72" min="1" max="1"/>
@@ -47774,7 +55180,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>будущие PL</t>
+          <t>PL-029</t>
         </is>
       </c>
       <c r="D30" s="4" t="n"/>
@@ -47796,7 +55202,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>межурочный узел</t>
+          <t>PL-030</t>
         </is>
       </c>
       <c r="D31" s="4" t="n"/>
@@ -47818,7 +55224,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>проверить</t>
+          <t>PL-031</t>
         </is>
       </c>
       <c r="D32" s="4" t="n"/>
@@ -47838,7 +55244,11 @@
           <t>Главная линия / контроль фокуса</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n"/>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>PL-032</t>
+        </is>
+      </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
@@ -47856,7 +55266,11 @@
           <t>Главная линия / техническая камера</t>
         </is>
       </c>
-      <c r="C34" s="4" t="n"/>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>PL-033</t>
+        </is>
+      </c>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
@@ -47874,7 +55288,11 @@
           <t>Научное применение / пример</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n"/>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>будущие PL</t>
+        </is>
+      </c>
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="n"/>
@@ -47892,7 +55310,11 @@
           <t>Исторически важная ограниченная ветка / художественное возрождение</t>
         </is>
       </c>
-      <c r="C36" s="4" t="n"/>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>межурочный узел</t>
+        </is>
+      </c>
       <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="n"/>
@@ -47905,7 +55327,11 @@
     </row>
     <row r="37" ht="20" customHeight="1" s="72">
       <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Главная линия / проверка перед покупкой</t>
+        </is>
+      </c>
       <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
@@ -47919,7 +55345,11 @@
     </row>
     <row r="38" ht="20" customHeight="1" s="72">
       <c r="A38" s="4" t="n"/>
-      <c r="B38" s="4" t="n"/>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Главная линия / учебная камера</t>
+        </is>
+      </c>
       <c r="C38" s="4" t="n"/>
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
@@ -47933,7 +55363,11 @@
     </row>
     <row r="39" ht="14" customHeight="1" s="72">
       <c r="A39" s="8" t="n"/>
-      <c r="B39" s="8" t="n"/>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Главная линия / осознанный выбор</t>
+        </is>
+      </c>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
@@ -47947,7 +55381,11 @@
     </row>
     <row r="40" ht="14" customHeight="1" s="72">
       <c r="A40" s="8" t="n"/>
-      <c r="B40" s="8" t="n"/>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Главная линия / простота входа</t>
+        </is>
+      </c>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="n"/>
@@ -47961,7 +55399,11 @@
     </row>
     <row r="41" ht="14" customHeight="1" s="72">
       <c r="A41" s="8" t="n"/>
-      <c r="B41" s="8" t="n"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Главная линия / системный выбор</t>
+        </is>
+      </c>
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
@@ -47975,7 +55417,11 @@
     </row>
     <row r="42" ht="14" customHeight="1" s="72">
       <c r="A42" s="8" t="n"/>
-      <c r="B42" s="8" t="n"/>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Главная линия / эксплуатационная проверка</t>
+        </is>
+      </c>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
@@ -47989,7 +55435,11 @@
     </row>
     <row r="43" ht="14" customHeight="1" s="72">
       <c r="A43" s="8" t="n"/>
-      <c r="B43" s="8" t="n"/>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Главная линия / практическая экономика</t>
+        </is>
+      </c>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
@@ -48003,7 +55453,11 @@
     </row>
     <row r="44" ht="14" customHeight="1" s="72">
       <c r="A44" s="8" t="n"/>
-      <c r="B44" s="8" t="n"/>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальное решение</t>
+        </is>
+      </c>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
@@ -48017,7 +55471,11 @@
     </row>
     <row r="45" ht="14" customHeight="1" s="72">
       <c r="A45" s="8" t="n"/>
-      <c r="B45" s="8" t="n"/>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальное мышление</t>
+        </is>
+      </c>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
@@ -48031,7 +55489,11 @@
     </row>
     <row r="46" ht="14" customHeight="1" s="72">
       <c r="A46" s="8" t="n"/>
-      <c r="B46" s="8" t="n"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Главная линия / композиционное решение</t>
+        </is>
+      </c>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
@@ -48044,6 +55506,11 @@
       </c>
     </row>
     <row r="47" ht="14" customHeight="1" s="72">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Главная линия / момент</t>
+        </is>
+      </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
           <t>Brownie / доступная камера</t>
@@ -48051,6 +55518,11 @@
       </c>
     </row>
     <row r="48" ht="14" customHeight="1" s="72">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Главная линия / точка съёмки</t>
+        </is>
+      </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
           <t>Brownie / цена и массовый рынок</t>
@@ -48058,6 +55530,11 @@
       </c>
     </row>
     <row r="49" ht="14" customHeight="1" s="72">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Главная линия / авторская ответственность</t>
+        </is>
+      </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
           <t>Brownie / детская аудитория и реклама</t>
@@ -48065,6 +55542,11 @@
       </c>
     </row>
     <row r="50" ht="14" customHeight="1" s="72">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Главная линия / авторская работа</t>
+        </is>
+      </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
           <t>Brownie / 120 roll film</t>
@@ -48072,6 +55554,11 @@
       </c>
     </row>
     <row r="51" ht="14" customHeight="1" s="72">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Главная линия / оптический принцип</t>
+        </is>
+      </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
           <t>Snapshot-культура / семейный альбом</t>
@@ -48079,6 +55566,11 @@
       </c>
     </row>
     <row r="52" ht="14" customHeight="1" s="72">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Главная линия / фокусировка</t>
+        </is>
+      </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Snapshot-культура / любительская практика</t>
@@ -48086,6 +55578,11 @@
       </c>
     </row>
     <row r="53" ht="14" customHeight="1" s="72">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Главная линия / световой контроль</t>
+        </is>
+      </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
           <t>Snapshot-культура / сервисная обработка</t>
@@ -48093,6 +55590,11 @@
       </c>
     </row>
     <row r="54" ht="14" customHeight="1" s="72">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Главная линия / угол зрения</t>
+        </is>
+      </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
           <t>Brownie / долгий жизненный цикл</t>
@@ -48100,6 +55602,11 @@
       </c>
     </row>
     <row r="55" ht="14" customHeight="1" s="72">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Главная линия / тип объектива</t>
+        </is>
+      </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
           <t>Snapshot-культура / культурный архив</t>
@@ -48107,6 +55614,11 @@
       </c>
     </row>
     <row r="56" ht="14" customHeight="1" s="72">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Главная линия / светосила</t>
+        </is>
+      </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
           <t>Brownie / мост к 35 мм</t>
@@ -48114,6 +55626,11 @@
       </c>
     </row>
     <row r="57" ht="14" customHeight="1" s="72">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Главная линия / оптическая коррекция</t>
+        </is>
+      </c>
       <c r="H57" s="75" t="inlineStr">
         <is>
           <t>35 мм / прозрачная рулонная плёнка</t>
@@ -48121,6 +55638,11 @@
       </c>
     </row>
     <row r="58" ht="14" customHeight="1" s="72">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Главная линия / просветление</t>
+        </is>
+      </c>
       <c r="H58" s="75" t="inlineStr">
         <is>
           <t>35 мм / киноистоки</t>
@@ -48128,6 +55650,11 @@
       </c>
     </row>
     <row r="59" ht="14" customHeight="1" s="72">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Главная линия / оптическая схема</t>
+        </is>
+      </c>
       <c r="H59" s="75" t="inlineStr">
         <is>
           <t>35 мм / ширина и перфорация</t>
@@ -48135,6 +55662,11 @@
       </c>
     </row>
     <row r="60" ht="14" customHeight="1" s="72">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Главная линия / механическая точность</t>
+        </is>
+      </c>
       <c r="H60" s="75" t="inlineStr">
         <is>
           <t>35 мм / Kinetoscope</t>
@@ -48142,6 +55674,11 @@
       </c>
     </row>
     <row r="61" ht="14" customHeight="1" s="72">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Главная линия / фокусировочный механизм</t>
+        </is>
+      </c>
       <c r="H61" s="75" t="inlineStr">
         <is>
           <t>35 мм / международный стандарт</t>
@@ -48149,6 +55686,11 @@
       </c>
     </row>
     <row r="62" ht="14" customHeight="1" s="72">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Главная линия / диафрагма</t>
+        </is>
+      </c>
       <c r="H62" s="75" t="inlineStr">
         <is>
           <t>35 мм / 24×36</t>
@@ -48156,6 +55698,11 @@
       </c>
     </row>
     <row r="63" ht="14" customHeight="1" s="72">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Главная линия / управление объективом</t>
+        </is>
+      </c>
       <c r="H63" s="75" t="inlineStr">
         <is>
           <t>35 мм / репортажность</t>
@@ -48163,6 +55710,11 @@
       </c>
     </row>
     <row r="64" ht="14" customHeight="1" s="72">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Главная линия / системная совместимость</t>
+        </is>
+      </c>
       <c r="H64" s="75" t="inlineStr">
         <is>
           <t>35 мм / коммерциализация Leica</t>
@@ -48170,6 +55722,11 @@
       </c>
     </row>
     <row r="65" ht="14" customHeight="1" s="72">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Главная линия / ручной контроль</t>
+        </is>
+      </c>
       <c r="H65" s="75" t="inlineStr">
         <is>
           <t>35 мм / мост к Leica I</t>
@@ -48177,6 +55734,11 @@
       </c>
     </row>
     <row r="66" ht="14" customHeight="1" s="72">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Главная линия / оптические материалы</t>
+        </is>
+      </c>
       <c r="H66" s="75" t="inlineStr">
         <is>
           <t>35 мм / 135 cartridge</t>
@@ -48184,6 +55746,11 @@
       </c>
     </row>
     <row r="67" ht="14" customHeight="1" s="72">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Главная линия / современная механика</t>
+        </is>
+      </c>
       <c r="H67" s="75" t="inlineStr">
         <is>
           <t>Leica I / прототип</t>
@@ -48191,6 +55758,11 @@
       </c>
     </row>
     <row r="68" ht="14" customHeight="1" s="72">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Главная линия / практические элементы</t>
+        </is>
+      </c>
       <c r="H68" s="75" t="inlineStr">
         <is>
           <t>Leica I / проверочная серия</t>
@@ -48198,6 +55770,11 @@
       </c>
     </row>
     <row r="69" ht="14" customHeight="1" s="72">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Главная линия / широкий угол</t>
+        </is>
+      </c>
       <c r="H69" s="75" t="inlineStr">
         <is>
           <t>Leica I / начало производства</t>
@@ -48205,6 +55782,11 @@
       </c>
     </row>
     <row r="70" ht="14" customHeight="1" s="72">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Главная линия / нормальный объектив</t>
+        </is>
+      </c>
       <c r="H70" s="75" t="inlineStr">
         <is>
           <t>Leica I / публичный дебют</t>
@@ -48212,6 +55794,11 @@
       </c>
     </row>
     <row r="71" ht="14" customHeight="1" s="72">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Главная линия / телефото</t>
+        </is>
+      </c>
       <c r="H71" s="75" t="inlineStr">
         <is>
           <t>Leica I / компактная камера</t>
@@ -48219,6 +55806,11 @@
       </c>
     </row>
     <row r="72" ht="14" customHeight="1" s="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Главная линия / исправление заблуждения</t>
+        </is>
+      </c>
       <c r="H72" s="75" t="inlineStr">
         <is>
           <t>Leica I / оптика и Elmar</t>
@@ -48226,6 +55818,11 @@
       </c>
     </row>
     <row r="73" ht="14" customHeight="1" s="72">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальный эксперимент</t>
+        </is>
+      </c>
       <c r="H73" s="75" t="inlineStr">
         <is>
           <t>Leica I / массовое принятие</t>
@@ -48233,6 +55830,11 @@
       </c>
     </row>
     <row r="74" ht="14" customHeight="1" s="72">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Главная линия / формат кадра</t>
+        </is>
+      </c>
       <c r="H74" s="75" t="inlineStr">
         <is>
           <t>Leica I / новая визуальная практика</t>
@@ -48240,6 +55842,11 @@
       </c>
     </row>
     <row r="75" ht="14" customHeight="1" s="72">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Главная линия / рабочий процесс</t>
+        </is>
+      </c>
       <c r="H75" s="75" t="inlineStr">
         <is>
           <t>Leica I / сменные объективы</t>
@@ -48247,6 +55854,11 @@
       </c>
     </row>
     <row r="76" ht="14" customHeight="1" s="72">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Главная линия / практическая характеристика</t>
+        </is>
+      </c>
       <c r="H76" s="75" t="inlineStr">
         <is>
           <t>Leica I / мост к дальномерной системе</t>
@@ -49594,6 +57206,398 @@
       <c r="H268" t="inlineStr">
         <is>
           <t>Большой формат / медленный рабочий процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / критерии</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / формат плёнки</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / проверка состояния</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / 35mm SLR</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / дальномер</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / компакт</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / формат и цена ошибки</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / система и объектив</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / батарейки и экспонометр</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / цена владения</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Выбор первой камеры / матрица решения</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Автор и камера / инструмент</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Автор и камера / место-рамка-момент</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Автор и камера / видеть свет</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Автор и камера / композиция</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Автор и камера / решающий момент</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Автор и камера / дистанция</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Автор и камера / объектив как язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Автор и камера / отношение к человеку</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Автор и камера / отбор и печать</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Автор и камера / техника усиливает решение</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Автор и камера / мост к объективам</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Объектив / базовое определение</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Объектив / линза против отверстия</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Объектив / фокальная плоскость</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Объектив / фокусировка</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Объектив / диафрагма</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Объектив / фокусное расстояние</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Объектив / фикс и зум</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Объектив / светосила</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Объектив / аберрации</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Объектив / просветление</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Объектив / характер изображения</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Объектив / анатомия</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Объектив / элементы и группы</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Объектив / корпус и центрировка</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Объектив / фокусировочный механизм</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Объектив / лепестки диафрагмы</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Объектив / управление диафрагмой</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Объектив / байонет</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Объектив / шкалы фокуса</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Объектив / стекло и покрытия</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Объектив / моторы и стабилизация</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Объектив / фильтр и бленда</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Объектив / осмотр перед покупкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / определение</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / широкий угол</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / нормальный объектив</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / телефото</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / перспектива и дистанция</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / одинаковый масштаб</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / формат кадра</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / фикс и зум</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / минимальная дистанция</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / мост к типам объективов</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Фокусное расстояние / маркировка объектива</t>
         </is>
       </c>
     </row>
@@ -49608,7 +57612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="40.6640625" customWidth="1" style="72" min="1" max="1"/>
@@ -49618,7 +57622,7 @@
     <row r="1" ht="40" customHeight="1" s="72">
       <c r="A1" s="32" t="inlineStr">
         <is>
-          <t>PHOTO LAB — History Map Master v0.17</t>
+          <t>PHOTO LAB — History Map Master v0.18</t>
         </is>
       </c>
       <c r="B1" s="20" t="n"/>
@@ -49643,7 +57647,7 @@
       </c>
       <c r="B3" s="80" t="inlineStr">
         <is>
-          <t>От оптических предпосылок камеры-обскуры до Leica I, полного Модуля 2 о плёнке и Модуля 3 по состоянию до PL-028: устройство, механика, автоматика, дальномерные камеры, SLR, compact, средний и большой формат; основа для PL-001–PL-028.</t>
+          <t>От оптических предпосылок камеры-обскуры до Leica I, полного Модуля 2 о плёнке и Модуля 3 до PL-030; начат Модуль 4 по объективам — PL-031, PL-032, PL-033. Основа для PL-001–PL-033.</t>
         </is>
       </c>
     </row>
@@ -49956,6 +57960,30 @@
       <c r="B29" s="75" t="inlineStr">
         <is>
           <t>PL-029: Как выбрать первую плёночную камеру — собрать практическую карту выбора: формат, тип камеры, ремонтопригодность, объектив, экспонометр, батарейки, цена владения и первые ошибки новичка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Что изменено в v0.18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Заполнены PL-029–PL-033: добавлены PL-HIST-0297…0351 по выбору первой плёночной камеры, роли автора, базовому определению объектива, устройству объектива и фокусному расстоянию. Добавлены источники SRC-241…SRC-266 и флагманские узлы PL-HIST-0297, PL-HIST-0308, PL-HIST-0319, PL-HIST-0330, PL-HIST-0342.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Следующий шаг</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PL-034: Широкоугольный объектив — собрать узлы по короткому фокусному расстоянию, широкому углу зрения, перспективе, переднему плану, архитектуре, улице и типичным ошибкам новичка.</t>
         </is>
       </c>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -1076,7 +1076,7 @@
     <row r="1" ht="40" customHeight="1" s="72">
       <c r="A1" s="31" t="inlineStr">
         <is>
-          <t>PHOTO LAB — Master Timeline v0.19</t>
+          <t>PHOTO LAB — Master Timeline v0.20</t>
         </is>
       </c>
       <c r="B1" s="20" t="n"/>
@@ -1147,12 +1147,12 @@
         </is>
       </c>
       <c r="B5" s="81">
-        <f>SUM(E10:E50)</f>
+        <f>SUM(E10:E55)</f>
         <v/>
       </c>
       <c r="C5" s="80" t="inlineStr">
         <is>
-          <t>Фактически заполненные PL; PL-040 пока планируется и даёт 0 узлов</t>
+          <t>Узлы для заполненных PL; PL-040 пока планируется и даёт 0 узлов</t>
         </is>
       </c>
       <c r="D5" s="75" t="n"/>
@@ -1863,7 +1863,7 @@
     <row r="51">
       <c r="D51" t="inlineStr">
         <is>
-          <t>будущие PL</t>
+          <t>PL-042</t>
         </is>
       </c>
       <c r="E51">
@@ -1874,7 +1874,7 @@
     <row r="52">
       <c r="D52" t="inlineStr">
         <is>
-          <t>межурочный узел</t>
+          <t>PL-043</t>
         </is>
       </c>
       <c r="E52">
@@ -1882,6 +1882,28 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
+      <c r="E53">
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$800,D53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
+      <c r="E54">
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$800,D54)</f>
+        <v/>
+      </c>
+    </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
@@ -1892,6 +1914,15 @@
         <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$800,"Фундаментальная предпосылка")</f>
         <v/>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
+      <c r="E55">
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$800,D55)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1903,6 +1934,15 @@
         <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$800,"Технология / процесс")</f>
         <v/>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>будущие PL</t>
+        </is>
+      </c>
+      <c r="E56">
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$800,D56)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1912,6 +1952,15 @@
       </c>
       <c r="B57">
         <f>COUNTIF('01_Master_Facts'!$Z$2:$Z$800,"Инструмент / устройство")</f>
+        <v/>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>межурочный узел</t>
+        </is>
+      </c>
+      <c r="E57">
+        <f>COUNTIF('01_Master_Facts'!$O$2:$O$800,D57)</f>
         <v/>
       </c>
     </row>
@@ -2018,7 +2067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA429"/>
+  <dimension ref="A1:AA484"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="14" customWidth="1" style="72" min="1" max="1"/>
@@ -54533,61 +54582,6521 @@
         </is>
       </c>
     </row>
-    <row r="430" ht="17" customHeight="1" s="72"/>
-    <row r="431" ht="17" customHeight="1" s="72"/>
-    <row r="432" ht="17" customHeight="1" s="72"/>
-    <row r="433" ht="17" customHeight="1" s="72"/>
-    <row r="434" ht="17" customHeight="1" s="72"/>
-    <row r="435" ht="17" customHeight="1" s="72"/>
-    <row r="436" ht="17" customHeight="1" s="72"/>
-    <row r="437" ht="17" customHeight="1" s="72"/>
-    <row r="438" ht="17" customHeight="1" s="72"/>
-    <row r="439" ht="17" customHeight="1" s="72"/>
-    <row r="440" ht="17" customHeight="1" s="72"/>
-    <row r="441" ht="17" customHeight="1" s="72"/>
-    <row r="442" ht="17" customHeight="1" s="72"/>
-    <row r="443" ht="17" customHeight="1" s="72"/>
-    <row r="444" ht="17" customHeight="1" s="72"/>
-    <row r="445" ht="17" customHeight="1" s="72"/>
-    <row r="446" ht="17" customHeight="1" s="72"/>
-    <row r="447" ht="17" customHeight="1" s="72"/>
-    <row r="448" ht="17" customHeight="1" s="72"/>
-    <row r="449" ht="17" customHeight="1" s="72"/>
-    <row r="450" ht="17" customHeight="1" s="72"/>
-    <row r="451" ht="17" customHeight="1" s="72"/>
-    <row r="452" ht="17" customHeight="1" s="72"/>
-    <row r="453" ht="17" customHeight="1" s="72"/>
-    <row r="454" ht="17" customHeight="1" s="72"/>
-    <row r="455" ht="17" customHeight="1" s="72"/>
-    <row r="456" ht="17" customHeight="1" s="72"/>
-    <row r="457" ht="17" customHeight="1" s="72"/>
-    <row r="458" ht="17" customHeight="1" s="72"/>
-    <row r="459" ht="17" customHeight="1" s="72"/>
-    <row r="460" ht="17" customHeight="1" s="72"/>
-    <row r="461" ht="17" customHeight="1" s="72"/>
-    <row r="462" ht="17" customHeight="1" s="72"/>
-    <row r="463" ht="17" customHeight="1" s="72"/>
-    <row r="464" ht="17" customHeight="1" s="72"/>
-    <row r="465" ht="17" customHeight="1" s="72"/>
-    <row r="466" ht="17" customHeight="1" s="72"/>
-    <row r="467" ht="17" customHeight="1" s="72"/>
-    <row r="468" ht="17" customHeight="1" s="72"/>
-    <row r="469" ht="17" customHeight="1" s="72"/>
-    <row r="470" ht="17" customHeight="1" s="72"/>
-    <row r="471" ht="17" customHeight="1" s="72"/>
-    <row r="472" ht="17" customHeight="1" s="72"/>
-    <row r="473" ht="17" customHeight="1" s="72"/>
-    <row r="474" ht="17" customHeight="1" s="72"/>
-    <row r="475" ht="17" customHeight="1" s="72"/>
-    <row r="476" ht="17" customHeight="1" s="72"/>
-    <row r="477" ht="17" customHeight="1" s="72"/>
-    <row r="478" ht="17" customHeight="1" s="72"/>
-    <row r="479" ht="17" customHeight="1" s="72"/>
-    <row r="480" ht="17" customHeight="1" s="72"/>
-    <row r="481" ht="17" customHeight="1" s="72"/>
-    <row r="482" ht="17" customHeight="1" s="72"/>
-    <row r="483" ht="17" customHeight="1" s="72"/>
-    <row r="484" ht="17" customHeight="1" s="72"/>
+    <row r="430" ht="17" customHeight="1" s="72">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>PL-HIST-0429</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>объектив / диафрагма</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>До ирисовой диафрагмы фотографы меняли количество света вручную: в объектив вставлялась тонкая металлическая пластина с одним просверленным отверстием — «стоп Уотерхауса» (Waterhouse stop, придуман в 1858 году). Разные отверстия давали разную яркость и глубину резкости, но менять их можно было только вручную, вынимая одну пластину и вставляя другую через щель в оправе объектива.</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Waterhouse stop (interchangeable aperture plate, 1858)</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>Диафрагма перестаёт быть просто «плавным окном»: до появления ирисового механизма с лепестками (примерно с 1900-х) фотографы буквально носили с собой набор металлических пластин с разными отверстиями и меняли их между кадрами вручную.</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>PL-041 — базовая экспозиция</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>f-number / число f</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>Главная линия / диафрагма</t>
+        </is>
+      </c>
+      <c r="N430" t="n">
+        <v>5</v>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>PL-042</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>SRC-312</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>Wikipedia — Waterhouse stop</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Waterhouse_stop</t>
+        </is>
+      </c>
+      <c r="S430" t="n">
+        <v>5</v>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>Флагман PL-042: не повторять «диафрагма — регулируемое окно» дословно (см. PL-021 PL-HIST-0213, PL-039 PL-HIST-0407) — показать, что современное плавное кольцо с лепестками появилось не сразу: раньше диафрагму меняли вручную, вставляя разные металлические пластины.</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>Рука вставляет тонкую металлическую пластину с отверстием в щель объектива; рядом — набор из 4–5 таких пластин разного диаметра.</t>
+        </is>
+      </c>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>#PL042 #aperture #waterhousestop #history #diaphragm</t>
+        </is>
+      </c>
+      <c r="Y430" t="inlineStr">
+        <is>
+          <t>Диафрагма / окно света</t>
+        </is>
+      </c>
+      <c r="Z430" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="17" customHeight="1" s="72">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>PL-HIST-0430</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>объектив / шкала f</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Число f работает наоборот интуиции: маленькое число f означает большое отверстие, а большое число f — маленькое отверстие.</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>F-number logic</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>Курс снимает главный страх новичка: f/2.8 светлее f/8 не потому, что число больше, а потому что отверстие шире.</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Диафрагма как окно</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Полные стопы диафрагмы</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>Главная линия / терминология</t>
+        </is>
+      </c>
+      <c r="N431" t="n">
+        <v>5</v>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>PL-042</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>SRC-297</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>Canon U.S.A. — What Is Aperture Photography?</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>https://www.usa.canon.com/learning/training-articles/training-articles-list/what-is-aperture</t>
+        </is>
+      </c>
+      <c r="S431" t="n">
+        <v>5</v>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>Дать очень коротко: f/2.8 — широко, f/8 — уже, f/16 — совсем узко.</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>Три круглых отверстия: f/2.8 большое, f/8 среднее, f/16 маленькое.</t>
+        </is>
+      </c>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>#PL042 #fnumber #fstop #aperture</t>
+        </is>
+      </c>
+      <c r="Y431" t="inlineStr">
+        <is>
+          <t>Диафрагма / число f</t>
+        </is>
+      </c>
+      <c r="Z431" t="inlineStr">
+        <is>
+          <t>Терминология / язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="17" customHeight="1" s="72">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>PL-HIST-0431</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>объектив / слабый свет</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Открытая диафрагма пропускает больше света и помогает снимать в помещении, вечером или в тени без слишком длинной выдержки.</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Wide aperture in low light</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>Диафрагма связывается с реальной съёмкой: открыть отверстие — значит дать плёнке или сенсору больше света.</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Число f</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Глубина резкости</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое применение</t>
+        </is>
+      </c>
+      <c r="N432" t="n">
+        <v>5</v>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>PL-042</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>SRC-296</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>Nikon USA — What is Aperture?</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/what-is-aperture</t>
+        </is>
+      </c>
+      <c r="S432" t="n">
+        <v>5</v>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>Связать с предыдущим модулем: светосильный объектив даёт запас света, но требует точного фокуса.</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>Камера у окна вечером: открытая диафрагма, широкий поток золотого света.</t>
+        </is>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>#PL042 #wideaperture #lowlight #lensspeed</t>
+        </is>
+      </c>
+      <c r="Y432" t="inlineStr">
+        <is>
+          <t>Диафрагма / съёмка в слабом свете</t>
+        </is>
+      </c>
+      <c r="Z432" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="17" customHeight="1" s="72">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>PL-HIST-0432</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>объектив / яркий свет</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Закрытая диафрагма пропускает меньше света: кадр темнеет, если не компенсировать это более длинной выдержкой или более высоким ISO.</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Narrow aperture / less light</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>Появляется логика компенсации: изменение диафрагмы сразу требует думать о выдержке и ISO.</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Открытая диафрагма</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Компенсация выдержкой или ISO</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>Главная линия / экспозиционная связь</t>
+        </is>
+      </c>
+      <c r="N433" t="n">
+        <v>5</v>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>PL-042</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>SRC-299</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Camera Exposure: Aperture, ISO &amp; Shutter Speed</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-exposure.htm</t>
+        </is>
+      </c>
+      <c r="S433" t="n">
+        <v>5</v>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>Не превращать в математику: показать, что закрыли окно — в комнате стало темнее, значит нужно больше времени или чувствительности.</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>Диафрагма почти закрыта; световой поток тонкий, рядом стрелка к более длинной выдержке.</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>#PL042 #narrowaperture #exposure #compensation</t>
+        </is>
+      </c>
+      <c r="Y433" t="inlineStr">
+        <is>
+          <t>Диафрагма / компенсация экспозиции</t>
+        </is>
+      </c>
+      <c r="Z433" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" ht="17" customHeight="1" s="72">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>PL-HIST-0433</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>объектив / резкость</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Диафрагма влияет не только на яркость, но и на глубину резкости: открытая диафрагма чаще размывает фон, закрытая — делает больше пространства резким.</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Aperture and depth of field</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>Диафрагма становится выразительным инструментом: она отделяет объект от фона или сохраняет резкость в глубину.</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Компенсация света</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>ГРИП как творческий выбор</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>Главная линия / глубина резкости</t>
+        </is>
+      </c>
+      <c r="N434" t="n">
+        <v>5</v>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>PL-042</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>SRC-297</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>Canon U.S.A. — What Is Aperture Photography?</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>https://www.usa.canon.com/learning/training-articles/training-articles-list/what-is-aperture</t>
+        </is>
+      </c>
+      <c r="S434" t="n">
+        <v>5</v>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>Важно: не обещать «всегда», потому что ГРИП зависит также от дистанции и фокусного расстояния.</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>Портрет с размытым фоном рядом с пейзажем, где резкость уходит далеко в глубину.</t>
+        </is>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>#PL042 #depthoffield #backgroundblur #focus</t>
+        </is>
+      </c>
+      <c r="Y434" t="inlineStr">
+        <is>
+          <t>Диафрагма / глубина резкости</t>
+        </is>
+      </c>
+      <c r="Z434" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" ht="17" customHeight="1" s="72">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>PL-HIST-0434</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>режим Av / A</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>В режиме приоритета диафрагмы фотограф выбирает отверстие, а камера подбирает выдержку для нужной экспозиции.</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Aperture priority / Av / A</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>Новичок получает удобный мост от автоматики к ручному контролю: сначала управлять глубиной резкости, а выдержку доверить камере.</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>ГРИП как выбор</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Выдержка как ответ камеры</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>Главная линия / режим камеры</t>
+        </is>
+      </c>
+      <c r="N435" t="n">
+        <v>4</v>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>PL-042</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>SRC-297</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>Canon U.S.A. — What Is Aperture Photography?</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>https://www.usa.canon.com/learning/training-articles/training-articles-list/what-is-aperture</t>
+        </is>
+      </c>
+      <c r="S435" t="n">
+        <v>5</v>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>Практический узел для приложения и урока: режим A/Av — лучший тренировочный режим для темы диафрагмы.</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>Диск режимов камеры на A/Av; фотограф выбирает f/2.8, камера показывает выдержку.</t>
+        </is>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>#PL042 #aperturepriority #Av #cameraMode</t>
+        </is>
+      </c>
+      <c r="Y435" t="inlineStr">
+        <is>
+          <t>Диафрагма / приоритет диафрагмы</t>
+        </is>
+      </c>
+      <c r="Z435" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" ht="17" customHeight="1" s="72">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>PL-HIST-0435</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>объектив / маркировка</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>производители объективов</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Максимальная диафрагма объектива показывает, насколько широко он может открыться: например, f/1.4, f/2 или f/2.8.</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Maximum aperture</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>Маркировка объектива становится понятной: цифра на корпусе — не просто название, а предел светового отверстия.</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Приоритет диафрагмы</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Светосила и цена/вес</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>Главная линия / маркировка объектива</t>
+        </is>
+      </c>
+      <c r="N436" t="n">
+        <v>4</v>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>PL-042</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>SRC-296</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>Nikon USA — What is Aperture?</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/what-is-aperture</t>
+        </is>
+      </c>
+      <c r="S436" t="n">
+        <v>5</v>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>Связать с PL-038 «Светосила»: сейчас используем это как экспозиционное окно.</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>Крупный план объектива с маркировкой 50mm 1:1.4; золотая стрелка на f/1.4.</t>
+        </is>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>#PL042 #maximumaperture #lensmarking #f14</t>
+        </is>
+      </c>
+      <c r="Y436" t="inlineStr">
+        <is>
+          <t>Диафрагма / максимальная диафрагма</t>
+        </is>
+      </c>
+      <c r="Z436" t="inlineStr">
+        <is>
+          <t>Терминология / язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="437" ht="17" customHeight="1" s="72">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>PL-HIST-0436</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>объектив / светосила</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Объектив с большой максимальной диафрагмой часто называют светосильным: он даёт больше света, но обычно требует больших линз, точного фокуса и стоит дороже.</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Lens speed / fast lens</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>Понятие «светосильный» связывается с практической ценой: больше света почти всегда означает компромиссы.</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Максимальная диафрагма</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Рабочая диафрагма</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>Главная линия / компромисс оптики</t>
+        </is>
+      </c>
+      <c r="N437" t="n">
+        <v>4</v>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>PL-042</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>SRC-298</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Exposure 101: Intro to Aperture</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/exposure-101-intro-to-aperture</t>
+        </is>
+      </c>
+      <c r="S437" t="n">
+        <v>5</v>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>Не делать культ f/1.4: объяснить, что светосила — инструмент, а не абсолютное качество.</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>Два объектива рядом: маленький f/2.8 и крупный f/1.4; золотые лучи разной ширины.</t>
+        </is>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>#PL042 #fastlens #lensspeed #compromise</t>
+        </is>
+      </c>
+      <c r="Y437" t="inlineStr">
+        <is>
+          <t>Диафрагма / светосильный объектив</t>
+        </is>
+      </c>
+      <c r="Z437" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="438" ht="17" customHeight="1" s="72">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>PL-HIST-0437</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>объектив / рабочая диафрагма</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Рабочая диафрагма — это не всегда максимально открыто: фотограф выбирает f/2, f/5.6 или f/11 под свет, резкость, фон и задачу кадра.</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Working aperture</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>Диафрагма перестаёт быть крайним положением и становится осознанным выбором под сцену.</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Светосила</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Стопы диафрагмы</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>Главная линия / авторский выбор</t>
+        </is>
+      </c>
+      <c r="N438" t="n">
+        <v>4</v>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>PL-042</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>SRC-299</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Camera Exposure: Aperture, ISO &amp; Shutter Speed</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-exposure.htm</t>
+        </is>
+      </c>
+      <c r="S438" t="n">
+        <v>5</v>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>Важный воспитательный момент: новичок не обязан всегда снимать на самой открытой дырке.</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>Шкала f/1.4—f/16, выбранная точка f/5.6; рядом кадр с балансом резкости и света.</t>
+        </is>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>#PL042 #workingaperture #f56 #choice</t>
+        </is>
+      </c>
+      <c r="Y438" t="inlineStr">
+        <is>
+          <t>Диафрагма / рабочее значение</t>
+        </is>
+      </c>
+      <c r="Z438" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="17" customHeight="1" s="72">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>PL-HIST-0438</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>экспозиционная шкала</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Один полный стоп диафрагмы меняет количество света в два раза, поэтому f-числа идут не линейно, а по особой последовательности.</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Aperture full stops</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>Фотограф начинает говорить на языке стопов: открыть на стоп — значит удвоить свет; закрыть на стоп — уменьшить вдвое.</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Рабочая диафрагма</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>PL-046 — стопы света</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>Главная линия / стопы</t>
+        </is>
+      </c>
+      <c r="N439" t="n">
+        <v>5</v>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>PL-042</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>SRC-299</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Camera Exposure: Aperture, ISO &amp; Shutter Speed</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-exposure.htm</t>
+        </is>
+      </c>
+      <c r="S439" t="n">
+        <v>5</v>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>Это мост к PL-046. Подать без сложной геометрии, только смысл «в два раза».</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>Лестница значений: f/2.8 → f/4 → f/5.6 → f/8; каждый шаг подписан 1 стоп.</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>#PL042 #stops #fstop #doubling</t>
+        </is>
+      </c>
+      <c r="Y439" t="inlineStr">
+        <is>
+          <t>Диафрагма / полные стопы</t>
+        </is>
+      </c>
+      <c r="Z439" t="inlineStr">
+        <is>
+          <t>Терминология / язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="17" customHeight="1" s="72">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>PL-HIST-0439</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>PHOTO LAB / модуль экспозиции</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>PHOTO LAB by VF</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Итог PL-042: диафрагма — это окно света. Она управляет количеством света и глубиной резкости, а значит соединяет техническую экспозицию с визуальным языком кадра.</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Aperture as exposure and visual language</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>Курс готов перейти к выдержке: если диафрагма отвечает за ширину светового потока, то выдержка отвечает за время его действия.</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Стопы диафрагмы</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>PL-043 — выдержка как время</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N440" t="n">
+        <v>5</v>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>PL-042</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>SRC-296</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>Nikon USA — What is Aperture?</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/what-is-aperture</t>
+        </is>
+      </c>
+      <c r="S440" t="n">
+        <v>5</v>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>Итоговая формула: ширина света + характер резкости.</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>Открывающееся окно превращается в шторки затвора; золотой луч меняет не ширину, а длительность.</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>#PL042 #summary #bridge #shutterspeed</t>
+        </is>
+      </c>
+      <c r="Y440" t="inlineStr">
+        <is>
+          <t>Диафрагма / итог и мост</t>
+        </is>
+      </c>
+      <c r="Z440" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" ht="17" customHeight="1" s="72">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>PL-HIST-0440</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>затвор / камера</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Выдержку физически создаёт не абстрактный таймер, а движущийся механизм затвора. У большинства плёночных и цифровых камер это шторно-щелевой (focal-plane) затвор: две шторки — открывающая и закрывающая — бегут одна за другой перед плёнкой или сенсором. На очень коротких выдержках вторая шторка стартует раньше, чем первая долетает до конца, и кадр экспонируется через бегущую щель, а не целиком одновременно.</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Focal-plane shutter mechanism / flash sync limit</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>Выдержка перестаёт быть просто «временем»: у неё есть механическое ограничение — скорость синхронизации со вспышкой (обычно около 1/200–1/250 с). Выше этой скорости кадр в любой момент времени открыт только частично — узкой бегущей щелью, поэтому обычная вспышка засветит не весь кадр.</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>PL-042 — диафрагма как окно</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Короткая выдержка</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>Главная линия / выдержка</t>
+        </is>
+      </c>
+      <c r="N441" t="n">
+        <v>5</v>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>PL-043</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>SRC-313</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>Wikipedia — Focal-plane shutter</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Focal-plane_shutter</t>
+        </is>
+      </c>
+      <c r="S441" t="n">
+        <v>5</v>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>Флагман PL-043: не повторять «выдержка — это время, за которое свет попадает на плёнку» дословно (см. PL-041 PL-HIST-0420) — объяснить механизм: две бегущие шторки и почему у выдержки есть техническое ограничение (синхронизация со вспышкой).</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>Схема кадра с двумя шторками затвора и узкой бегущей щелью между ними; рядом — вспышка и подпись «1/250 с — предел синхронизации».</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>#PL043 #shutterspeed #focalplaneshutter #flashsync #mechanism</t>
+        </is>
+      </c>
+      <c r="Y441" t="inlineStr">
+        <is>
+          <t>Выдержка / базовое определение</t>
+        </is>
+      </c>
+      <c r="Z441" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="AA441" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" ht="17" customHeight="1" s="72">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>PL-HIST-0441</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>движение / спорт / улица</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Короткая выдержка, например 1/500 или 1/1000 секунды, помогает заморозить движение и снизить смаз от объекта.</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Fast shutter / freeze motion</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>Выдержка связывает экспозицию с моментом: фотограф может остановить жест, каплю воды или движение человека.</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Базовое определение выдержки</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Длинная выдержка</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>Главная линия / движение</t>
+        </is>
+      </c>
+      <c r="N442" t="n">
+        <v>5</v>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>PL-043</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>SRC-302</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>Nikon USA — Capturing or Freezing Motion in Photos</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/capturing-or-freezing-motion-in-photos</t>
+        </is>
+      </c>
+      <c r="S442" t="n">
+        <v>5</v>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>Показывать не только спорт: шаг человека, взмах руки, велосипед — ближе к реальной жизни новичка.</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>Капля воды или бегущий человек: резкий силуэт при 1/1000.</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>#PL043 #fastshutter #freezemotion #motion</t>
+        </is>
+      </c>
+      <c r="Y442" t="inlineStr">
+        <is>
+          <t>Выдержка / заморозка движения</t>
+        </is>
+      </c>
+      <c r="Z442" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="17" customHeight="1" s="72">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>PL-HIST-0442</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>движение / вода / свет</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Длинная выдержка накапливает свет дольше и может показать движение как размытие: воду, облака, фары, людей.</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Slow shutter / motion blur</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>Фотограф видит, что смаз не всегда ошибка: иногда это способ показать время внутри неподвижного кадра.</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Короткая выдержка</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Секунды и доли секунды</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>Главная линия / движение</t>
+        </is>
+      </c>
+      <c r="N443" t="n">
+        <v>5</v>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>PL-043</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>SRC-301</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Using Camera Shutter Speed Creatively</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-shutter-speed.htm</t>
+        </is>
+      </c>
+      <c r="S443" t="n">
+        <v>5</v>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>Очень сильная философская мысль: фотография может не только остановить время, но и накопить его.</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>Ночной город с длинными следами фар; рядом штатив и секундная шкала.</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>#PL043 #slowshutter #motionblur #longexposure</t>
+        </is>
+      </c>
+      <c r="Y443" t="inlineStr">
+        <is>
+          <t>Выдержка / длинная выдержка</t>
+        </is>
+      </c>
+      <c r="Z443" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="444" ht="17" customHeight="1" s="72">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>PL-HIST-0443</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>шкала камеры</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Выдержка измеряется секундами и долями секунды: 1/1000, 1/250, 1/60, 1/15, 1 секунда и дольше.</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Shutter speed scale</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>Шкала выдержек становится читаемой: чем меньше знаменатель, тем дольше свет действует на материал.</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Длинная выдержка</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Смаз камеры</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>Главная линия / шкала выдержек</t>
+        </is>
+      </c>
+      <c r="N444" t="n">
+        <v>5</v>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>PL-043</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>SRC-300</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding Shutter Speed</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-shutter-speed</t>
+        </is>
+      </c>
+      <c r="S444" t="n">
+        <v>5</v>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>Нужно проговорить частую ошибку: 1/30 длиннее, чем 1/250.</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>Вертикальная шкала выдержек от 1/1000 до 1s; золотые полосы становятся длиннее вниз.</t>
+        </is>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>#PL043 #shutterscale #fractions #seconds</t>
+        </is>
+      </c>
+      <c r="Y444" t="inlineStr">
+        <is>
+          <t>Выдержка / шкала времени</t>
+        </is>
+      </c>
+      <c r="Z444" t="inlineStr">
+        <is>
+          <t>Терминология / язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="445" ht="17" customHeight="1" s="72">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>PL-HIST-0444</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>камера в руках</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Если выдержка слишком длинная для съёмки с рук, камера успевает сдвинуться, и весь кадр становится нерезким.</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Camera shake</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>Новичок отличает смаз от ошибки фокуса: иногда проблема не в объективе, а во времени выдержки.</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Шкала выдержек</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Штатив и стабилизация</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>Главная линия / техническая ошибка</t>
+        </is>
+      </c>
+      <c r="N445" t="n">
+        <v>5</v>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>PL-043</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>SRC-301</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Using Camera Shutter Speed Creatively</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-shutter-speed.htm</t>
+        </is>
+      </c>
+      <c r="S445" t="n">
+        <v>5</v>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>Связать с будущим модулем «Фокус и резкость»: нерезкость бывает от фокуса и от движения.</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>Два кадра одной сцены: резкий на короткой выдержке и дрожащий на длинной.</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>#PL043 #camerashake #blur #handheld</t>
+        </is>
+      </c>
+      <c r="Y445" t="inlineStr">
+        <is>
+          <t>Выдержка / шевелёнка</t>
+        </is>
+      </c>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="446" ht="17" customHeight="1" s="72">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>PL-HIST-0445</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>штатив / ночная съёмка</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Штатив или опора позволяют использовать длинную выдержку без смаза камеры, когда нужно накопить больше света.</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>Tripod for long exposure</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>Выдержка становится инструментом съёмки в слабом свете: можно не только повышать ISO, но и дать свету больше времени.</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Смаз камеры</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>ND и длинная выдержка</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>Главная линия / практическое применение</t>
+        </is>
+      </c>
+      <c r="N446" t="n">
+        <v>4</v>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>PL-043</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>SRC-301</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Using Camera Shutter Speed Creatively</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-shutter-speed.htm</t>
+        </is>
+      </c>
+      <c r="S446" t="n">
+        <v>5</v>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>Показать простую практику: поставить камеру на стол и снять одну и ту же сцену на 1/15 и 1 секунду.</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>Камера на штативе в тёмной комнате; световой поток идёт долго и спокойно.</t>
+        </is>
+      </c>
+      <c r="V446" t="inlineStr">
+        <is>
+          <t>#PL043 #tripod #longexposure #lowlight</t>
+        </is>
+      </c>
+      <c r="Y446" t="inlineStr">
+        <is>
+          <t>Выдержка / штатив</t>
+        </is>
+      </c>
+      <c r="Z446" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="447" ht="17" customHeight="1" s="72">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>PL-HIST-0446</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>нейтральный фильтр / дневная съёмка</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Длинную выдержку можно использовать даже днём, если уменьшить количество света нейтральным ND-фильтром.</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>ND filter and shutter speed</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>Фотограф учится управлять временем независимо от яркости сцены: фильтр убирает свет, выдержка показывает движение.</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Штатив и длинная выдержка</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Приоритет выдержки</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>Главная линия / расширение контроля</t>
+        </is>
+      </c>
+      <c r="N447" t="n">
+        <v>4</v>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>PL-043</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>SRC-310</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>Nikon USA — When to Use Graduated Neutral Density Filters</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/when-to-use-graduated-neutral-density-filters</t>
+        </is>
+      </c>
+      <c r="S447" t="n">
+        <v>5</v>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>Мост к теме стопов: ND-фильтры часто описываются в стопах.</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>Водопад днём: ND-фильтр перед объективом, вода превращается в мягкую ленту.</t>
+        </is>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>#PL043 #NDfilter #longexposure #stops</t>
+        </is>
+      </c>
+      <c r="Y447" t="inlineStr">
+        <is>
+          <t>Выдержка / ND и время</t>
+        </is>
+      </c>
+      <c r="Z447" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="448" ht="17" customHeight="1" s="72">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>PL-HIST-0447</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>режим Tv / S</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>В режиме приоритета выдержки фотограф выбирает время, а камера подбирает диафрагму и/или ISO для нормальной экспозиции.</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Shutter priority / Tv / S</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>Новичок получает режим для тренировки движения: заморозить, смазать или сделать панорамирование.</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>ND и длинная выдержка</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Панорамирование</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>Главная линия / режим камеры</t>
+        </is>
+      </c>
+      <c r="N448" t="n">
+        <v>4</v>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>PL-043</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>SRC-307</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>Canon Canada — Canon Outside of Auto: Photography 101</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>https://www.canon.ca/CanonOutsideOfAuto/photography101</t>
+        </is>
+      </c>
+      <c r="S448" t="n">
+        <v>5</v>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>Для Canon — Tv, для Nikon/Sony часто S. Не усложнять, но дать связку.</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>Диск режимов на Tv/S; рядом бегущий человек и выбранная выдержка 1/250.</t>
+        </is>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>#PL043 #shutterpriority #Tv #Smode</t>
+        </is>
+      </c>
+      <c r="Y448" t="inlineStr">
+        <is>
+          <t>Выдержка / приоритет выдержки</t>
+        </is>
+      </c>
+      <c r="Z448" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="449" ht="17" customHeight="1" s="72">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>PL-HIST-0448</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>движение / съёмка с проводкой</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Панорамирование использует сравнительно длинную выдержку и движение камеры вместе с объектом: фон смазывается, объект остаётся читаемым.</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Panning</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>Выдержка перестаёт быть только защитой от смаза: она становится способом передать скорость.</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Приоритет выдержки</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Эквивалентная экспозиция</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+      <c r="N449" t="n">
+        <v>4</v>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>PL-043</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>SRC-302</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>Nikon USA — Capturing or Freezing Motion in Photos</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/capturing-or-freezing-motion-in-photos</t>
+        </is>
+      </c>
+      <c r="S449" t="n">
+        <v>5</v>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>Хорошая практика для урока: снять велосипедиста или машину на 1/30–1/60 с проводкой.</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>Фотограф ведёт камеру за велосипедистом; фон превращается в горизонтальные полосы.</t>
+        </is>
+      </c>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>#PL043 #panning #motion #creativeblur</t>
+        </is>
+      </c>
+      <c r="Y449" t="inlineStr">
+        <is>
+          <t>Выдержка / проводка</t>
+        </is>
+      </c>
+      <c r="Z449" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="450" ht="17" customHeight="1" s="72">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>PL-HIST-0449</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>ручной режим / экспозиция</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Изменение выдержки на один стоп можно компенсировать диафрагмой: если укоротить время вдвое, нужно открыть отверстие на стоп для той же яркости.</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Shutter/aperture compensation</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>Появляется логика эквивалентных экспозиций: яркость может остаться той же, но движение и глубина резкости изменятся.</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Панорамирование</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>ISO как третий параметр</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>Главная линия / эквивалентность</t>
+        </is>
+      </c>
+      <c r="N450" t="n">
+        <v>5</v>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>PL-043</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>SRC-308</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>Canon Canada — Canon Outside of Auto: Tips</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>https://www.canon.ca/CanonOutsideOfAuto/tips?lang=en</t>
+        </is>
+      </c>
+      <c r="S450" t="n">
+        <v>5</v>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>Мост к PL-045 и PL-046: именно здесь ученик начинает понимать «переставлять настройки».</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>Весы экспозиции: слева 1/250 + f/4, справа 1/125 + f/5.6, баланс одинаковый.</t>
+        </is>
+      </c>
+      <c r="V450" t="inlineStr">
+        <is>
+          <t>#PL043 #equivalentexposure #stops #aperture</t>
+        </is>
+      </c>
+      <c r="Y450" t="inlineStr">
+        <is>
+          <t>Выдержка / компенсация стопами</t>
+        </is>
+      </c>
+      <c r="Z450" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="451" ht="17" customHeight="1" s="72">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>PL-HIST-0450</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>PHOTO LAB / модуль экспозиции</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>PHOTO LAB by VF</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Итог PL-043: выдержка — это время действия света. Она управляет яркостью и движением: может заморозить момент или показать его след.</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Shutter speed as time decision</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>Курс готов перейти к ISO: если диафрагма — ширина, выдержка — время, то ISO задаёт чувствительность материала или усиление сигнала.</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Компенсация выдержкой</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>PL-044 — ISO как чувствительность</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N451" t="n">
+        <v>5</v>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>PL-043</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>SRC-300</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding Shutter Speed</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-shutter-speed</t>
+        </is>
+      </c>
+      <c r="S451" t="n">
+        <v>5</v>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>Формула урока: выдержка отвечает за время, а время отвечает за движение.</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>Затвор закрывается, рядом появляется катушка ISO 400 и цифровая шкала ISO.</t>
+        </is>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>#PL043 #summary #bridge #ISO</t>
+        </is>
+      </c>
+      <c r="Y451" t="inlineStr">
+        <is>
+          <t>Выдержка / итог и мост</t>
+        </is>
+      </c>
+      <c r="Z451" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" ht="17" customHeight="1" s="72">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>PL-HIST-0451</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>плёнка / сенсор</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>У цифровой камеры ISO не меняет физическую чувствительность самого сенсора к свету — светочувствительность фотодиодов остаётся постоянной. Повышение ISO — это усиление уже полученного сигнала (аналоговое и/или цифровое обработчиком камеры), похожее на прибавление громкости: сигнал становится «громче», но вместе с ним усиливается и шум.</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>ISO as post-exposure signal gain (digital) vs. physical emulsion sensitivity (film)</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>ISO перестаёт быть «третьим источником света»: на цифровой камере он не собирает больше света на сенсоре — количество света по-прежнему определяют только диафрагма и выдержка, а ISO лишь усиливает уже отснятый сигнал той же ценой более заметного шума. На плёнке ситуация другая: там чувствительность — физическое свойство самой эмульсии (размер кристаллов галогенида серебра), а не последующее усиление.</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>PL-043 — выдержка как время</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>ISO плёнки и цифровое ISO</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>Главная линия / ISO</t>
+        </is>
+      </c>
+      <c r="N452" t="n">
+        <v>5</v>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>SRC-314</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>PetaPixel — ISO Has Nothing to Do with Exposure</t>
+        </is>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>https://petapixel.com/2020/03/05/iso-has-nothing-to-do-with-exposure-an-explanation-for-beginners/</t>
+        </is>
+      </c>
+      <c r="S452" t="n">
+        <v>4</v>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>Флагман PL-044: не повторять «ISO — чувствительность, выше ISO — меньше света нужно» дословно (см. PL-041 PL-HIST-0421) — уточнить механизм: на цифре ISO усиливает сигнал уже после экспозиции, а не собирает больше света; на плёнке чувствительность физическая. Это тонкость, о которой спорят и сами инженеры — подать как интересный факт, а не как строгий консенсус.</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>Слева — фотодиод сенсора с постоянным размером; справа — усилитель сигнала с ручкой громкости и подписью «ISO = громкость, не яркость источника».</t>
+        </is>
+      </c>
+      <c r="V452" t="inlineStr">
+        <is>
+          <t>#PL044 #ISO #signalgain #digitalsensor #noise</t>
+        </is>
+      </c>
+      <c r="Y452" t="inlineStr">
+        <is>
+          <t>ISO / базовое определение</t>
+        </is>
+      </c>
+      <c r="Z452" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="AA452" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" ht="17" customHeight="1" s="72">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>PL-HIST-0452</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>плёночная катушка</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>На плёнке ISO обычно выбирается до съёмки: зарядил ISO 400 — весь ролик снимаешь как ISO 400, если не принимаешь специальное решение о push/pull.</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Film ISO / box speed</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>Новичок понимает отличие плёнки от цифры: чувствительность нельзя свободно менять после каждого кадра без последствий.</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>ISO как чувствительность</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Цифровое ISO</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>Главная линия / плёнка</t>
+        </is>
+      </c>
+      <c r="N453" t="n">
+        <v>5</v>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>SRC-305</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>Canon U.S.A. — Photography Terms for Every New Photographer</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>https://www.usa.canon.com/learning/training-articles/training-articles-list/10-photography-terms-every-new-photographer-needs-to-know</t>
+        </is>
+      </c>
+      <c r="S453" t="n">
+        <v>5</v>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>Связать с PL-018: там ISO был материалом; здесь — параметр экспозиции в реальной съёмке.</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>Кассета плёнки с крупной надписью ISO 400 и счётчик кадров 1–36.</t>
+        </is>
+      </c>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>#PL044 #filmISO #boxspeed #filmphotography</t>
+        </is>
+      </c>
+      <c r="Y453" t="inlineStr">
+        <is>
+          <t>ISO / плёночная чувствительность</t>
+        </is>
+      </c>
+      <c r="Z453" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" ht="17" customHeight="1" s="72">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>PL-HIST-0453</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>цифровая камера</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>В цифровой камере ISO связано с чувствительностью/усилением сигнала: его можно менять от кадра к кадру, но рост ISO обычно повышает шум.</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Digital ISO / signal gain</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>Появляется честное различие: плёночное зерно и цифровой шум похожи по ощущению, но имеют разную природу.</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Плёночное ISO</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Шум и зерно</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>Главная линия / цифровой мост</t>
+        </is>
+      </c>
+      <c r="N454" t="n">
+        <v>5</v>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>SRC-304</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>Nikon — What is ISO in photography?</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>https://www.nikon.nl/nl_NL/learn-and-explore/magazine/tips-and-tricks/what-is-iso</t>
+        </is>
+      </c>
+      <c r="S454" t="n">
+        <v>5</v>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>Не углубляться в электронику, но отметить: ISO в цифре — не то же самое, что чувствительность кристаллов плёнки.</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>Экран камеры с ISO 100 → 3200; рядом увеличенный фрагмент с цифровым шумом.</t>
+        </is>
+      </c>
+      <c r="V454" t="inlineStr">
+        <is>
+          <t>#PL044 #digitalISO #noise #sensor</t>
+        </is>
+      </c>
+      <c r="Y454" t="inlineStr">
+        <is>
+          <t>ISO / цифровое ISO</t>
+        </is>
+      </c>
+      <c r="Z454" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="17" customHeight="1" s="72">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>PL-HIST-0454</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>качество изображения</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Низкое ISO обычно даёт более чистое изображение, но требует больше света: шире диафрагму, длиннее выдержку или более яркую сцену.</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Low ISO / clean image</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>ISO связывается с качеством: меньше усиления или более медленная плёнка часто дают более аккуратную фактуру.</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Цифровое ISO</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Высокое ISO</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>Главная линия / качество</t>
+        </is>
+      </c>
+      <c r="N455" t="n">
+        <v>4</v>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>SRC-304</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>Nikon — What is ISO in photography?</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>https://www.nikon.nl/nl_NL/learn-and-explore/magazine/tips-and-tricks/what-is-iso</t>
+        </is>
+      </c>
+      <c r="S455" t="n">
+        <v>5</v>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>Формула для новичка: ISO 100 — красиво и чисто, но просит света.</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>Солнечная сцена, ISO 100, мелкая фактура без заметного зерна/шума.</t>
+        </is>
+      </c>
+      <c r="V455" t="inlineStr">
+        <is>
+          <t>#PL044 #lowISO #imagequality #cleanimage</t>
+        </is>
+      </c>
+      <c r="Y455" t="inlineStr">
+        <is>
+          <t>ISO / низкая чувствительность</t>
+        </is>
+      </c>
+      <c r="Z455" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="17" customHeight="1" s="72">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>PL-HIST-0455</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>слабый свет / движение</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Высокое ISO помогает снимать при меньшем количестве света или использовать более короткую выдержку, но платой становятся зерно или шум.</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>High ISO / less light needed</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>ISO становится инструментом спасения кадра: лучше шумный резкий кадр, чем чистый, но смазанный.</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Низкое ISO</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>ISO и выдержка</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>Главная линия / компромисс</t>
+        </is>
+      </c>
+      <c r="N456" t="n">
+        <v>5</v>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>SRC-303</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding ISO Sensitivity</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-iso-sensitivity</t>
+        </is>
+      </c>
+      <c r="S456" t="n">
+        <v>5</v>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t>Полезный практический вывод: ISO поднимают не от лени, а когда нужно удержать выдержку или диафрагму.</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>Ночная улица: ISO 1600 позволяет удержать 1/125, но в тенях видна фактура.</t>
+        </is>
+      </c>
+      <c r="V456" t="inlineStr">
+        <is>
+          <t>#PL044 #highISO #grain #noise #lowlight</t>
+        </is>
+      </c>
+      <c r="Y456" t="inlineStr">
+        <is>
+          <t>ISO / высокая чувствительность</t>
+        </is>
+      </c>
+      <c r="Z456" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="457" ht="17" customHeight="1" s="72">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>PL-HIST-0456</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>движение / съёмка с рук</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Повышение ISO позволяет укоротить выдержку: материалу или сенсору нужно меньше света, поэтому время экспозиции можно сделать короче.</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>ISO and shutter speed</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>Ученик видит практическую связь: ISO помогает бороться со смазом, когда нельзя открыть диафрагму сильнее.</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Высокое ISO</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>ISO и диафрагма</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>Главная линия / связь параметров</t>
+        </is>
+      </c>
+      <c r="N457" t="n">
+        <v>5</v>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>SRC-303</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding ISO Sensitivity</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-iso-sensitivity</t>
+        </is>
+      </c>
+      <c r="S457" t="n">
+        <v>5</v>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>Пример: было 1/30 при ISO 100, стало 1/125 при ISO 400 при той же диафрагме.</t>
+        </is>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>Шкала ISO 100 → 400, выдержка рядом меняется с 1/30 на 1/125.</t>
+        </is>
+      </c>
+      <c r="V457" t="inlineStr">
+        <is>
+          <t>#PL044 #ISO #shutterspeed #handheld</t>
+        </is>
+      </c>
+      <c r="Y457" t="inlineStr">
+        <is>
+          <t>ISO / связь с выдержкой</t>
+        </is>
+      </c>
+      <c r="Z457" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" ht="17" customHeight="1" s="72">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>PL-HIST-0457</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>глубина резкости / диафрагма</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Повышение ISO может позволить закрыть диафрагму и получить больше глубины резкости при той же выдержке.</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>ISO and aperture</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>ISO помогает не только в темноте, но и в выборе резкости: можно сохранить скорость затвора и закрыть отверстие.</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>ISO и выдержка</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>ISO в треугольнике</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>Главная линия / связь параметров</t>
+        </is>
+      </c>
+      <c r="N458" t="n">
+        <v>4</v>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>SRC-306</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>Nikon — Mastering the Exposure Triangle</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>https://www.nikon.nl/nl_NL/learn-and-explore/magazine/tips-and-tricks/understanding-the-exposure-triangle</t>
+        </is>
+      </c>
+      <c r="S458" t="n">
+        <v>5</v>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>Хорошо показать в пейзаже или уличной сцене: нужна резкость в глубину, но света мало.</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>Уличная сцена: ISO 800 позволяет f/8 вместо f/4, глубина резкости увеличивается.</t>
+        </is>
+      </c>
+      <c r="V458" t="inlineStr">
+        <is>
+          <t>#PL044 #ISO #aperture #depthoffield</t>
+        </is>
+      </c>
+      <c r="Y458" t="inlineStr">
+        <is>
+          <t>ISO / связь с диафрагмой</t>
+        </is>
+      </c>
+      <c r="Z458" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" ht="17" customHeight="1" s="72">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>PL-HIST-0458</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>автоматика камеры</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Auto ISO даёт камере право менять чувствительность, чтобы удержать нужную выдержку или диафрагму в меняющемся свете.</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Auto ISO</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>Современная автоматика становится понятной: она не отменяет экспозицию, а автоматически двигает один из её параметров.</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>ISO и диафрагма</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Ручной ISO</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>Главная линия / автоматизация</t>
+        </is>
+      </c>
+      <c r="N459" t="n">
+        <v>4</v>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>SRC-304</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>Nikon — What is ISO in photography?</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>https://www.nikon.nl/nl_NL/learn-and-explore/magazine/tips-and-tricks/what-is-iso</t>
+        </is>
+      </c>
+      <c r="S459" t="n">
+        <v>5</v>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>Связать с PL-023: автоматика полезна, если понимаешь, что именно она меняет.</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>Экран камеры: Auto ISO, минимальная выдержка 1/125, верхний предел ISO 3200.</t>
+        </is>
+      </c>
+      <c r="V459" t="inlineStr">
+        <is>
+          <t>#PL044 #autoISO #cameraautomation #exposure</t>
+        </is>
+      </c>
+      <c r="Y459" t="inlineStr">
+        <is>
+          <t>ISO / Auto ISO</t>
+        </is>
+      </c>
+      <c r="Z459" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="460" ht="17" customHeight="1" s="72">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>PL-HIST-0459</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>ручной режим / обучение</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Ручной выбор ISO нужен, когда фотограф хочет заранее контролировать фактуру, зерно/шум и диапазон доступных выдержек.</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Manual ISO choice</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>ISO перестаёт быть аварийной настройкой и становится частью авторского контроля над материалом.</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Auto ISO</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>Главная линия / авторский выбор</t>
+        </is>
+      </c>
+      <c r="N460" t="n">
+        <v>4</v>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>SRC-303</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding ISO Sensitivity</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-iso-sensitivity</t>
+        </is>
+      </c>
+      <c r="S460" t="n">
+        <v>5</v>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>Хороший мост к плёночному мышлению: выбор ISO — это выбор характера съёмки.</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>Три карточки выбора: ISO 100 — свет/чистота, ISO 400 — универсально, ISO 1600 — темнота/фактура.</t>
+        </is>
+      </c>
+      <c r="V460" t="inlineStr">
+        <is>
+          <t>#PL044 #manualISO #grain #authorchoice</t>
+        </is>
+      </c>
+      <c r="Y460" t="inlineStr">
+        <is>
+          <t>ISO / ручной выбор</t>
+        </is>
+      </c>
+      <c r="Z460" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" ht="17" customHeight="1" s="72">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>PL-HIST-0460</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>экспозиционный треугольник</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>ISO — третий угол треугольника: он не заменяет диафрагму и выдержку, а меняет условия, в которых они подбираются.</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>ISO as third exposure variable</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>Ученик готов собрать три параметра в единую модель: ширина света, время света и чувствительность.</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Ручной выбор ISO</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>PL-045 — экспозиционный треугольник</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>Главная линия / модель</t>
+        </is>
+      </c>
+      <c r="N461" t="n">
+        <v>5</v>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>SRC-306</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>Nikon — Mastering the Exposure Triangle</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>https://www.nikon.nl/nl_NL/learn-and-explore/magazine/tips-and-tricks/understanding-the-exposure-triangle</t>
+        </is>
+      </c>
+      <c r="S461" t="n">
+        <v>5</v>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>Финальная сцепка: aperture = сколько за момент, shutter = как долго, ISO = сколько нужно.</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>Треугольник с тремя вершинами; ISO подсвечивается золотом, остальные две вершины уже знакомы.</t>
+        </is>
+      </c>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>#PL044 #ISO #exposuretriangle #balance</t>
+        </is>
+      </c>
+      <c r="Y461" t="inlineStr">
+        <is>
+          <t>ISO / место в треугольнике</t>
+        </is>
+      </c>
+      <c r="Z461" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="462" ht="17" customHeight="1" s="72">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>PL-HIST-0461</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>PHOTO LAB / модуль экспозиции</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>PHOTO LAB by VF</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Итог PL-044: ISO — это чувствительность или усиление. Оно помогает снимать при меньшем свете, но влияет на качество, фактуру и доступные пары настроек.</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>ISO as exposure constraint</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>После диафрагмы, выдержки и ISO курс переходит к их общей системе — экспозиционному треугольнику.</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>ISO в треугольнике</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>PL-045 — экспозиционный треугольник</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N462" t="n">
+        <v>5</v>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>SRC-303</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding ISO Sensitivity</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-iso-sensitivity</t>
+        </is>
+      </c>
+      <c r="S462" t="n">
+        <v>5</v>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>Главная мысль: ISO — не волшебная яркость, а компромисс между светом, временем, резкостью и фактурой.</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>Катушка плёнки и цифровой сенсор стоят рядом; над ними одна шкала ISO.</t>
+        </is>
+      </c>
+      <c r="V462" t="inlineStr">
+        <is>
+          <t>#PL044 #summary #bridge #exposuretriangle</t>
+        </is>
+      </c>
+      <c r="Y462" t="inlineStr">
+        <is>
+          <t>ISO / итог и мост</t>
+        </is>
+      </c>
+      <c r="Z462" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="17" customHeight="1" s="72">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>PL-HIST-0462</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>камера / ручной режим</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>Модель «экспозиционного треугольника» ставит диафрагму, выдержку и ISO как три равноправные вершины — но физически на количество света, попадающего на сенсор, влияют только диафрагма и выдержка. ISO ничего не «собирает»: он лишь усиливает уже отснятый сигнал, поэтому часть инженеров и фотографов называет классический треугольник педагогическим упрощением, а не точной физической моделью.</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Exposure triangle critique / ISO invariance</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>Треугольник остаётся полезным способом думать о съёмке, но перестаёт быть буквальной физикой: фотограф учится различать «сколько света я собрал» (диафрагма + выдержка) и «как я усилил то, что собрал» (ISO) — это два разных вопроса, а не три равных угла одной фигуры.</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>PL-044 — ISO как чувствительность</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Три параметра и их эффекты</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>Главная линия / учебная модель</t>
+        </is>
+      </c>
+      <c r="N463" t="n">
+        <v>5</v>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>SRC-315</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>FastRawViewer — The Unbearable Lightness of Mystic "Exposure" Triangle</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>https://www.fastrawviewer.com/blog/mystic-exposure-triangle</t>
+        </is>
+      </c>
+      <c r="S463" t="n">
+        <v>4</v>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>Флагман PL-045: не повторять вводную формулировку треугольника из PL-041 (PL-HIST-0422) дословно вместе с тем же самым дисклеймером «это модель, а не физика» — здесь эту мысль нужно обосновать: показать, почему именно ISO выбивается из треугольника (не собирает свет, а усиливает сигнал), а не просто заявить это как данность.</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>Классический треугольник (диафрагма/выдержка/ISO), но одна вершина (ISO) нарисована пунктиром с подписью «не совсем то же самое, что две другие».</t>
+        </is>
+      </c>
+      <c r="V463" t="inlineStr">
+        <is>
+          <t>#PL045 #exposuretriangle #ISOinvariance #criticism #model</t>
+        </is>
+      </c>
+      <c r="Y463" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / базовая модель</t>
+        </is>
+      </c>
+      <c r="Z463" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="AA463" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="17" customHeight="1" s="72">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>PL-HIST-0463</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>три параметра экспозиции</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Каждая вершина треугольника влияет на яркость и на внешний вид кадра: диафрагма — на ГРИП, выдержка — на движение, ISO — на зерно или шум.</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Exposure variables and visual effects</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>Экспозиция становится не только измерением света, но и выбором визуального характера фотографии.</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Базовая модель треугольника</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Баланс параметров</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>Главная линия / визуальные эффекты</t>
+        </is>
+      </c>
+      <c r="N464" t="n">
+        <v>5</v>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>SRC-307</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>Canon Canada — Canon Outside of Auto: Photography 101</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>https://www.canon.ca/CanonOutsideOfAuto/photography101</t>
+        </is>
+      </c>
+      <c r="S464" t="n">
+        <v>5</v>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>Это центральная образовательная польза: настройки отвечают не только за «светлее/темнее».</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>Три мини-кадра: размытый фон, смазанное движение, зернистая фактура.</t>
+        </is>
+      </c>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>#PL045 #visualeffects #depthoffield #motion #grain</t>
+        </is>
+      </c>
+      <c r="Y464" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / визуальные эффекты</t>
+        </is>
+      </c>
+      <c r="Z464" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="17" customHeight="1" s="72">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>PL-HIST-0464</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>ручной режим</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>Если изменить один параметр, экспозиция изменится; чтобы сохранить яркость, нужно компенсировать это другим параметром.</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>Exposure balance / compensation</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>Фотограф начинает мыслить балансом: настройки не живут отдельно, они разговаривают друг с другом.</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Три эффекта параметров</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>Эквивалентные экспозиции</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>Главная линия / баланс</t>
+        </is>
+      </c>
+      <c r="N465" t="n">
+        <v>5</v>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>SRC-308</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>Canon Canada — Canon Outside of Auto: Tips</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>https://www.canon.ca/CanonOutsideOfAuto/tips?lang=en</t>
+        </is>
+      </c>
+      <c r="S465" t="n">
+        <v>5</v>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t>Дать через простую фразу: открыл окно — сократи время; поднял ISO — можно закрыть диафрагму.</t>
+        </is>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>Весы с тремя чашами: aperture, shutter, ISO; одна двигается, две компенсируют.</t>
+        </is>
+      </c>
+      <c r="V465" t="inlineStr">
+        <is>
+          <t>#PL045 #balance #compensation #settings</t>
+        </is>
+      </c>
+      <c r="Y465" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / баланс</t>
+        </is>
+      </c>
+      <c r="Z465" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" ht="17" customHeight="1" s="72">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>PL-HIST-0465</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>эквивалентные настройки</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Одинаковую яркость можно получить разными парами настроек: например, один вариант лучше для портрета, другой — для движения или пейзажа.</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>Equivalent exposure choices</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>Экспозиция перестаёт быть единственной правильной комбинацией: появляется авторский выбор под задачу кадра.</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Баланс параметров</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Портретный сценарий</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>Главная линия / эквивалентность</t>
+        </is>
+      </c>
+      <c r="N466" t="n">
+        <v>5</v>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>SRC-299</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Camera Exposure: Aperture, ISO &amp; Shutter Speed</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-exposure.htm</t>
+        </is>
+      </c>
+      <c r="S466" t="n">
+        <v>5</v>
+      </c>
+      <c r="T466" t="inlineStr">
+        <is>
+          <t>Пример в карточке: f/2.8 1/500 ISO 400 и f/5.6 1/125 ISO 400 — похожая яркость, разная ГРИП/движение.</t>
+        </is>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>Три карточки настроек с одинаковой яркостью кадра, но разной глубиной резкости и движением.</t>
+        </is>
+      </c>
+      <c r="V466" t="inlineStr">
+        <is>
+          <t>#PL045 #equivalentexposure #stops #choice</t>
+        </is>
+      </c>
+      <c r="Y466" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / эквивалентные варианты</t>
+        </is>
+      </c>
+      <c r="Z466" t="inlineStr">
+        <is>
+          <t>Терминология / язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" ht="17" customHeight="1" s="72">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>PL-HIST-0466</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>портрет</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>В портрете фотограф часто начинает с диафрагмы: выбирает степень размытия фона, а затем подбирает выдержку и ISO.</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>Portrait exposure priority</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>Треугольник превращается в практический маршрут: сначала решить, что важно визуально, потом балансировать свет.</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Эквивалентные варианты</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>Сценарий движения</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+      <c r="N467" t="n">
+        <v>4</v>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>SRC-306</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>Nikon — Mastering the Exposure Triangle</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>https://www.nikon.nl/nl_NL/learn-and-explore/magazine/tips-and-tricks/understanding-the-exposure-triangle</t>
+        </is>
+      </c>
+      <c r="S467" t="n">
+        <v>5</v>
+      </c>
+      <c r="T467" t="inlineStr">
+        <is>
+          <t>Показать: для портрета важнее фон и лицо, поэтому старт с aperture.</t>
+        </is>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>Портрет у окна: вершина aperture подсвечена, фон мягко размыт.</t>
+        </is>
+      </c>
+      <c r="V467" t="inlineStr">
+        <is>
+          <t>#PL045 #portrait #aperturefirst #depthoffield</t>
+        </is>
+      </c>
+      <c r="Y467" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / портретный сценарий</t>
+        </is>
+      </c>
+      <c r="Z467" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" ht="17" customHeight="1" s="72">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>PL-HIST-0467</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>движение / репортаж</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>При движении фотограф часто начинает с выдержки: выбирает, заморозить действие или оставить смаз, а затем балансирует диафрагму и ISO.</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Motion exposure priority</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>Треугольник помогает выбрать главный параметр под сюжет: движение диктует время.</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Портретный сценарий</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Сценарий слабого света</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+      <c r="N468" t="n">
+        <v>4</v>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>SRC-300</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding Shutter Speed</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-shutter-speed</t>
+        </is>
+      </c>
+      <c r="S468" t="n">
+        <v>5</v>
+      </c>
+      <c r="T468" t="inlineStr">
+        <is>
+          <t>Пример: ребёнок бежит — сначала 1/500, потом решаем f и ISO.</t>
+        </is>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>Уличный кадр с бегущим ребёнком; вершина shutter подсвечена золотом.</t>
+        </is>
+      </c>
+      <c r="V468" t="inlineStr">
+        <is>
+          <t>#PL045 #motion #shutterfirst #reportage</t>
+        </is>
+      </c>
+      <c r="Y468" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / сценарий движения</t>
+        </is>
+      </c>
+      <c r="Z468" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="469" ht="17" customHeight="1" s="72">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>PL-HIST-0468</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>слабый свет</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>В слабом свете ISO часто становится параметром спасения: когда нельзя открыть диафрагму или удлинить выдержку, чувствительность повышают.</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>Low-light exposure priority</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>Ученик понимает компромисс: лучше принять шум/зерно, чем потерять момент из-за смаза или недодержки.</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Сценарий движения</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Режимы A/Av и S/Tv</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>Главная линия / компромисс</t>
+        </is>
+      </c>
+      <c r="N469" t="n">
+        <v>4</v>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>SRC-303</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding ISO Sensitivity</t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-iso-sensitivity</t>
+        </is>
+      </c>
+      <c r="S469" t="n">
+        <v>5</v>
+      </c>
+      <c r="T469" t="inlineStr">
+        <is>
+          <t>Сделать очень жизненно: вечер, человек двигается, f уже открыта, выдержку длиннее нельзя — поднимаем ISO.</t>
+        </is>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>Вечернее кафе, камера показывает f/2, 1/125, ISO 1600; вершина ISO подсвечена.</t>
+        </is>
+      </c>
+      <c r="V469" t="inlineStr">
+        <is>
+          <t>#PL045 #lowlight #ISO #compromise</t>
+        </is>
+      </c>
+      <c r="Y469" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / слабый свет</t>
+        </is>
+      </c>
+      <c r="Z469" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="17" customHeight="1" s="72">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>PL-HIST-0469</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>режимы камеры</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Полуавтоматические режимы A/Av и S/Tv не отменяют треугольник: фотограф выбирает главный параметр, а камера компенсирует остальные.</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>Semi-auto modes and triangle</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>Автоматика становится понятной и управляемой: камера помогает, но не выбирает смысл кадра за автора.</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Слабый свет</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>Ручной режим</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>Главная линия / автоматизация</t>
+        </is>
+      </c>
+      <c r="N470" t="n">
+        <v>4</v>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>SRC-307</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>Canon Canada — Canon Outside of Auto: Photography 101</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>https://www.canon.ca/CanonOutsideOfAuto/photography101</t>
+        </is>
+      </c>
+      <c r="S470" t="n">
+        <v>5</v>
+      </c>
+      <c r="T470" t="inlineStr">
+        <is>
+          <t>Связать с PL-023: автоматика полезна именно тогда, когда ученик понимает её логику.</t>
+        </is>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>Две половины экрана: Av — выбран f/2.8, Tv — выбран 1/500; треугольник остаётся рядом.</t>
+        </is>
+      </c>
+      <c r="V470" t="inlineStr">
+        <is>
+          <t>#PL045 #Av #Tv #automation #control</t>
+        </is>
+      </c>
+      <c r="Y470" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / полуавтоматические режимы</t>
+        </is>
+      </c>
+      <c r="Z470" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="471" ht="17" customHeight="1" s="72">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>PL-HIST-0470</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>ручной режим / творческая съёмка</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>В ручном режиме фотограф сам фиксирует все три параметра и принимает полную ответственность за свет, движение, резкость и фактуру.</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>Manual exposure decision</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>Ручной режим перестаёт быть страшной аббревиатурой M: это просто режим, где треугольник не двигается без решения фотографа.</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Полуавтоматические режимы</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>Авторская экспозиция</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>Главная линия / ручной контроль</t>
+        </is>
+      </c>
+      <c r="N471" t="n">
+        <v>4</v>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>SRC-306</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>Nikon — Mastering the Exposure Triangle</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>https://www.nikon.nl/nl_NL/learn-and-explore/magazine/tips-and-tricks/understanding-the-exposure-triangle</t>
+        </is>
+      </c>
+      <c r="S471" t="n">
+        <v>5</v>
+      </c>
+      <c r="T471" t="inlineStr">
+        <is>
+          <t>Важно не романтизировать Manual: это не «профессиональный режим», а режим полного контроля, когда он нужен.</t>
+        </is>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>Камера в режиме M; три шкалы выставлены вручную и соединены золотыми линиями.</t>
+        </is>
+      </c>
+      <c r="V471" t="inlineStr">
+        <is>
+          <t>#PL045 #manualmode #Mmode #control</t>
+        </is>
+      </c>
+      <c r="Y471" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / ручной режим</t>
+        </is>
+      </c>
+      <c r="Z471" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" ht="17" customHeight="1" s="72">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>PL-HIST-0471</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>реальная сцена</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Хорошая экспозиция — не всегда средняя яркость: иногда кадр должен быть тёмным, светлым, контрастным или мягким по авторскому замыслу.</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Creative exposure intent</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>Треугольник становится языком: фотограф использует настройки, чтобы передать настроение, а не только попасть в «ноль» экспонометра.</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Ручной режим</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>Стопы света</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>Главная линия / авторский выбор</t>
+        </is>
+      </c>
+      <c r="N472" t="n">
+        <v>5</v>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>SRC-309</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Exposure 101: An Intro to Exposure</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/exposure-101-an-intro-to-exposure</t>
+        </is>
+      </c>
+      <c r="S472" t="n">
+        <v>5</v>
+      </c>
+      <c r="T472" t="inlineStr">
+        <is>
+          <t>Очень PHOTO LAB мысль: техника нужна, чтобы точнее выразить, а не чтобы угадать единственный правильный ответ.</t>
+        </is>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>Одна сцена в трёх экспозициях: низкий ключ, нормальная, высокий ключ; все намеренные.</t>
+        </is>
+      </c>
+      <c r="V472" t="inlineStr">
+        <is>
+          <t>#PL045 #creativeexposure #intent #mood</t>
+        </is>
+      </c>
+      <c r="Y472" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / авторский выбор</t>
+        </is>
+      </c>
+      <c r="Z472" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="473" ht="17" customHeight="1" s="72">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>PL-HIST-0472</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>PHOTO LAB / модуль экспозиции</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>PHOTO LAB by VF</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Итог PL-045: экспозиционный треугольник — это способ видеть связь между диафрагмой, выдержкой и ISO. Меняя одно, фотограф меняет всё изображение.</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>Exposure triangle as decision system</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>Курс готов перейти к стопам света — единому языку, который позволяет точно менять любые параметры экспозиции.</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Авторская экспозиция</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>PL-046 — стопы света</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N473" t="n">
+        <v>5</v>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>SRC-306</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>Nikon — Mastering the Exposure Triangle</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>https://www.nikon.nl/nl_NL/learn-and-explore/magazine/tips-and-tricks/understanding-the-exposure-triangle</t>
+        </is>
+      </c>
+      <c r="S473" t="n">
+        <v>5</v>
+      </c>
+      <c r="T473" t="inlineStr">
+        <is>
+          <t>Финальный тезис: треугольник не заучивают, его используют для решений.</t>
+        </is>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>Треугольник превращается в линейку стопов; золотые деления ведут к следующему уроку.</t>
+        </is>
+      </c>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>#PL045 #summary #bridge #stops</t>
+        </is>
+      </c>
+      <c r="Y473" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / итог и мост</t>
+        </is>
+      </c>
+      <c r="Z473" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
+    <row r="474" ht="17" customHeight="1" s="72">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>PL-HIST-0473</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>экспозиционная шкала</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Стоп света — это шаг, который меняет количество света в два раза: плюс один стоп — вдвое больше света, минус один стоп — вдвое меньше.</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Stop of light</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>Фотограф получает общий язык экспозиции: диафрагму, выдержку, ISO и фильтры можно сравнивать одной мерой.</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>PL-045 — экспозиционный треугольник</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>Плюс и минус стоп</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>Главная линия / стопы</t>
+        </is>
+      </c>
+      <c r="N474" t="n">
+        <v>5</v>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>SRC-309</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Exposure 101: An Intro to Exposure</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/exposure-101-an-intro-to-exposure</t>
+        </is>
+      </c>
+      <c r="S474" t="n">
+        <v>5</v>
+      </c>
+      <c r="T474" t="inlineStr">
+        <is>
+          <t>Флагман PL-046: стоп — главный язык практической фотографии, а не сложная теория.</t>
+        </is>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>Золотая шкала: -2, -1, 0, +1, +2; каждый шаг вдвое меняет ширину светового потока.</t>
+        </is>
+      </c>
+      <c r="V474" t="inlineStr">
+        <is>
+          <t>#PL046 #stops #doubling #exposure</t>
+        </is>
+      </c>
+      <c r="Y474" t="inlineStr">
+        <is>
+          <t>Стопы света / базовое определение</t>
+        </is>
+      </c>
+      <c r="Z474" t="inlineStr">
+        <is>
+          <t>Ключевой исторический узел</t>
+        </is>
+      </c>
+      <c r="AA474" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="475" ht="17" customHeight="1" s="72">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>PL-HIST-0474</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>экспозиционная коррекция</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>+1 стоп означает вдвое больше света; −1 стоп означает вдвое меньше света. Это может быть изменение диафрагмы, выдержки, ISO или фильтра.</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>+1 / -1 stop</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>Ученик начинает мыслить не конкретными кнопками, а количеством света, которое он добавляет или убирает.</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Стоп света</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>Стопы диафрагмы</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>Главная линия / язык экспозиции</t>
+        </is>
+      </c>
+      <c r="N475" t="n">
+        <v>5</v>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>SRC-310</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>Nikon USA — When to Use Graduated Neutral Density Filters</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/when-to-use-graduated-neutral-density-filters</t>
+        </is>
+      </c>
+      <c r="S475" t="n">
+        <v>5</v>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
+          <t>Дать максимально просто: один стоп — это x2 или /2.</t>
+        </is>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>Два кадра рядом: +1 stop светлее, -1 stop темнее; между ними знак ×2 / ÷2.</t>
+        </is>
+      </c>
+      <c r="V475" t="inlineStr">
+        <is>
+          <t>#PL046 #plusstop #minusstop #light</t>
+        </is>
+      </c>
+      <c r="Y475" t="inlineStr">
+        <is>
+          <t>Стопы света / плюс-минус стоп</t>
+        </is>
+      </c>
+      <c r="Z475" t="inlineStr">
+        <is>
+          <t>Терминология / язык</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="17" customHeight="1" s="72">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>PL-HIST-0475</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>диафрагма / шкала f</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>В диафрагме полный стоп — это переход между стандартными f-значениями, например f/2.8 → f/4 → f/5.6 → f/8.</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Aperture full-stop scale</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>Непонятная шкала f-чисел превращается в практическую лестницу света: каждый шаг закрытия уменьшает свет вдвое.</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>+1/-1 стоп</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>Стопы выдержки</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>Главная линия / диафрагма</t>
+        </is>
+      </c>
+      <c r="N476" t="n">
+        <v>5</v>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>SRC-299</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Camera Exposure: Aperture, ISO &amp; Shutter Speed</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-exposure.htm</t>
+        </is>
+      </c>
+      <c r="S476" t="n">
+        <v>5</v>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>Не объяснять sqrt(2) в основном тексте; оставить в комментарии/доп. материале при желании.</t>
+        </is>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>Круги диафрагмы уменьшаются ступенями; подписи f/2.8, f/4, f/5.6, f/8.</t>
+        </is>
+      </c>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>#PL046 #aperturestops #fstop #scale</t>
+        </is>
+      </c>
+      <c r="Y476" t="inlineStr">
+        <is>
+          <t>Стопы света / диафрагма</t>
+        </is>
+      </c>
+      <c r="Z476" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" ht="17" customHeight="1" s="72">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>PL-HIST-0476</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>выдержка / шкала времени</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>В выдержке один стоп — это удвоение или сокращение времени: 1/250 → 1/125 даёт вдвое больше света, а 1/250 → 1/500 — вдвое меньше.</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Shutter speed full-stop scale</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>Шкала выдержки становится интуитивной: время света можно удваивать или делить пополам.</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Стопы диафрагмы</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>Стопы ISO</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>Главная линия / выдержка</t>
+        </is>
+      </c>
+      <c r="N477" t="n">
+        <v>5</v>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>SRC-309</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Exposure 101: An Intro to Exposure</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/exposure-101-an-intro-to-exposure</t>
+        </is>
+      </c>
+      <c r="S477" t="n">
+        <v>5</v>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>Сделать визуально на линейке времени: чем длиннее полоска, тем больше свет успел воздействовать.</t>
+        </is>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>Таймлайн: 1/500, 1/250, 1/125, 1/60; световые полосы удваиваются.</t>
+        </is>
+      </c>
+      <c r="V477" t="inlineStr">
+        <is>
+          <t>#PL046 #shutterstops #time #doubling</t>
+        </is>
+      </c>
+      <c r="Y477" t="inlineStr">
+        <is>
+          <t>Стопы света / выдержка</t>
+        </is>
+      </c>
+      <c r="Z477" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="17" customHeight="1" s="72">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>PL-HIST-0477</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>ISO / чувствительность</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>В ISO один стоп — это удвоение или деление чувствительности: ISO 100 → 200 → 400 → 800.</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>ISO full-stop scale</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>Ученик видит, что ISO тоже подчиняется языку стопов: рост чувствительности позволяет требовать меньше света.</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Стопы выдержки</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>Третьи стопы</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>Главная линия / ISO</t>
+        </is>
+      </c>
+      <c r="N478" t="n">
+        <v>5</v>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>SRC-303</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding ISO Sensitivity</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-iso-sensitivity</t>
+        </is>
+      </c>
+      <c r="S478" t="n">
+        <v>5</v>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>Связать с PL-044: ISO повышается не бесплатно — вместе с ним растут зерно или шум.</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>Столбцы ISO 100, 200, 400, 800; под ними требуемый свет уменьшается.</t>
+        </is>
+      </c>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>#PL046 #ISOstops #ISO100 #ISO400</t>
+        </is>
+      </c>
+      <c r="Y478" t="inlineStr">
+        <is>
+          <t>Стопы света / ISO</t>
+        </is>
+      </c>
+      <c r="Z478" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" ht="17" customHeight="1" s="72">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>PL-HIST-0478</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>современная камера</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Многие камеры позволяют менять экспозицию не только полными стопами, но и половинами или третями стопа для более точной настройки.</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>1/2 and 1/3 stop increments</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>Стопы становятся практическим интерфейсом камеры: клик колеса — маленькое точное изменение света.</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Стопы ISO</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>Эквивалентные стопы</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>Главная линия / интерфейс камеры</t>
+        </is>
+      </c>
+      <c r="N479" t="n">
+        <v>4</v>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>SRC-299</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Camera Exposure: Aperture, ISO &amp; Shutter Speed</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-exposure.htm</t>
+        </is>
+      </c>
+      <c r="S479" t="n">
+        <v>5</v>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>Новичку достаточно знать: полный стоп — большой шаг, 1/3 стопа — тонкая настройка.</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>Камера показывает шкалу −1…0…+1 с мелкими делениями по 1/3.</t>
+        </is>
+      </c>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>#PL046 #thirdstops #cameraSettings #precision</t>
+        </is>
+      </c>
+      <c r="Y479" t="inlineStr">
+        <is>
+          <t>Стопы света / дробные шаги</t>
+        </is>
+      </c>
+      <c r="Z479" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="17" customHeight="1" s="72">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>PL-HIST-0479</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>ручной режим / практика</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Эквивалентные стопы позволяют менять вид кадра без изменения общей яркости: открыть диафрагму на стоп и укоротить выдержку на стоп.</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Equivalent stops / trade-off</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>Фотограф отделяет яркость от художественного эффекта: свет тот же, но фон, движение и фактура меняются.</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Дробные стопы</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>ND-фильтры в стопах</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>Главная линия / эквивалентность</t>
+        </is>
+      </c>
+      <c r="N480" t="n">
+        <v>5</v>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>SRC-308</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>Canon Canada — Canon Outside of Auto: Tips</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>https://www.canon.ca/CanonOutsideOfAuto/tips?lang=en</t>
+        </is>
+      </c>
+      <c r="S480" t="n">
+        <v>5</v>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>Это ключевой практический узел всего модуля экспозиции.</t>
+        </is>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>Две настройки на карточках: f/4 1/250 и f/2.8 1/500; общий знак «та же яркость».</t>
+        </is>
+      </c>
+      <c r="V480" t="inlineStr">
+        <is>
+          <t>#PL046 #equivalentstops #tradeoff #exposure</t>
+        </is>
+      </c>
+      <c r="Y480" t="inlineStr">
+        <is>
+          <t>Стопы света / эквивалентные изменения</t>
+        </is>
+      </c>
+      <c r="Z480" t="inlineStr">
+        <is>
+          <t>Технология / процесс</t>
+        </is>
+      </c>
+    </row>
+    <row r="481" ht="17" customHeight="1" s="72">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>PL-HIST-0480</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>ND-фильтр</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>ND-фильтр уменьшает количество света и обычно описывается в стопах: например, −3 стопа позволяет сделать выдержку в восемь раз длиннее.</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>ND filter stops</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>Стопы выходят за пределы трёх настроек камеры: фильтр тоже становится частью экспозиционной математики.</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Эквивалентные стопы</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>Экспокоррекция</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>Главная линия / фильтры</t>
+        </is>
+      </c>
+      <c r="N481" t="n">
+        <v>4</v>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>SRC-310</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>Nikon USA — When to Use Graduated Neutral Density Filters</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/when-to-use-graduated-neutral-density-filters</t>
+        </is>
+      </c>
+      <c r="S481" t="n">
+        <v>5</v>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>Пример: без фильтра 1/250, с ND −3 стопа около 1/30 при той же диафрагме/ISO.</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>ND-фильтр закрывает объектив; световой поток уменьшается тремя ступенями.</t>
+        </is>
+      </c>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>#PL046 #NDfilter #stops #longexposure</t>
+        </is>
+      </c>
+      <c r="Y481" t="inlineStr">
+        <is>
+          <t>Стопы света / ND-фильтр</t>
+        </is>
+      </c>
+      <c r="Z481" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="482" ht="17" customHeight="1" s="72">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>PL-HIST-0481</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>экспокоррекция / EV</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>фотограф</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Экспокоррекция в камере тоже читается в стопах или EV: +1 делает кадр светлее, −1 темнее относительно замера.</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Exposure compensation / EV</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>Фотограф учится управлять автоматикой: не спорить с камерой, а давать ей понятную команду на светлее или темнее.</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>ND-фильтры</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>Недодержка и передержка</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>Главная линия / экспокоррекция</t>
+        </is>
+      </c>
+      <c r="N482" t="n">
+        <v>5</v>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>SRC-311</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Exposure Compensation and How Do We Use It?</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/exposure-compensation-and-how-do-we-use-it</t>
+        </is>
+      </c>
+      <c r="S482" t="n">
+        <v>5</v>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>Хороший мост к PL-047/PL-048: теперь можно объяснить недодержку и передержку через стопы.</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>Шкала экспокоррекции −3…0…+3; указатель стоит на +1.</t>
+        </is>
+      </c>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>#PL046 #EV #exposurecompensation #metering</t>
+        </is>
+      </c>
+      <c r="Y482" t="inlineStr">
+        <is>
+          <t>Стопы света / экспокоррекция</t>
+        </is>
+      </c>
+      <c r="Z482" t="inlineStr">
+        <is>
+          <t>Инструмент / устройство</t>
+        </is>
+      </c>
+    </row>
+    <row r="483" ht="17" customHeight="1" s="72">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>PL-HIST-0482</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>практика PHOTO LAB</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>ученик PHOTO LAB</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Практика стопов: снять одну сцену в норме, затем на −1, +1, −2 и +2 стопа, чтобы увидеть, как меняется не только яркость, но и настроение.</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>Stop practice / bracketing</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>Стопы становятся видимыми руками: ученик перестаёт бояться чисел и начинает чувствовать шаг света.</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Экспокоррекция</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>Итог стопов</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>Практика / обучение</t>
+        </is>
+      </c>
+      <c r="N483" t="n">
+        <v>4</v>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>SRC-311</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Exposure Compensation and How Do We Use It?</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/exposure-compensation-and-how-do-we-use-it</t>
+        </is>
+      </c>
+      <c r="S483" t="n">
+        <v>5</v>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>Можно связать с ботом: тест на +1/-1 и практическая миссия.</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>Пять кадров одной сцены: −2, −1, 0, +1, +2; золотая рамка вокруг выбранного настроения.</t>
+        </is>
+      </c>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>#PL046 #practice #bracketing #exposure</t>
+        </is>
+      </c>
+      <c r="Y483" t="inlineStr">
+        <is>
+          <t>Стопы света / практика</t>
+        </is>
+      </c>
+      <c r="Z483" t="inlineStr">
+        <is>
+          <t>Применение / жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="484" ht="17" customHeight="1" s="72">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>PL-HIST-0483</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>сегодня</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>примерно</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>глобально</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>PHOTO LAB / модуль экспозиции</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>PHOTO LAB by VF</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Итог PL-046: стопы света — это общий язык экспозиции. Они позволяют точно добавлять или убирать свет через диафрагму, выдержку, ISO, фильтр или экспокоррекцию.</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Оптические инструменты</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>Stops as exposure language</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>Курс готов перейти к ошибкам экспозиции: теперь недодержку и передержку можно объяснять не словами «темно» и «светло», а конкретными стопами.</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Практика стопов</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>PL-047 — недодержка</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+      <c r="N484" t="n">
+        <v>5</v>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>SRC-309</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Exposure 101: An Intro to Exposure</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/exposure-101-an-intro-to-exposure</t>
+        </is>
+      </c>
+      <c r="S484" t="n">
+        <v>5</v>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>Финальный мост: стопы — база для PL-047 и PL-048.</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>Шкала стопов ведёт к двум зонам: тени/недодержка и света/передержка.</t>
+        </is>
+      </c>
+      <c r="V484" t="inlineStr">
+        <is>
+          <t>#PL046 #summary #bridge #underexposure #overexposure</t>
+        </is>
+      </c>
+      <c r="Y484" t="inlineStr">
+        <is>
+          <t>Стопы света / итог и мост</t>
+        </is>
+      </c>
+      <c r="Z484" t="inlineStr">
+        <is>
+          <t>Связь / переход</t>
+        </is>
+      </c>
+    </row>
     <row r="485" ht="17" customHeight="1" s="72"/>
     <row r="486" ht="17" customHeight="1" s="72"/>
     <row r="487" ht="17" customHeight="1" s="72"/>
@@ -54743,12 +61252,12 @@
       </c>
       <c r="B3" s="76" t="inlineStr">
         <is>
-          <t>camera lucida, stereoscope, portable camera obscura, compact 35mm cameras, Leica I, Leica system, rangefinder lineage, SLR, TLR, compact point-and-shoot, средний формат, большой формат, view camera, устройство плёночной камеры, выбор первой камеры, авторская роль камеры, объектив, элементы объектива, байонет, диафрагма, фокусное расстояние, угол зрения, широкий угол, нормальный 50 мм, портретный объектив, телеобъектив, светосила, диафрагма, базовая экспозиция</t>
+          <t>camera lucida, stereoscope, portable camera obscura, compact 35mm cameras, Leica I, Leica system, rangefinder lineage, SLR, TLR, compact point-and-shoot, средний формат, большой формат, view camera, устройство плёночной камеры, выбор первой камеры, авторская роль камеры, объектив, элементы объектива, байонет, диафрагма, фокусное расстояние, угол зрения, широкий угол, нормальный 50 мм, портретный объектив, телеобъектив, светосила, диафрагма, базовая экспозиция, диафрагма как окно, выдержка как время, ISO как чувствительность, экспозиционный треугольник, стопы света</t>
         </is>
       </c>
       <c r="C3" s="76" t="inlineStr">
         <is>
-          <t>PL-001 / PL-009 / PL-010 / PL-021–PL-039 / PL-041 / будущие PL</t>
+          <t>PL-001 / PL-009 / PL-010 / PL-021–PL-039 / PL-041–PL-046 / будущие PL</t>
         </is>
       </c>
       <c r="D3" s="76" t="inlineStr">
@@ -54758,7 +61267,7 @@
       </c>
       <c r="E3" s="76" t="inlineStr">
         <is>
-          <t>Оптическая и камерная линия: от оптических предпосылок к устройству камеры, объективам, типам фокусных расстояний и базовому управлению светом через экспозицию.</t>
+          <t>Оптическая и камерная линия: от оптических предпосылок к устройству камеры, объективам, типам фокусных расстояний и управлению экспозицией через диафрагму, выдержку, ISO и стопы света.</t>
         </is>
       </c>
     </row>
@@ -55073,7 +61582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="9.6640625" customWidth="1" style="72" min="1" max="1"/>
@@ -56431,25 +62940,185 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>PL-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Диафрагма как окно</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PL-HIST-0429…0439</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Диафрагма — это окно света: она управляет количеством света и глубиной резкости, превращая экспозицию в визуальный выбор.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>основа заполнена</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://t.me/photolab_vf_pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PL-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Выдержка как время</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PL-HIST-0440…0450</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Выдержка — это время действия света: она управляет яркостью, заморозкой движения, смазом, длинной экспозицией и ощущением времени в кадре.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>основа заполнена</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://t.me/photolab_vf_pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ISO как чувствительность</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PL-HIST-0451…0461</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ISO задаёт чувствительность материала или усиление сигнала: помогает снимать при меньшем свете, но влияет на зерно, шум и доступные пары настроек.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>основа заполнена</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://t.me/photolab_vf_pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PL-HIST-0462…0472</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник связывает диафрагму, выдержку и ISO: изменение одного параметра меняет яркость и визуальный характер кадра.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>основа заполнена</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://t.me/photolab_vf_pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Стопы света</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PL-HIST-0473…0483</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Стопы света — общий язык экспозиции: каждый полный стоп добавляет или убирает свет в два раза через диафрагму, выдержку, ISO, фильтр или экспокоррекцию.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>основа заполнена</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://t.me/photolab_vf_pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>будущие PL</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Расширение после PL-041</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>PL-042 — диафрагма как окно; PL-043 — выдержка как время; PL-044 — ISO как чувствительность</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>После базового определения экспозиции курс переходит к трём главным параметрам и стопам света.</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Расширение после PL-046</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PL-047 — недодержка; PL-048 — передержка; PL-049 — экспонометр; PL-050 — Sunny 16</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>После языка стопов курс переходит к ошибкам и измерению экспозиции: недодержка, передержка, экспонометр и солнечное правило.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
@@ -56469,7 +63138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E297"/>
+  <dimension ref="A1:E317"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="14" customWidth="1" style="72" min="1" max="1"/>
@@ -64495,6 +71164,546 @@
       <c r="E297" t="inlineStr">
         <is>
           <t>Общий образовательный источник; проверено по содержанию статьи вручную</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>SRC-296</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Nikon USA — What is Aperture?</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/what-is-aperture</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>PL-042: aperture/f-stop, wide vs narrow aperture, depth of field</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Nikon USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>SRC-297</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Canon U.S.A. — What Is Aperture Photography?</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>https://www.usa.canon.com/learning/training-articles/training-articles-list/what-is-aperture</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>PL-042: aperture as lens opening and depth-of-field control</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Canon</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>SRC-298</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Exposure 101: Intro to Aperture</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/exposure-101-intro-to-aperture</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>PL-042: aperture exposure control and maximum aperture / lens speed</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>SRC-299</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Camera Exposure: Aperture, ISO &amp; Shutter Speed</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-exposure.htm</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>PL-042/PL-045/PL-046: exposure triangle, f-stop sequence, equivalent exposure</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>SRC-300</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding Shutter Speed</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-shutter-speed</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>PL-043: shutter speed as exposure time and motion control</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Nikon USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>SRC-301</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Cambridge in Colour — Using Camera Shutter Speed Creatively</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>https://www.cambridgeincolour.com/tutorials/camera-shutter-speed.htm</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>PL-043: creative use of shutter speed, motion blur/freezing, long exposure</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>SRC-302</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Nikon USA — Capturing or Freezing Motion in Photos</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/capturing-or-freezing-motion-in-photos</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>PL-043: fast shutter, slow shutter, panning and motion representation</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Nikon USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>SRC-303</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Nikon USA — Understanding ISO Sensitivity</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/understanding-iso-sensitivity</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>PL-044/PL-045: ISO sensitivity, required light, shutter/aperture relationship</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Nikon USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>SRC-304</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Nikon — What is ISO in photography?</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>https://www.nikon.nl/nl_NL/learn-and-explore/magazine/tips-and-tricks/what-is-iso</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>PL-044: ISO as part of exposure triangle; higher/lower ISO in practice</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Nikon</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>SRC-305</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Canon U.S.A. — Photography Terms for Every New Photographer</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>https://www.usa.canon.com/learning/training-articles/training-articles-list/10-photography-terms-every-new-photographer-needs-to-know</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>PL-044/PL-045: aperture, shutter speed and ISO terminology; analog ISO as film sensitivity</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Canon</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>SRC-306</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Nikon — Mastering the Exposure Triangle</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>https://www.nikon.nl/nl_NL/learn-and-explore/magazine/tips-and-tricks/understanding-the-exposure-triangle</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>PL-045: exposure triangle and balancing aperture, shutter speed and ISO</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Nikon</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>SRC-307</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Canon Canada — Canon Outside of Auto: Photography 101</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>https://www.canon.ca/CanonOutsideOfAuto/photography101</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>PL-045: three exposure elements and balancing aperture/shutter/ISO</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Canon Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>SRC-308</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Canon Canada — Canon Outside of Auto: Tips</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>https://www.canon.ca/CanonOutsideOfAuto/tips?lang=en</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>PL-045/PL-046: one-stop compensation and relationship of aperture, shutter and ISO</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Canon Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>SRC-309</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Exposure 101: An Intro to Exposure</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/exposure-101-an-intro-to-exposure</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>PL-046: stop as doubling/halving light; exposure as creative control</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>SRC-310</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Nikon USA — When to Use Graduated Neutral Density Filters</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>https://www.nikonusa.com/learn-and-explore/c/tips-and-techniques/when-to-use-graduated-neutral-density-filters</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>PL-046: photographers describe light in stops; full stop as double/half light; ND filters</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>официальный образовательный материал Nikon USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>SRC-311</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>B&amp;H eXplora — Exposure Compensation and How Do We Use It?</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>https://www.bhphotovideo.com/explora/photography/tips-and-solutions/exposure-compensation-and-how-do-we-use-it</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>PL-046: exposure compensation and EV/stop scale in practical shooting</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>профильный образовательный источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>SRC-312</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Wikipedia — Waterhouse stop</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Waterhouse_stop</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>PL-042: history of interchangeable aperture plates before iris diaphragm</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>проверка исторического факта, замена дубля PL-HIST-0429</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>SRC-313</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Wikipedia — Focal-plane shutter</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Focal-plane_shutter</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>PL-043: focal-plane shutter curtain mechanism and flash sync speed limit</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>проверка технического факта, замена дубля PL-HIST-0440</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>SRC-314</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>PetaPixel — ISO Has Nothing to Do with Exposure</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>https://petapixel.com/2020/03/05/iso-has-nothing-to-do-with-exposure-an-explanation-for-beginners/</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>PL-044: ISO as post-exposure signal gain, not sensor sensitivity</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>проверка технического факта, замена дубля PL-HIST-0451</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>SRC-315</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>FastRawViewer — The Unbearable Lightness of Mystic "Exposure" Triangle</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>https://www.fastrawviewer.com/blog/mystic-exposure-triangle</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>PL-045: critique of exposure triangle model, ISO invariance</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>проверка технического факта, замена дубля PL-HIST-0462</t>
         </is>
       </c>
     </row>
@@ -64512,7 +71721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H345"/>
+  <dimension ref="A1:H400"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="13.6640625" customWidth="1" style="72" min="1" max="1"/>
@@ -65614,7 +72823,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>будущие PL</t>
+          <t>PL-042</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -65634,7 +72843,11 @@
           <t>Главная линия / визуальное решение</t>
         </is>
       </c>
-      <c r="C44" s="8" t="n"/>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>PL-043</t>
+        </is>
+      </c>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
@@ -65652,7 +72865,11 @@
           <t>Главная линия / визуальное мышление</t>
         </is>
       </c>
-      <c r="C45" s="8" t="n"/>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>PL-044</t>
+        </is>
+      </c>
       <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
@@ -65670,7 +72887,11 @@
           <t>Главная линия / композиционное решение</t>
         </is>
       </c>
-      <c r="C46" s="8" t="n"/>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>PL-045</t>
+        </is>
+      </c>
       <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
@@ -65687,6 +72908,11 @@
           <t>Главная линия / момент</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PL-046</t>
+        </is>
+      </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
           <t>Brownie / доступная камера</t>
@@ -65699,6 +72925,11 @@
           <t>Главная линия / точка съёмки</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>будущие PL</t>
+        </is>
+      </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
           <t>Brownie / цена и массовый рынок</t>
@@ -67921,6 +75152,391 @@
       <c r="H345" t="inlineStr">
         <is>
           <t>Экспозиция / авторский выбор</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Диафрагма / окно света</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Диафрагма / число f</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Диафрагма / съёмка в слабом свете</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Диафрагма / компенсация экспозиции</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Диафрагма / глубина резкости</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Диафрагма / приоритет диафрагмы</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Диафрагма / максимальная диафрагма</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Диафрагма / светосильный объектив</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Диафрагма / рабочее значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Диафрагма / полные стопы</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Диафрагма / итог и мост</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Выдержка / базовое определение</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Выдержка / заморозка движения</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Выдержка / длинная выдержка</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Выдержка / шкала времени</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Выдержка / шевелёнка</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Выдержка / штатив</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Выдержка / ND и время</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Выдержка / приоритет выдержки</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Выдержка / проводка</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Выдержка / компенсация стопами</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Выдержка / итог и мост</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>ISO / базовое определение</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>ISO / плёночная чувствительность</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>ISO / цифровое ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>ISO / низкая чувствительность</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>ISO / высокая чувствительность</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>ISO / связь с выдержкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>ISO / связь с диафрагмой</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>ISO / Auto ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>ISO / ручной выбор</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>ISO / место в треугольнике</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>ISO / итог и мост</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / базовая модель</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / визуальные эффекты</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / баланс</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / эквивалентные варианты</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / портретный сценарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / сценарий движения</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / слабый свет</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / полуавтоматические режимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / ручной режим</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / авторский выбор</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Экспозиционный треугольник / итог и мост</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Стопы света / базовое определение</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Стопы света / плюс-минус стоп</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Стопы света / диафрагма</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Стопы света / выдержка</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Стопы света / ISO</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Стопы света / дробные шаги</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Стопы света / эквивалентные изменения</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Стопы света / ND-фильтр</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Стопы света / экспокоррекция</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Стопы света / практика</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Стопы света / итог и мост</t>
         </is>
       </c>
     </row>
@@ -67935,7 +75551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13"/>
   <cols>
     <col width="40.6640625" customWidth="1" style="72" min="1" max="1"/>
@@ -67945,7 +75561,7 @@
     <row r="1" ht="40" customHeight="1" s="72">
       <c r="A1" s="32" t="inlineStr">
         <is>
-          <t>PHOTO LAB — History Map Master v0.19</t>
+          <t>PHOTO LAB — History Map Master v0.20</t>
         </is>
       </c>
       <c r="B1" s="20" t="n"/>
@@ -67970,7 +75586,7 @@
       </c>
       <c r="B3" s="80" t="inlineStr">
         <is>
-          <t>От оптических предпосылок камеры-обскуры до Leica I, полный Модуль 2 о плёнке, Модуль 3 до PL-030; в Модуле 4 заполнены PL-031–PL-039; Модуль 5 начат с PL-041. Основа для PL-001–PL-041, кроме PL-040, который оставлен отдельным будущим заполнением.</t>
+          <t>От оптических предпосылок камеры-обскуры до Leica I, полный Модуль 2 о плёнке, Модуль 3 до PL-030, Модуль 4 до PL-039; Модуль 5 заполнен PL-041–PL-046. PL-040 пока оставлен отдельным будущим заполнением.</t>
         </is>
       </c>
     </row>
@@ -68331,6 +75947,30 @@
       <c r="B33" t="inlineStr">
         <is>
           <t>PL-040: Почему объективы рисуют по-разному — отдельное заполнение перед продолжением PL-042–PL-050.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Что изменено в v0.20</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Заполнены PL-042–PL-046: добавлены PL-HIST-0429…0483 по диафрагме как окну света, выдержке как времени, ISO как чувствительности, экспозиционному треугольнику и стопам света. Добавлены источники SRC-296…SRC-311 и флагманские узлы PL-HIST-0429, PL-HIST-0440, PL-HIST-0451, PL-HIST-0462, PL-HIST-0473.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Следующий шаг</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PL-047: Недодержка — разобрать нехватку света, потерю деталей в тенях, отличие плёнки и цифры, экспокоррекцию и практику намеренной/случайной недодержки. PL-040 остаётся отдельным долгом в Модуле 4.</t>
         </is>
       </c>
     </row>
